--- a/Excel/对话表.xlsx
+++ b/Excel/对话表.xlsx
@@ -523,13 +523,11 @@
           <t>通用</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>firstMeeting</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>开场：打招呼 + 接待/拒绝分支</t>
@@ -545,13 +543,11 @@
           <t>通用</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>waitingReception</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>已经打过招呼、再点他时说的话（同样要带接待/拒绝）</t>
@@ -577,7 +573,6 @@
           <t>needTalk</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>小游戏类需求「Need_修理电路」的说辞与交付分支</t>
@@ -603,7 +598,6 @@
           <t>needTalk</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>条件类需求「Need_新需求」的说辞与交付分支</t>
@@ -629,7 +623,6 @@
           <t>needTalk</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>条件类需求「Need_要蓝色椅子」的说辞与交付分支</t>
@@ -645,13 +638,11 @@
           <t>通用</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>feedbackDisappointed</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>服务超时后说的话</t>
@@ -667,13 +658,11 @@
           <t>通用</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>feedbackPlain</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>只有小游戏类会走到</t>
@@ -689,13 +678,11 @@
           <t>通用</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>feedbackFine</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>只有小游戏类会走到</t>
@@ -711,13 +698,11 @@
           <t>通用</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>feedbackPerfect</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>条件类交付成功 / 小游戏满分</t>
@@ -733,14 +718,11 @@
           <t>通用</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>smallTalk</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -751,14 +733,11 @@
           <t>通用</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>smallTalk</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -769,14 +748,11 @@
           <t>通用</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>smallTalk</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -797,7 +773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -922,8 +898,6 @@
       <c r="D3" t="n">
         <v>1</v>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Line</t>
@@ -934,19 +908,14 @@
           <t>你好，打扰了……请问今晚还有空房吗？</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Branch</t>
@@ -964,9 +933,6 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
         <v>2</v>
       </c>
@@ -986,10 +952,8 @@
           <t>Accept</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>visitor</t>
@@ -1019,19 +983,14 @@
           <t>太好了，谢谢你！</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
         <v>2</v>
       </c>
       <c r="E7" t="n">
         <v>2</v>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Branch</t>
@@ -1042,12 +1001,8 @@
           <t>抱歉，今天恐怕招待不了你</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
         <v>2</v>
       </c>
@@ -1067,10 +1022,8 @@
           <t>Reject</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
           <t>visitor</t>
@@ -1100,934 +1053,810 @@
           <t>这样啊……那我改天再来。</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>（先想一下）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>visitor</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>calm</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>好的，我在这儿等着。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
         <v>20001</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>visitor</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>calm</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>我还能再等一会儿，你先忙。</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
+    </row>
+    <row r="13">
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>Branch</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>久等了，请进</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>CanAcceptGuest</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="inlineStr">
+    <row r="14">
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>Accept</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr">
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
         <is>
           <t>visitor</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>happy</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2</v>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>谢谢你！</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="n">
-        <v>2</v>
-      </c>
-      <c r="E14" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
+    </row>
+    <row r="16">
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>Branch</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>抱歉，今天恐怕招待不了你</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" t="n">
-        <v>2</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" t="inlineStr">
+    </row>
+    <row r="17">
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>Reject</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
         <is>
           <t>visitor</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>sad</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" t="n">
-        <v>2</v>
-      </c>
-      <c r="F16" t="n">
-        <v>2</v>
-      </c>
-      <c r="G16" t="inlineStr">
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>这样啊……那我改天再来。</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="n">
-        <v>2</v>
-      </c>
-      <c r="E17" t="n">
+    </row>
+    <row r="19">
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="n">
         <v>3</v>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>Branch</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>（先不打扰他）</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
         <v>30001</v>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>visitor</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>confused</t>
         </is>
       </c>
-      <c r="D18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>{需求}</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="n">
-        <v>2</v>
-      </c>
-      <c r="E19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
+    </row>
+    <row r="21">
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>Branch</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t>我来看看</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="n">
-        <v>2</v>
-      </c>
-      <c r="E20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" t="inlineStr">
+    </row>
+    <row r="22">
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>StartMinigame</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="n">
-        <v>2</v>
-      </c>
-      <c r="E21" t="n">
-        <v>2</v>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
+    </row>
+    <row r="23">
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>Branch</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>等我准备一下</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
         <is>
           <t>visitor</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>calm</t>
         </is>
       </c>
-      <c r="D22" t="n">
-        <v>2</v>
-      </c>
-      <c r="E22" t="n">
-        <v>2</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" t="inlineStr">
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="inlineStr">
         <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <t>好，我等着。</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
         <v>30002</v>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>visitor</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>calm</t>
         </is>
       </c>
-      <c r="D23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="inlineStr">
         <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t>{需求}</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="n">
-        <v>2</v>
-      </c>
-      <c r="E24" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr">
+    </row>
+    <row r="26">
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" t="inlineStr">
         <is>
           <t>Branch</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t>我把你要的搬来了</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>RoomHasNeedFurniture</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
+    <row r="27">
+      <c r="B27" t="inlineStr">
         <is>
           <t>visitor</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>happy</t>
         </is>
       </c>
-      <c r="D25" t="n">
-        <v>2</v>
-      </c>
-      <c r="E25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" t="inlineStr">
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" t="inlineStr">
         <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>就是这个！太谢谢你了。</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="n">
-        <v>2</v>
-      </c>
-      <c r="E26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" t="n">
-        <v>2</v>
-      </c>
-      <c r="G26" t="inlineStr">
+    </row>
+    <row r="28">
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <t>CompleteNeed(perfect)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="n">
-        <v>2</v>
-      </c>
-      <c r="E27" t="n">
-        <v>2</v>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr">
+    </row>
+    <row r="29">
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2</v>
+      </c>
+      <c r="G29" t="inlineStr">
         <is>
           <t>Branch</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr">
         <is>
           <t>我这就去弄</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr">
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
         <is>
           <t>visitor</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>calm</t>
         </is>
       </c>
-      <c r="D28" t="n">
-        <v>2</v>
-      </c>
-      <c r="E28" t="n">
-        <v>2</v>
-      </c>
-      <c r="F28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" t="inlineStr">
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" t="inlineStr">
         <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
+      <c r="H30" s="3" t="inlineStr">
         <is>
           <t>好，我不急，你慢慢来。</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="n">
-        <v>2</v>
-      </c>
-      <c r="E29" t="n">
-        <v>3</v>
-      </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Branch</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>抱歉，这个我办不到</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>visitor</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>sad</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>2</v>
-      </c>
-      <c r="E30" t="n">
-        <v>3</v>
-      </c>
-      <c r="F30" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Line</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>唉……那也没办法。</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
       <c r="D31" t="n">
         <v>2</v>
       </c>
       <c r="E31" t="n">
         <v>3</v>
       </c>
-      <c r="F31" t="n">
-        <v>2</v>
-      </c>
       <c r="G31" t="inlineStr">
         <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>抱歉，这个我办不到</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>visitor</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>sad</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" t="n">
+        <v>3</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>唉……那也没办法。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="D33" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t>Reject</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
         <v>30003</v>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>visitor</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>calm</t>
         </is>
       </c>
-      <c r="D32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr">
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" t="inlineStr">
         <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="H34" s="3" t="inlineStr">
         <is>
           <t>{需求}</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="n">
-        <v>2</v>
-      </c>
-      <c r="E33" t="n">
-        <v>1</v>
-      </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr">
+    </row>
+    <row r="35">
+      <c r="D35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" t="inlineStr">
         <is>
           <t>Branch</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr">
         <is>
           <t>我把你要的搬来了</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>RoomHasNeedFurniture</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr">
+    <row r="36">
+      <c r="B36" t="inlineStr">
         <is>
           <t>visitor</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>happy</t>
         </is>
       </c>
-      <c r="D34" t="n">
-        <v>2</v>
-      </c>
-      <c r="E34" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" t="inlineStr">
+      <c r="D36" t="n">
+        <v>2</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" t="inlineStr">
         <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
+      <c r="H36" s="3" t="inlineStr">
         <is>
           <t>就是这个！太谢谢你了。</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="n">
-        <v>2</v>
-      </c>
-      <c r="E35" t="n">
-        <v>1</v>
-      </c>
-      <c r="F35" t="n">
-        <v>2</v>
-      </c>
-      <c r="G35" t="inlineStr">
+    </row>
+    <row r="37">
+      <c r="D37" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2</v>
+      </c>
+      <c r="G37" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr">
+      <c r="H37" s="3" t="inlineStr">
         <is>
           <t>CompleteNeed(perfect)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="n">
-        <v>2</v>
-      </c>
-      <c r="E36" t="n">
-        <v>2</v>
-      </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
+    </row>
+    <row r="38">
+      <c r="D38" t="n">
+        <v>2</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2</v>
+      </c>
+      <c r="G38" t="inlineStr">
         <is>
           <t>Branch</t>
         </is>
       </c>
-      <c r="H36" s="3" t="inlineStr">
+      <c r="H38" s="3" t="inlineStr">
         <is>
           <t>我这就去弄</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr">
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
         <is>
           <t>visitor</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>calm</t>
         </is>
       </c>
-      <c r="D37" t="n">
-        <v>2</v>
-      </c>
-      <c r="E37" t="n">
-        <v>2</v>
-      </c>
-      <c r="F37" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" t="inlineStr">
+      <c r="D39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E39" t="n">
+        <v>2</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" t="inlineStr">
         <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr">
+      <c r="H39" s="3" t="inlineStr">
         <is>
           <t>好，我不急，你慢慢来。</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="n">
-        <v>2</v>
-      </c>
-      <c r="E38" t="n">
-        <v>3</v>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Branch</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>抱歉，这个我办不到</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>visitor</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>sad</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>2</v>
-      </c>
-      <c r="E39" t="n">
-        <v>3</v>
-      </c>
-      <c r="F39" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Line</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>唉……那也没办法。</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
       <c r="D40" t="n">
         <v>2</v>
       </c>
       <c r="E40" t="n">
         <v>3</v>
       </c>
-      <c r="F40" t="n">
-        <v>2</v>
-      </c>
       <c r="G40" t="inlineStr">
         <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>抱歉，这个我办不到</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>visitor</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>sad</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E41" t="n">
+        <v>3</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>唉……那也没办法。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="D42" t="n">
+        <v>2</v>
+      </c>
+      <c r="E42" t="n">
+        <v>3</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
+      <c r="H42" s="3" t="inlineStr">
         <is>
           <t>Reject</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>40001</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>visitor</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>sad</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Line</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>算了……可能是我要求太多了。</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>40002</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>visitor</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>calm</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>1</v>
-      </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Line</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>嗯，还行吧，谢谢你。</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>40003</v>
+        <v>40001</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -2036,14 +1865,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="D43" t="n">
         <v>1</v>
       </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
           <t>Line</t>
@@ -2051,14 +1878,13 @@
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>挺好的，比我原本想的还妥帖些。</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>算了……可能是我要求太多了。</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>40004</v>
+        <v>40002</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -2067,14 +1893,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>calm</t>
         </is>
       </c>
       <c r="D44" t="n">
         <v>1</v>
       </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
           <t>Line</t>
@@ -2082,14 +1906,13 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>太完美了，我会记住这地方的。</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>嗯，还行吧，谢谢你。</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>50001</v>
+        <v>40003</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -2098,14 +1921,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>happy</t>
         </is>
       </c>
       <c r="D45" t="n">
         <v>1</v>
       </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
           <t>Line</t>
@@ -2113,14 +1934,13 @@
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>这屋子比我想的舒服多了。</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>挺好的，比我原本想的还妥帖些。</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>50002</v>
+        <v>40004</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -2129,14 +1949,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>happy</t>
         </is>
       </c>
       <c r="D46" t="n">
         <v>1</v>
       </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
           <t>Line</t>
@@ -2144,41 +1962,93 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>难得能这么安静地待一会儿。</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>太完美了，我会记住这地方的。</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
+        <v>50001</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>visitor</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>calm</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>这屋子比我想的舒服多了。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>50002</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>visitor</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>calm</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>难得能这么安静地待一会儿。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
         <v>50003</v>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>visitor</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>happy</t>
         </is>
       </c>
-      <c r="D47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr">
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" t="inlineStr">
         <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr">
+      <c r="H49" s="3" t="inlineStr">
         <is>
           <t>下次路过，我还来。</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -2371,13 +2241,11 @@
           <t>Need_修理电路</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
           <t>crow</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2445,13 +2313,11 @@
           <t>Need_新需求</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
           <t>fox</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2519,13 +2385,11 @@
           <t>Need_要蓝色椅子</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
           <t>hedgehog</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2573,7 +2437,6 @@
           <t>rabbit</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">

--- a/Excel/对话表.xlsx
+++ b/Excel/对话表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\2026MasterHouse\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D794DCC-50CD-4766-9588-D51D7EF1AB70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4F9EA5A-5022-441E-9347-F3B08E48F1BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1695" windowWidth="28800" windowHeight="15510" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5295" yWindow="2475" windowWidth="28800" windowHeight="15510" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="对话组" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2595" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2594" uniqueCount="248">
   <si>
     <t>对话组ID</t>
   </si>
@@ -757,6 +757,18 @@
   </si>
   <si>
     <t>rabbit</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Need_制作咖啡</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>条件类需求「Need_制作咖啡」的说辞与交付分支</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>好</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1237,13 +1249,13 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>245</v>
       </c>
       <c r="D6" t="s">
         <v>21</v>
       </c>
       <c r="F6" t="s">
-        <v>25</v>
+        <v>246</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.15">
@@ -1573,7 +1585,7 @@
         <v>58</v>
       </c>
       <c r="C30" t="s">
-        <v>24</v>
+        <v>245</v>
       </c>
       <c r="D30" t="s">
         <v>21</v>
@@ -2531,9 +2543,10 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xWindow="766" yWindow="396" count="3">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="可选值" prompt="八个触发分类，见「参考」页" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
             <xm:f>参考!$A$2:$A$9</xm:f>
@@ -2889,7 +2902,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.15">
       <c r="D17" t="s">
         <v>155</v>
       </c>
@@ -2906,7 +2919,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B18" t="s">
         <v>150</v>
       </c>
@@ -2929,7 +2942,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.15">
       <c r="D19" t="s">
         <v>155</v>
       </c>
@@ -2943,7 +2956,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -2963,7 +2976,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.15">
       <c r="D21" t="s">
         <v>155</v>
       </c>
@@ -2977,7 +2990,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.15">
       <c r="D22" t="s">
         <v>155</v>
       </c>
@@ -2994,7 +3007,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.15">
       <c r="D23" t="s">
         <v>155</v>
       </c>
@@ -3008,7 +3021,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B24" t="s">
         <v>150</v>
       </c>
@@ -3031,7 +3044,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -3051,7 +3064,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.15">
       <c r="D26" t="s">
         <v>155</v>
       </c>
@@ -3062,13 +3075,10 @@
         <v>156</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="I26" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.15">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B27" t="s">
         <v>150</v>
       </c>
@@ -3091,7 +3101,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.15">
       <c r="D28" t="s">
         <v>155</v>
       </c>
@@ -3108,7 +3118,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.15">
       <c r="D29" t="s">
         <v>155</v>
       </c>
@@ -3122,7 +3132,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B30" t="s">
         <v>150</v>
       </c>
@@ -3145,7 +3155,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.15">
       <c r="D31" t="s">
         <v>155</v>
       </c>
@@ -3159,7 +3169,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B32" t="s">
         <v>150</v>
       </c>

--- a/Excel/对话表.xlsx
+++ b/Excel/对话表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xinxinhe\Documents\2026MasterHouse\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{856B7E6A-C876-4EE3-8D85-D992AEA9DD1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C025B37A-69C8-44F3-862C-1A6C8B46EAC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13515" yWindow="1125" windowWidth="15000" windowHeight="13260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="对话组" sheetId="1" r:id="rId1"/>
@@ -2667,7 +2667,7 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xWindow="766" yWindow="396" count="3">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xWindow="327" yWindow="314" count="3">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="可选值" prompt="八个触发分类，见「参考」页" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
             <xm:f>参考!$A$2:$A$9</xm:f>

--- a/Excel/对话表.xlsx
+++ b/Excel/对话表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xinxinhe\Documents\2026MasterHouse\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\2026MasterHouse\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFC1D678-FC60-4D42-8D9C-B229101EF423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D4E3BDE-CB7A-41A3-9A3C-2B446FF46317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="40695" yWindow="2295" windowWidth="32805" windowHeight="18330" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="对话组" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2010" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2010" uniqueCount="308">
   <si>
     <t>对话组ID</t>
   </si>
@@ -1058,13 +1058,17 @@
   </si>
   <si>
     <t>Need_电路教程</t>
+  </si>
+  <si>
+    <t>那，那好吧，那我只能去其他地方看看了，55555……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1104,6 +1108,8 @@
       <b/>
       <sz val="11"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <i/>
@@ -1128,12 +1134,16 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1145,10 +1155,14 @@
       <sz val="11"/>
       <color theme="3" tint="0.39997558519241921"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1160,6 +1174,8 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1641,7 +1657,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F91"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="11" style="42" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -1651,7 +1667,7 @@
     <col min="6" max="6" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
@@ -1671,7 +1687,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A2" s="41" t="s">
         <v>6</v>
       </c>
@@ -1691,7 +1707,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A3" s="42" t="s">
         <v>12</v>
       </c>
@@ -1705,7 +1721,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A4" s="42" t="s">
         <v>16</v>
       </c>
@@ -1719,7 +1735,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A5" s="42">
         <v>30001</v>
       </c>
@@ -1736,7 +1752,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A6" s="42">
         <v>30002</v>
       </c>
@@ -1753,7 +1769,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A7" s="42" t="s">
         <v>26</v>
       </c>
@@ -1767,7 +1783,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A8" s="42" t="s">
         <v>29</v>
       </c>
@@ -1781,7 +1797,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A9" s="42" t="s">
         <v>32</v>
       </c>
@@ -1795,7 +1811,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A10" s="42" t="s">
         <v>34</v>
       </c>
@@ -1809,7 +1825,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A11" s="42" t="s">
         <v>37</v>
       </c>
@@ -1820,7 +1836,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A12" s="42" t="s">
         <v>39</v>
       </c>
@@ -1831,7 +1847,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A13" s="42" t="s">
         <v>40</v>
       </c>
@@ -1842,10 +1858,10 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:6" s="38" customFormat="1">
+    <row r="14" spans="1:6" s="38" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A14" s="43"/>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A15" s="42" t="s">
         <v>41</v>
       </c>
@@ -1859,7 +1875,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A16" s="42" t="s">
         <v>43</v>
       </c>
@@ -1873,7 +1889,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A17" s="42">
         <v>30102</v>
       </c>
@@ -1890,7 +1906,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A18" s="42">
         <v>30101</v>
       </c>
@@ -1907,7 +1923,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A19" s="42" t="s">
         <v>44</v>
       </c>
@@ -1921,7 +1937,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A20" s="42" t="s">
         <v>45</v>
       </c>
@@ -1935,7 +1951,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A21" s="42">
         <v>40103</v>
       </c>
@@ -1949,7 +1965,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A22" s="42" t="s">
         <v>46</v>
       </c>
@@ -1963,7 +1979,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A23" s="42" t="s">
         <v>47</v>
       </c>
@@ -1974,7 +1990,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A24" s="42" t="s">
         <v>48</v>
       </c>
@@ -1985,7 +2001,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A25" s="42" t="s">
         <v>49</v>
       </c>
@@ -1996,10 +2012,10 @@
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:6" s="38" customFormat="1">
+    <row r="26" spans="1:6" s="38" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A26" s="43"/>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A27" s="42" t="s">
         <v>50</v>
       </c>
@@ -2013,7 +2029,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A28" s="42" t="s">
         <v>52</v>
       </c>
@@ -2027,7 +2043,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A29" s="42">
         <v>30202</v>
       </c>
@@ -2044,7 +2060,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A30" s="42">
         <v>30203</v>
       </c>
@@ -2061,7 +2077,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A31" s="42">
         <v>30201</v>
       </c>
@@ -2078,7 +2094,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A32" s="42" t="s">
         <v>53</v>
       </c>
@@ -2092,7 +2108,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A33" s="42" t="s">
         <v>54</v>
       </c>
@@ -2106,7 +2122,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A34" s="42" t="s">
         <v>55</v>
       </c>
@@ -2120,7 +2136,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A35" s="42" t="s">
         <v>56</v>
       </c>
@@ -2134,7 +2150,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A36" s="42" t="s">
         <v>57</v>
       </c>
@@ -2145,7 +2161,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A37" s="42" t="s">
         <v>58</v>
       </c>
@@ -2156,7 +2172,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A38" s="42" t="s">
         <v>59</v>
       </c>
@@ -2167,10 +2183,10 @@
         <v>38</v>
       </c>
     </row>
-    <row r="39" spans="1:6" s="38" customFormat="1">
+    <row r="39" spans="1:6" s="38" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A39" s="43"/>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A40" s="42" t="s">
         <v>60</v>
       </c>
@@ -2184,7 +2200,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A41" s="42" t="s">
         <v>62</v>
       </c>
@@ -2198,7 +2214,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A42" s="42">
         <v>30302</v>
       </c>
@@ -2215,7 +2231,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A43" s="42">
         <v>30303</v>
       </c>
@@ -2232,7 +2248,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A44" s="42">
         <v>30301</v>
       </c>
@@ -2249,7 +2265,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A45" s="42" t="s">
         <v>63</v>
       </c>
@@ -2263,7 +2279,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A46" s="42" t="s">
         <v>64</v>
       </c>
@@ -2277,7 +2293,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A47" s="42" t="s">
         <v>65</v>
       </c>
@@ -2291,7 +2307,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A48" s="42" t="s">
         <v>66</v>
       </c>
@@ -2305,7 +2321,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A49" s="42" t="s">
         <v>67</v>
       </c>
@@ -2316,7 +2332,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A50" s="42" t="s">
         <v>68</v>
       </c>
@@ -2327,7 +2343,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A51" s="42" t="s">
         <v>69</v>
       </c>
@@ -2338,10 +2354,10 @@
         <v>38</v>
       </c>
     </row>
-    <row r="52" spans="1:6" s="38" customFormat="1">
+    <row r="52" spans="1:6" s="38" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A52" s="43"/>
     </row>
-    <row r="53" spans="1:6">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A53" s="42" t="s">
         <v>70</v>
       </c>
@@ -2355,7 +2371,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="54" spans="1:6">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A54" s="42" t="s">
         <v>72</v>
       </c>
@@ -2369,7 +2385,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="55" spans="1:6">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A55" s="42">
         <v>30402</v>
       </c>
@@ -2386,7 +2402,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="56" spans="1:6">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A56" s="42">
         <v>30403</v>
       </c>
@@ -2403,7 +2419,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A57" s="42">
         <v>30401</v>
       </c>
@@ -2420,7 +2436,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A58" s="42" t="s">
         <v>73</v>
       </c>
@@ -2434,7 +2450,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A59" s="42" t="s">
         <v>74</v>
       </c>
@@ -2448,7 +2464,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="60" spans="1:6">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A60" s="42" t="s">
         <v>75</v>
       </c>
@@ -2462,7 +2478,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="61" spans="1:6">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A61" s="42" t="s">
         <v>76</v>
       </c>
@@ -2476,7 +2492,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="62" spans="1:6">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A62" s="42" t="s">
         <v>77</v>
       </c>
@@ -2487,7 +2503,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="63" spans="1:6">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A63" s="42" t="s">
         <v>78</v>
       </c>
@@ -2498,7 +2514,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="64" spans="1:6">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A64" s="42" t="s">
         <v>79</v>
       </c>
@@ -2509,10 +2525,10 @@
         <v>38</v>
       </c>
     </row>
-    <row r="65" spans="1:6" s="38" customFormat="1">
+    <row r="65" spans="1:6" s="38" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A65" s="43"/>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A66" s="42" t="s">
         <v>80</v>
       </c>
@@ -2526,7 +2542,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A67" s="42" t="s">
         <v>82</v>
       </c>
@@ -2540,7 +2556,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A68" s="42">
         <v>30502</v>
       </c>
@@ -2557,7 +2573,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A69" s="42">
         <v>30503</v>
       </c>
@@ -2574,7 +2590,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A70" s="42">
         <v>30501</v>
       </c>
@@ -2591,7 +2607,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="71" spans="1:6">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A71" s="42" t="s">
         <v>83</v>
       </c>
@@ -2605,7 +2621,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A72" s="42" t="s">
         <v>84</v>
       </c>
@@ -2619,7 +2635,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A73" s="42" t="s">
         <v>85</v>
       </c>
@@ -2633,7 +2649,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A74" s="42" t="s">
         <v>86</v>
       </c>
@@ -2647,7 +2663,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A75" s="42" t="s">
         <v>87</v>
       </c>
@@ -2658,7 +2674,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A76" s="42" t="s">
         <v>88</v>
       </c>
@@ -2669,7 +2685,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A77" s="42" t="s">
         <v>89</v>
       </c>
@@ -2680,10 +2696,10 @@
         <v>38</v>
       </c>
     </row>
-    <row r="78" spans="1:6" s="38" customFormat="1">
+    <row r="78" spans="1:6" s="38" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A78" s="43"/>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A79" s="42" t="s">
         <v>90</v>
       </c>
@@ -2697,7 +2713,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A80" s="42" t="s">
         <v>92</v>
       </c>
@@ -2711,7 +2727,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A81" s="42">
         <v>30602</v>
       </c>
@@ -2728,7 +2744,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="82" spans="1:6">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A82" s="42">
         <v>30603</v>
       </c>
@@ -2745,7 +2761,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="83" spans="1:6">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A83" s="42">
         <v>30601</v>
       </c>
@@ -2762,7 +2778,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A84" s="42" t="s">
         <v>93</v>
       </c>
@@ -2776,7 +2792,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A85" s="42" t="s">
         <v>94</v>
       </c>
@@ -2790,7 +2806,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A86" s="42" t="s">
         <v>95</v>
       </c>
@@ -2804,7 +2820,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A87" s="42" t="s">
         <v>96</v>
       </c>
@@ -2818,7 +2834,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A88" s="42" t="s">
         <v>97</v>
       </c>
@@ -2829,7 +2845,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A89" s="42" t="s">
         <v>98</v>
       </c>
@@ -2840,7 +2856,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="90" spans="1:6">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A90" s="42" t="s">
         <v>99</v>
       </c>
@@ -2851,7 +2867,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="91" spans="1:6" s="38" customFormat="1">
+    <row r="91" spans="1:6" s="38" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A91" s="43"/>
     </row>
   </sheetData>
@@ -2888,7 +2904,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J558"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="11" style="20" customWidth="1"/>
     <col min="2" max="2" width="10" style="6" customWidth="1"/>
@@ -2901,7 +2917,7 @@
     <col min="11" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15">
+    <row r="1" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -2933,7 +2949,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15.75">
+    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
         <v>6</v>
       </c>
@@ -2962,7 +2978,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:10" s="13" customFormat="1" ht="21">
+    <row r="3" spans="1:10" s="13" customFormat="1" ht="21" x14ac:dyDescent="0.4">
       <c r="A3" s="23" t="s">
         <v>12</v>
       </c>
@@ -2988,7 +3004,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="4" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="4" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A4" s="10"/>
       <c r="B4" s="9" t="s">
         <v>116</v>
@@ -3009,7 +3025,7 @@
       </c>
       <c r="I4" s="9"/>
     </row>
-    <row r="5" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="5" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A5" s="10"/>
       <c r="B5" s="9" t="s">
         <v>116</v>
@@ -3030,7 +3046,7 @@
       </c>
       <c r="I5" s="9"/>
     </row>
-    <row r="6" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="6" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="10"/>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -3041,7 +3057,7 @@
       <c r="H6" s="17"/>
       <c r="I6" s="9"/>
     </row>
-    <row r="7" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="7" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A7" s="10"/>
       <c r="B7" s="9" t="s">
         <v>147</v>
@@ -3069,7 +3085,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="8" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="8" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A8" s="10"/>
       <c r="B8" s="9" t="s">
         <v>116</v>
@@ -3094,7 +3110,7 @@
       </c>
       <c r="I8" s="9"/>
     </row>
-    <row r="9" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="9" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A9" s="10"/>
       <c r="B9" s="9" t="s">
         <v>116</v>
@@ -3119,7 +3135,7 @@
       </c>
       <c r="I9" s="9"/>
     </row>
-    <row r="10" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="10" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A10" s="10"/>
       <c r="B10" s="9" t="s">
         <v>116</v>
@@ -3144,7 +3160,7 @@
       </c>
       <c r="I10" s="9"/>
     </row>
-    <row r="11" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="11" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A11" s="10"/>
       <c r="B11" s="9" t="s">
         <v>116</v>
@@ -3169,7 +3185,7 @@
       </c>
       <c r="I11" s="9"/>
     </row>
-    <row r="12" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="12" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A12" s="10"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -3180,7 +3196,7 @@
       <c r="H12" s="17"/>
       <c r="I12" s="9"/>
     </row>
-    <row r="13" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="13" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A13" s="10"/>
       <c r="B13" s="9" t="s">
         <v>147</v>
@@ -3206,7 +3222,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="14" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="14" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A14" s="10"/>
       <c r="B14" s="9" t="s">
         <v>116</v>
@@ -3231,7 +3247,7 @@
       </c>
       <c r="I14" s="9"/>
     </row>
-    <row r="15" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="15" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A15" s="10"/>
       <c r="B15" s="9" t="s">
         <v>116</v>
@@ -3256,7 +3272,7 @@
       </c>
       <c r="I15" s="9"/>
     </row>
-    <row r="16" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="16" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A16" s="10"/>
       <c r="B16" s="9" t="s">
         <v>116</v>
@@ -3281,7 +3297,7 @@
       </c>
       <c r="I16" s="9"/>
     </row>
-    <row r="17" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="17" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A17" s="10"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -3292,7 +3308,7 @@
       <c r="H17" s="17"/>
       <c r="I17" s="9"/>
     </row>
-    <row r="18" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="18" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A18" s="10"/>
       <c r="B18" s="9" t="s">
         <v>147</v>
@@ -3318,7 +3334,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="19" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="19" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A19" s="10"/>
       <c r="B19" s="9" t="s">
         <v>116</v>
@@ -3343,7 +3359,7 @@
       </c>
       <c r="I19" s="9"/>
     </row>
-    <row r="20" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="20" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A20" s="10"/>
       <c r="B20" s="9" t="s">
         <v>116</v>
@@ -3368,7 +3384,7 @@
       </c>
       <c r="I20" s="9"/>
     </row>
-    <row r="21" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="21" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A21" s="10"/>
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
@@ -3379,7 +3395,7 @@
       <c r="H21" s="11"/>
       <c r="I21" s="9"/>
     </row>
-    <row r="22" spans="1:10" s="13" customFormat="1" ht="21.75" customHeight="1">
+    <row r="22" spans="1:10" s="13" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="23">
         <v>20001</v>
       </c>
@@ -3405,7 +3421,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="23" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="23" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A23" s="10"/>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
@@ -3416,7 +3432,7 @@
       <c r="H23" s="11"/>
       <c r="I23" s="9"/>
     </row>
-    <row r="24" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="24" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A24" s="10"/>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
@@ -3437,7 +3453,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="25" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="25" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A25" s="10"/>
       <c r="B25" s="9" t="s">
         <v>116</v>
@@ -3462,7 +3478,7 @@
       </c>
       <c r="I25" s="9"/>
     </row>
-    <row r="26" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="26" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A26" s="10"/>
       <c r="B26" s="9" t="s">
         <v>116</v>
@@ -3487,7 +3503,7 @@
       </c>
       <c r="I26" s="9"/>
     </row>
-    <row r="27" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="27" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A27" s="10"/>
       <c r="B27" s="9"/>
       <c r="C27" s="9"/>
@@ -3498,7 +3514,7 @@
       <c r="H27" s="11"/>
       <c r="I27" s="9"/>
     </row>
-    <row r="28" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="28" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A28" s="10"/>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
@@ -3517,7 +3533,7 @@
       </c>
       <c r="I28" s="9"/>
     </row>
-    <row r="29" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="29" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A29" s="10"/>
       <c r="B29" s="9" t="s">
         <v>116</v>
@@ -3542,7 +3558,7 @@
       </c>
       <c r="I29" s="9"/>
     </row>
-    <row r="30" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="30" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A30" s="10"/>
       <c r="B30" s="9" t="s">
         <v>116</v>
@@ -3567,7 +3583,7 @@
       </c>
       <c r="I30" s="9"/>
     </row>
-    <row r="31" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="31" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A31" s="10"/>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
@@ -3578,7 +3594,7 @@
       <c r="H31" s="11"/>
       <c r="I31" s="9"/>
     </row>
-    <row r="32" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="32" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A32" s="10"/>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
@@ -3597,7 +3613,7 @@
       </c>
       <c r="I32" s="9"/>
     </row>
-    <row r="33" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="33" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A33" s="10"/>
       <c r="B33" s="9" t="s">
         <v>116</v>
@@ -3622,7 +3638,7 @@
       </c>
       <c r="I33" s="9"/>
     </row>
-    <row r="34" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="34" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A34" s="10"/>
       <c r="B34" s="9" t="s">
         <v>116</v>
@@ -3647,7 +3663,7 @@
       </c>
       <c r="I34" s="9"/>
     </row>
-    <row r="35" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="35" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A35" s="10"/>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
@@ -3658,7 +3674,7 @@
       <c r="H35" s="18"/>
       <c r="I35" s="9"/>
     </row>
-    <row r="36" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="36" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A36" s="10"/>
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
@@ -3669,7 +3685,7 @@
       <c r="H36" s="11"/>
       <c r="I36" s="9"/>
     </row>
-    <row r="37" spans="1:10" s="32" customFormat="1" ht="21">
+    <row r="37" spans="1:10" s="32" customFormat="1" ht="21" x14ac:dyDescent="0.4">
       <c r="A37" s="23">
         <v>30001</v>
       </c>
@@ -3695,7 +3711,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="16.5">
+    <row r="38" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A38" s="19"/>
       <c r="B38" s="13"/>
       <c r="C38" s="13"/>
@@ -3707,7 +3723,7 @@
       <c r="I38" s="13"/>
       <c r="J38" s="13"/>
     </row>
-    <row r="39" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="39" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A39" s="19"/>
       <c r="B39" s="9" t="s">
         <v>147</v>
@@ -3729,7 +3745,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="40" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="40" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A40" s="19"/>
       <c r="B40" s="9" t="s">
         <v>116</v>
@@ -3753,7 +3769,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="41" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="41" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A41" s="19"/>
       <c r="B41" s="9" t="s">
         <v>116</v>
@@ -3780,7 +3796,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="16.5">
+    <row r="42" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A42" s="19"/>
       <c r="B42" s="13"/>
       <c r="C42" s="13"/>
@@ -3792,7 +3808,7 @@
       <c r="I42" s="13"/>
       <c r="J42" s="13"/>
     </row>
-    <row r="43" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="43" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A43" s="19"/>
       <c r="B43" s="9" t="s">
         <v>147</v>
@@ -3814,7 +3830,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="44" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="44" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A44" s="19"/>
       <c r="B44" s="9" t="s">
         <v>116</v>
@@ -3838,7 +3854,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="45" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="45" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A45" s="19"/>
       <c r="B45" s="9" t="s">
         <v>116</v>
@@ -3862,7 +3878,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="46" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="46" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A46" s="10"/>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
@@ -3873,7 +3889,7 @@
       <c r="H46" s="11"/>
       <c r="I46" s="9"/>
     </row>
-    <row r="47" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="47" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A47" s="10"/>
       <c r="B47" s="9"/>
       <c r="C47" s="9"/>
@@ -3884,7 +3900,7 @@
       <c r="H47" s="11"/>
       <c r="I47" s="9"/>
     </row>
-    <row r="48" spans="1:10" s="32" customFormat="1" ht="21">
+    <row r="48" spans="1:10" s="32" customFormat="1" ht="21" x14ac:dyDescent="0.4">
       <c r="A48" s="23">
         <v>30002</v>
       </c>
@@ -3910,7 +3926,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="16.5">
+    <row r="49" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A49" s="19"/>
       <c r="B49" s="13"/>
       <c r="C49" s="13"/>
@@ -3922,7 +3938,7 @@
       <c r="I49" s="13"/>
       <c r="J49" s="13"/>
     </row>
-    <row r="50" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="50" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A50" s="19"/>
       <c r="B50" s="9" t="s">
         <v>147</v>
@@ -3944,7 +3960,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="51" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="51" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A51" s="19"/>
       <c r="B51" s="9" t="s">
         <v>116</v>
@@ -3968,7 +3984,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="52" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="52" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A52" s="19"/>
       <c r="B52" s="9" t="s">
         <v>116</v>
@@ -3995,7 +4011,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="16.5">
+    <row r="53" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A53" s="19"/>
       <c r="B53" s="13"/>
       <c r="C53" s="13"/>
@@ -4007,7 +4023,7 @@
       <c r="I53" s="13"/>
       <c r="J53" s="13"/>
     </row>
-    <row r="54" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="54" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A54" s="19"/>
       <c r="B54" s="9" t="s">
         <v>147</v>
@@ -4029,7 +4045,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="55" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="55" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A55" s="19"/>
       <c r="B55" s="9" t="s">
         <v>116</v>
@@ -4053,7 +4069,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="56" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="56" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A56" s="19"/>
       <c r="B56" s="9" t="s">
         <v>116</v>
@@ -4077,7 +4093,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="16.5">
+    <row r="57" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A57" s="19"/>
       <c r="B57" s="13"/>
       <c r="C57" s="13"/>
@@ -4089,7 +4105,7 @@
       <c r="I57" s="13"/>
       <c r="J57" s="13"/>
     </row>
-    <row r="58" spans="1:10" s="46" customFormat="1" ht="16.5">
+    <row r="58" spans="1:10" s="46" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A58" s="23" t="s">
         <v>26</v>
       </c>
@@ -4115,7 +4131,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="59" spans="1:10" s="48" customFormat="1">
+    <row r="59" spans="1:10" s="48" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A59" s="47"/>
       <c r="D59" s="47"/>
       <c r="E59" s="47"/>
@@ -4123,7 +4139,7 @@
       <c r="H59" s="49"/>
       <c r="J59" s="53"/>
     </row>
-    <row r="60" spans="1:10" s="46" customFormat="1" ht="16.5">
+    <row r="60" spans="1:10" s="46" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A60" s="23" t="s">
         <v>29</v>
       </c>
@@ -4149,7 +4165,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="61" spans="1:10" s="48" customFormat="1">
+    <row r="61" spans="1:10" s="48" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A61" s="47"/>
       <c r="D61" s="47"/>
       <c r="E61" s="47"/>
@@ -4157,7 +4173,7 @@
       <c r="H61" s="49"/>
       <c r="J61" s="53"/>
     </row>
-    <row r="62" spans="1:10" s="46" customFormat="1" ht="16.5">
+    <row r="62" spans="1:10" s="46" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A62" s="23" t="s">
         <v>32</v>
       </c>
@@ -4183,7 +4199,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="63" spans="1:10" s="48" customFormat="1">
+    <row r="63" spans="1:10" s="48" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A63" s="47"/>
       <c r="D63" s="47"/>
       <c r="E63" s="47"/>
@@ -4191,7 +4207,7 @@
       <c r="H63" s="49"/>
       <c r="J63" s="53"/>
     </row>
-    <row r="64" spans="1:10" s="46" customFormat="1" ht="16.5">
+    <row r="64" spans="1:10" s="46" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A64" s="23" t="s">
         <v>34</v>
       </c>
@@ -4217,7 +4233,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="65" spans="1:10" s="48" customFormat="1">
+    <row r="65" spans="1:10" s="48" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A65" s="47"/>
       <c r="D65" s="47"/>
       <c r="E65" s="47"/>
@@ -4225,7 +4241,7 @@
       <c r="H65" s="49"/>
       <c r="J65" s="53"/>
     </row>
-    <row r="66" spans="1:10" s="46" customFormat="1" ht="16.5">
+    <row r="66" spans="1:10" s="46" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A66" s="23" t="s">
         <v>37</v>
       </c>
@@ -4251,7 +4267,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="67" spans="1:10" s="48" customFormat="1">
+    <row r="67" spans="1:10" s="48" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A67" s="47"/>
       <c r="D67" s="47"/>
       <c r="E67" s="47"/>
@@ -4259,7 +4275,7 @@
       <c r="H67" s="49"/>
       <c r="J67" s="53"/>
     </row>
-    <row r="68" spans="1:10" s="46" customFormat="1" ht="16.5">
+    <row r="68" spans="1:10" s="46" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A68" s="23" t="s">
         <v>39</v>
       </c>
@@ -4285,7 +4301,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="69" spans="1:10" s="48" customFormat="1">
+    <row r="69" spans="1:10" s="48" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A69" s="47"/>
       <c r="D69" s="47"/>
       <c r="E69" s="47"/>
@@ -4293,7 +4309,7 @@
       <c r="H69" s="49"/>
       <c r="J69" s="53"/>
     </row>
-    <row r="70" spans="1:10" s="46" customFormat="1" ht="16.5">
+    <row r="70" spans="1:10" s="46" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A70" s="23" t="s">
         <v>40</v>
       </c>
@@ -4319,20 +4335,20 @@
         <v>239</v>
       </c>
     </row>
-    <row r="71" spans="1:10">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.15">
       <c r="H71" s="21"/>
     </row>
-    <row r="72" spans="1:10" s="51" customFormat="1" ht="40.5" customHeight="1">
+    <row r="72" spans="1:10" s="51" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="50"/>
       <c r="D72" s="50"/>
       <c r="E72" s="50"/>
       <c r="F72" s="50"/>
       <c r="H72" s="52"/>
     </row>
-    <row r="73" spans="1:10">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.15">
       <c r="H73" s="21"/>
     </row>
-    <row r="74" spans="1:10" s="13" customFormat="1" ht="21">
+    <row r="74" spans="1:10" s="13" customFormat="1" ht="21" x14ac:dyDescent="0.4">
       <c r="A74" s="23">
         <v>10101</v>
       </c>
@@ -4358,7 +4374,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="75" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="75" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A75" s="10"/>
       <c r="B75" s="9" t="s">
         <v>116</v>
@@ -4379,7 +4395,7 @@
       </c>
       <c r="I75" s="9"/>
     </row>
-    <row r="76" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="76" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A76" s="10"/>
       <c r="B76" s="9" t="s">
         <v>116</v>
@@ -4400,7 +4416,7 @@
       </c>
       <c r="I76" s="9"/>
     </row>
-    <row r="77" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="77" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A77" s="10"/>
       <c r="B77" s="9"/>
       <c r="C77" s="9"/>
@@ -4411,7 +4427,7 @@
       <c r="H77" s="17"/>
       <c r="I77" s="9"/>
     </row>
-    <row r="78" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="78" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A78" s="10"/>
       <c r="B78" s="9" t="s">
         <v>147</v>
@@ -4439,7 +4455,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="79" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="79" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A79" s="10"/>
       <c r="B79" s="9" t="s">
         <v>116</v>
@@ -4464,7 +4480,7 @@
       </c>
       <c r="I79" s="9"/>
     </row>
-    <row r="80" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="80" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A80" s="10"/>
       <c r="B80" s="9" t="s">
         <v>116</v>
@@ -4489,7 +4505,7 @@
       </c>
       <c r="I80" s="9"/>
     </row>
-    <row r="81" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="81" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A81" s="10"/>
       <c r="B81" s="9" t="s">
         <v>116</v>
@@ -4514,7 +4530,7 @@
       </c>
       <c r="I81" s="9"/>
     </row>
-    <row r="82" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="82" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A82" s="10"/>
       <c r="B82" s="9" t="s">
         <v>116</v>
@@ -4539,7 +4555,7 @@
       </c>
       <c r="I82" s="9"/>
     </row>
-    <row r="83" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="83" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A83" s="10"/>
       <c r="B83" s="9"/>
       <c r="C83" s="9"/>
@@ -4550,7 +4566,7 @@
       <c r="H83" s="17"/>
       <c r="I83" s="9"/>
     </row>
-    <row r="84" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="84" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A84" s="10"/>
       <c r="B84" s="9" t="s">
         <v>147</v>
@@ -4576,7 +4592,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="85" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="85" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A85" s="10"/>
       <c r="B85" s="9" t="s">
         <v>116</v>
@@ -4601,7 +4617,7 @@
       </c>
       <c r="I85" s="9"/>
     </row>
-    <row r="86" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="86" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A86" s="10"/>
       <c r="B86" s="9" t="s">
         <v>116</v>
@@ -4626,7 +4642,7 @@
       </c>
       <c r="I86" s="9"/>
     </row>
-    <row r="87" spans="1:10" s="13" customFormat="1" ht="33">
+    <row r="87" spans="1:10" s="13" customFormat="1" ht="33" x14ac:dyDescent="0.3">
       <c r="A87" s="10"/>
       <c r="B87" s="9" t="s">
         <v>116</v>
@@ -4651,7 +4667,7 @@
       </c>
       <c r="I87" s="9"/>
     </row>
-    <row r="88" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="88" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A88" s="10"/>
       <c r="B88" s="9"/>
       <c r="C88" s="9"/>
@@ -4662,7 +4678,7 @@
       <c r="H88" s="17"/>
       <c r="I88" s="9"/>
     </row>
-    <row r="89" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="89" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A89" s="10"/>
       <c r="B89" s="9" t="s">
         <v>147</v>
@@ -4688,7 +4704,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="90" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="90" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A90" s="10"/>
       <c r="B90" s="9" t="s">
         <v>116</v>
@@ -4713,7 +4729,7 @@
       </c>
       <c r="I90" s="9"/>
     </row>
-    <row r="91" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="91" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A91" s="10"/>
       <c r="B91" s="9" t="s">
         <v>116</v>
@@ -4738,7 +4754,7 @@
       </c>
       <c r="I91" s="9"/>
     </row>
-    <row r="92" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="92" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A92" s="10"/>
       <c r="B92" s="9"/>
       <c r="C92" s="9"/>
@@ -4749,7 +4765,7 @@
       <c r="H92" s="11"/>
       <c r="I92" s="9"/>
     </row>
-    <row r="93" spans="1:10" s="13" customFormat="1" ht="21.75" customHeight="1">
+    <row r="93" spans="1:10" s="13" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="23">
         <v>20101</v>
       </c>
@@ -4775,7 +4791,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="94" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="94" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A94" s="10"/>
       <c r="B94" s="9"/>
       <c r="C94" s="9"/>
@@ -4786,7 +4802,7 @@
       <c r="H94" s="11"/>
       <c r="I94" s="9"/>
     </row>
-    <row r="95" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="95" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A95" s="10"/>
       <c r="B95" s="9"/>
       <c r="C95" s="9"/>
@@ -4807,7 +4823,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="96" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="96" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A96" s="10"/>
       <c r="B96" s="9" t="s">
         <v>116</v>
@@ -4832,7 +4848,7 @@
       </c>
       <c r="I96" s="9"/>
     </row>
-    <row r="97" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="97" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A97" s="10"/>
       <c r="B97" s="9" t="s">
         <v>116</v>
@@ -4857,7 +4873,7 @@
       </c>
       <c r="I97" s="9"/>
     </row>
-    <row r="98" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="98" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A98" s="10"/>
       <c r="B98" s="9"/>
       <c r="C98" s="9"/>
@@ -4868,7 +4884,7 @@
       <c r="H98" s="11"/>
       <c r="I98" s="9"/>
     </row>
-    <row r="99" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="99" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A99" s="10"/>
       <c r="B99" s="9"/>
       <c r="C99" s="9"/>
@@ -4887,7 +4903,7 @@
       </c>
       <c r="I99" s="9"/>
     </row>
-    <row r="100" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="100" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A100" s="10"/>
       <c r="B100" s="9" t="s">
         <v>116</v>
@@ -4912,7 +4928,7 @@
       </c>
       <c r="I100" s="9"/>
     </row>
-    <row r="101" spans="1:10" s="13" customFormat="1" ht="33">
+    <row r="101" spans="1:10" s="13" customFormat="1" ht="33" x14ac:dyDescent="0.3">
       <c r="A101" s="10"/>
       <c r="B101" s="9" t="s">
         <v>116</v>
@@ -4937,7 +4953,7 @@
       </c>
       <c r="I101" s="9"/>
     </row>
-    <row r="102" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="102" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A102" s="10"/>
       <c r="B102" s="9"/>
       <c r="C102" s="9"/>
@@ -4948,7 +4964,7 @@
       <c r="H102" s="11"/>
       <c r="I102" s="9"/>
     </row>
-    <row r="103" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="103" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A103" s="10"/>
       <c r="B103" s="9"/>
       <c r="C103" s="9"/>
@@ -4967,7 +4983,7 @@
       </c>
       <c r="I103" s="9"/>
     </row>
-    <row r="104" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="104" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A104" s="10"/>
       <c r="B104" s="9" t="s">
         <v>116</v>
@@ -4992,7 +5008,7 @@
       </c>
       <c r="I104" s="9"/>
     </row>
-    <row r="105" spans="1:10" s="13" customFormat="1" ht="33">
+    <row r="105" spans="1:10" s="13" customFormat="1" ht="33" x14ac:dyDescent="0.3">
       <c r="A105" s="10"/>
       <c r="B105" s="9" t="s">
         <v>116</v>
@@ -5017,7 +5033,7 @@
       </c>
       <c r="I105" s="9"/>
     </row>
-    <row r="106" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="106" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A106" s="10"/>
       <c r="B106" s="9"/>
       <c r="C106" s="9"/>
@@ -5028,7 +5044,7 @@
       <c r="H106" s="18"/>
       <c r="I106" s="9"/>
     </row>
-    <row r="107" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="107" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A107" s="10"/>
       <c r="B107" s="9"/>
       <c r="C107" s="9"/>
@@ -5039,7 +5055,7 @@
       <c r="H107" s="11"/>
       <c r="I107" s="9"/>
     </row>
-    <row r="108" spans="1:10" s="32" customFormat="1" ht="21">
+    <row r="108" spans="1:10" s="32" customFormat="1" ht="21" x14ac:dyDescent="0.4">
       <c r="A108" s="23">
         <v>30101</v>
       </c>
@@ -5065,7 +5081,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="109" spans="1:10" ht="16.5">
+    <row r="109" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A109" s="19"/>
       <c r="B109" s="13"/>
       <c r="C109" s="13"/>
@@ -5077,7 +5093,7 @@
       <c r="I109" s="13"/>
       <c r="J109" s="13"/>
     </row>
-    <row r="110" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="110" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A110" s="19"/>
       <c r="B110" s="9" t="s">
         <v>147</v>
@@ -5102,7 +5118,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="111" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="111" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A111" s="19"/>
       <c r="B111" s="9" t="s">
         <v>116</v>
@@ -5126,7 +5142,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="112" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="112" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A112" s="19"/>
       <c r="B112" s="9" t="s">
         <v>116</v>
@@ -5153,7 +5169,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="113" spans="1:10" ht="16.5">
+    <row r="113" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A113" s="19"/>
       <c r="B113" s="13"/>
       <c r="C113" s="13"/>
@@ -5165,7 +5181,7 @@
       <c r="I113" s="13"/>
       <c r="J113" s="13"/>
     </row>
-    <row r="114" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="114" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A114" s="19"/>
       <c r="B114" s="9" t="s">
         <v>147</v>
@@ -5187,7 +5203,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="115" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="115" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A115" s="19"/>
       <c r="B115" s="9" t="s">
         <v>116</v>
@@ -5211,7 +5227,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="116" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="116" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A116" s="19"/>
       <c r="B116" s="9" t="s">
         <v>116</v>
@@ -5235,7 +5251,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="117" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="117" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A117" s="10"/>
       <c r="B117" s="9"/>
       <c r="C117" s="9"/>
@@ -5246,7 +5262,7 @@
       <c r="H117" s="11"/>
       <c r="I117" s="9"/>
     </row>
-    <row r="118" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="118" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A118" s="10"/>
       <c r="B118" s="9"/>
       <c r="C118" s="9"/>
@@ -5257,7 +5273,7 @@
       <c r="H118" s="11"/>
       <c r="I118" s="9"/>
     </row>
-    <row r="119" spans="1:10" s="32" customFormat="1" ht="21">
+    <row r="119" spans="1:10" s="32" customFormat="1" ht="21" x14ac:dyDescent="0.4">
       <c r="A119" s="23">
         <v>30102</v>
       </c>
@@ -5283,7 +5299,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="120" spans="1:10" ht="16.5">
+    <row r="120" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A120" s="19"/>
       <c r="B120" s="13"/>
       <c r="C120" s="13"/>
@@ -5295,7 +5311,7 @@
       <c r="I120" s="13"/>
       <c r="J120" s="13"/>
     </row>
-    <row r="121" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="121" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A121" s="19"/>
       <c r="B121" s="9" t="s">
         <v>147</v>
@@ -5317,7 +5333,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="122" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="122" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A122" s="19"/>
       <c r="B122" s="9" t="s">
         <v>116</v>
@@ -5341,7 +5357,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="123" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="123" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A123" s="19"/>
       <c r="B123" s="9" t="s">
         <v>116</v>
@@ -5368,7 +5384,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="124" spans="1:10" ht="16.5">
+    <row r="124" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A124" s="19"/>
       <c r="B124" s="13"/>
       <c r="C124" s="13"/>
@@ -5380,7 +5396,7 @@
       <c r="I124" s="13"/>
       <c r="J124" s="13"/>
     </row>
-    <row r="125" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="125" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A125" s="19"/>
       <c r="B125" s="9" t="s">
         <v>147</v>
@@ -5402,7 +5418,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="126" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="126" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A126" s="19"/>
       <c r="B126" s="9" t="s">
         <v>116</v>
@@ -5426,7 +5442,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="127" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="127" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A127" s="19"/>
       <c r="B127" s="9" t="s">
         <v>116</v>
@@ -5450,7 +5466,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="128" spans="1:10" ht="16.5">
+    <row r="128" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A128" s="19"/>
       <c r="B128" s="13"/>
       <c r="C128" s="13"/>
@@ -5462,7 +5478,7 @@
       <c r="I128" s="13"/>
       <c r="J128" s="13"/>
     </row>
-    <row r="129" spans="1:10" s="46" customFormat="1" ht="16.5">
+    <row r="129" spans="1:10" s="46" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A129" s="23">
         <v>40101</v>
       </c>
@@ -5488,14 +5504,14 @@
         <v>236</v>
       </c>
     </row>
-    <row r="130" spans="1:10" s="48" customFormat="1">
+    <row r="130" spans="1:10" s="48" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A130" s="47"/>
       <c r="D130" s="47"/>
       <c r="E130" s="47"/>
       <c r="F130" s="47"/>
       <c r="H130" s="49"/>
     </row>
-    <row r="131" spans="1:10" s="46" customFormat="1" ht="16.5">
+    <row r="131" spans="1:10" s="46" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A131" s="23">
         <v>40102</v>
       </c>
@@ -5521,14 +5537,14 @@
         <v>237</v>
       </c>
     </row>
-    <row r="132" spans="1:10" s="48" customFormat="1">
+    <row r="132" spans="1:10" s="48" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A132" s="47"/>
       <c r="D132" s="47"/>
       <c r="E132" s="47"/>
       <c r="F132" s="47"/>
       <c r="H132" s="49"/>
     </row>
-    <row r="133" spans="1:10" s="46" customFormat="1" ht="16.5">
+    <row r="133" spans="1:10" s="46" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A133" s="23">
         <v>40103</v>
       </c>
@@ -5554,14 +5570,14 @@
         <v>237</v>
       </c>
     </row>
-    <row r="134" spans="1:10" s="48" customFormat="1">
+    <row r="134" spans="1:10" s="48" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A134" s="47"/>
       <c r="D134" s="47"/>
       <c r="E134" s="47"/>
       <c r="F134" s="47"/>
       <c r="H134" s="49"/>
     </row>
-    <row r="135" spans="1:10" s="46" customFormat="1" ht="16.5">
+    <row r="135" spans="1:10" s="46" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A135" s="23">
         <v>40104</v>
       </c>
@@ -5587,14 +5603,14 @@
         <v>238</v>
       </c>
     </row>
-    <row r="136" spans="1:10" s="48" customFormat="1">
+    <row r="136" spans="1:10" s="48" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A136" s="47"/>
       <c r="D136" s="47"/>
       <c r="E136" s="47"/>
       <c r="F136" s="47"/>
       <c r="H136" s="49"/>
     </row>
-    <row r="137" spans="1:10" s="46" customFormat="1" ht="16.5">
+    <row r="137" spans="1:10" s="46" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A137" s="23">
         <v>50101</v>
       </c>
@@ -5620,14 +5636,14 @@
         <v>239</v>
       </c>
     </row>
-    <row r="138" spans="1:10" s="48" customFormat="1">
+    <row r="138" spans="1:10" s="48" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A138" s="47"/>
       <c r="D138" s="47"/>
       <c r="E138" s="47"/>
       <c r="F138" s="47"/>
       <c r="H138" s="49"/>
     </row>
-    <row r="139" spans="1:10" s="46" customFormat="1" ht="16.5">
+    <row r="139" spans="1:10" s="46" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A139" s="23">
         <v>50102</v>
       </c>
@@ -5653,14 +5669,14 @@
         <v>239</v>
       </c>
     </row>
-    <row r="140" spans="1:10" s="48" customFormat="1">
+    <row r="140" spans="1:10" s="48" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A140" s="47"/>
       <c r="D140" s="47"/>
       <c r="E140" s="47"/>
       <c r="F140" s="47"/>
       <c r="H140" s="49"/>
     </row>
-    <row r="141" spans="1:10" s="46" customFormat="1" ht="16.5">
+    <row r="141" spans="1:10" s="46" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A141" s="23">
         <v>50103</v>
       </c>
@@ -5686,20 +5702,20 @@
         <v>239</v>
       </c>
     </row>
-    <row r="142" spans="1:10">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.15">
       <c r="H142" s="21"/>
     </row>
-    <row r="143" spans="1:10" s="51" customFormat="1" ht="40.5" customHeight="1">
+    <row r="143" spans="1:10" s="51" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A143" s="50"/>
       <c r="D143" s="50"/>
       <c r="E143" s="50"/>
       <c r="F143" s="50"/>
       <c r="H143" s="52"/>
     </row>
-    <row r="144" spans="1:10">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.15">
       <c r="H144" s="21"/>
     </row>
-    <row r="145" spans="1:10" s="13" customFormat="1" ht="21">
+    <row r="145" spans="1:10" s="13" customFormat="1" ht="21" x14ac:dyDescent="0.4">
       <c r="A145" s="23">
         <v>10201</v>
       </c>
@@ -5725,7 +5741,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="146" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="146" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A146" s="10"/>
       <c r="B146" s="9" t="s">
         <v>116</v>
@@ -5746,7 +5762,7 @@
       </c>
       <c r="I146" s="9"/>
     </row>
-    <row r="147" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="147" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A147" s="10"/>
       <c r="B147" s="9" t="s">
         <v>116</v>
@@ -5767,7 +5783,7 @@
       </c>
       <c r="I147" s="9"/>
     </row>
-    <row r="148" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="148" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A148" s="10"/>
       <c r="B148" s="9"/>
       <c r="C148" s="9"/>
@@ -5778,7 +5794,7 @@
       <c r="H148" s="17"/>
       <c r="I148" s="9"/>
     </row>
-    <row r="149" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="149" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A149" s="10"/>
       <c r="B149" s="9" t="s">
         <v>147</v>
@@ -5806,7 +5822,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="150" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="150" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A150" s="10"/>
       <c r="B150" s="9" t="s">
         <v>116</v>
@@ -5831,7 +5847,7 @@
       </c>
       <c r="I150" s="9"/>
     </row>
-    <row r="151" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="151" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A151" s="10"/>
       <c r="B151" s="9" t="s">
         <v>116</v>
@@ -5856,7 +5872,7 @@
       </c>
       <c r="I151" s="9"/>
     </row>
-    <row r="152" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="152" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A152" s="10"/>
       <c r="B152" s="9" t="s">
         <v>116</v>
@@ -5881,7 +5897,7 @@
       </c>
       <c r="I152" s="9"/>
     </row>
-    <row r="153" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="153" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A153" s="10"/>
       <c r="B153" s="9" t="s">
         <v>116</v>
@@ -5906,7 +5922,7 @@
       </c>
       <c r="I153" s="9"/>
     </row>
-    <row r="154" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="154" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A154" s="10"/>
       <c r="B154" s="9"/>
       <c r="C154" s="9"/>
@@ -5917,7 +5933,7 @@
       <c r="H154" s="17"/>
       <c r="I154" s="9"/>
     </row>
-    <row r="155" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="155" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A155" s="10"/>
       <c r="B155" s="9" t="s">
         <v>147</v>
@@ -5943,7 +5959,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="156" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="156" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A156" s="10"/>
       <c r="B156" s="9" t="s">
         <v>116</v>
@@ -5968,7 +5984,7 @@
       </c>
       <c r="I156" s="9"/>
     </row>
-    <row r="157" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="157" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A157" s="10"/>
       <c r="B157" s="9" t="s">
         <v>116</v>
@@ -5993,7 +6009,7 @@
       </c>
       <c r="I157" s="9"/>
     </row>
-    <row r="158" spans="1:10" s="13" customFormat="1" ht="33">
+    <row r="158" spans="1:10" s="13" customFormat="1" ht="33" x14ac:dyDescent="0.3">
       <c r="A158" s="10"/>
       <c r="B158" s="9" t="s">
         <v>116</v>
@@ -6014,11 +6030,11 @@
         <v>119</v>
       </c>
       <c r="H158" s="11" t="s">
-        <v>249</v>
+        <v>307</v>
       </c>
       <c r="I158" s="9"/>
     </row>
-    <row r="159" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="159" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A159" s="10"/>
       <c r="B159" s="9"/>
       <c r="C159" s="9"/>
@@ -6029,7 +6045,7 @@
       <c r="H159" s="17"/>
       <c r="I159" s="9"/>
     </row>
-    <row r="160" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="160" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A160" s="10"/>
       <c r="B160" s="9" t="s">
         <v>147</v>
@@ -6055,7 +6071,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="161" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="161" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A161" s="10"/>
       <c r="B161" s="9" t="s">
         <v>116</v>
@@ -6080,7 +6096,7 @@
       </c>
       <c r="I161" s="9"/>
     </row>
-    <row r="162" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="162" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A162" s="10"/>
       <c r="B162" s="9" t="s">
         <v>116</v>
@@ -6105,7 +6121,7 @@
       </c>
       <c r="I162" s="9"/>
     </row>
-    <row r="163" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="163" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A163" s="10"/>
       <c r="B163" s="9"/>
       <c r="C163" s="9"/>
@@ -6116,7 +6132,7 @@
       <c r="H163" s="11"/>
       <c r="I163" s="9"/>
     </row>
-    <row r="164" spans="1:10" s="13" customFormat="1" ht="21.75" customHeight="1">
+    <row r="164" spans="1:10" s="13" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A164" s="23">
         <v>20201</v>
       </c>
@@ -6142,7 +6158,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="165" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="165" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A165" s="10"/>
       <c r="B165" s="9"/>
       <c r="C165" s="9"/>
@@ -6153,7 +6169,7 @@
       <c r="H165" s="11"/>
       <c r="I165" s="9"/>
     </row>
-    <row r="166" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="166" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A166" s="10"/>
       <c r="B166" s="9"/>
       <c r="C166" s="9"/>
@@ -6174,7 +6190,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="167" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="167" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A167" s="10"/>
       <c r="B167" s="9" t="s">
         <v>116</v>
@@ -6199,7 +6215,7 @@
       </c>
       <c r="I167" s="9"/>
     </row>
-    <row r="168" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="168" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A168" s="10"/>
       <c r="B168" s="9" t="s">
         <v>116</v>
@@ -6224,7 +6240,7 @@
       </c>
       <c r="I168" s="9"/>
     </row>
-    <row r="169" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="169" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A169" s="10"/>
       <c r="B169" s="9"/>
       <c r="C169" s="9"/>
@@ -6235,7 +6251,7 @@
       <c r="H169" s="11"/>
       <c r="I169" s="9"/>
     </row>
-    <row r="170" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="170" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A170" s="10"/>
       <c r="B170" s="9"/>
       <c r="C170" s="9"/>
@@ -6254,7 +6270,7 @@
       </c>
       <c r="I170" s="9"/>
     </row>
-    <row r="171" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="171" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A171" s="10"/>
       <c r="B171" s="9" t="s">
         <v>116</v>
@@ -6279,7 +6295,7 @@
       </c>
       <c r="I171" s="9"/>
     </row>
-    <row r="172" spans="1:10" s="13" customFormat="1" ht="33">
+    <row r="172" spans="1:10" s="13" customFormat="1" ht="33" x14ac:dyDescent="0.3">
       <c r="A172" s="10"/>
       <c r="B172" s="9" t="s">
         <v>116</v>
@@ -6304,7 +6320,7 @@
       </c>
       <c r="I172" s="9"/>
     </row>
-    <row r="173" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="173" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A173" s="10"/>
       <c r="B173" s="9"/>
       <c r="C173" s="9"/>
@@ -6315,7 +6331,7 @@
       <c r="H173" s="11"/>
       <c r="I173" s="9"/>
     </row>
-    <row r="174" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="174" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A174" s="10"/>
       <c r="B174" s="9"/>
       <c r="C174" s="9"/>
@@ -6334,7 +6350,7 @@
       </c>
       <c r="I174" s="9"/>
     </row>
-    <row r="175" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="175" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A175" s="10"/>
       <c r="B175" s="9" t="s">
         <v>116</v>
@@ -6359,7 +6375,7 @@
       </c>
       <c r="I175" s="9"/>
     </row>
-    <row r="176" spans="1:10" s="13" customFormat="1" ht="33">
+    <row r="176" spans="1:10" s="13" customFormat="1" ht="33" x14ac:dyDescent="0.3">
       <c r="A176" s="10"/>
       <c r="B176" s="9" t="s">
         <v>116</v>
@@ -6384,7 +6400,7 @@
       </c>
       <c r="I176" s="9"/>
     </row>
-    <row r="177" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="177" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A177" s="10"/>
       <c r="B177" s="9"/>
       <c r="C177" s="9"/>
@@ -6395,7 +6411,7 @@
       <c r="H177" s="18"/>
       <c r="I177" s="9"/>
     </row>
-    <row r="178" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="178" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A178" s="10"/>
       <c r="B178" s="9"/>
       <c r="C178" s="9"/>
@@ -6406,7 +6422,7 @@
       <c r="H178" s="11"/>
       <c r="I178" s="9"/>
     </row>
-    <row r="179" spans="1:10" s="32" customFormat="1" ht="21">
+    <row r="179" spans="1:10" s="32" customFormat="1" ht="21" x14ac:dyDescent="0.4">
       <c r="A179" s="23">
         <v>30201</v>
       </c>
@@ -6432,7 +6448,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="180" spans="1:10" ht="16.5">
+    <row r="180" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A180" s="19"/>
       <c r="B180" s="13"/>
       <c r="C180" s="13"/>
@@ -6444,7 +6460,7 @@
       <c r="I180" s="13"/>
       <c r="J180" s="13"/>
     </row>
-    <row r="181" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="181" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A181" s="19"/>
       <c r="B181" s="9" t="s">
         <v>147</v>
@@ -6469,7 +6485,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="182" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="182" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A182" s="19"/>
       <c r="B182" s="9" t="s">
         <v>116</v>
@@ -6493,7 +6509,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="183" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="183" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A183" s="19"/>
       <c r="B183" s="9" t="s">
         <v>116</v>
@@ -6518,7 +6534,7 @@
       </c>
       <c r="J183" s="39"/>
     </row>
-    <row r="184" spans="1:10" ht="16.5">
+    <row r="184" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A184" s="19"/>
       <c r="B184" s="13"/>
       <c r="C184" s="13"/>
@@ -6530,7 +6546,7 @@
       <c r="I184" s="13"/>
       <c r="J184" s="13"/>
     </row>
-    <row r="185" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="185" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A185" s="19"/>
       <c r="B185" s="9" t="s">
         <v>147</v>
@@ -6552,7 +6568,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="186" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="186" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A186" s="19"/>
       <c r="B186" s="9" t="s">
         <v>116</v>
@@ -6576,7 +6592,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="187" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="187" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A187" s="19"/>
       <c r="B187" s="9" t="s">
         <v>116</v>
@@ -6600,7 +6616,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="188" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="188" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A188" s="10"/>
       <c r="B188" s="9"/>
       <c r="C188" s="9"/>
@@ -6611,7 +6627,7 @@
       <c r="H188" s="11"/>
       <c r="I188" s="9"/>
     </row>
-    <row r="189" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="189" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A189" s="10"/>
       <c r="B189" s="9"/>
       <c r="C189" s="9"/>
@@ -6622,7 +6638,7 @@
       <c r="H189" s="11"/>
       <c r="I189" s="9"/>
     </row>
-    <row r="190" spans="1:10" s="32" customFormat="1" ht="21">
+    <row r="190" spans="1:10" s="32" customFormat="1" ht="21" x14ac:dyDescent="0.4">
       <c r="A190" s="23">
         <v>30202</v>
       </c>
@@ -6648,7 +6664,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="191" spans="1:10" ht="16.5">
+    <row r="191" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A191" s="19"/>
       <c r="B191" s="13"/>
       <c r="C191" s="13"/>
@@ -6660,7 +6676,7 @@
       <c r="I191" s="13"/>
       <c r="J191" s="13"/>
     </row>
-    <row r="192" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="192" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A192" s="19"/>
       <c r="B192" s="9" t="s">
         <v>147</v>
@@ -6682,7 +6698,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="193" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="193" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A193" s="19"/>
       <c r="B193" s="9" t="s">
         <v>116</v>
@@ -6706,7 +6722,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="194" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="194" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A194" s="19"/>
       <c r="B194" s="9" t="s">
         <v>116</v>
@@ -6733,7 +6749,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="195" spans="1:10" ht="16.5">
+    <row r="195" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A195" s="19"/>
       <c r="B195" s="13"/>
       <c r="C195" s="13"/>
@@ -6745,7 +6761,7 @@
       <c r="I195" s="13"/>
       <c r="J195" s="13"/>
     </row>
-    <row r="196" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="196" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A196" s="19"/>
       <c r="B196" s="9" t="s">
         <v>147</v>
@@ -6767,7 +6783,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="197" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="197" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A197" s="19"/>
       <c r="B197" s="9" t="s">
         <v>116</v>
@@ -6791,7 +6807,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="198" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="198" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A198" s="19"/>
       <c r="B198" s="9" t="s">
         <v>116</v>
@@ -6815,7 +6831,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="199" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="199" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A199" s="10"/>
       <c r="B199" s="9"/>
       <c r="C199" s="9"/>
@@ -6826,7 +6842,7 @@
       <c r="H199" s="11"/>
       <c r="I199" s="9"/>
     </row>
-    <row r="200" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="200" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A200" s="10"/>
       <c r="B200" s="9"/>
       <c r="C200" s="9"/>
@@ -6837,7 +6853,7 @@
       <c r="H200" s="11"/>
       <c r="I200" s="9"/>
     </row>
-    <row r="201" spans="1:10" s="32" customFormat="1" ht="21">
+    <row r="201" spans="1:10" s="32" customFormat="1" ht="21" x14ac:dyDescent="0.4">
       <c r="A201" s="23">
         <v>30203</v>
       </c>
@@ -6863,7 +6879,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="202" spans="1:10" ht="16.5">
+    <row r="202" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A202" s="19"/>
       <c r="B202" s="13"/>
       <c r="C202" s="13"/>
@@ -6875,7 +6891,7 @@
       <c r="I202" s="13"/>
       <c r="J202" s="13"/>
     </row>
-    <row r="203" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="203" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A203" s="19"/>
       <c r="B203" s="9" t="s">
         <v>147</v>
@@ -6897,7 +6913,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="204" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="204" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A204" s="19"/>
       <c r="B204" s="9" t="s">
         <v>116</v>
@@ -6921,7 +6937,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="205" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="205" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A205" s="19"/>
       <c r="B205" s="9" t="s">
         <v>116</v>
@@ -6948,7 +6964,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="206" spans="1:10" ht="16.5">
+    <row r="206" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A206" s="19"/>
       <c r="B206" s="13"/>
       <c r="C206" s="13"/>
@@ -6960,7 +6976,7 @@
       <c r="I206" s="13"/>
       <c r="J206" s="13"/>
     </row>
-    <row r="207" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="207" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A207" s="19"/>
       <c r="B207" s="9" t="s">
         <v>147</v>
@@ -6982,7 +6998,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="208" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="208" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A208" s="19"/>
       <c r="B208" s="9" t="s">
         <v>116</v>
@@ -7006,7 +7022,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="209" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="209" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A209" s="19"/>
       <c r="B209" s="9" t="s">
         <v>116</v>
@@ -7030,7 +7046,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="210" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="210" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A210" s="10"/>
       <c r="B210" s="9"/>
       <c r="C210" s="9"/>
@@ -7041,7 +7057,7 @@
       <c r="H210" s="11"/>
       <c r="I210" s="9"/>
     </row>
-    <row r="211" spans="1:10" ht="16.5">
+    <row r="211" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A211" s="19"/>
       <c r="B211" s="13"/>
       <c r="C211" s="13"/>
@@ -7053,7 +7069,7 @@
       <c r="I211" s="13"/>
       <c r="J211" s="13"/>
     </row>
-    <row r="212" spans="1:10" s="46" customFormat="1" ht="16.5">
+    <row r="212" spans="1:10" s="46" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A212" s="23">
         <v>40201</v>
       </c>
@@ -7079,14 +7095,14 @@
         <v>236</v>
       </c>
     </row>
-    <row r="213" spans="1:10" s="48" customFormat="1">
+    <row r="213" spans="1:10" s="48" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A213" s="47"/>
       <c r="D213" s="47"/>
       <c r="E213" s="47"/>
       <c r="F213" s="47"/>
       <c r="H213" s="49"/>
     </row>
-    <row r="214" spans="1:10" s="46" customFormat="1" ht="16.5">
+    <row r="214" spans="1:10" s="46" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A214" s="23">
         <v>40202</v>
       </c>
@@ -7112,14 +7128,14 @@
         <v>237</v>
       </c>
     </row>
-    <row r="215" spans="1:10" s="48" customFormat="1">
+    <row r="215" spans="1:10" s="48" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A215" s="47"/>
       <c r="D215" s="47"/>
       <c r="E215" s="47"/>
       <c r="F215" s="47"/>
       <c r="H215" s="49"/>
     </row>
-    <row r="216" spans="1:10" s="46" customFormat="1" ht="16.5">
+    <row r="216" spans="1:10" s="46" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A216" s="23">
         <v>40203</v>
       </c>
@@ -7145,14 +7161,14 @@
         <v>237</v>
       </c>
     </row>
-    <row r="217" spans="1:10" s="48" customFormat="1">
+    <row r="217" spans="1:10" s="48" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A217" s="47"/>
       <c r="D217" s="47"/>
       <c r="E217" s="47"/>
       <c r="F217" s="47"/>
       <c r="H217" s="49"/>
     </row>
-    <row r="218" spans="1:10" s="46" customFormat="1" ht="16.5">
+    <row r="218" spans="1:10" s="46" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A218" s="23">
         <v>40204</v>
       </c>
@@ -7178,14 +7194,14 @@
         <v>238</v>
       </c>
     </row>
-    <row r="219" spans="1:10" s="48" customFormat="1">
+    <row r="219" spans="1:10" s="48" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A219" s="47"/>
       <c r="D219" s="47"/>
       <c r="E219" s="47"/>
       <c r="F219" s="47"/>
       <c r="H219" s="49"/>
     </row>
-    <row r="220" spans="1:10" s="46" customFormat="1" ht="16.5">
+    <row r="220" spans="1:10" s="46" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A220" s="23">
         <v>50201</v>
       </c>
@@ -7211,14 +7227,14 @@
         <v>239</v>
       </c>
     </row>
-    <row r="221" spans="1:10" s="48" customFormat="1">
+    <row r="221" spans="1:10" s="48" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A221" s="47"/>
       <c r="D221" s="47"/>
       <c r="E221" s="47"/>
       <c r="F221" s="47"/>
       <c r="H221" s="49"/>
     </row>
-    <row r="222" spans="1:10" s="46" customFormat="1" ht="16.5">
+    <row r="222" spans="1:10" s="46" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A222" s="23">
         <v>50202</v>
       </c>
@@ -7244,14 +7260,14 @@
         <v>239</v>
       </c>
     </row>
-    <row r="223" spans="1:10" s="48" customFormat="1">
+    <row r="223" spans="1:10" s="48" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A223" s="47"/>
       <c r="D223" s="47"/>
       <c r="E223" s="47"/>
       <c r="F223" s="47"/>
       <c r="H223" s="49"/>
     </row>
-    <row r="224" spans="1:10" s="46" customFormat="1" ht="16.5">
+    <row r="224" spans="1:10" s="46" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A224" s="23">
         <v>50203</v>
       </c>
@@ -7277,20 +7293,20 @@
         <v>239</v>
       </c>
     </row>
-    <row r="225" spans="1:10">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.15">
       <c r="H225" s="21"/>
     </row>
-    <row r="226" spans="1:10" s="51" customFormat="1" ht="40.5" customHeight="1">
+    <row r="226" spans="1:10" s="51" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A226" s="50"/>
       <c r="D226" s="50"/>
       <c r="E226" s="50"/>
       <c r="F226" s="50"/>
       <c r="H226" s="52"/>
     </row>
-    <row r="227" spans="1:10">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.15">
       <c r="H227" s="21"/>
     </row>
-    <row r="228" spans="1:10" s="13" customFormat="1" ht="21">
+    <row r="228" spans="1:10" s="13" customFormat="1" ht="21" x14ac:dyDescent="0.4">
       <c r="A228" s="23">
         <v>10301</v>
       </c>
@@ -7316,7 +7332,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="229" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="229" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A229" s="10"/>
       <c r="B229" s="9" t="s">
         <v>116</v>
@@ -7337,7 +7353,7 @@
       </c>
       <c r="I229" s="9"/>
     </row>
-    <row r="230" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="230" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A230" s="10"/>
       <c r="B230" s="9" t="s">
         <v>116</v>
@@ -7358,7 +7374,7 @@
       </c>
       <c r="I230" s="9"/>
     </row>
-    <row r="231" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="231" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A231" s="10"/>
       <c r="B231" s="9"/>
       <c r="C231" s="9"/>
@@ -7369,7 +7385,7 @@
       <c r="H231" s="17"/>
       <c r="I231" s="9"/>
     </row>
-    <row r="232" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="232" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A232" s="10"/>
       <c r="B232" s="9" t="s">
         <v>147</v>
@@ -7397,7 +7413,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="233" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="233" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A233" s="10"/>
       <c r="B233" s="9" t="s">
         <v>116</v>
@@ -7422,7 +7438,7 @@
       </c>
       <c r="I233" s="9"/>
     </row>
-    <row r="234" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="234" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A234" s="10"/>
       <c r="B234" s="9" t="s">
         <v>116</v>
@@ -7447,7 +7463,7 @@
       </c>
       <c r="I234" s="9"/>
     </row>
-    <row r="235" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="235" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A235" s="10"/>
       <c r="B235" s="9" t="s">
         <v>116</v>
@@ -7472,7 +7488,7 @@
       </c>
       <c r="I235" s="9"/>
     </row>
-    <row r="236" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="236" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A236" s="10"/>
       <c r="B236" s="9" t="s">
         <v>116</v>
@@ -7497,7 +7513,7 @@
       </c>
       <c r="I236" s="9"/>
     </row>
-    <row r="237" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="237" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A237" s="10"/>
       <c r="B237" s="9"/>
       <c r="C237" s="9"/>
@@ -7508,7 +7524,7 @@
       <c r="H237" s="17"/>
       <c r="I237" s="9"/>
     </row>
-    <row r="238" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="238" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A238" s="10"/>
       <c r="B238" s="9" t="s">
         <v>147</v>
@@ -7534,7 +7550,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="239" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="239" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A239" s="10"/>
       <c r="B239" s="9" t="s">
         <v>116</v>
@@ -7559,7 +7575,7 @@
       </c>
       <c r="I239" s="9"/>
     </row>
-    <row r="240" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="240" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A240" s="10"/>
       <c r="B240" s="9" t="s">
         <v>116</v>
@@ -7584,7 +7600,7 @@
       </c>
       <c r="I240" s="9"/>
     </row>
-    <row r="241" spans="1:10" s="13" customFormat="1" ht="33">
+    <row r="241" spans="1:10" s="13" customFormat="1" ht="33" x14ac:dyDescent="0.3">
       <c r="A241" s="10"/>
       <c r="B241" s="9" t="s">
         <v>116</v>
@@ -7609,7 +7625,7 @@
       </c>
       <c r="I241" s="9"/>
     </row>
-    <row r="242" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="242" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A242" s="10"/>
       <c r="B242" s="9"/>
       <c r="C242" s="9"/>
@@ -7620,7 +7636,7 @@
       <c r="H242" s="17"/>
       <c r="I242" s="9"/>
     </row>
-    <row r="243" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="243" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A243" s="10"/>
       <c r="B243" s="9" t="s">
         <v>147</v>
@@ -7646,7 +7662,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="244" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="244" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A244" s="10"/>
       <c r="B244" s="9" t="s">
         <v>116</v>
@@ -7671,7 +7687,7 @@
       </c>
       <c r="I244" s="9"/>
     </row>
-    <row r="245" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="245" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A245" s="10"/>
       <c r="B245" s="9" t="s">
         <v>116</v>
@@ -7696,7 +7712,7 @@
       </c>
       <c r="I245" s="9"/>
     </row>
-    <row r="246" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="246" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A246" s="10"/>
       <c r="B246" s="9"/>
       <c r="C246" s="9"/>
@@ -7707,7 +7723,7 @@
       <c r="H246" s="11"/>
       <c r="I246" s="9"/>
     </row>
-    <row r="247" spans="1:10" s="13" customFormat="1" ht="21.75" customHeight="1">
+    <row r="247" spans="1:10" s="13" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A247" s="23">
         <v>20301</v>
       </c>
@@ -7733,7 +7749,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="248" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="248" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A248" s="10"/>
       <c r="B248" s="9"/>
       <c r="C248" s="9"/>
@@ -7744,7 +7760,7 @@
       <c r="H248" s="11"/>
       <c r="I248" s="9"/>
     </row>
-    <row r="249" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="249" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A249" s="10"/>
       <c r="B249" s="9"/>
       <c r="C249" s="9"/>
@@ -7765,7 +7781,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="250" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="250" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A250" s="10"/>
       <c r="B250" s="9" t="s">
         <v>116</v>
@@ -7790,7 +7806,7 @@
       </c>
       <c r="I250" s="9"/>
     </row>
-    <row r="251" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="251" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A251" s="10"/>
       <c r="B251" s="9" t="s">
         <v>116</v>
@@ -7815,7 +7831,7 @@
       </c>
       <c r="I251" s="9"/>
     </row>
-    <row r="252" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="252" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A252" s="10"/>
       <c r="B252" s="9"/>
       <c r="C252" s="9"/>
@@ -7826,7 +7842,7 @@
       <c r="H252" s="11"/>
       <c r="I252" s="9"/>
     </row>
-    <row r="253" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="253" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A253" s="10"/>
       <c r="B253" s="9"/>
       <c r="C253" s="9"/>
@@ -7845,7 +7861,7 @@
       </c>
       <c r="I253" s="9"/>
     </row>
-    <row r="254" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="254" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A254" s="10"/>
       <c r="B254" s="9" t="s">
         <v>116</v>
@@ -7870,7 +7886,7 @@
       </c>
       <c r="I254" s="9"/>
     </row>
-    <row r="255" spans="1:10" s="13" customFormat="1" ht="33">
+    <row r="255" spans="1:10" s="13" customFormat="1" ht="33" x14ac:dyDescent="0.3">
       <c r="A255" s="10"/>
       <c r="B255" s="9" t="s">
         <v>116</v>
@@ -7895,7 +7911,7 @@
       </c>
       <c r="I255" s="9"/>
     </row>
-    <row r="256" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="256" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A256" s="10"/>
       <c r="B256" s="9"/>
       <c r="C256" s="9"/>
@@ -7906,7 +7922,7 @@
       <c r="H256" s="11"/>
       <c r="I256" s="9"/>
     </row>
-    <row r="257" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="257" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A257" s="10"/>
       <c r="B257" s="9"/>
       <c r="C257" s="9"/>
@@ -7925,7 +7941,7 @@
       </c>
       <c r="I257" s="9"/>
     </row>
-    <row r="258" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="258" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A258" s="10"/>
       <c r="B258" s="9" t="s">
         <v>116</v>
@@ -7950,7 +7966,7 @@
       </c>
       <c r="I258" s="9"/>
     </row>
-    <row r="259" spans="1:10" s="13" customFormat="1" ht="33">
+    <row r="259" spans="1:10" s="13" customFormat="1" ht="33" x14ac:dyDescent="0.3">
       <c r="A259" s="10"/>
       <c r="B259" s="9" t="s">
         <v>116</v>
@@ -7975,7 +7991,7 @@
       </c>
       <c r="I259" s="9"/>
     </row>
-    <row r="260" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="260" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A260" s="10"/>
       <c r="B260" s="9"/>
       <c r="C260" s="9"/>
@@ -7986,7 +8002,7 @@
       <c r="H260" s="18"/>
       <c r="I260" s="9"/>
     </row>
-    <row r="261" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="261" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A261" s="10"/>
       <c r="B261" s="9"/>
       <c r="C261" s="9"/>
@@ -7997,7 +8013,7 @@
       <c r="H261" s="11"/>
       <c r="I261" s="9"/>
     </row>
-    <row r="262" spans="1:10" s="32" customFormat="1" ht="21">
+    <row r="262" spans="1:10" s="32" customFormat="1" ht="21" x14ac:dyDescent="0.4">
       <c r="A262" s="23">
         <v>30301</v>
       </c>
@@ -8023,7 +8039,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="263" spans="1:10" ht="16.5">
+    <row r="263" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A263" s="19"/>
       <c r="B263" s="13"/>
       <c r="C263" s="13"/>
@@ -8035,7 +8051,7 @@
       <c r="I263" s="13"/>
       <c r="J263" s="13"/>
     </row>
-    <row r="264" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="264" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A264" s="19"/>
       <c r="B264" s="9" t="s">
         <v>147</v>
@@ -8060,7 +8076,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="265" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="265" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A265" s="19"/>
       <c r="B265" s="9" t="s">
         <v>116</v>
@@ -8084,7 +8100,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="266" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="266" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A266" s="19"/>
       <c r="B266" s="9" t="s">
         <v>116</v>
@@ -8109,7 +8125,7 @@
       </c>
       <c r="J266" s="39"/>
     </row>
-    <row r="267" spans="1:10" ht="16.5">
+    <row r="267" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A267" s="19"/>
       <c r="B267" s="13"/>
       <c r="C267" s="13"/>
@@ -8121,7 +8137,7 @@
       <c r="I267" s="13"/>
       <c r="J267" s="13"/>
     </row>
-    <row r="268" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="268" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A268" s="19"/>
       <c r="B268" s="9" t="s">
         <v>147</v>
@@ -8143,7 +8159,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="269" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="269" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A269" s="19"/>
       <c r="B269" s="9" t="s">
         <v>116</v>
@@ -8167,7 +8183,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="270" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="270" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A270" s="19"/>
       <c r="B270" s="9" t="s">
         <v>116</v>
@@ -8191,7 +8207,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="271" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="271" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A271" s="10"/>
       <c r="B271" s="9"/>
       <c r="C271" s="9"/>
@@ -8202,7 +8218,7 @@
       <c r="H271" s="11"/>
       <c r="I271" s="9"/>
     </row>
-    <row r="272" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="272" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A272" s="10"/>
       <c r="B272" s="9"/>
       <c r="C272" s="9"/>
@@ -8213,7 +8229,7 @@
       <c r="H272" s="11"/>
       <c r="I272" s="9"/>
     </row>
-    <row r="273" spans="1:10" s="32" customFormat="1" ht="21">
+    <row r="273" spans="1:10" s="32" customFormat="1" ht="21" x14ac:dyDescent="0.4">
       <c r="A273" s="23">
         <v>30302</v>
       </c>
@@ -8239,7 +8255,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="274" spans="1:10" ht="16.5">
+    <row r="274" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A274" s="19"/>
       <c r="B274" s="13"/>
       <c r="C274" s="13"/>
@@ -8251,7 +8267,7 @@
       <c r="I274" s="13"/>
       <c r="J274" s="13"/>
     </row>
-    <row r="275" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="275" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A275" s="19"/>
       <c r="B275" s="9" t="s">
         <v>147</v>
@@ -8273,7 +8289,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="276" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="276" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A276" s="19"/>
       <c r="B276" s="9" t="s">
         <v>116</v>
@@ -8297,7 +8313,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="277" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="277" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A277" s="19"/>
       <c r="B277" s="9" t="s">
         <v>116</v>
@@ -8324,7 +8340,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="278" spans="1:10" ht="16.5">
+    <row r="278" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A278" s="19"/>
       <c r="B278" s="13"/>
       <c r="C278" s="13"/>
@@ -8336,7 +8352,7 @@
       <c r="I278" s="13"/>
       <c r="J278" s="13"/>
     </row>
-    <row r="279" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="279" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A279" s="19"/>
       <c r="B279" s="9" t="s">
         <v>147</v>
@@ -8358,7 +8374,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="280" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="280" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A280" s="19"/>
       <c r="B280" s="9" t="s">
         <v>116</v>
@@ -8382,7 +8398,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="281" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="281" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A281" s="19"/>
       <c r="B281" s="9" t="s">
         <v>116</v>
@@ -8406,7 +8422,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="282" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="282" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A282" s="19"/>
       <c r="B282" s="9"/>
       <c r="C282" s="9"/>
@@ -8416,7 +8432,7 @@
       <c r="G282" s="28"/>
       <c r="H282" s="29"/>
     </row>
-    <row r="283" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="283" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A283" s="19"/>
       <c r="B283" s="9"/>
       <c r="C283" s="9"/>
@@ -8426,7 +8442,7 @@
       <c r="G283" s="28"/>
       <c r="H283" s="29"/>
     </row>
-    <row r="284" spans="1:10" s="32" customFormat="1" ht="21">
+    <row r="284" spans="1:10" s="32" customFormat="1" ht="21" x14ac:dyDescent="0.4">
       <c r="A284" s="23">
         <v>30303</v>
       </c>
@@ -8452,7 +8468,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="285" spans="1:10" ht="16.5">
+    <row r="285" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A285" s="19"/>
       <c r="B285" s="13"/>
       <c r="C285" s="13"/>
@@ -8464,7 +8480,7 @@
       <c r="I285" s="13"/>
       <c r="J285" s="13"/>
     </row>
-    <row r="286" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="286" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A286" s="19"/>
       <c r="B286" s="9" t="s">
         <v>147</v>
@@ -8486,7 +8502,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="287" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="287" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A287" s="19"/>
       <c r="B287" s="9" t="s">
         <v>116</v>
@@ -8510,7 +8526,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="288" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="288" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A288" s="19"/>
       <c r="B288" s="9" t="s">
         <v>116</v>
@@ -8537,7 +8553,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="289" spans="1:10" ht="16.5">
+    <row r="289" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A289" s="19"/>
       <c r="B289" s="13"/>
       <c r="C289" s="13"/>
@@ -8549,7 +8565,7 @@
       <c r="I289" s="13"/>
       <c r="J289" s="13"/>
     </row>
-    <row r="290" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="290" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A290" s="19"/>
       <c r="B290" s="9" t="s">
         <v>147</v>
@@ -8571,7 +8587,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="291" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="291" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A291" s="19"/>
       <c r="B291" s="9" t="s">
         <v>116</v>
@@ -8595,7 +8611,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="292" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="292" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A292" s="19"/>
       <c r="B292" s="9" t="s">
         <v>116</v>
@@ -8619,7 +8635,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="293" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="293" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A293" s="19"/>
       <c r="B293" s="9"/>
       <c r="C293" s="9"/>
@@ -8629,7 +8645,7 @@
       <c r="G293" s="28"/>
       <c r="H293" s="29"/>
     </row>
-    <row r="294" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="294" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A294" s="19"/>
       <c r="B294" s="9"/>
       <c r="C294" s="9"/>
@@ -8639,7 +8655,7 @@
       <c r="G294" s="28"/>
       <c r="H294" s="29"/>
     </row>
-    <row r="295" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="295" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A295" s="19"/>
       <c r="B295" s="9"/>
       <c r="C295" s="9"/>
@@ -8649,7 +8665,7 @@
       <c r="G295" s="28"/>
       <c r="H295" s="29"/>
     </row>
-    <row r="296" spans="1:10" ht="16.5">
+    <row r="296" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A296" s="19"/>
       <c r="B296" s="13"/>
       <c r="C296" s="13"/>
@@ -8661,7 +8677,7 @@
       <c r="I296" s="13"/>
       <c r="J296" s="13"/>
     </row>
-    <row r="297" spans="1:10" s="46" customFormat="1" ht="16.5">
+    <row r="297" spans="1:10" s="46" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A297" s="23">
         <v>40301</v>
       </c>
@@ -8687,14 +8703,14 @@
         <v>236</v>
       </c>
     </row>
-    <row r="298" spans="1:10" s="48" customFormat="1">
+    <row r="298" spans="1:10" s="48" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A298" s="47"/>
       <c r="D298" s="47"/>
       <c r="E298" s="47"/>
       <c r="F298" s="47"/>
       <c r="H298" s="49"/>
     </row>
-    <row r="299" spans="1:10" s="46" customFormat="1" ht="16.5">
+    <row r="299" spans="1:10" s="46" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A299" s="23">
         <v>40302</v>
       </c>
@@ -8720,14 +8736,14 @@
         <v>237</v>
       </c>
     </row>
-    <row r="300" spans="1:10" s="48" customFormat="1">
+    <row r="300" spans="1:10" s="48" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A300" s="47"/>
       <c r="D300" s="47"/>
       <c r="E300" s="47"/>
       <c r="F300" s="47"/>
       <c r="H300" s="49"/>
     </row>
-    <row r="301" spans="1:10" s="46" customFormat="1" ht="16.5">
+    <row r="301" spans="1:10" s="46" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A301" s="23">
         <v>40303</v>
       </c>
@@ -8753,14 +8769,14 @@
         <v>237</v>
       </c>
     </row>
-    <row r="302" spans="1:10" s="48" customFormat="1">
+    <row r="302" spans="1:10" s="48" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A302" s="47"/>
       <c r="D302" s="47"/>
       <c r="E302" s="47"/>
       <c r="F302" s="47"/>
       <c r="H302" s="49"/>
     </row>
-    <row r="303" spans="1:10" s="46" customFormat="1" ht="16.5">
+    <row r="303" spans="1:10" s="46" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A303" s="23">
         <v>40304</v>
       </c>
@@ -8786,14 +8802,14 @@
         <v>238</v>
       </c>
     </row>
-    <row r="304" spans="1:10" s="48" customFormat="1">
+    <row r="304" spans="1:10" s="48" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A304" s="47"/>
       <c r="D304" s="47"/>
       <c r="E304" s="47"/>
       <c r="F304" s="47"/>
       <c r="H304" s="49"/>
     </row>
-    <row r="305" spans="1:10" s="46" customFormat="1" ht="16.5">
+    <row r="305" spans="1:10" s="46" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A305" s="23">
         <v>50301</v>
       </c>
@@ -8819,14 +8835,14 @@
         <v>239</v>
       </c>
     </row>
-    <row r="306" spans="1:10" s="48" customFormat="1">
+    <row r="306" spans="1:10" s="48" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A306" s="47"/>
       <c r="D306" s="47"/>
       <c r="E306" s="47"/>
       <c r="F306" s="47"/>
       <c r="H306" s="49"/>
     </row>
-    <row r="307" spans="1:10" s="46" customFormat="1" ht="16.5">
+    <row r="307" spans="1:10" s="46" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A307" s="23">
         <v>50302</v>
       </c>
@@ -8852,14 +8868,14 @@
         <v>239</v>
       </c>
     </row>
-    <row r="308" spans="1:10" s="48" customFormat="1">
+    <row r="308" spans="1:10" s="48" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A308" s="47"/>
       <c r="D308" s="47"/>
       <c r="E308" s="47"/>
       <c r="F308" s="47"/>
       <c r="H308" s="49"/>
     </row>
-    <row r="309" spans="1:10" s="46" customFormat="1" ht="16.5">
+    <row r="309" spans="1:10" s="46" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A309" s="23">
         <v>50303</v>
       </c>
@@ -8885,20 +8901,20 @@
         <v>239</v>
       </c>
     </row>
-    <row r="310" spans="1:10">
+    <row r="310" spans="1:10" x14ac:dyDescent="0.15">
       <c r="H310" s="21"/>
     </row>
-    <row r="311" spans="1:10" s="51" customFormat="1" ht="40.5" customHeight="1">
+    <row r="311" spans="1:10" s="51" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A311" s="50"/>
       <c r="D311" s="50"/>
       <c r="E311" s="50"/>
       <c r="F311" s="50"/>
       <c r="H311" s="52"/>
     </row>
-    <row r="312" spans="1:10">
+    <row r="312" spans="1:10" x14ac:dyDescent="0.15">
       <c r="H312" s="21"/>
     </row>
-    <row r="313" spans="1:10" s="13" customFormat="1" ht="21">
+    <row r="313" spans="1:10" s="13" customFormat="1" ht="21" x14ac:dyDescent="0.4">
       <c r="A313" s="23">
         <v>10401</v>
       </c>
@@ -8924,7 +8940,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="314" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="314" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A314" s="10"/>
       <c r="B314" s="9" t="s">
         <v>116</v>
@@ -8945,7 +8961,7 @@
       </c>
       <c r="I314" s="9"/>
     </row>
-    <row r="315" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="315" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A315" s="10"/>
       <c r="B315" s="9" t="s">
         <v>116</v>
@@ -8966,7 +8982,7 @@
       </c>
       <c r="I315" s="9"/>
     </row>
-    <row r="316" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="316" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A316" s="10"/>
       <c r="B316" s="9"/>
       <c r="C316" s="9"/>
@@ -8977,7 +8993,7 @@
       <c r="H316" s="17"/>
       <c r="I316" s="9"/>
     </row>
-    <row r="317" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="317" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A317" s="10"/>
       <c r="B317" s="9" t="s">
         <v>147</v>
@@ -9005,7 +9021,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="318" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="318" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A318" s="10"/>
       <c r="B318" s="9" t="s">
         <v>116</v>
@@ -9030,7 +9046,7 @@
       </c>
       <c r="I318" s="9"/>
     </row>
-    <row r="319" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="319" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A319" s="10"/>
       <c r="B319" s="9" t="s">
         <v>116</v>
@@ -9055,7 +9071,7 @@
       </c>
       <c r="I319" s="9"/>
     </row>
-    <row r="320" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="320" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A320" s="10"/>
       <c r="B320" s="9" t="s">
         <v>116</v>
@@ -9080,7 +9096,7 @@
       </c>
       <c r="I320" s="9"/>
     </row>
-    <row r="321" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="321" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A321" s="10"/>
       <c r="B321" s="9" t="s">
         <v>116</v>
@@ -9105,7 +9121,7 @@
       </c>
       <c r="I321" s="9"/>
     </row>
-    <row r="322" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="322" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A322" s="10"/>
       <c r="B322" s="9"/>
       <c r="C322" s="9"/>
@@ -9116,7 +9132,7 @@
       <c r="H322" s="17"/>
       <c r="I322" s="9"/>
     </row>
-    <row r="323" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="323" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A323" s="10"/>
       <c r="B323" s="9" t="s">
         <v>147</v>
@@ -9142,7 +9158,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="324" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="324" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A324" s="10"/>
       <c r="B324" s="9" t="s">
         <v>116</v>
@@ -9167,7 +9183,7 @@
       </c>
       <c r="I324" s="9"/>
     </row>
-    <row r="325" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="325" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A325" s="10"/>
       <c r="B325" s="9" t="s">
         <v>116</v>
@@ -9192,7 +9208,7 @@
       </c>
       <c r="I325" s="9"/>
     </row>
-    <row r="326" spans="1:10" s="13" customFormat="1" ht="33">
+    <row r="326" spans="1:10" s="13" customFormat="1" ht="33" x14ac:dyDescent="0.3">
       <c r="A326" s="10"/>
       <c r="B326" s="9" t="s">
         <v>116</v>
@@ -9217,7 +9233,7 @@
       </c>
       <c r="I326" s="9"/>
     </row>
-    <row r="327" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="327" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A327" s="10"/>
       <c r="B327" s="9"/>
       <c r="C327" s="9"/>
@@ -9228,7 +9244,7 @@
       <c r="H327" s="17"/>
       <c r="I327" s="9"/>
     </row>
-    <row r="328" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="328" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A328" s="10"/>
       <c r="B328" s="9" t="s">
         <v>147</v>
@@ -9254,7 +9270,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="329" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="329" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A329" s="10"/>
       <c r="B329" s="9" t="s">
         <v>116</v>
@@ -9279,7 +9295,7 @@
       </c>
       <c r="I329" s="9"/>
     </row>
-    <row r="330" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="330" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A330" s="10"/>
       <c r="B330" s="9" t="s">
         <v>116</v>
@@ -9304,7 +9320,7 @@
       </c>
       <c r="I330" s="9"/>
     </row>
-    <row r="331" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="331" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A331" s="10"/>
       <c r="B331" s="9"/>
       <c r="C331" s="9"/>
@@ -9315,7 +9331,7 @@
       <c r="H331" s="11"/>
       <c r="I331" s="9"/>
     </row>
-    <row r="332" spans="1:10" s="13" customFormat="1" ht="21.75" customHeight="1">
+    <row r="332" spans="1:10" s="13" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A332" s="23">
         <v>20401</v>
       </c>
@@ -9341,7 +9357,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="333" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="333" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A333" s="10"/>
       <c r="B333" s="9"/>
       <c r="C333" s="9"/>
@@ -9352,7 +9368,7 @@
       <c r="H333" s="11"/>
       <c r="I333" s="9"/>
     </row>
-    <row r="334" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="334" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A334" s="10"/>
       <c r="B334" s="9"/>
       <c r="C334" s="9"/>
@@ -9373,7 +9389,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="335" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="335" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A335" s="10"/>
       <c r="B335" s="9" t="s">
         <v>116</v>
@@ -9398,7 +9414,7 @@
       </c>
       <c r="I335" s="9"/>
     </row>
-    <row r="336" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="336" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A336" s="10"/>
       <c r="B336" s="9" t="s">
         <v>116</v>
@@ -9423,7 +9439,7 @@
       </c>
       <c r="I336" s="9"/>
     </row>
-    <row r="337" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="337" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A337" s="10"/>
       <c r="B337" s="9"/>
       <c r="C337" s="9"/>
@@ -9434,7 +9450,7 @@
       <c r="H337" s="11"/>
       <c r="I337" s="9"/>
     </row>
-    <row r="338" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="338" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A338" s="10"/>
       <c r="B338" s="9"/>
       <c r="C338" s="9"/>
@@ -9453,7 +9469,7 @@
       </c>
       <c r="I338" s="9"/>
     </row>
-    <row r="339" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="339" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A339" s="10"/>
       <c r="B339" s="9" t="s">
         <v>116</v>
@@ -9478,7 +9494,7 @@
       </c>
       <c r="I339" s="9"/>
     </row>
-    <row r="340" spans="1:10" s="13" customFormat="1" ht="33">
+    <row r="340" spans="1:10" s="13" customFormat="1" ht="33" x14ac:dyDescent="0.3">
       <c r="A340" s="10"/>
       <c r="B340" s="9" t="s">
         <v>116</v>
@@ -9503,7 +9519,7 @@
       </c>
       <c r="I340" s="9"/>
     </row>
-    <row r="341" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="341" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A341" s="10"/>
       <c r="B341" s="9"/>
       <c r="C341" s="9"/>
@@ -9514,7 +9530,7 @@
       <c r="H341" s="11"/>
       <c r="I341" s="9"/>
     </row>
-    <row r="342" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="342" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A342" s="10"/>
       <c r="B342" s="9"/>
       <c r="C342" s="9"/>
@@ -9533,7 +9549,7 @@
       </c>
       <c r="I342" s="9"/>
     </row>
-    <row r="343" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="343" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A343" s="10"/>
       <c r="B343" s="9" t="s">
         <v>116</v>
@@ -9558,7 +9574,7 @@
       </c>
       <c r="I343" s="9"/>
     </row>
-    <row r="344" spans="1:10" s="13" customFormat="1" ht="33">
+    <row r="344" spans="1:10" s="13" customFormat="1" ht="33" x14ac:dyDescent="0.3">
       <c r="A344" s="10"/>
       <c r="B344" s="9" t="s">
         <v>116</v>
@@ -9583,7 +9599,7 @@
       </c>
       <c r="I344" s="9"/>
     </row>
-    <row r="345" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="345" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A345" s="10"/>
       <c r="B345" s="9"/>
       <c r="C345" s="9"/>
@@ -9594,7 +9610,7 @@
       <c r="H345" s="18"/>
       <c r="I345" s="9"/>
     </row>
-    <row r="346" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="346" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A346" s="10"/>
       <c r="B346" s="9"/>
       <c r="C346" s="9"/>
@@ -9605,7 +9621,7 @@
       <c r="H346" s="11"/>
       <c r="I346" s="9"/>
     </row>
-    <row r="347" spans="1:10" s="32" customFormat="1" ht="21">
+    <row r="347" spans="1:10" s="32" customFormat="1" ht="21" x14ac:dyDescent="0.4">
       <c r="A347" s="23">
         <v>30401</v>
       </c>
@@ -9631,7 +9647,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="348" spans="1:10" ht="16.5">
+    <row r="348" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A348" s="19"/>
       <c r="B348" s="13"/>
       <c r="C348" s="13"/>
@@ -9643,7 +9659,7 @@
       <c r="I348" s="13"/>
       <c r="J348" s="13"/>
     </row>
-    <row r="349" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="349" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A349" s="19"/>
       <c r="B349" s="9" t="s">
         <v>147</v>
@@ -9668,7 +9684,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="350" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="350" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A350" s="19"/>
       <c r="B350" s="9" t="s">
         <v>116</v>
@@ -9692,7 +9708,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="351" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="351" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A351" s="19"/>
       <c r="B351" s="9" t="s">
         <v>116</v>
@@ -9717,7 +9733,7 @@
       </c>
       <c r="J351" s="39"/>
     </row>
-    <row r="352" spans="1:10" ht="16.5">
+    <row r="352" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A352" s="19"/>
       <c r="B352" s="13"/>
       <c r="C352" s="13"/>
@@ -9729,7 +9745,7 @@
       <c r="I352" s="13"/>
       <c r="J352" s="13"/>
     </row>
-    <row r="353" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="353" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A353" s="19"/>
       <c r="B353" s="9" t="s">
         <v>147</v>
@@ -9751,7 +9767,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="354" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="354" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A354" s="19"/>
       <c r="B354" s="9" t="s">
         <v>116</v>
@@ -9775,7 +9791,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="355" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="355" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A355" s="19"/>
       <c r="B355" s="9" t="s">
         <v>116</v>
@@ -9799,7 +9815,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="356" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="356" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A356" s="10"/>
       <c r="B356" s="9"/>
       <c r="C356" s="9"/>
@@ -9810,7 +9826,7 @@
       <c r="H356" s="11"/>
       <c r="I356" s="9"/>
     </row>
-    <row r="357" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="357" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A357" s="10"/>
       <c r="B357" s="9"/>
       <c r="C357" s="9"/>
@@ -9821,7 +9837,7 @@
       <c r="H357" s="11"/>
       <c r="I357" s="9"/>
     </row>
-    <row r="358" spans="1:10" s="32" customFormat="1" ht="21">
+    <row r="358" spans="1:10" s="32" customFormat="1" ht="21" x14ac:dyDescent="0.4">
       <c r="A358" s="23">
         <v>30402</v>
       </c>
@@ -9847,7 +9863,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="359" spans="1:10" ht="16.5">
+    <row r="359" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A359" s="19"/>
       <c r="B359" s="13"/>
       <c r="C359" s="13"/>
@@ -9859,7 +9875,7 @@
       <c r="I359" s="13"/>
       <c r="J359" s="13"/>
     </row>
-    <row r="360" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="360" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A360" s="19"/>
       <c r="B360" s="9" t="s">
         <v>147</v>
@@ -9881,7 +9897,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="361" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="361" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A361" s="19"/>
       <c r="B361" s="9" t="s">
         <v>116</v>
@@ -9905,7 +9921,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="362" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="362" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A362" s="19"/>
       <c r="B362" s="9" t="s">
         <v>116</v>
@@ -9932,7 +9948,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="363" spans="1:10" ht="16.5">
+    <row r="363" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A363" s="19"/>
       <c r="B363" s="13"/>
       <c r="C363" s="13"/>
@@ -9944,7 +9960,7 @@
       <c r="I363" s="13"/>
       <c r="J363" s="13"/>
     </row>
-    <row r="364" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="364" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A364" s="19"/>
       <c r="B364" s="9" t="s">
         <v>147</v>
@@ -9966,7 +9982,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="365" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="365" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A365" s="19"/>
       <c r="B365" s="9" t="s">
         <v>116</v>
@@ -9990,7 +10006,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="366" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="366" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A366" s="19"/>
       <c r="B366" s="9" t="s">
         <v>116</v>
@@ -10014,7 +10030,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="367" spans="1:10" ht="16.5">
+    <row r="367" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A367" s="19"/>
       <c r="B367" s="13"/>
       <c r="C367" s="13"/>
@@ -10026,7 +10042,7 @@
       <c r="I367" s="13"/>
       <c r="J367" s="13"/>
     </row>
-    <row r="368" spans="1:10" s="32" customFormat="1" ht="21">
+    <row r="368" spans="1:10" s="32" customFormat="1" ht="21" x14ac:dyDescent="0.4">
       <c r="A368" s="23">
         <v>30403</v>
       </c>
@@ -10052,7 +10068,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="369" spans="1:10" ht="16.5">
+    <row r="369" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A369" s="19"/>
       <c r="B369" s="13"/>
       <c r="C369" s="13"/>
@@ -10064,7 +10080,7 @@
       <c r="I369" s="13"/>
       <c r="J369" s="13"/>
     </row>
-    <row r="370" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="370" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A370" s="19"/>
       <c r="B370" s="9" t="s">
         <v>147</v>
@@ -10086,7 +10102,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="371" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="371" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A371" s="19"/>
       <c r="B371" s="9" t="s">
         <v>116</v>
@@ -10110,7 +10126,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="372" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="372" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A372" s="19"/>
       <c r="B372" s="9" t="s">
         <v>116</v>
@@ -10137,7 +10153,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="373" spans="1:10" ht="16.5">
+    <row r="373" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A373" s="19"/>
       <c r="B373" s="13"/>
       <c r="C373" s="13"/>
@@ -10149,7 +10165,7 @@
       <c r="I373" s="13"/>
       <c r="J373" s="13"/>
     </row>
-    <row r="374" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="374" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A374" s="19"/>
       <c r="B374" s="9" t="s">
         <v>147</v>
@@ -10171,7 +10187,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="375" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="375" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A375" s="19"/>
       <c r="B375" s="9" t="s">
         <v>116</v>
@@ -10195,7 +10211,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="376" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="376" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A376" s="19"/>
       <c r="B376" s="9" t="s">
         <v>116</v>
@@ -10219,7 +10235,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="377" spans="1:10" ht="16.5">
+    <row r="377" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A377" s="19"/>
       <c r="B377" s="13"/>
       <c r="C377" s="13"/>
@@ -10231,7 +10247,7 @@
       <c r="I377" s="13"/>
       <c r="J377" s="13"/>
     </row>
-    <row r="378" spans="1:10" ht="16.5">
+    <row r="378" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A378" s="19"/>
       <c r="B378" s="13"/>
       <c r="C378" s="13"/>
@@ -10243,7 +10259,7 @@
       <c r="I378" s="13"/>
       <c r="J378" s="13"/>
     </row>
-    <row r="379" spans="1:10" s="46" customFormat="1" ht="16.5">
+    <row r="379" spans="1:10" s="46" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A379" s="23">
         <v>40401</v>
       </c>
@@ -10269,14 +10285,14 @@
         <v>236</v>
       </c>
     </row>
-    <row r="380" spans="1:10" s="48" customFormat="1">
+    <row r="380" spans="1:10" s="48" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A380" s="47"/>
       <c r="D380" s="47"/>
       <c r="E380" s="47"/>
       <c r="F380" s="47"/>
       <c r="H380" s="49"/>
     </row>
-    <row r="381" spans="1:10" s="46" customFormat="1" ht="16.5">
+    <row r="381" spans="1:10" s="46" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A381" s="23">
         <v>40402</v>
       </c>
@@ -10302,14 +10318,14 @@
         <v>237</v>
       </c>
     </row>
-    <row r="382" spans="1:10" s="48" customFormat="1">
+    <row r="382" spans="1:10" s="48" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A382" s="47"/>
       <c r="D382" s="47"/>
       <c r="E382" s="47"/>
       <c r="F382" s="47"/>
       <c r="H382" s="49"/>
     </row>
-    <row r="383" spans="1:10" s="46" customFormat="1" ht="16.5">
+    <row r="383" spans="1:10" s="46" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A383" s="23">
         <v>40403</v>
       </c>
@@ -10335,14 +10351,14 @@
         <v>237</v>
       </c>
     </row>
-    <row r="384" spans="1:10" s="48" customFormat="1">
+    <row r="384" spans="1:10" s="48" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A384" s="47"/>
       <c r="D384" s="47"/>
       <c r="E384" s="47"/>
       <c r="F384" s="47"/>
       <c r="H384" s="49"/>
     </row>
-    <row r="385" spans="1:10" s="46" customFormat="1" ht="16.5">
+    <row r="385" spans="1:10" s="46" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A385" s="23">
         <v>40404</v>
       </c>
@@ -10368,14 +10384,14 @@
         <v>238</v>
       </c>
     </row>
-    <row r="386" spans="1:10" s="48" customFormat="1">
+    <row r="386" spans="1:10" s="48" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A386" s="47"/>
       <c r="D386" s="47"/>
       <c r="E386" s="47"/>
       <c r="F386" s="47"/>
       <c r="H386" s="49"/>
     </row>
-    <row r="387" spans="1:10" s="46" customFormat="1" ht="16.5">
+    <row r="387" spans="1:10" s="46" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A387" s="23">
         <v>50401</v>
       </c>
@@ -10401,14 +10417,14 @@
         <v>239</v>
       </c>
     </row>
-    <row r="388" spans="1:10" s="48" customFormat="1">
+    <row r="388" spans="1:10" s="48" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A388" s="47"/>
       <c r="D388" s="47"/>
       <c r="E388" s="47"/>
       <c r="F388" s="47"/>
       <c r="H388" s="49"/>
     </row>
-    <row r="389" spans="1:10" s="46" customFormat="1" ht="16.5">
+    <row r="389" spans="1:10" s="46" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A389" s="23">
         <v>50402</v>
       </c>
@@ -10434,14 +10450,14 @@
         <v>239</v>
       </c>
     </row>
-    <row r="390" spans="1:10" s="48" customFormat="1">
+    <row r="390" spans="1:10" s="48" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A390" s="47"/>
       <c r="D390" s="47"/>
       <c r="E390" s="47"/>
       <c r="F390" s="47"/>
       <c r="H390" s="49"/>
     </row>
-    <row r="391" spans="1:10" s="46" customFormat="1" ht="16.5">
+    <row r="391" spans="1:10" s="46" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A391" s="23">
         <v>50403</v>
       </c>
@@ -10467,20 +10483,20 @@
         <v>239</v>
       </c>
     </row>
-    <row r="392" spans="1:10">
+    <row r="392" spans="1:10" x14ac:dyDescent="0.15">
       <c r="H392" s="21"/>
     </row>
-    <row r="393" spans="1:10" s="51" customFormat="1" ht="40.5" customHeight="1">
+    <row r="393" spans="1:10" s="51" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A393" s="50"/>
       <c r="D393" s="50"/>
       <c r="E393" s="50"/>
       <c r="F393" s="50"/>
       <c r="H393" s="52"/>
     </row>
-    <row r="394" spans="1:10">
+    <row r="394" spans="1:10" x14ac:dyDescent="0.15">
       <c r="H394" s="21"/>
     </row>
-    <row r="395" spans="1:10" s="13" customFormat="1" ht="21">
+    <row r="395" spans="1:10" s="13" customFormat="1" ht="21" x14ac:dyDescent="0.4">
       <c r="A395" s="23">
         <v>10501</v>
       </c>
@@ -10506,7 +10522,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="396" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="396" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A396" s="10"/>
       <c r="B396" s="9" t="s">
         <v>116</v>
@@ -10527,7 +10543,7 @@
       </c>
       <c r="I396" s="9"/>
     </row>
-    <row r="397" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="397" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A397" s="10"/>
       <c r="B397" s="9" t="s">
         <v>116</v>
@@ -10548,7 +10564,7 @@
       </c>
       <c r="I397" s="9"/>
     </row>
-    <row r="398" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="398" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A398" s="10"/>
       <c r="B398" s="9"/>
       <c r="C398" s="9"/>
@@ -10559,7 +10575,7 @@
       <c r="H398" s="17"/>
       <c r="I398" s="9"/>
     </row>
-    <row r="399" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="399" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A399" s="10"/>
       <c r="B399" s="9" t="s">
         <v>147</v>
@@ -10587,7 +10603,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="400" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="400" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A400" s="10"/>
       <c r="B400" s="9" t="s">
         <v>116</v>
@@ -10612,7 +10628,7 @@
       </c>
       <c r="I400" s="9"/>
     </row>
-    <row r="401" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="401" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A401" s="10"/>
       <c r="B401" s="9" t="s">
         <v>116</v>
@@ -10637,7 +10653,7 @@
       </c>
       <c r="I401" s="9"/>
     </row>
-    <row r="402" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="402" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A402" s="10"/>
       <c r="B402" s="9" t="s">
         <v>116</v>
@@ -10662,7 +10678,7 @@
       </c>
       <c r="I402" s="9"/>
     </row>
-    <row r="403" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="403" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A403" s="10"/>
       <c r="B403" s="9" t="s">
         <v>116</v>
@@ -10687,7 +10703,7 @@
       </c>
       <c r="I403" s="9"/>
     </row>
-    <row r="404" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="404" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A404" s="10"/>
       <c r="B404" s="9"/>
       <c r="C404" s="9"/>
@@ -10698,7 +10714,7 @@
       <c r="H404" s="17"/>
       <c r="I404" s="9"/>
     </row>
-    <row r="405" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="405" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A405" s="10"/>
       <c r="B405" s="9" t="s">
         <v>147</v>
@@ -10724,7 +10740,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="406" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="406" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A406" s="10"/>
       <c r="B406" s="9" t="s">
         <v>116</v>
@@ -10749,7 +10765,7 @@
       </c>
       <c r="I406" s="9"/>
     </row>
-    <row r="407" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="407" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A407" s="10"/>
       <c r="B407" s="9" t="s">
         <v>116</v>
@@ -10774,7 +10790,7 @@
       </c>
       <c r="I407" s="9"/>
     </row>
-    <row r="408" spans="1:10" s="13" customFormat="1" ht="33">
+    <row r="408" spans="1:10" s="13" customFormat="1" ht="33" x14ac:dyDescent="0.3">
       <c r="A408" s="10"/>
       <c r="B408" s="9" t="s">
         <v>116</v>
@@ -10795,11 +10811,11 @@
         <v>119</v>
       </c>
       <c r="H408" s="11" t="s">
-        <v>249</v>
+        <v>307</v>
       </c>
       <c r="I408" s="9"/>
     </row>
-    <row r="409" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="409" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A409" s="10"/>
       <c r="B409" s="9"/>
       <c r="C409" s="9"/>
@@ -10810,7 +10826,7 @@
       <c r="H409" s="17"/>
       <c r="I409" s="9"/>
     </row>
-    <row r="410" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="410" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A410" s="10"/>
       <c r="B410" s="9" t="s">
         <v>147</v>
@@ -10836,7 +10852,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="411" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="411" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A411" s="10"/>
       <c r="B411" s="9" t="s">
         <v>116</v>
@@ -10861,7 +10877,7 @@
       </c>
       <c r="I411" s="9"/>
     </row>
-    <row r="412" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="412" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A412" s="10"/>
       <c r="B412" s="9" t="s">
         <v>116</v>
@@ -10886,7 +10902,7 @@
       </c>
       <c r="I412" s="9"/>
     </row>
-    <row r="413" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="413" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A413" s="10"/>
       <c r="B413" s="9"/>
       <c r="C413" s="9"/>
@@ -10897,7 +10913,7 @@
       <c r="H413" s="11"/>
       <c r="I413" s="9"/>
     </row>
-    <row r="414" spans="1:10" s="13" customFormat="1" ht="21.75" customHeight="1">
+    <row r="414" spans="1:10" s="13" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A414" s="23">
         <v>20501</v>
       </c>
@@ -10923,7 +10939,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="415" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="415" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A415" s="10"/>
       <c r="B415" s="9"/>
       <c r="C415" s="9"/>
@@ -10934,7 +10950,7 @@
       <c r="H415" s="11"/>
       <c r="I415" s="9"/>
     </row>
-    <row r="416" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="416" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A416" s="10"/>
       <c r="B416" s="9"/>
       <c r="C416" s="9"/>
@@ -10955,7 +10971,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="417" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="417" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A417" s="10"/>
       <c r="B417" s="9" t="s">
         <v>116</v>
@@ -10980,7 +10996,7 @@
       </c>
       <c r="I417" s="9"/>
     </row>
-    <row r="418" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="418" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A418" s="10"/>
       <c r="B418" s="9" t="s">
         <v>116</v>
@@ -11005,7 +11021,7 @@
       </c>
       <c r="I418" s="9"/>
     </row>
-    <row r="419" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="419" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A419" s="10"/>
       <c r="B419" s="9"/>
       <c r="C419" s="9"/>
@@ -11016,7 +11032,7 @@
       <c r="H419" s="11"/>
       <c r="I419" s="9"/>
     </row>
-    <row r="420" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="420" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A420" s="10"/>
       <c r="B420" s="9"/>
       <c r="C420" s="9"/>
@@ -11035,7 +11051,7 @@
       </c>
       <c r="I420" s="9"/>
     </row>
-    <row r="421" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="421" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A421" s="10"/>
       <c r="B421" s="9" t="s">
         <v>116</v>
@@ -11060,7 +11076,7 @@
       </c>
       <c r="I421" s="9"/>
     </row>
-    <row r="422" spans="1:10" s="13" customFormat="1" ht="33">
+    <row r="422" spans="1:10" s="13" customFormat="1" ht="33" x14ac:dyDescent="0.3">
       <c r="A422" s="10"/>
       <c r="B422" s="9" t="s">
         <v>116</v>
@@ -11085,7 +11101,7 @@
       </c>
       <c r="I422" s="9"/>
     </row>
-    <row r="423" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="423" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A423" s="10"/>
       <c r="B423" s="9"/>
       <c r="C423" s="9"/>
@@ -11096,7 +11112,7 @@
       <c r="H423" s="11"/>
       <c r="I423" s="9"/>
     </row>
-    <row r="424" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="424" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A424" s="10"/>
       <c r="B424" s="9"/>
       <c r="C424" s="9"/>
@@ -11115,7 +11131,7 @@
       </c>
       <c r="I424" s="9"/>
     </row>
-    <row r="425" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="425" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A425" s="10"/>
       <c r="B425" s="9" t="s">
         <v>116</v>
@@ -11140,7 +11156,7 @@
       </c>
       <c r="I425" s="9"/>
     </row>
-    <row r="426" spans="1:10" s="13" customFormat="1" ht="33">
+    <row r="426" spans="1:10" s="13" customFormat="1" ht="33" x14ac:dyDescent="0.3">
       <c r="A426" s="10"/>
       <c r="B426" s="9" t="s">
         <v>116</v>
@@ -11165,7 +11181,7 @@
       </c>
       <c r="I426" s="9"/>
     </row>
-    <row r="427" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="427" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A427" s="10"/>
       <c r="B427" s="9"/>
       <c r="C427" s="9"/>
@@ -11176,7 +11192,7 @@
       <c r="H427" s="18"/>
       <c r="I427" s="9"/>
     </row>
-    <row r="428" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="428" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A428" s="10"/>
       <c r="B428" s="9"/>
       <c r="C428" s="9"/>
@@ -11187,7 +11203,7 @@
       <c r="H428" s="11"/>
       <c r="I428" s="9"/>
     </row>
-    <row r="429" spans="1:10" s="32" customFormat="1" ht="21">
+    <row r="429" spans="1:10" s="32" customFormat="1" ht="21" x14ac:dyDescent="0.4">
       <c r="A429" s="23">
         <v>30501</v>
       </c>
@@ -11213,7 +11229,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="430" spans="1:10" ht="16.5">
+    <row r="430" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A430" s="19"/>
       <c r="B430" s="13"/>
       <c r="C430" s="13"/>
@@ -11225,7 +11241,7 @@
       <c r="I430" s="13"/>
       <c r="J430" s="13"/>
     </row>
-    <row r="431" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="431" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A431" s="19"/>
       <c r="B431" s="9" t="s">
         <v>147</v>
@@ -11250,7 +11266,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="432" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="432" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A432" s="19"/>
       <c r="B432" s="9" t="s">
         <v>116</v>
@@ -11274,7 +11290,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="433" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="433" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A433" s="19"/>
       <c r="B433" s="9" t="s">
         <v>116</v>
@@ -11299,7 +11315,7 @@
       </c>
       <c r="J433" s="39"/>
     </row>
-    <row r="434" spans="1:10" ht="16.5">
+    <row r="434" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A434" s="19"/>
       <c r="B434" s="13"/>
       <c r="C434" s="13"/>
@@ -11311,7 +11327,7 @@
       <c r="I434" s="13"/>
       <c r="J434" s="13"/>
     </row>
-    <row r="435" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="435" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A435" s="19"/>
       <c r="B435" s="9" t="s">
         <v>147</v>
@@ -11333,7 +11349,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="436" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="436" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A436" s="19"/>
       <c r="B436" s="9" t="s">
         <v>116</v>
@@ -11357,7 +11373,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="437" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="437" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A437" s="19"/>
       <c r="B437" s="9" t="s">
         <v>116</v>
@@ -11381,7 +11397,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="438" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="438" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A438" s="10"/>
       <c r="B438" s="9"/>
       <c r="C438" s="9"/>
@@ -11392,7 +11408,7 @@
       <c r="H438" s="11"/>
       <c r="I438" s="9"/>
     </row>
-    <row r="439" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="439" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A439" s="10"/>
       <c r="B439" s="9"/>
       <c r="C439" s="9"/>
@@ -11403,7 +11419,7 @@
       <c r="H439" s="11"/>
       <c r="I439" s="9"/>
     </row>
-    <row r="440" spans="1:10" s="32" customFormat="1" ht="21">
+    <row r="440" spans="1:10" s="32" customFormat="1" ht="21" x14ac:dyDescent="0.4">
       <c r="A440" s="23">
         <v>30502</v>
       </c>
@@ -11429,7 +11445,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="441" spans="1:10" ht="16.5">
+    <row r="441" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A441" s="19"/>
       <c r="B441" s="13"/>
       <c r="C441" s="13"/>
@@ -11441,7 +11457,7 @@
       <c r="I441" s="13"/>
       <c r="J441" s="13"/>
     </row>
-    <row r="442" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="442" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A442" s="19"/>
       <c r="B442" s="9" t="s">
         <v>147</v>
@@ -11463,7 +11479,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="443" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="443" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A443" s="19"/>
       <c r="B443" s="9" t="s">
         <v>116</v>
@@ -11487,7 +11503,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="444" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="444" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A444" s="19"/>
       <c r="B444" s="9" t="s">
         <v>116</v>
@@ -11514,7 +11530,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="445" spans="1:10" ht="16.5">
+    <row r="445" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A445" s="19"/>
       <c r="B445" s="13"/>
       <c r="C445" s="13"/>
@@ -11526,7 +11542,7 @@
       <c r="I445" s="13"/>
       <c r="J445" s="13"/>
     </row>
-    <row r="446" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="446" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A446" s="19"/>
       <c r="B446" s="9" t="s">
         <v>147</v>
@@ -11548,7 +11564,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="447" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="447" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A447" s="19"/>
       <c r="B447" s="9" t="s">
         <v>116</v>
@@ -11572,7 +11588,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="448" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="448" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A448" s="19"/>
       <c r="B448" s="9" t="s">
         <v>116</v>
@@ -11596,7 +11612,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="449" spans="1:10" ht="16.5">
+    <row r="449" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A449" s="19"/>
       <c r="B449" s="13"/>
       <c r="C449" s="13"/>
@@ -11608,7 +11624,7 @@
       <c r="I449" s="13"/>
       <c r="J449" s="13"/>
     </row>
-    <row r="450" spans="1:10" ht="16.5">
+    <row r="450" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A450" s="19"/>
       <c r="B450" s="13"/>
       <c r="C450" s="13"/>
@@ -11620,7 +11636,7 @@
       <c r="I450" s="13"/>
       <c r="J450" s="13"/>
     </row>
-    <row r="451" spans="1:10" ht="16.5">
+    <row r="451" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A451" s="19"/>
       <c r="B451" s="13"/>
       <c r="C451" s="13"/>
@@ -11632,7 +11648,7 @@
       <c r="I451" s="13"/>
       <c r="J451" s="13"/>
     </row>
-    <row r="452" spans="1:10" s="32" customFormat="1" ht="21">
+    <row r="452" spans="1:10" s="32" customFormat="1" ht="21" x14ac:dyDescent="0.4">
       <c r="A452" s="23">
         <v>30503</v>
       </c>
@@ -11658,7 +11674,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="453" spans="1:10" ht="16.5">
+    <row r="453" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A453" s="19"/>
       <c r="B453" s="13"/>
       <c r="C453" s="13"/>
@@ -11670,7 +11686,7 @@
       <c r="I453" s="13"/>
       <c r="J453" s="13"/>
     </row>
-    <row r="454" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="454" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A454" s="19"/>
       <c r="B454" s="9" t="s">
         <v>147</v>
@@ -11692,7 +11708,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="455" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="455" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A455" s="19"/>
       <c r="B455" s="9" t="s">
         <v>116</v>
@@ -11716,7 +11732,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="456" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="456" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A456" s="19"/>
       <c r="B456" s="9" t="s">
         <v>116</v>
@@ -11743,7 +11759,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="457" spans="1:10" ht="16.5">
+    <row r="457" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A457" s="19"/>
       <c r="B457" s="13"/>
       <c r="C457" s="13"/>
@@ -11755,7 +11771,7 @@
       <c r="I457" s="13"/>
       <c r="J457" s="13"/>
     </row>
-    <row r="458" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="458" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A458" s="19"/>
       <c r="B458" s="9" t="s">
         <v>147</v>
@@ -11777,7 +11793,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="459" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="459" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A459" s="19"/>
       <c r="B459" s="9" t="s">
         <v>116</v>
@@ -11801,7 +11817,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="460" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="460" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A460" s="19"/>
       <c r="B460" s="9" t="s">
         <v>116</v>
@@ -11825,7 +11841,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="461" spans="1:10" ht="16.5">
+    <row r="461" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A461" s="19"/>
       <c r="B461" s="13"/>
       <c r="C461" s="13"/>
@@ -11837,7 +11853,7 @@
       <c r="I461" s="13"/>
       <c r="J461" s="13"/>
     </row>
-    <row r="462" spans="1:10" s="46" customFormat="1" ht="16.5">
+    <row r="462" spans="1:10" s="46" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A462" s="23">
         <v>40501</v>
       </c>
@@ -11863,14 +11879,14 @@
         <v>236</v>
       </c>
     </row>
-    <row r="463" spans="1:10" s="48" customFormat="1">
+    <row r="463" spans="1:10" s="48" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A463" s="47"/>
       <c r="D463" s="47"/>
       <c r="E463" s="47"/>
       <c r="F463" s="47"/>
       <c r="H463" s="49"/>
     </row>
-    <row r="464" spans="1:10" s="46" customFormat="1" ht="16.5">
+    <row r="464" spans="1:10" s="46" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A464" s="23">
         <v>40502</v>
       </c>
@@ -11896,14 +11912,14 @@
         <v>237</v>
       </c>
     </row>
-    <row r="465" spans="1:10" s="48" customFormat="1">
+    <row r="465" spans="1:10" s="48" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A465" s="47"/>
       <c r="D465" s="47"/>
       <c r="E465" s="47"/>
       <c r="F465" s="47"/>
       <c r="H465" s="49"/>
     </row>
-    <row r="466" spans="1:10" s="46" customFormat="1" ht="16.5">
+    <row r="466" spans="1:10" s="46" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A466" s="23">
         <v>40503</v>
       </c>
@@ -11929,14 +11945,14 @@
         <v>237</v>
       </c>
     </row>
-    <row r="467" spans="1:10" s="48" customFormat="1">
+    <row r="467" spans="1:10" s="48" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A467" s="47"/>
       <c r="D467" s="47"/>
       <c r="E467" s="47"/>
       <c r="F467" s="47"/>
       <c r="H467" s="49"/>
     </row>
-    <row r="468" spans="1:10" s="46" customFormat="1" ht="16.5">
+    <row r="468" spans="1:10" s="46" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A468" s="23">
         <v>40504</v>
       </c>
@@ -11962,14 +11978,14 @@
         <v>238</v>
       </c>
     </row>
-    <row r="469" spans="1:10" s="48" customFormat="1">
+    <row r="469" spans="1:10" s="48" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A469" s="47"/>
       <c r="D469" s="47"/>
       <c r="E469" s="47"/>
       <c r="F469" s="47"/>
       <c r="H469" s="49"/>
     </row>
-    <row r="470" spans="1:10" s="46" customFormat="1" ht="16.5">
+    <row r="470" spans="1:10" s="46" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A470" s="23">
         <v>50501</v>
       </c>
@@ -11995,14 +12011,14 @@
         <v>239</v>
       </c>
     </row>
-    <row r="471" spans="1:10" s="48" customFormat="1">
+    <row r="471" spans="1:10" s="48" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A471" s="47"/>
       <c r="D471" s="47"/>
       <c r="E471" s="47"/>
       <c r="F471" s="47"/>
       <c r="H471" s="49"/>
     </row>
-    <row r="472" spans="1:10" s="46" customFormat="1" ht="16.5">
+    <row r="472" spans="1:10" s="46" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A472" s="23">
         <v>50502</v>
       </c>
@@ -12028,14 +12044,14 @@
         <v>239</v>
       </c>
     </row>
-    <row r="473" spans="1:10" s="48" customFormat="1">
+    <row r="473" spans="1:10" s="48" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A473" s="47"/>
       <c r="D473" s="47"/>
       <c r="E473" s="47"/>
       <c r="F473" s="47"/>
       <c r="H473" s="49"/>
     </row>
-    <row r="474" spans="1:10" s="46" customFormat="1" ht="16.5">
+    <row r="474" spans="1:10" s="46" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A474" s="23">
         <v>50503</v>
       </c>
@@ -12061,17 +12077,17 @@
         <v>239</v>
       </c>
     </row>
-    <row r="476" spans="1:10" s="51" customFormat="1" ht="40.5" customHeight="1">
+    <row r="476" spans="1:10" s="51" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A476" s="50"/>
       <c r="D476" s="50"/>
       <c r="E476" s="50"/>
       <c r="F476" s="50"/>
       <c r="H476" s="52"/>
     </row>
-    <row r="477" spans="1:10">
+    <row r="477" spans="1:10" x14ac:dyDescent="0.15">
       <c r="H477" s="21"/>
     </row>
-    <row r="478" spans="1:10" s="13" customFormat="1" ht="21">
+    <row r="478" spans="1:10" s="13" customFormat="1" ht="21" x14ac:dyDescent="0.4">
       <c r="A478" s="23">
         <v>10601</v>
       </c>
@@ -12097,7 +12113,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="479" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="479" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A479" s="10"/>
       <c r="B479" s="9" t="s">
         <v>116</v>
@@ -12118,7 +12134,7 @@
       </c>
       <c r="I479" s="9"/>
     </row>
-    <row r="480" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="480" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A480" s="10"/>
       <c r="B480" s="9" t="s">
         <v>116</v>
@@ -12139,7 +12155,7 @@
       </c>
       <c r="I480" s="9"/>
     </row>
-    <row r="481" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="481" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A481" s="10"/>
       <c r="B481" s="9"/>
       <c r="C481" s="9"/>
@@ -12150,7 +12166,7 @@
       <c r="H481" s="17"/>
       <c r="I481" s="9"/>
     </row>
-    <row r="482" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="482" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A482" s="10"/>
       <c r="B482" s="9" t="s">
         <v>147</v>
@@ -12178,7 +12194,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="483" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="483" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A483" s="10"/>
       <c r="B483" s="9" t="s">
         <v>116</v>
@@ -12203,7 +12219,7 @@
       </c>
       <c r="I483" s="9"/>
     </row>
-    <row r="484" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="484" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A484" s="10"/>
       <c r="B484" s="9" t="s">
         <v>116</v>
@@ -12228,7 +12244,7 @@
       </c>
       <c r="I484" s="9"/>
     </row>
-    <row r="485" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="485" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A485" s="10"/>
       <c r="B485" s="9" t="s">
         <v>116</v>
@@ -12253,7 +12269,7 @@
       </c>
       <c r="I485" s="9"/>
     </row>
-    <row r="486" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="486" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A486" s="10"/>
       <c r="B486" s="9" t="s">
         <v>116</v>
@@ -12278,7 +12294,7 @@
       </c>
       <c r="I486" s="9"/>
     </row>
-    <row r="487" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="487" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A487" s="10"/>
       <c r="B487" s="9"/>
       <c r="C487" s="9"/>
@@ -12289,7 +12305,7 @@
       <c r="H487" s="17"/>
       <c r="I487" s="9"/>
     </row>
-    <row r="488" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="488" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A488" s="10"/>
       <c r="B488" s="9" t="s">
         <v>147</v>
@@ -12315,7 +12331,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="489" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="489" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A489" s="10"/>
       <c r="B489" s="9" t="s">
         <v>116</v>
@@ -12340,7 +12356,7 @@
       </c>
       <c r="I489" s="9"/>
     </row>
-    <row r="490" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="490" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A490" s="10"/>
       <c r="B490" s="9" t="s">
         <v>116</v>
@@ -12365,7 +12381,7 @@
       </c>
       <c r="I490" s="9"/>
     </row>
-    <row r="491" spans="1:10" s="13" customFormat="1" ht="33">
+    <row r="491" spans="1:10" s="13" customFormat="1" ht="33" x14ac:dyDescent="0.3">
       <c r="A491" s="10"/>
       <c r="B491" s="9" t="s">
         <v>116</v>
@@ -12390,7 +12406,7 @@
       </c>
       <c r="I491" s="9"/>
     </row>
-    <row r="492" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="492" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A492" s="10"/>
       <c r="B492" s="9"/>
       <c r="C492" s="9"/>
@@ -12401,7 +12417,7 @@
       <c r="H492" s="17"/>
       <c r="I492" s="9"/>
     </row>
-    <row r="493" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="493" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A493" s="10"/>
       <c r="B493" s="9" t="s">
         <v>147</v>
@@ -12427,7 +12443,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="494" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="494" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A494" s="10"/>
       <c r="B494" s="9" t="s">
         <v>116</v>
@@ -12452,7 +12468,7 @@
       </c>
       <c r="I494" s="9"/>
     </row>
-    <row r="495" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="495" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A495" s="10"/>
       <c r="B495" s="9" t="s">
         <v>116</v>
@@ -12477,7 +12493,7 @@
       </c>
       <c r="I495" s="9"/>
     </row>
-    <row r="496" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="496" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A496" s="10"/>
       <c r="B496" s="9"/>
       <c r="C496" s="9"/>
@@ -12488,7 +12504,7 @@
       <c r="H496" s="11"/>
       <c r="I496" s="9"/>
     </row>
-    <row r="497" spans="1:10" s="13" customFormat="1" ht="21.75" customHeight="1">
+    <row r="497" spans="1:10" s="13" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A497" s="23">
         <v>20601</v>
       </c>
@@ -12514,7 +12530,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="498" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="498" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A498" s="10"/>
       <c r="B498" s="9"/>
       <c r="C498" s="9"/>
@@ -12525,7 +12541,7 @@
       <c r="H498" s="11"/>
       <c r="I498" s="9"/>
     </row>
-    <row r="499" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="499" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A499" s="10"/>
       <c r="B499" s="9"/>
       <c r="C499" s="9"/>
@@ -12546,7 +12562,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="500" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="500" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A500" s="10"/>
       <c r="B500" s="9" t="s">
         <v>116</v>
@@ -12571,7 +12587,7 @@
       </c>
       <c r="I500" s="9"/>
     </row>
-    <row r="501" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="501" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A501" s="10"/>
       <c r="B501" s="9" t="s">
         <v>116</v>
@@ -12596,7 +12612,7 @@
       </c>
       <c r="I501" s="9"/>
     </row>
-    <row r="502" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="502" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A502" s="10"/>
       <c r="B502" s="9"/>
       <c r="C502" s="9"/>
@@ -12607,7 +12623,7 @@
       <c r="H502" s="11"/>
       <c r="I502" s="9"/>
     </row>
-    <row r="503" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="503" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A503" s="10"/>
       <c r="B503" s="9"/>
       <c r="C503" s="9"/>
@@ -12626,7 +12642,7 @@
       </c>
       <c r="I503" s="9"/>
     </row>
-    <row r="504" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="504" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A504" s="10"/>
       <c r="B504" s="9" t="s">
         <v>116</v>
@@ -12651,7 +12667,7 @@
       </c>
       <c r="I504" s="9"/>
     </row>
-    <row r="505" spans="1:10" s="13" customFormat="1" ht="33">
+    <row r="505" spans="1:10" s="13" customFormat="1" ht="33" x14ac:dyDescent="0.3">
       <c r="A505" s="10"/>
       <c r="B505" s="9" t="s">
         <v>116</v>
@@ -12676,7 +12692,7 @@
       </c>
       <c r="I505" s="9"/>
     </row>
-    <row r="506" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="506" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A506" s="10"/>
       <c r="B506" s="9"/>
       <c r="C506" s="9"/>
@@ -12687,7 +12703,7 @@
       <c r="H506" s="11"/>
       <c r="I506" s="9"/>
     </row>
-    <row r="507" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="507" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A507" s="10"/>
       <c r="B507" s="9"/>
       <c r="C507" s="9"/>
@@ -12706,7 +12722,7 @@
       </c>
       <c r="I507" s="9"/>
     </row>
-    <row r="508" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="508" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A508" s="10"/>
       <c r="B508" s="9" t="s">
         <v>116</v>
@@ -12731,7 +12747,7 @@
       </c>
       <c r="I508" s="9"/>
     </row>
-    <row r="509" spans="1:10" s="13" customFormat="1" ht="33">
+    <row r="509" spans="1:10" s="13" customFormat="1" ht="33" x14ac:dyDescent="0.3">
       <c r="A509" s="10"/>
       <c r="B509" s="9" t="s">
         <v>116</v>
@@ -12756,7 +12772,7 @@
       </c>
       <c r="I509" s="9"/>
     </row>
-    <row r="510" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="510" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A510" s="10"/>
       <c r="B510" s="9"/>
       <c r="C510" s="9"/>
@@ -12767,7 +12783,7 @@
       <c r="H510" s="18"/>
       <c r="I510" s="9"/>
     </row>
-    <row r="511" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="511" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A511" s="10"/>
       <c r="B511" s="9"/>
       <c r="C511" s="9"/>
@@ -12778,7 +12794,7 @@
       <c r="H511" s="11"/>
       <c r="I511" s="9"/>
     </row>
-    <row r="512" spans="1:10" s="32" customFormat="1" ht="21">
+    <row r="512" spans="1:10" s="32" customFormat="1" ht="21" x14ac:dyDescent="0.4">
       <c r="A512" s="23">
         <v>30601</v>
       </c>
@@ -12804,7 +12820,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="513" spans="1:10" ht="16.5">
+    <row r="513" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A513" s="19"/>
       <c r="B513" s="13"/>
       <c r="C513" s="13"/>
@@ -12816,7 +12832,7 @@
       <c r="I513" s="13"/>
       <c r="J513" s="13"/>
     </row>
-    <row r="514" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="514" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A514" s="19"/>
       <c r="B514" s="9" t="s">
         <v>147</v>
@@ -12841,7 +12857,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="515" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="515" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A515" s="19"/>
       <c r="B515" s="9" t="s">
         <v>116</v>
@@ -12865,7 +12881,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="516" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="516" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A516" s="19"/>
       <c r="B516" s="9" t="s">
         <v>116</v>
@@ -12890,7 +12906,7 @@
       </c>
       <c r="J516" s="39"/>
     </row>
-    <row r="517" spans="1:10" ht="16.5">
+    <row r="517" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A517" s="19"/>
       <c r="B517" s="13"/>
       <c r="C517" s="13"/>
@@ -12902,7 +12918,7 @@
       <c r="I517" s="13"/>
       <c r="J517" s="13"/>
     </row>
-    <row r="518" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="518" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A518" s="19"/>
       <c r="B518" s="9" t="s">
         <v>147</v>
@@ -12924,7 +12940,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="519" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="519" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A519" s="19"/>
       <c r="B519" s="9" t="s">
         <v>116</v>
@@ -12948,7 +12964,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="520" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="520" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A520" s="19"/>
       <c r="B520" s="9" t="s">
         <v>116</v>
@@ -12972,7 +12988,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="521" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="521" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A521" s="10"/>
       <c r="B521" s="9"/>
       <c r="C521" s="9"/>
@@ -12983,7 +12999,7 @@
       <c r="H521" s="11"/>
       <c r="I521" s="9"/>
     </row>
-    <row r="522" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="522" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A522" s="10"/>
       <c r="B522" s="9"/>
       <c r="C522" s="9"/>
@@ -12994,7 +13010,7 @@
       <c r="H522" s="11"/>
       <c r="I522" s="9"/>
     </row>
-    <row r="523" spans="1:10" s="32" customFormat="1" ht="21">
+    <row r="523" spans="1:10" s="32" customFormat="1" ht="21" x14ac:dyDescent="0.4">
       <c r="A523" s="23">
         <v>30602</v>
       </c>
@@ -13020,7 +13036,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="524" spans="1:10" ht="16.5">
+    <row r="524" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A524" s="19"/>
       <c r="B524" s="13"/>
       <c r="C524" s="13"/>
@@ -13032,7 +13048,7 @@
       <c r="I524" s="13"/>
       <c r="J524" s="13"/>
     </row>
-    <row r="525" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="525" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A525" s="19"/>
       <c r="B525" s="9" t="s">
         <v>147</v>
@@ -13054,7 +13070,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="526" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="526" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A526" s="19"/>
       <c r="B526" s="9" t="s">
         <v>116</v>
@@ -13078,7 +13094,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="527" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="527" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A527" s="19"/>
       <c r="B527" s="9" t="s">
         <v>116</v>
@@ -13105,7 +13121,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="528" spans="1:10" ht="16.5">
+    <row r="528" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A528" s="19"/>
       <c r="B528" s="13"/>
       <c r="C528" s="13"/>
@@ -13117,7 +13133,7 @@
       <c r="I528" s="13"/>
       <c r="J528" s="13"/>
     </row>
-    <row r="529" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="529" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A529" s="19"/>
       <c r="B529" s="9" t="s">
         <v>147</v>
@@ -13139,7 +13155,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="530" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="530" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A530" s="19"/>
       <c r="B530" s="9" t="s">
         <v>116</v>
@@ -13163,7 +13179,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="531" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="531" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A531" s="19"/>
       <c r="B531" s="9" t="s">
         <v>116</v>
@@ -13187,7 +13203,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="532" spans="1:10" ht="16.5">
+    <row r="532" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A532" s="19"/>
       <c r="B532" s="13"/>
       <c r="C532" s="13"/>
@@ -13199,7 +13215,7 @@
       <c r="I532" s="13"/>
       <c r="J532" s="13"/>
     </row>
-    <row r="533" spans="1:10" ht="16.5">
+    <row r="533" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A533" s="19"/>
       <c r="B533" s="13"/>
       <c r="C533" s="13"/>
@@ -13211,7 +13227,7 @@
       <c r="I533" s="13"/>
       <c r="J533" s="13"/>
     </row>
-    <row r="534" spans="1:10" ht="16.5">
+    <row r="534" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A534" s="19"/>
       <c r="B534" s="13"/>
       <c r="C534" s="13"/>
@@ -13223,7 +13239,7 @@
       <c r="I534" s="13"/>
       <c r="J534" s="13"/>
     </row>
-    <row r="535" spans="1:10" s="32" customFormat="1" ht="21">
+    <row r="535" spans="1:10" s="32" customFormat="1" ht="21" x14ac:dyDescent="0.4">
       <c r="A535" s="23">
         <v>30603</v>
       </c>
@@ -13249,7 +13265,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="536" spans="1:10" ht="16.5">
+    <row r="536" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A536" s="19"/>
       <c r="B536" s="13"/>
       <c r="C536" s="13"/>
@@ -13261,7 +13277,7 @@
       <c r="I536" s="13"/>
       <c r="J536" s="13"/>
     </row>
-    <row r="537" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="537" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A537" s="19"/>
       <c r="B537" s="9" t="s">
         <v>147</v>
@@ -13283,7 +13299,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="538" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="538" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A538" s="19"/>
       <c r="B538" s="9" t="s">
         <v>116</v>
@@ -13307,7 +13323,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="539" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="539" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A539" s="19"/>
       <c r="B539" s="9" t="s">
         <v>116</v>
@@ -13334,7 +13350,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="540" spans="1:10" ht="16.5">
+    <row r="540" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A540" s="19"/>
       <c r="B540" s="13"/>
       <c r="C540" s="13"/>
@@ -13346,7 +13362,7 @@
       <c r="I540" s="13"/>
       <c r="J540" s="13"/>
     </row>
-    <row r="541" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="541" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A541" s="19"/>
       <c r="B541" s="9" t="s">
         <v>147</v>
@@ -13368,7 +13384,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="542" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="542" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A542" s="19"/>
       <c r="B542" s="9" t="s">
         <v>116</v>
@@ -13392,7 +13408,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="543" spans="1:10" s="13" customFormat="1" ht="16.5">
+    <row r="543" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A543" s="19"/>
       <c r="B543" s="9" t="s">
         <v>116</v>
@@ -13416,7 +13432,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="544" spans="1:10" ht="16.5">
+    <row r="544" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A544" s="19"/>
       <c r="B544" s="13"/>
       <c r="C544" s="13"/>
@@ -13428,7 +13444,7 @@
       <c r="I544" s="13"/>
       <c r="J544" s="13"/>
     </row>
-    <row r="545" spans="1:10" ht="16.5">
+    <row r="545" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A545" s="19"/>
       <c r="B545" s="13"/>
       <c r="C545" s="13"/>
@@ -13440,7 +13456,7 @@
       <c r="I545" s="13"/>
       <c r="J545" s="13"/>
     </row>
-    <row r="546" spans="1:10" s="46" customFormat="1" ht="16.5">
+    <row r="546" spans="1:10" s="46" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A546" s="23">
         <v>40601</v>
       </c>
@@ -13466,14 +13482,14 @@
         <v>236</v>
       </c>
     </row>
-    <row r="547" spans="1:10" s="48" customFormat="1">
+    <row r="547" spans="1:10" s="48" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A547" s="47"/>
       <c r="D547" s="47"/>
       <c r="E547" s="47"/>
       <c r="F547" s="47"/>
       <c r="H547" s="49"/>
     </row>
-    <row r="548" spans="1:10" s="46" customFormat="1" ht="16.5">
+    <row r="548" spans="1:10" s="46" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A548" s="23">
         <v>40602</v>
       </c>
@@ -13499,14 +13515,14 @@
         <v>237</v>
       </c>
     </row>
-    <row r="549" spans="1:10" s="48" customFormat="1">
+    <row r="549" spans="1:10" s="48" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A549" s="47"/>
       <c r="D549" s="47"/>
       <c r="E549" s="47"/>
       <c r="F549" s="47"/>
       <c r="H549" s="49"/>
     </row>
-    <row r="550" spans="1:10" s="46" customFormat="1" ht="16.5">
+    <row r="550" spans="1:10" s="46" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A550" s="23">
         <v>40603</v>
       </c>
@@ -13532,14 +13548,14 @@
         <v>237</v>
       </c>
     </row>
-    <row r="551" spans="1:10" s="48" customFormat="1">
+    <row r="551" spans="1:10" s="48" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A551" s="47"/>
       <c r="D551" s="47"/>
       <c r="E551" s="47"/>
       <c r="F551" s="47"/>
       <c r="H551" s="49"/>
     </row>
-    <row r="552" spans="1:10" s="46" customFormat="1" ht="16.5">
+    <row r="552" spans="1:10" s="46" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A552" s="23">
         <v>40604</v>
       </c>
@@ -13565,14 +13581,14 @@
         <v>238</v>
       </c>
     </row>
-    <row r="553" spans="1:10" s="48" customFormat="1">
+    <row r="553" spans="1:10" s="48" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A553" s="47"/>
       <c r="D553" s="47"/>
       <c r="E553" s="47"/>
       <c r="F553" s="47"/>
       <c r="H553" s="49"/>
     </row>
-    <row r="554" spans="1:10" s="46" customFormat="1" ht="16.5">
+    <row r="554" spans="1:10" s="46" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A554" s="23">
         <v>50601</v>
       </c>
@@ -13598,14 +13614,14 @@
         <v>239</v>
       </c>
     </row>
-    <row r="555" spans="1:10" s="48" customFormat="1">
+    <row r="555" spans="1:10" s="48" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A555" s="47"/>
       <c r="D555" s="47"/>
       <c r="E555" s="47"/>
       <c r="F555" s="47"/>
       <c r="H555" s="49"/>
     </row>
-    <row r="556" spans="1:10" s="46" customFormat="1" ht="16.5">
+    <row r="556" spans="1:10" s="46" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A556" s="23">
         <v>50602</v>
       </c>
@@ -13631,14 +13647,14 @@
         <v>239</v>
       </c>
     </row>
-    <row r="557" spans="1:10" s="48" customFormat="1">
+    <row r="557" spans="1:10" s="48" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A557" s="47"/>
       <c r="D557" s="47"/>
       <c r="E557" s="47"/>
       <c r="F557" s="47"/>
       <c r="H557" s="49"/>
     </row>
-    <row r="558" spans="1:10" s="46" customFormat="1" ht="16.5">
+    <row r="558" spans="1:10" s="46" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A558" s="23">
         <v>50603</v>
       </c>
@@ -13692,7 +13708,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F42"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="52" customWidth="1"/>
@@ -13700,7 +13716,7 @@
     <col min="6" max="6" width="74.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>3</v>
       </c>
@@ -13714,7 +13730,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -13728,7 +13744,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -13742,7 +13758,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -13756,7 +13772,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -13770,7 +13786,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>30</v>
       </c>
@@ -13784,7 +13800,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>33</v>
       </c>
@@ -13798,7 +13814,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>35</v>
       </c>
@@ -13812,7 +13828,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>38</v>
       </c>
@@ -13820,7 +13836,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A12" s="3" t="s">
         <v>106</v>
       </c>
@@ -13834,7 +13850,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>119</v>
       </c>
@@ -13845,7 +13861,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>122</v>
       </c>
@@ -13856,7 +13872,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>120</v>
       </c>
@@ -13867,7 +13883,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A18" s="3" t="s">
         <v>101</v>
       </c>
@@ -13875,7 +13891,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>116</v>
       </c>
@@ -13883,7 +13899,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>147</v>
       </c>
@@ -13891,7 +13907,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>152</v>
       </c>
@@ -13899,7 +13915,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A23" s="3" t="s">
         <v>102</v>
       </c>
@@ -13914,7 +13930,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
         <v>117</v>
       </c>
@@ -13922,7 +13938,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
         <v>128</v>
       </c>
@@ -13930,7 +13946,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
         <v>129</v>
       </c>
@@ -13938,7 +13954,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
         <v>130</v>
       </c>
@@ -13946,7 +13962,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
         <v>131</v>
       </c>
@@ -13954,7 +13970,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A29" t="s">
         <v>132</v>
       </c>
@@ -13962,7 +13978,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
         <v>133</v>
       </c>
@@ -13970,7 +13986,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
         <v>134</v>
       </c>
@@ -13978,7 +13994,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A34" s="3" t="s">
         <v>136</v>
       </c>
@@ -13986,7 +14002,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A35" t="s">
         <v>142</v>
       </c>
@@ -13994,7 +14010,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A36" t="s">
         <v>121</v>
       </c>
@@ -14002,7 +14018,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A37" t="s">
         <v>127</v>
       </c>
@@ -14010,7 +14026,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A38" t="s">
         <v>158</v>
       </c>
@@ -14018,7 +14034,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A39" t="s">
         <v>162</v>
       </c>
@@ -14026,7 +14042,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A40" t="s">
         <v>167</v>
       </c>
@@ -14034,7 +14050,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A41" t="s">
         <v>172</v>
       </c>
@@ -14042,7 +14058,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A42" t="s">
         <v>177</v>
       </c>

--- a/Excel/对话表.xlsx
+++ b/Excel/对话表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xinxinhe\Documents\2026MasterHouse\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{402BC368-6F2D-452A-A739-561BEB04D947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE999EAE-5991-4E9E-9095-A62E8360E4CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6885" yWindow="2640" windowWidth="20505" windowHeight="7410" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="对话组" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2141" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2141" uniqueCount="432">
   <si>
     <t>对话组ID</t>
   </si>
@@ -598,10 +598,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>cheetah_平静</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>一个游戏关卡</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -658,920 +654,910 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>cat_开心</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>老板！我是豹冲冲！这里能放球包吗？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>当然，豹冲冲，欢迎来到Master House~</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在还有房间嘛，我好想好好休息一下~</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>嘿嘿好的，我去放行李啦~</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>那，那好吧，那我只能去其他地方看看了，55555…....</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>嗯呢！我等你！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>嗯嗯，那我先去放行李啦~</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>嗯嗯，我等你，但是如果要等很久的话我会很难过的…...</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>豹冲冲-入住</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>豹冲冲-想一下</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>豹冲冲-家具1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>豹冲冲-电路1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>RoomHasNeedFurniture</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Need_电路教程</t>
+  </si>
+  <si>
+    <t>好的，我先去放行李了。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>哦哦……那我改天再来吧。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>还在找，辛苦再等待下~</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>你是觉得我要求太多了吗</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>好的，我去找找咩，安排好了跟您说~</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>goat_开心</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>嗯嗯，我等你！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Branch</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>已完成</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>已经按照你的要求布置好房间啦~</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CompleteNeed(perfect)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>10201</t>
+  </si>
+  <si>
+    <t>leopard</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>20201</t>
+  </si>
+  <si>
+    <t>needTalk</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>条件类需求「Need_新需求」的说辞与交付分支</t>
+  </si>
+  <si>
+    <t>40201</t>
+  </si>
+  <si>
+    <t>40202</t>
+  </si>
+  <si>
+    <t>40203</t>
+  </si>
+  <si>
+    <t>40204</t>
+  </si>
+  <si>
+    <t>50201</t>
+  </si>
+  <si>
+    <t>50202</t>
+  </si>
+  <si>
+    <t>50203</t>
+  </si>
+  <si>
+    <t>10301</t>
+  </si>
+  <si>
+    <t>20301</t>
+  </si>
+  <si>
+    <t>40301</t>
+  </si>
+  <si>
+    <t>40302</t>
+  </si>
+  <si>
+    <t>40303</t>
+  </si>
+  <si>
+    <t>40304</t>
+  </si>
+  <si>
+    <t>50301</t>
+  </si>
+  <si>
+    <t>50302</t>
+  </si>
+  <si>
+    <t>50303</t>
+  </si>
+  <si>
+    <t>10401</t>
+  </si>
+  <si>
+    <t>20401</t>
+  </si>
+  <si>
+    <t>40401</t>
+  </si>
+  <si>
+    <t>40402</t>
+  </si>
+  <si>
+    <t>40403</t>
+  </si>
+  <si>
+    <t>40404</t>
+  </si>
+  <si>
+    <t>50401</t>
+  </si>
+  <si>
+    <t>50402</t>
+  </si>
+  <si>
+    <t>50403</t>
+  </si>
+  <si>
+    <t>10501</t>
+  </si>
+  <si>
+    <t>20501</t>
+  </si>
+  <si>
+    <t>40501</t>
+  </si>
+  <si>
+    <t>40502</t>
+  </si>
+  <si>
+    <t>feedbackPlain</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>40503</t>
+  </si>
+  <si>
+    <t>40504</t>
+  </si>
+  <si>
+    <t>50501</t>
+  </si>
+  <si>
+    <t>50502</t>
+  </si>
+  <si>
+    <t>50503</t>
+  </si>
+  <si>
+    <t>10601</t>
+  </si>
+  <si>
+    <t>firstMeeting</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>20601</t>
+  </si>
+  <si>
+    <t>40601</t>
+  </si>
+  <si>
+    <t>40602</t>
+  </si>
+  <si>
+    <t>40603</t>
+  </si>
+  <si>
+    <t>40604</t>
+  </si>
+  <si>
+    <t>50601</t>
+  </si>
+  <si>
+    <t>50602</t>
+  </si>
+  <si>
+    <t>50603</t>
+  </si>
+  <si>
+    <t>豹酷酷-入住</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>leopard_伤心</t>
+  </si>
+  <si>
+    <t>豹酷酷-想一下</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>豹酷酷-家具1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>豹酷酷-电路1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>豹酷酷-其他需求1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>leopard_开心</t>
+  </si>
+  <si>
+    <t>牛莱-入住</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>yak_伤心</t>
+  </si>
+  <si>
+    <t>牛莱-想一下</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>牛莱-家具1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>牛莱-电路1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>牛莱-其他需求1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>yak_开心</t>
+  </si>
+  <si>
+    <t>兔米露-入住</t>
+  </si>
+  <si>
+    <t>rabbit_伤心</t>
+  </si>
+  <si>
+    <t>兔米露-想一下</t>
+  </si>
+  <si>
+    <t>兔米露-家具1</t>
+  </si>
+  <si>
+    <t>兔米露-电路1</t>
+  </si>
+  <si>
+    <t>兔米露-其他需求1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>rabbit_开心</t>
+  </si>
+  <si>
+    <t>嘉嚎-入住</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>wolf_伤心</t>
+  </si>
+  <si>
+    <t>嘉嚎-想一下</t>
+  </si>
+  <si>
+    <t>嘉嚎-家具1</t>
+  </si>
+  <si>
+    <t>嘉嚎-电路1</t>
+  </si>
+  <si>
+    <t>嘉嚎-其他需求1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>wolf_开心</t>
+  </si>
+  <si>
+    <t>牛小顿-入住</t>
+  </si>
+  <si>
+    <t>ox_伤心</t>
+  </si>
+  <si>
+    <t>牛小顿-想一下</t>
+  </si>
+  <si>
+    <t>牛小顿-家具1</t>
+  </si>
+  <si>
+    <t>牛小顿-电路1</t>
+  </si>
+  <si>
+    <t>牛小顿-其他1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ox_开心</t>
+  </si>
+  <si>
+    <t>player</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>好，我会等你的。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>不好意思咩，现在有些忙碌，暂时没有办法满足您的需求咩。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reject</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>嗯，还行吧，比之前好多了</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>这里还不错嘛，感觉能好好歇一会儿。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>我刚刚是不是跑太快了？算了，问题不大。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>这里真好，之后备赛还来这里。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>您好，我是棒球队队长——豹酷酷。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>明天我们棒球队在旁边体育场有比赛，辛苦您帮我查下今晚是否还有空房间？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>好的，队长，欢迎来到Master House~</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>查找中......</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>听说豹冲冲也在这里入住，请把我的房间安排在离他远点的地方。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>好的，我尽量满足您的要求，这是您的房卡咩。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>谢谢您！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>非常抱歉，目前没有能够满足您要求的房间咩。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>没关系，我再去其他地方看看。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>您稍等，我再帮您确认一下房间。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>谢谢您，麻烦了。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>好的，谢谢。我现在过去确认一下。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>抱歉啊，还是没有找到合适的房间。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>明白了，那我今天只能换个地方休息了。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>好的，不着急。我再等您一会儿。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>我带了训练服和奖杯，需要有衣柜和展示架。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>看起来还不错，是我需要的，谢谢你。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>没关系，可能今天确实比较忙。辛苦您了。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>谢谢您愿意帮忙。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>非常好，我喜欢这里的。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>这里比我想象中安静，很适合休息。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>棒球比赛前，休息质量也很重要。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>下次备赛，我会来这里。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>您好，我叫牛莱，是一名钢琴老师。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>牛莱老师，欢迎您来到Master House哇！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在还有房间吗？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>我可能要在房间里练练琴，需要一间隔音比较好的房间。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>明白，我们这里都是实体墙，隔音很棒咩。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>那就好，我担心影响到其他客人。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>另外，我不太喜欢有人说“对牛弹琴”这个词。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>好咩，我立马把这个词从Master House的空气里清理掉！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>很好。你很有教养。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>非常抱歉咩，目前没有能够满足您要求的房间。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>没关系，那我先走了哞。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>好的，我正好再看一遍谱子。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>房间安排好了哞？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>谢谢。希望今晚能有一个安静的休止音符。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>没关系，曲谱有起承转合，我想，找到一个合适的房间也是这样。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以帮我准备一个谱架吗？曲子还需要修改，放在桌上看不太方便。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>好吧，那我先把曲子背下来。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>yak_开心</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>很好，高度正合适。你的服务很贴心哞。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>突然有学生约了课，请问有钢琴可以借用吗？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>仓库里有一架我奶奶留下的电子琴，但是电路老化了需要修理下。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>没关系，已经帮到我大忙了，我会耐心等待的。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>请问有咖啡吗？想喝现磨的哞。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>算了……可能今天你确实太忙了。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>嗯，还可以，谢谢你。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>这里很安静，适合把谱子再看一遍。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>下次休假，我也许还会来。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>老板，我在小众点评上看到了这家高分民宿，请问还有房间嘛？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>哇，您是idol兔米露吗，我超级喜欢你！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>嗯，我是。不过，可以小点声嘛~</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>嗯嗯好的，我现在就查看房间!（小声）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>我想要一间私密性比较好的房间，可以嘛？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>嗯嗯，我会尽量安排！这是您的房卡~</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>感谢你，我先去休息啦。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>非常抱歉咩，目前没有能够满足您要求的房间咩。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">	啊……没关系啦，我再去其他地方看看。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>您稍等下，我还在找合适的房间。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>好呀，我正好补一下妆。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>找到合适的房间了嘛？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>rabbit_平静</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>嗯嗯，我等你，希望不要等太久，我等会还有粉丝见面会要参加。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>老板，请问房间可以提供化妆镜嘛？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>嗯呐，我等你。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>rabbit_开心</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>谢谢老板，是我喜欢的样子呢，您真的很贴心（饭撒）~</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>房间的唱片机好像断触了，可以帮忙修理一下嘛？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>不好意思咩，现在有些忙碌，暂时没有办法满足偶像您的需求咩。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>路演完好累啊，请问这里提供咖啡嘛？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>好咩，我去为偶像制作咩~</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>没关系啦，你已经很努力了。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>嗯，其实还可以，谢谢你。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>太完美了，我会记住这里的。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>这里真不错呀，感觉可以好好充电。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>下次路过，我还会来的。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>你好，我是总裁——嘉嚎。你是，这儿的老板？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>是的，总裁，欢迎来到Master House~</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>这里，比我想象中……还要朴素呢。今天还有空房间吗？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>好的，稍等我来找找咩。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>帮我安排一个高级总裁套房吧。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>啊…...这，目前还不提供这种房型呢，普通房间可以吗？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>行吧，我勉强试试看。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>非常抱歉咩，目前没有合适房间咩。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>好吧，不过你们酒店的接待能力也该提升下了。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>找到了吗，小羊老板？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>谢谢，帮我把行李提上去吧。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>还在找，辛苦再等待下咩。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以，但不要让我等太久。我的时间很宝贵。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>呜，这床好硬，帮我换一张高级席梦思床吧。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>wolf_开心</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>嗯，这样才稍微像样，你的服务我很满意。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>这里的灯光不够稳定，影响我思考集团的重要决策。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>看来这里的服务标准，还有提升空间。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>嗯，勉强可以接受。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>还不错，比我预想的像样一些。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>很好，这才是我需要的效率。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>咖啡呢？我只喝现磨的。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>不要叫我挑剔，我只是标准比较清楚。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>我不要你觉得，我要我觉得</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>您好，我叫牛小顿，想要住宿。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>欢迎您来到Master House，我来看看还有没有空闲房间。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>我没有什么特殊需求，安静就好。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>已经帮您安排好了，这是房卡。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>谢谢。（四处张望）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>好的，不过一旦有，请立马通知我哞。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>好的，等待过程中我顺便观察下民宿布局。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>找到合适的房间了哞？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>嗯嗯，那我先去放行李。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ox_平静</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果方便的话，房间里能加一张小桌子吗？我需要整理下线索。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>嗯嗯，我会等你的。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ox_开心</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>非常感谢，我相信用张桌子一定能更快理清线索。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>晚上台灯总是一闪一闪的，帮忙修一下好吗？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>整理线索好困，有咖啡提供吗？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>这里真不错啊哞。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>好的，我先去放行李。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>是我预期中的样子，谢谢你。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>我要一间明亮的房间！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>明白，安排！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>哇！是我想要的布置喵！！！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>cheetah_伤心</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>cheetah_开心</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>cat_开心</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>老板！我是豹冲冲！这里能放球包吗？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>当然，豹冲冲，欢迎来到Master House~</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>现在还有房间嘛，我好想好好休息一下~</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>嘿嘿好的，我去放行李啦~</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>那，那好吧，那我只能去其他地方看看了，55555…....</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>嗯呢！我等你！</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>嗯嗯，那我先去放行李啦~</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>嗯嗯，我等你，但是如果要等很久的话我会很难过的…...</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>豹冲冲-入住</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>豹冲冲-想一下</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>豹冲冲-家具1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>豹冲冲-电路1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>RoomHasNeedFurniture</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Need_电路教程</t>
-  </si>
-  <si>
-    <t>好的，我先去放行李了。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>哦哦……那我改天再来吧。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>还在找，辛苦再等待下~</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>你是觉得我要求太多了吗</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>好的，我去找找咩，安排好了跟您说~</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>goat_开心</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>嗯嗯，我等你！</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Branch</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>已完成</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>已经按照你的要求布置好房间啦~</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>CompleteNeed(perfect)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>10201</t>
-  </si>
-  <si>
-    <t>leopard</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>20201</t>
-  </si>
-  <si>
-    <t>needTalk</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>条件类需求「Need_新需求」的说辞与交付分支</t>
-  </si>
-  <si>
-    <t>40201</t>
-  </si>
-  <si>
-    <t>40202</t>
-  </si>
-  <si>
-    <t>40203</t>
-  </si>
-  <si>
-    <t>40204</t>
-  </si>
-  <si>
-    <t>50201</t>
-  </si>
-  <si>
-    <t>50202</t>
-  </si>
-  <si>
-    <t>50203</t>
-  </si>
-  <si>
-    <t>10301</t>
-  </si>
-  <si>
-    <t>20301</t>
-  </si>
-  <si>
-    <t>40301</t>
-  </si>
-  <si>
-    <t>40302</t>
-  </si>
-  <si>
-    <t>40303</t>
-  </si>
-  <si>
-    <t>40304</t>
-  </si>
-  <si>
-    <t>50301</t>
-  </si>
-  <si>
-    <t>50302</t>
-  </si>
-  <si>
-    <t>50303</t>
-  </si>
-  <si>
-    <t>10401</t>
-  </si>
-  <si>
-    <t>20401</t>
-  </si>
-  <si>
-    <t>40401</t>
-  </si>
-  <si>
-    <t>40402</t>
-  </si>
-  <si>
-    <t>40403</t>
-  </si>
-  <si>
-    <t>40404</t>
-  </si>
-  <si>
-    <t>50401</t>
-  </si>
-  <si>
-    <t>50402</t>
-  </si>
-  <si>
-    <t>50403</t>
-  </si>
-  <si>
-    <t>10501</t>
-  </si>
-  <si>
-    <t>20501</t>
-  </si>
-  <si>
-    <t>40501</t>
-  </si>
-  <si>
-    <t>40502</t>
-  </si>
-  <si>
-    <t>feedbackPlain</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>40503</t>
-  </si>
-  <si>
-    <t>40504</t>
-  </si>
-  <si>
-    <t>50501</t>
-  </si>
-  <si>
-    <t>50502</t>
-  </si>
-  <si>
-    <t>50503</t>
-  </si>
-  <si>
-    <t>10601</t>
-  </si>
-  <si>
-    <t>firstMeeting</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>20601</t>
-  </si>
-  <si>
-    <t>40601</t>
-  </si>
-  <si>
-    <t>40602</t>
-  </si>
-  <si>
-    <t>40603</t>
-  </si>
-  <si>
-    <t>40604</t>
-  </si>
-  <si>
-    <t>50601</t>
-  </si>
-  <si>
-    <t>50602</t>
-  </si>
-  <si>
-    <t>50603</t>
-  </si>
-  <si>
-    <t>豹酷酷-入住</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>leopard_伤心</t>
-  </si>
-  <si>
-    <t>leopard_平静</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>豹酷酷-想一下</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>豹酷酷-家具1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>豹酷酷-电路1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>豹酷酷-其他需求1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>leopard_开心</t>
-  </si>
-  <si>
-    <t>牛莱-入住</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>yak_伤心</t>
-  </si>
-  <si>
-    <t>牛莱-想一下</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>牛莱-家具1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>牛莱-电路1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>牛莱-其他需求1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>yak_开心</t>
-  </si>
-  <si>
-    <t>兔米露-入住</t>
-  </si>
-  <si>
-    <t>rabbit_伤心</t>
-  </si>
-  <si>
-    <t>兔米露-想一下</t>
-  </si>
-  <si>
-    <t>兔米露-家具1</t>
-  </si>
-  <si>
-    <t>兔米露-电路1</t>
-  </si>
-  <si>
-    <t>兔米露-其他需求1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>rabbit_开心</t>
-  </si>
-  <si>
-    <t>嘉嚎-入住</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>wolf_伤心</t>
-  </si>
-  <si>
-    <t>嘉嚎-想一下</t>
-  </si>
-  <si>
-    <t>嘉嚎-家具1</t>
-  </si>
-  <si>
-    <t>嘉嚎-电路1</t>
-  </si>
-  <si>
-    <t>嘉嚎-其他需求1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>wolf_开心</t>
-  </si>
-  <si>
-    <t>牛小顿-入住</t>
-  </si>
-  <si>
-    <t>ox_伤心</t>
-  </si>
-  <si>
-    <t>牛小顿-想一下</t>
-  </si>
-  <si>
-    <t>牛小顿-家具1</t>
-  </si>
-  <si>
-    <t>牛小顿-电路1</t>
-  </si>
-  <si>
-    <t>牛小顿-其他1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ox_开心</t>
-  </si>
-  <si>
-    <t>player</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>好，我会等你的。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>不好意思咩，现在有些忙碌，暂时没有办法满足您的需求咩。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Reject</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>嗯，还行吧，比之前好多了</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>这里还不错嘛，感觉能好好歇一会儿。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>我刚刚是不是跑太快了？算了，问题不大。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>这里真好，之后备赛还来这里。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>您好，我是棒球队队长——豹酷酷。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>明天我们棒球队在旁边体育场有比赛，辛苦您帮我查下今晚是否还有空房间？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>好的，队长，欢迎来到Master House~</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>查找中......</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>听说豹冲冲也在这里入住，请把我的房间安排在离他远点的地方。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>好的，我尽量满足您的要求，这是您的房卡咩。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>谢谢您！</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>非常抱歉，目前没有能够满足您要求的房间咩。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>没关系，我再去其他地方看看。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>您稍等，我再帮您确认一下房间。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>谢谢您，麻烦了。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>好的，谢谢。我现在过去确认一下。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>抱歉啊，还是没有找到合适的房间。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>明白了，那我今天只能换个地方休息了。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>好的，不着急。我再等您一会儿。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>我带了训练服和奖杯，需要有衣柜和展示架。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>leopard_开心</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>看起来还不错，是我需要的，谢谢你。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>没关系，可能今天确实比较忙。辛苦您了。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>谢谢您愿意帮忙。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>非常好，我喜欢这里的。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>这里比我想象中安静，很适合休息。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>棒球比赛前，休息质量也很重要。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>下次备赛，我会来这里。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>您好，我叫牛莱，是一名钢琴老师。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>牛莱老师，欢迎您来到Master House哇！</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>现在还有房间吗？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>我可能要在房间里练练琴，需要一间隔音比较好的房间。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>明白，我们这里都是实体墙，隔音很棒咩。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>那就好，我担心影响到其他客人。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>另外，我不太喜欢有人说“对牛弹琴”这个词。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>好咩，我立马把这个词从Master House的空气里清理掉！</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>很好。你很有教养。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>非常抱歉咩，目前没有能够满足您要求的房间。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>没关系，那我先走了哞。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>好的，我正好再看一遍谱子。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>房间安排好了哞？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>谢谢。希望今晚能有一个安静的休止音符。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>没关系，曲谱有起承转合，我想，找到一个合适的房间也是这样。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>可以帮我准备一个谱架吗？曲子还需要修改，放在桌上看不太方便。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>好吧，那我先把曲子背下来。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>yak_开心</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>很好，高度正合适。你的服务很贴心哞。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>突然有学生约了课，请问有钢琴可以借用吗？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>仓库里有一架我奶奶留下的电子琴，但是电路老化了需要修理下。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>没关系，已经帮到我大忙了，我会耐心等待的。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>请问有咖啡吗？想喝现磨的哞。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>算了……可能今天你确实太忙了。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>嗯，还可以，谢谢你。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>这里很安静，适合把谱子再看一遍。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>下次休假，我也许还会来。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>老板，我在小众点评上看到了这家高分民宿，请问还有房间嘛？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>哇，您是idol兔米露吗，我超级喜欢你！</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>嗯，我是。不过，可以小点声嘛~</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>嗯嗯好的，我现在就查看房间!（小声）</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>我想要一间私密性比较好的房间，可以嘛？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>嗯嗯，我会尽量安排！这是您的房卡~</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>感谢你，我先去休息啦。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>非常抱歉咩，目前没有能够满足您要求的房间咩。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">	啊……没关系啦，我再去其他地方看看。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>您稍等下，我还在找合适的房间。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>好呀，我正好补一下妆。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>找到合适的房间了嘛？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>rabbit_平静</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>嗯嗯，我等你，希望不要等太久，我等会还有粉丝见面会要参加。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>老板，请问房间可以提供化妆镜嘛？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>嗯呐，我等你。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>rabbit_开心</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>谢谢老板，是我喜欢的样子呢，您真的很贴心（饭撒）~</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>房间的唱片机好像断触了，可以帮忙修理一下嘛？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>不好意思咩，现在有些忙碌，暂时没有办法满足偶像您的需求咩。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>路演完好累啊，请问这里提供咖啡嘛？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>好咩，我去为偶像制作咩~</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>没关系啦，你已经很努力了。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>嗯，其实还可以，谢谢你。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>太完美了，我会记住这里的。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>这里真不错呀，感觉可以好好充电。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>下次路过，我还会来的。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>你好，我是总裁——嘉嚎。你是，这儿的老板？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>是的，总裁，欢迎来到Master House~</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>这里，比我想象中……还要朴素呢。今天还有空房间吗？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>好的，稍等我来找找咩。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>帮我安排一个高级总裁套房吧。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>啊…...这，目前还不提供这种房型呢，普通房间可以吗？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>行吧，我勉强试试看。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>非常抱歉咩，目前没有合适房间咩。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>好吧，不过你们酒店的接待能力也该提升下了。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>找到了吗，小羊老板？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>谢谢，帮我把行李提上去吧。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>还在找，辛苦再等待下咩。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>可以，但不要让我等太久。我的时间很宝贵。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>呜，这床好硬，帮我换一张高级席梦思床吧。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>wolf_开心</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>嗯，这样才稍微像样，你的服务我很满意。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>这里的灯光不够稳定，影响我思考集团的重要决策。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>看来这里的服务标准，还有提升空间。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>嗯，勉强可以接受。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>还不错，比我预想的像样一些。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>很好，这才是我需要的效率。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>咖啡呢？我只喝现磨的。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>不要叫我挑剔，我只是标准比较清楚。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>我不要你觉得，我要我觉得</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>您好，我叫牛小顿，想要住宿。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>欢迎您来到Master House，我来看看还有没有空闲房间。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>我没有什么特殊需求，安静就好。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>已经帮您安排好了，这是房卡。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>谢谢。（四处张望）</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>好的，不过一旦有，请立马通知我哞。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>好的，等待过程中我顺便观察下民宿布局。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>找到合适的房间了哞？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>嗯嗯，那我先去放行李。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ox_平静</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>如果方便的话，房间里能加一张小桌子吗？我需要整理下线索。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>嗯嗯，我会等你的。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ox_开心</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>非常感谢，我相信用张桌子一定能更快理清线索。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>晚上台灯总是一闪一闪的，帮忙修一下好吗？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>整理线索好困，有咖啡提供吗？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>这里真不错啊哞。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>好的，我先去放行李。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>是我预期中的样子，谢谢你。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>我要一间明亮的房间！</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>明白，安排！</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>哇！是我想要的布置喵！！！</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2357,7 +2343,7 @@
         <v>133</v>
       </c>
       <c r="C6" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D6" t="s">
         <v>20</v>
@@ -2419,7 +2405,7 @@
         <v>173</v>
       </c>
       <c r="F10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2463,7 +2449,7 @@
         <v>40</v>
       </c>
       <c r="B15" t="s">
-        <v>172</v>
+        <v>215</v>
       </c>
       <c r="D15" t="s">
         <v>14</v>
@@ -2477,7 +2463,7 @@
         <v>42</v>
       </c>
       <c r="B16" t="s">
-        <v>172</v>
+        <v>215</v>
       </c>
       <c r="D16" t="s">
         <v>17</v>
@@ -2491,10 +2477,10 @@
         <v>30102</v>
       </c>
       <c r="B17" t="s">
-        <v>172</v>
+        <v>215</v>
       </c>
       <c r="C17" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D17" t="s">
         <v>20</v>
@@ -2508,7 +2494,7 @@
         <v>30101</v>
       </c>
       <c r="B18" t="s">
-        <v>172</v>
+        <v>215</v>
       </c>
       <c r="C18" t="s">
         <v>23</v>
@@ -2525,7 +2511,7 @@
         <v>43</v>
       </c>
       <c r="B19" t="s">
-        <v>172</v>
+        <v>215</v>
       </c>
       <c r="D19" t="s">
         <v>26</v>
@@ -2539,7 +2525,7 @@
         <v>44</v>
       </c>
       <c r="B20" t="s">
-        <v>172</v>
+        <v>215</v>
       </c>
       <c r="D20" t="s">
         <v>29</v>
@@ -2553,7 +2539,7 @@
         <v>40103</v>
       </c>
       <c r="B21" t="s">
-        <v>172</v>
+        <v>215</v>
       </c>
       <c r="D21" t="s">
         <v>32</v>
@@ -2567,7 +2553,7 @@
         <v>45</v>
       </c>
       <c r="B22" t="s">
-        <v>172</v>
+        <v>215</v>
       </c>
       <c r="D22" t="s">
         <v>34</v>
@@ -2581,7 +2567,7 @@
         <v>46</v>
       </c>
       <c r="B23" t="s">
-        <v>172</v>
+        <v>215</v>
       </c>
       <c r="D23" t="s">
         <v>37</v>
@@ -2592,7 +2578,7 @@
         <v>47</v>
       </c>
       <c r="B24" t="s">
-        <v>172</v>
+        <v>215</v>
       </c>
       <c r="D24" t="s">
         <v>37</v>
@@ -2603,7 +2589,7 @@
         <v>48</v>
       </c>
       <c r="B25" t="s">
-        <v>172</v>
+        <v>215</v>
       </c>
       <c r="D25" t="s">
         <v>37</v>
@@ -2614,10 +2600,10 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="7" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B27" t="s">
-        <v>218</v>
+        <v>172</v>
       </c>
       <c r="D27" t="s">
         <v>14</v>
@@ -2628,10 +2614,10 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="7" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B28" t="s">
-        <v>218</v>
+        <v>172</v>
       </c>
       <c r="D28" t="s">
         <v>17</v>
@@ -2645,10 +2631,10 @@
         <v>30202</v>
       </c>
       <c r="B29" t="s">
-        <v>218</v>
+        <v>172</v>
       </c>
       <c r="C29" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D29" t="s">
         <v>20</v>
@@ -2662,16 +2648,16 @@
         <v>30203</v>
       </c>
       <c r="B30" t="s">
-        <v>218</v>
+        <v>172</v>
       </c>
       <c r="C30" t="s">
         <v>22</v>
       </c>
       <c r="D30" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F30" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -2679,7 +2665,7 @@
         <v>30201</v>
       </c>
       <c r="B31" t="s">
-        <v>218</v>
+        <v>172</v>
       </c>
       <c r="C31" t="s">
         <v>23</v>
@@ -2693,10 +2679,10 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="7" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B32" t="s">
-        <v>218</v>
+        <v>172</v>
       </c>
       <c r="D32" t="s">
         <v>26</v>
@@ -2707,10 +2693,10 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="7" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B33" t="s">
-        <v>218</v>
+        <v>172</v>
       </c>
       <c r="D33" t="s">
         <v>29</v>
@@ -2721,10 +2707,10 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="7" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B34" t="s">
-        <v>218</v>
+        <v>172</v>
       </c>
       <c r="D34" t="s">
         <v>32</v>
@@ -2735,10 +2721,10 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="7" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B35" t="s">
-        <v>218</v>
+        <v>172</v>
       </c>
       <c r="D35" t="s">
         <v>173</v>
@@ -2749,10 +2735,10 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="7" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B36" t="s">
-        <v>218</v>
+        <v>172</v>
       </c>
       <c r="D36" t="s">
         <v>37</v>
@@ -2760,10 +2746,10 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="7" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B37" t="s">
-        <v>218</v>
+        <v>172</v>
       </c>
       <c r="D37" t="s">
         <v>37</v>
@@ -2771,10 +2757,10 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="7" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B38" t="s">
-        <v>218</v>
+        <v>172</v>
       </c>
       <c r="D38" t="s">
         <v>37</v>
@@ -2785,7 +2771,7 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="7" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B40" t="s">
         <v>54</v>
@@ -2799,7 +2785,7 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="7" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B41" t="s">
         <v>54</v>
@@ -2819,7 +2805,7 @@
         <v>54</v>
       </c>
       <c r="C42" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D42" t="s">
         <v>20</v>
@@ -2842,7 +2828,7 @@
         <v>20</v>
       </c>
       <c r="F43" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -2864,7 +2850,7 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="7" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B45" t="s">
         <v>54</v>
@@ -2878,7 +2864,7 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="7" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B46" t="s">
         <v>54</v>
@@ -2892,7 +2878,7 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="7" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B47" t="s">
         <v>54</v>
@@ -2906,7 +2892,7 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="7" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B48" t="s">
         <v>54</v>
@@ -2920,7 +2906,7 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="7" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B49" t="s">
         <v>54</v>
@@ -2931,7 +2917,7 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="7" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B50" t="s">
         <v>54</v>
@@ -2942,7 +2928,7 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="7" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B51" t="s">
         <v>54</v>
@@ -2956,7 +2942,7 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="7" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B53" t="s">
         <v>13</v>
@@ -2970,7 +2956,7 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="7" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B54" t="s">
         <v>13</v>
@@ -2990,7 +2976,7 @@
         <v>13</v>
       </c>
       <c r="C55" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D55" t="s">
         <v>20</v>
@@ -3013,7 +2999,7 @@
         <v>20</v>
       </c>
       <c r="F56" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -3035,7 +3021,7 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="7" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B58" t="s">
         <v>13</v>
@@ -3049,7 +3035,7 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="7" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B59" t="s">
         <v>13</v>
@@ -3063,7 +3049,7 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="7" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B60" t="s">
         <v>13</v>
@@ -3077,7 +3063,7 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="7" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B61" t="s">
         <v>13</v>
@@ -3091,7 +3077,7 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="7" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B62" t="s">
         <v>13</v>
@@ -3102,7 +3088,7 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="7" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B63" t="s">
         <v>13</v>
@@ -3113,7 +3099,7 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="7" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B64" t="s">
         <v>13</v>
@@ -3127,7 +3113,7 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="7" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B66" t="s">
         <v>49</v>
@@ -3141,7 +3127,7 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="7" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B67" t="s">
         <v>49</v>
@@ -3161,7 +3147,7 @@
         <v>49</v>
       </c>
       <c r="C68" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D68" t="s">
         <v>20</v>
@@ -3184,7 +3170,7 @@
         <v>20</v>
       </c>
       <c r="F69" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -3206,7 +3192,7 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="7" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B71" t="s">
         <v>49</v>
@@ -3220,13 +3206,13 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="7" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B72" t="s">
         <v>49</v>
       </c>
       <c r="D72" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F72" t="s">
         <v>30</v>
@@ -3234,7 +3220,7 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="7" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B73" t="s">
         <v>49</v>
@@ -3248,7 +3234,7 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="7" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B74" t="s">
         <v>49</v>
@@ -3262,7 +3248,7 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="7" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B75" t="s">
         <v>49</v>
@@ -3273,7 +3259,7 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="7" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B76" t="s">
         <v>49</v>
@@ -3284,7 +3270,7 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="7" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B77" t="s">
         <v>49</v>
@@ -3298,13 +3284,13 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="7" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B79" t="s">
         <v>52</v>
       </c>
       <c r="D79" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="F79" t="s">
         <v>15</v>
@@ -3312,7 +3298,7 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="7" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B80" t="s">
         <v>52</v>
@@ -3332,7 +3318,7 @@
         <v>52</v>
       </c>
       <c r="C81" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D81" t="s">
         <v>20</v>
@@ -3355,7 +3341,7 @@
         <v>20</v>
       </c>
       <c r="F82" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -3377,7 +3363,7 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="7" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B84" t="s">
         <v>52</v>
@@ -3391,7 +3377,7 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="7" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B85" t="s">
         <v>52</v>
@@ -3405,7 +3391,7 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="7" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B86" t="s">
         <v>52</v>
@@ -3419,7 +3405,7 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="7" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B87" t="s">
         <v>52</v>
@@ -3433,7 +3419,7 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="7" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B88" t="s">
         <v>52</v>
@@ -3444,7 +3430,7 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="7" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B89" t="s">
         <v>52</v>
@@ -3455,7 +3441,7 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="7" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B90" t="s">
         <v>52</v>
@@ -3505,7 +3491,7 @@
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.75" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="5.5" bestFit="1" customWidth="1"/>
@@ -3605,7 +3591,7 @@
     <row r="4" spans="1:10" s="13" customFormat="1" ht="16.5">
       <c r="A4" s="14"/>
       <c r="B4" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C4" s="15" t="s">
         <v>135</v>
@@ -3658,7 +3644,7 @@
     <row r="7" spans="1:10" s="13" customFormat="1" ht="16.5">
       <c r="A7" s="14"/>
       <c r="B7" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>135</v>
@@ -3711,7 +3697,7 @@
     <row r="9" spans="1:10" s="13" customFormat="1" ht="16.5">
       <c r="A9" s="14"/>
       <c r="B9" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>135</v>
@@ -3754,7 +3740,7 @@
         <v>73</v>
       </c>
       <c r="H10" s="17" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="I10" s="15"/>
     </row>
@@ -3797,7 +3783,7 @@
     <row r="13" spans="1:10" s="13" customFormat="1" ht="16.5">
       <c r="A13" s="14"/>
       <c r="B13" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>135</v>
@@ -3823,7 +3809,7 @@
     <row r="14" spans="1:10" s="13" customFormat="1" ht="16.5">
       <c r="A14" s="14"/>
       <c r="B14" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C14" s="15" t="s">
         <v>151</v>
@@ -3920,7 +3906,7 @@
     <row r="19" spans="1:10" s="13" customFormat="1" ht="16.5">
       <c r="A19" s="14"/>
       <c r="B19" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C19" s="15" t="s">
         <v>135</v>
@@ -3946,7 +3932,7 @@
     <row r="20" spans="1:10" s="13" customFormat="1" ht="16.5">
       <c r="A20" s="14"/>
       <c r="B20" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C20" s="15" t="s">
         <v>135</v>
@@ -4065,7 +4051,7 @@
     <row r="26" spans="1:10" s="13" customFormat="1" ht="16.5">
       <c r="A26" s="14"/>
       <c r="B26" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C26" s="15" t="s">
         <v>135</v>
@@ -4108,7 +4094,7 @@
         <v>73</v>
       </c>
       <c r="H27" s="17" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="I27" s="15"/>
     </row>
@@ -4209,7 +4195,7 @@
         <v>73</v>
       </c>
       <c r="H32" s="16" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="I32" s="15"/>
     </row>
@@ -4267,7 +4253,7 @@
     <row r="36" spans="1:10" s="13" customFormat="1" ht="16.5">
       <c r="A36" s="14"/>
       <c r="B36" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C36" s="15" t="s">
         <v>135</v>
@@ -4285,7 +4271,7 @@
         <v>73</v>
       </c>
       <c r="H36" s="27" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="I36" s="15"/>
     </row>
@@ -4370,7 +4356,7 @@
       </c>
       <c r="I41" s="10"/>
       <c r="J41" s="12" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="16.5">
@@ -4388,7 +4374,7 @@
     <row r="43" spans="1:10" s="13" customFormat="1" ht="16.5">
       <c r="A43" s="31"/>
       <c r="B43" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C43" s="15" t="s">
         <v>135</v>
@@ -4410,7 +4396,7 @@
     <row r="44" spans="1:10" s="13" customFormat="1" ht="16.5">
       <c r="A44" s="31"/>
       <c r="B44" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C44" s="15" t="s">
         <v>135</v>
@@ -4428,16 +4414,16 @@
         <v>145</v>
       </c>
       <c r="H44" s="16" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="45" spans="1:10" s="13" customFormat="1" ht="16.5">
       <c r="A45" s="31"/>
       <c r="B45" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D45" s="28">
         <v>2</v>
@@ -4452,10 +4438,10 @@
         <v>73</v>
       </c>
       <c r="H45" s="27" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="J45" s="34" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.5">
@@ -4495,7 +4481,7 @@
     <row r="48" spans="1:10" s="13" customFormat="1" ht="16.5">
       <c r="A48" s="31"/>
       <c r="B48" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C48" s="15" t="s">
         <v>135</v>
@@ -4517,7 +4503,7 @@
     <row r="49" spans="1:10" s="13" customFormat="1" ht="33">
       <c r="A49" s="31"/>
       <c r="B49" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C49" s="15" t="s">
         <v>135</v>
@@ -4535,7 +4521,7 @@
         <v>145</v>
       </c>
       <c r="H49" s="16" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="50" spans="1:10" s="13" customFormat="1" ht="16.5">
@@ -4555,7 +4541,7 @@
         <v>76</v>
       </c>
       <c r="H50" s="23" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="51" spans="1:10" s="13" customFormat="1" ht="16.5">
@@ -4570,7 +4556,7 @@
     <row r="52" spans="1:10" s="13" customFormat="1" ht="16.5">
       <c r="A52" s="31"/>
       <c r="B52" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C52" s="15" t="s">
         <v>135</v>
@@ -4583,13 +4569,13 @@
       </c>
       <c r="F52" s="18"/>
       <c r="G52" s="19" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H52" s="24" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="I52" s="13" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="53" spans="1:10" s="13" customFormat="1" ht="16.5">
@@ -4609,16 +4595,16 @@
         <v>145</v>
       </c>
       <c r="H53" s="16" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="54" spans="1:10" s="13" customFormat="1" ht="16.5">
       <c r="A54" s="14"/>
       <c r="B54" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C54" s="15" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D54" s="28">
         <v>2</v>
@@ -4633,7 +4619,7 @@
         <v>73</v>
       </c>
       <c r="H54" s="41" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="I54" s="15"/>
     </row>
@@ -4654,7 +4640,7 @@
         <v>156</v>
       </c>
       <c r="H55" s="23" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="I55" s="15"/>
     </row>
@@ -4721,7 +4707,7 @@
     <row r="60" spans="1:10" s="13" customFormat="1" ht="16.5">
       <c r="A60" s="31"/>
       <c r="B60" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C60" s="15" t="s">
         <v>135</v>
@@ -4734,7 +4720,7 @@
       </c>
       <c r="F60" s="18"/>
       <c r="G60" s="19" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H60" s="24" t="s">
         <v>154</v>
@@ -4743,7 +4729,7 @@
     <row r="61" spans="1:10" s="13" customFormat="1" ht="16.5">
       <c r="A61" s="31"/>
       <c r="B61" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C61" s="15" t="s">
         <v>135</v>
@@ -4767,7 +4753,7 @@
     <row r="62" spans="1:10" s="13" customFormat="1" ht="16.5">
       <c r="A62" s="31"/>
       <c r="B62" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C62" s="15" t="s">
         <v>135</v>
@@ -4788,7 +4774,7 @@
         <v>153</v>
       </c>
       <c r="J62" s="34" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.5">
@@ -4806,7 +4792,7 @@
     <row r="64" spans="1:10" s="13" customFormat="1" ht="16.5">
       <c r="A64" s="31"/>
       <c r="B64" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C64" s="15" t="s">
         <v>135</v>
@@ -4828,7 +4814,7 @@
     <row r="65" spans="1:10" s="13" customFormat="1" ht="16.5">
       <c r="A65" s="31"/>
       <c r="B65" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C65" s="15" t="s">
         <v>135</v>
@@ -4852,7 +4838,7 @@
     <row r="66" spans="1:10" s="13" customFormat="1" ht="16.5">
       <c r="A66" s="31"/>
       <c r="B66" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C66" s="15" t="s">
         <v>135</v>
@@ -4904,11 +4890,11 @@
         <v>73</v>
       </c>
       <c r="H68" s="11" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="I68" s="36"/>
       <c r="J68" s="37" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="69" spans="1:10">
@@ -4927,7 +4913,7 @@
         <v>70</v>
       </c>
       <c r="C70" s="35" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D70" s="30" t="s">
         <v>72</v>
@@ -4938,11 +4924,11 @@
         <v>73</v>
       </c>
       <c r="H70" s="11" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I70" s="36"/>
       <c r="J70" s="37" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="71" spans="1:10">
@@ -4961,7 +4947,7 @@
         <v>70</v>
       </c>
       <c r="C72" s="35" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D72" s="30" t="s">
         <v>72</v>
@@ -4972,11 +4958,11 @@
         <v>73</v>
       </c>
       <c r="H72" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I72" s="36"/>
       <c r="J72" s="37" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="73" spans="1:10">
@@ -4995,7 +4981,7 @@
         <v>70</v>
       </c>
       <c r="C74" s="35" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D74" s="30" t="s">
         <v>72</v>
@@ -5006,11 +4992,11 @@
         <v>73</v>
       </c>
       <c r="H74" s="11" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I74" s="36"/>
       <c r="J74" s="37" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="75" spans="1:10">
@@ -5029,7 +5015,7 @@
         <v>70</v>
       </c>
       <c r="C76" s="35" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D76" s="30" t="s">
         <v>72</v>
@@ -5040,11 +5026,11 @@
         <v>73</v>
       </c>
       <c r="H76" s="11" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I76" s="36"/>
       <c r="J76" s="37" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="77" spans="1:10">
@@ -5063,7 +5049,7 @@
         <v>70</v>
       </c>
       <c r="C78" s="35" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D78" s="30" t="s">
         <v>72</v>
@@ -5074,11 +5060,11 @@
         <v>73</v>
       </c>
       <c r="H78" s="11" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I78" s="36"/>
       <c r="J78" s="37" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="79" spans="1:10">
@@ -5097,7 +5083,7 @@
         <v>70</v>
       </c>
       <c r="C80" s="35" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D80" s="30" t="s">
         <v>72</v>
@@ -5108,11 +5094,11 @@
         <v>73</v>
       </c>
       <c r="H80" s="11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I80" s="36"/>
       <c r="J80" s="37" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="81" spans="1:10">
@@ -5149,7 +5135,7 @@
         <v>70</v>
       </c>
       <c r="C85" s="35" t="s">
-        <v>174</v>
+        <v>84</v>
       </c>
       <c r="D85" s="9">
         <v>1</v>
@@ -5160,17 +5146,17 @@
         <v>73</v>
       </c>
       <c r="H85" s="11" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="I85" s="10"/>
       <c r="J85" s="12" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.5">
       <c r="A86" s="14"/>
       <c r="B86" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C86" s="15" t="s">
         <v>135</v>
@@ -5184,7 +5170,7 @@
         <v>73</v>
       </c>
       <c r="H86" s="16" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="I86" s="15"/>
       <c r="J86" s="13"/>
@@ -5195,7 +5181,7 @@
         <v>70</v>
       </c>
       <c r="C87" s="15" t="s">
-        <v>174</v>
+        <v>84</v>
       </c>
       <c r="D87" s="14">
         <v>3</v>
@@ -5206,7 +5192,7 @@
         <v>73</v>
       </c>
       <c r="H87" s="17" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="I87" s="15"/>
       <c r="J87" s="13"/>
@@ -5226,7 +5212,7 @@
     <row r="89" spans="1:10" ht="16.5">
       <c r="A89" s="14"/>
       <c r="B89" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C89" s="15" t="s">
         <v>135</v>
@@ -5257,7 +5243,7 @@
         <v>70</v>
       </c>
       <c r="C90" s="15" t="s">
-        <v>174</v>
+        <v>84</v>
       </c>
       <c r="D90" s="14">
         <v>4</v>
@@ -5272,7 +5258,7 @@
         <v>73</v>
       </c>
       <c r="H90" s="17" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="I90" s="15"/>
       <c r="J90" s="13"/>
@@ -5280,7 +5266,7 @@
     <row r="91" spans="1:10" ht="16.5">
       <c r="A91" s="14"/>
       <c r="B91" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C91" s="15" t="s">
         <v>135</v>
@@ -5298,7 +5284,7 @@
         <v>73</v>
       </c>
       <c r="H91" s="17" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="I91" s="15"/>
       <c r="J91" s="13"/>
@@ -5309,7 +5295,7 @@
         <v>70</v>
       </c>
       <c r="C92" s="15" t="s">
-        <v>174</v>
+        <v>84</v>
       </c>
       <c r="D92" s="14">
         <v>4</v>
@@ -5324,7 +5310,7 @@
         <v>73</v>
       </c>
       <c r="H92" s="17" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="I92" s="15"/>
       <c r="J92" s="13"/>
@@ -5335,7 +5321,7 @@
         <v>70</v>
       </c>
       <c r="C93" s="15" t="s">
-        <v>174</v>
+        <v>84</v>
       </c>
       <c r="D93" s="21">
         <v>4</v>
@@ -5370,7 +5356,7 @@
     <row r="95" spans="1:10" ht="16.5">
       <c r="A95" s="14"/>
       <c r="B95" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C95" s="15" t="s">
         <v>135</v>
@@ -5399,7 +5385,7 @@
         <v>70</v>
       </c>
       <c r="C96" s="15" t="s">
-        <v>174</v>
+        <v>84</v>
       </c>
       <c r="D96" s="21">
         <v>4</v>
@@ -5422,7 +5408,7 @@
     <row r="97" spans="1:10" ht="16.5">
       <c r="A97" s="14"/>
       <c r="B97" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C97" s="15" t="s">
         <v>151</v>
@@ -5451,7 +5437,7 @@
         <v>70</v>
       </c>
       <c r="C98" s="15" t="s">
-        <v>189</v>
+        <v>265</v>
       </c>
       <c r="D98" s="14">
         <v>4</v>
@@ -5466,7 +5452,7 @@
         <v>73</v>
       </c>
       <c r="H98" s="16" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="I98" s="15"/>
       <c r="J98" s="13"/>
@@ -5489,7 +5475,7 @@
         <v>101</v>
       </c>
       <c r="C100" s="15" t="s">
-        <v>174</v>
+        <v>84</v>
       </c>
       <c r="D100" s="18">
         <v>4</v>
@@ -5515,7 +5501,7 @@
         <v>70</v>
       </c>
       <c r="C101" s="15" t="s">
-        <v>174</v>
+        <v>84</v>
       </c>
       <c r="D101" s="25">
         <v>4</v>
@@ -5541,7 +5527,7 @@
         <v>70</v>
       </c>
       <c r="C102" s="15" t="s">
-        <v>174</v>
+        <v>84</v>
       </c>
       <c r="D102" s="28">
         <v>4</v>
@@ -5556,7 +5542,7 @@
         <v>73</v>
       </c>
       <c r="H102" s="27" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I102" s="15"/>
       <c r="J102" s="13"/>
@@ -5581,7 +5567,7 @@
         <v>70</v>
       </c>
       <c r="C104" s="35" t="s">
-        <v>174</v>
+        <v>84</v>
       </c>
       <c r="D104" s="9">
         <v>1</v>
@@ -5596,7 +5582,7 @@
       </c>
       <c r="I104" s="10"/>
       <c r="J104" s="12" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="105" spans="1:10" ht="16.5">
@@ -5636,7 +5622,7 @@
     <row r="107" spans="1:10" ht="16.5">
       <c r="A107" s="14"/>
       <c r="B107" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C107" s="15" t="s">
         <v>135</v>
@@ -5665,7 +5651,7 @@
         <v>70</v>
       </c>
       <c r="C108" s="15" t="s">
-        <v>174</v>
+        <v>84</v>
       </c>
       <c r="D108" s="14">
         <v>2</v>
@@ -5680,7 +5666,7 @@
         <v>73</v>
       </c>
       <c r="H108" s="17" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="I108" s="15"/>
       <c r="J108" s="13"/>
@@ -5745,7 +5731,7 @@
         <v>70</v>
       </c>
       <c r="C112" s="15" t="s">
-        <v>174</v>
+        <v>84</v>
       </c>
       <c r="D112" s="14">
         <v>2</v>
@@ -5771,7 +5757,7 @@
         <v>70</v>
       </c>
       <c r="C113" s="15" t="s">
-        <v>174</v>
+        <v>84</v>
       </c>
       <c r="D113" s="14">
         <v>2</v>
@@ -5786,7 +5772,7 @@
         <v>73</v>
       </c>
       <c r="H113" s="16" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="I113" s="15"/>
       <c r="J113" s="13"/>
@@ -5848,7 +5834,7 @@
     <row r="117" spans="1:10" ht="16.5">
       <c r="A117" s="14"/>
       <c r="B117" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C117" s="15" t="s">
         <v>135</v>
@@ -5877,7 +5863,7 @@
         <v>70</v>
       </c>
       <c r="C118" s="15" t="s">
-        <v>174</v>
+        <v>84</v>
       </c>
       <c r="D118" s="28">
         <v>2</v>
@@ -5892,7 +5878,7 @@
         <v>73</v>
       </c>
       <c r="H118" s="27" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="I118" s="15"/>
       <c r="J118" s="13"/>
@@ -5929,7 +5915,7 @@
         <v>70</v>
       </c>
       <c r="C121" s="35" t="s">
-        <v>174</v>
+        <v>84</v>
       </c>
       <c r="D121" s="30">
         <v>1</v>
@@ -5944,7 +5930,7 @@
       </c>
       <c r="I121" s="10"/>
       <c r="J121" s="12" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="122" spans="1:10" ht="16.5">
@@ -5962,7 +5948,7 @@
     <row r="123" spans="1:10" ht="16.5">
       <c r="A123" s="31"/>
       <c r="B123" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C123" s="15" t="s">
         <v>135</v>
@@ -5986,7 +5972,7 @@
     <row r="124" spans="1:10" ht="16.5">
       <c r="A124" s="31"/>
       <c r="B124" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C124" s="15" t="s">
         <v>135</v>
@@ -6004,7 +5990,7 @@
         <v>145</v>
       </c>
       <c r="H124" s="16" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I124" s="13"/>
       <c r="J124" s="13"/>
@@ -6015,7 +6001,7 @@
         <v>70</v>
       </c>
       <c r="C125" s="15" t="s">
-        <v>174</v>
+        <v>84</v>
       </c>
       <c r="D125" s="28">
         <v>2</v>
@@ -6030,7 +6016,7 @@
         <v>73</v>
       </c>
       <c r="H125" s="27" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="I125" s="13"/>
       <c r="J125" s="13"/>
@@ -6072,7 +6058,7 @@
     <row r="128" spans="1:10" ht="16.5">
       <c r="A128" s="31"/>
       <c r="B128" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C128" s="15" t="s">
         <v>135</v>
@@ -6096,7 +6082,7 @@
     <row r="129" spans="1:10" ht="33">
       <c r="A129" s="31"/>
       <c r="B129" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C129" s="15" t="s">
         <v>135</v>
@@ -6114,7 +6100,7 @@
         <v>145</v>
       </c>
       <c r="H129" s="16" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="I129" s="13"/>
       <c r="J129" s="34"/>
@@ -6156,7 +6142,7 @@
     <row r="132" spans="1:10" ht="16.5">
       <c r="A132" s="31"/>
       <c r="B132" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C132" s="15" t="s">
         <v>135</v>
@@ -6169,23 +6155,23 @@
       </c>
       <c r="F132" s="18"/>
       <c r="G132" s="19" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H132" s="24" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="I132" s="13" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="J132" s="13"/>
     </row>
     <row r="133" spans="1:10" ht="16.5">
       <c r="A133" s="31"/>
       <c r="B133" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C133" s="15" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D133" s="31">
         <v>2</v>
@@ -6200,7 +6186,7 @@
         <v>145</v>
       </c>
       <c r="H133" s="16" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I133" s="13"/>
       <c r="J133" s="13"/>
@@ -6211,7 +6197,7 @@
         <v>70</v>
       </c>
       <c r="C134" s="15" t="s">
-        <v>190</v>
+        <v>270</v>
       </c>
       <c r="D134" s="28">
         <v>2</v>
@@ -6226,7 +6212,7 @@
         <v>73</v>
       </c>
       <c r="H134" s="41" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="I134" s="13"/>
       <c r="J134" s="13"/>
@@ -6248,7 +6234,7 @@
         <v>156</v>
       </c>
       <c r="H135" s="23" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="I135" s="13"/>
       <c r="J135" s="34"/>
@@ -6309,7 +6295,7 @@
         <v>70</v>
       </c>
       <c r="C140" s="35" t="s">
-        <v>174</v>
+        <v>84</v>
       </c>
       <c r="D140" s="30">
         <v>1</v>
@@ -6324,7 +6310,7 @@
       </c>
       <c r="I140" s="10"/>
       <c r="J140" s="12" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="141" spans="1:10" ht="16.5">
@@ -6342,7 +6328,7 @@
     <row r="142" spans="1:10" ht="16.5">
       <c r="A142" s="31"/>
       <c r="B142" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C142" s="15" t="s">
         <v>135</v>
@@ -6366,7 +6352,7 @@
     <row r="143" spans="1:10" ht="16.5">
       <c r="A143" s="31"/>
       <c r="B143" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C143" s="15" t="s">
         <v>135</v>
@@ -6392,7 +6378,7 @@
     <row r="144" spans="1:10" ht="16.5">
       <c r="A144" s="31"/>
       <c r="B144" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C144" s="15" t="s">
         <v>135</v>
@@ -6414,7 +6400,7 @@
       </c>
       <c r="I144" s="13"/>
       <c r="J144" s="34" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="145" spans="1:10" ht="16.5">
@@ -6432,7 +6418,7 @@
     <row r="146" spans="1:10" ht="16.5">
       <c r="A146" s="31"/>
       <c r="B146" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C146" s="15" t="s">
         <v>135</v>
@@ -6456,7 +6442,7 @@
     <row r="147" spans="1:10" ht="16.5">
       <c r="A147" s="31"/>
       <c r="B147" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C147" s="15" t="s">
         <v>135</v>
@@ -6482,7 +6468,7 @@
     <row r="148" spans="1:10" ht="16.5">
       <c r="A148" s="31"/>
       <c r="B148" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C148" s="15" t="s">
         <v>135</v>
@@ -6525,7 +6511,7 @@
         <v>70</v>
       </c>
       <c r="C150" s="35" t="s">
-        <v>189</v>
+        <v>265</v>
       </c>
       <c r="D150" s="30" t="s">
         <v>72</v>
@@ -6536,11 +6522,11 @@
         <v>73</v>
       </c>
       <c r="H150" s="11" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I150" s="36"/>
       <c r="J150" s="35" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="151" spans="1:10">
@@ -6558,7 +6544,7 @@
         <v>70</v>
       </c>
       <c r="C152" s="35" t="s">
-        <v>174</v>
+        <v>84</v>
       </c>
       <c r="D152" s="30" t="s">
         <v>72</v>
@@ -6569,11 +6555,11 @@
         <v>73</v>
       </c>
       <c r="H152" s="11" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="I152" s="36"/>
       <c r="J152" s="35" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="153" spans="1:10">
@@ -6591,7 +6577,7 @@
         <v>70</v>
       </c>
       <c r="C154" s="35" t="s">
-        <v>174</v>
+        <v>84</v>
       </c>
       <c r="D154" s="30" t="s">
         <v>72</v>
@@ -6602,11 +6588,11 @@
         <v>73</v>
       </c>
       <c r="H154" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I154" s="36"/>
       <c r="J154" s="35" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="155" spans="1:10">
@@ -6624,7 +6610,7 @@
         <v>70</v>
       </c>
       <c r="C156" s="35" t="s">
-        <v>190</v>
+        <v>270</v>
       </c>
       <c r="D156" s="30" t="s">
         <v>72</v>
@@ -6635,11 +6621,11 @@
         <v>73</v>
       </c>
       <c r="H156" s="11" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I156" s="36"/>
       <c r="J156" s="35" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="157" spans="1:10">
@@ -6657,7 +6643,7 @@
         <v>70</v>
       </c>
       <c r="C158" s="35" t="s">
-        <v>190</v>
+        <v>270</v>
       </c>
       <c r="D158" s="30" t="s">
         <v>72</v>
@@ -6668,11 +6654,11 @@
         <v>73</v>
       </c>
       <c r="H158" s="11" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="I158" s="36"/>
       <c r="J158" s="35" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="159" spans="1:10">
@@ -6690,7 +6676,7 @@
         <v>70</v>
       </c>
       <c r="C160" s="35" t="s">
-        <v>190</v>
+        <v>270</v>
       </c>
       <c r="D160" s="30" t="s">
         <v>72</v>
@@ -6701,11 +6687,11 @@
         <v>73</v>
       </c>
       <c r="H160" s="11" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="I160" s="36"/>
       <c r="J160" s="35" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="161" spans="1:10">
@@ -6723,7 +6709,7 @@
         <v>70</v>
       </c>
       <c r="C162" s="35" t="s">
-        <v>190</v>
+        <v>270</v>
       </c>
       <c r="D162" s="30" t="s">
         <v>72</v>
@@ -6734,11 +6720,11 @@
         <v>73</v>
       </c>
       <c r="H162" s="11" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="I162" s="36"/>
       <c r="J162" s="35" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="163" spans="1:10">
@@ -6775,7 +6761,7 @@
         <v>70</v>
       </c>
       <c r="C166" s="35" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D166" s="9">
         <v>1</v>
@@ -6786,11 +6772,11 @@
         <v>73</v>
       </c>
       <c r="H166" s="11" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="I166" s="10"/>
       <c r="J166" s="12" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="167" spans="1:10" ht="33">
@@ -6799,7 +6785,7 @@
         <v>70</v>
       </c>
       <c r="C167" s="13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D167" s="14">
         <v>2</v>
@@ -6810,7 +6796,7 @@
         <v>73</v>
       </c>
       <c r="H167" s="16" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="I167" s="15"/>
       <c r="J167" s="13"/>
@@ -6818,7 +6804,7 @@
     <row r="168" spans="1:10" ht="16.5">
       <c r="A168" s="14"/>
       <c r="B168" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C168" s="15" t="s">
         <v>135</v>
@@ -6832,7 +6818,7 @@
         <v>73</v>
       </c>
       <c r="H168" s="16" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="I168" s="15"/>
       <c r="J168" s="13"/>
@@ -6840,7 +6826,7 @@
     <row r="169" spans="1:10" ht="16.5">
       <c r="A169" s="14"/>
       <c r="B169" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C169" s="15" t="s">
         <v>135</v>
@@ -6854,7 +6840,7 @@
         <v>145</v>
       </c>
       <c r="H169" s="17" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="I169" s="15"/>
       <c r="J169" s="13"/>
@@ -6874,7 +6860,7 @@
     <row r="171" spans="1:10" ht="16.5">
       <c r="A171" s="14"/>
       <c r="B171" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C171" s="15" t="s">
         <v>135</v>
@@ -6905,7 +6891,7 @@
         <v>70</v>
       </c>
       <c r="C172" s="15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D172" s="14">
         <v>5</v>
@@ -6920,7 +6906,7 @@
         <v>73</v>
       </c>
       <c r="H172" s="16" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="I172" s="15"/>
       <c r="J172" s="13"/>
@@ -6928,7 +6914,7 @@
     <row r="173" spans="1:10" ht="16.5">
       <c r="A173" s="14"/>
       <c r="B173" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C173" s="15" t="s">
         <v>135</v>
@@ -6946,7 +6932,7 @@
         <v>73</v>
       </c>
       <c r="H173" s="17" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="I173" s="15"/>
       <c r="J173" s="13"/>
@@ -6957,7 +6943,7 @@
         <v>70</v>
       </c>
       <c r="C174" s="15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D174" s="14">
         <v>5</v>
@@ -6972,7 +6958,7 @@
         <v>73</v>
       </c>
       <c r="H174" s="17" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="I174" s="15"/>
       <c r="J174" s="13"/>
@@ -6983,7 +6969,7 @@
         <v>70</v>
       </c>
       <c r="C175" s="15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D175" s="21">
         <v>5</v>
@@ -7018,7 +7004,7 @@
     <row r="177" spans="1:10" ht="16.5">
       <c r="A177" s="14"/>
       <c r="B177" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C177" s="15" t="s">
         <v>135</v>
@@ -7047,7 +7033,7 @@
         <v>70</v>
       </c>
       <c r="C178" s="15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D178" s="21">
         <v>5</v>
@@ -7070,7 +7056,7 @@
     <row r="179" spans="1:10" ht="16.5">
       <c r="A179" s="14"/>
       <c r="B179" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C179" s="15" t="s">
         <v>151</v>
@@ -7088,7 +7074,7 @@
         <v>73</v>
       </c>
       <c r="H179" s="17" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="I179" s="15"/>
       <c r="J179" s="13"/>
@@ -7099,7 +7085,7 @@
         <v>70</v>
       </c>
       <c r="C180" s="15" t="s">
-        <v>268</v>
+        <v>430</v>
       </c>
       <c r="D180" s="14">
         <v>5</v>
@@ -7114,7 +7100,7 @@
         <v>73</v>
       </c>
       <c r="H180" s="16" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="I180" s="15"/>
       <c r="J180" s="13"/>
@@ -7137,10 +7123,10 @@
         <v>101</v>
       </c>
       <c r="C182" s="15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D182" s="18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E182" s="18">
         <v>3</v>
@@ -7163,7 +7149,7 @@
         <v>70</v>
       </c>
       <c r="C183" s="15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D183" s="14">
         <v>5</v>
@@ -7178,7 +7164,7 @@
         <v>73</v>
       </c>
       <c r="H183" s="27" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="I183" s="15"/>
       <c r="J183" s="13"/>
@@ -7189,7 +7175,7 @@
         <v>70</v>
       </c>
       <c r="C184" s="15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D184" s="14">
         <v>5</v>
@@ -7204,7 +7190,7 @@
         <v>73</v>
       </c>
       <c r="H184" s="27" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="I184" s="15"/>
       <c r="J184" s="13"/>
@@ -7229,7 +7215,7 @@
         <v>70</v>
       </c>
       <c r="C186" s="35" t="s">
-        <v>269</v>
+        <v>85</v>
       </c>
       <c r="D186" s="9">
         <v>1</v>
@@ -7244,7 +7230,7 @@
       </c>
       <c r="I186" s="10"/>
       <c r="J186" s="12" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="187" spans="1:10" ht="16.5">
@@ -7284,7 +7270,7 @@
     <row r="189" spans="1:10" ht="16.5">
       <c r="A189" s="14"/>
       <c r="B189" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C189" s="15" t="s">
         <v>135</v>
@@ -7313,7 +7299,7 @@
         <v>70</v>
       </c>
       <c r="C190" s="15" t="s">
-        <v>269</v>
+        <v>85</v>
       </c>
       <c r="D190" s="14">
         <v>2</v>
@@ -7328,7 +7314,7 @@
         <v>73</v>
       </c>
       <c r="H190" s="17" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="I190" s="15"/>
       <c r="J190" s="13"/>
@@ -7371,7 +7357,7 @@
         <v>70</v>
       </c>
       <c r="C193" s="15" t="s">
-        <v>269</v>
+        <v>85</v>
       </c>
       <c r="D193" s="14">
         <v>2</v>
@@ -7386,7 +7372,7 @@
         <v>145</v>
       </c>
       <c r="H193" s="16" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="I193" s="15"/>
       <c r="J193" s="13"/>
@@ -7397,7 +7383,7 @@
         <v>70</v>
       </c>
       <c r="C194" s="15" t="s">
-        <v>269</v>
+        <v>85</v>
       </c>
       <c r="D194" s="14">
         <v>2</v>
@@ -7412,7 +7398,7 @@
         <v>73</v>
       </c>
       <c r="H194" s="16" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="I194" s="15"/>
       <c r="J194" s="13"/>
@@ -7452,7 +7438,7 @@
     <row r="197" spans="1:10" ht="16.5">
       <c r="A197" s="14"/>
       <c r="B197" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C197" s="15" t="s">
         <v>135</v>
@@ -7481,7 +7467,7 @@
         <v>70</v>
       </c>
       <c r="C198" s="15" t="s">
-        <v>269</v>
+        <v>85</v>
       </c>
       <c r="D198" s="28">
         <v>2</v>
@@ -7496,7 +7482,7 @@
         <v>73</v>
       </c>
       <c r="H198" s="27" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="I198" s="15"/>
       <c r="J198" s="13"/>
@@ -7533,7 +7519,7 @@
         <v>70</v>
       </c>
       <c r="C201" s="35" t="s">
-        <v>269</v>
+        <v>85</v>
       </c>
       <c r="D201" s="30">
         <v>1</v>
@@ -7544,11 +7530,11 @@
         <v>73</v>
       </c>
       <c r="H201" s="11" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="I201" s="10"/>
       <c r="J201" s="12" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="202" spans="1:10" ht="16.5">
@@ -7566,7 +7552,7 @@
     <row r="203" spans="1:10" ht="16.5">
       <c r="A203" s="31"/>
       <c r="B203" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C203" s="15" t="s">
         <v>135</v>
@@ -7590,7 +7576,7 @@
     <row r="204" spans="1:10" ht="16.5">
       <c r="A204" s="31"/>
       <c r="B204" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C204" s="15" t="s">
         <v>135</v>
@@ -7608,7 +7594,7 @@
         <v>145</v>
       </c>
       <c r="H204" s="16" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I204" s="13"/>
       <c r="J204" s="13"/>
@@ -7616,7 +7602,7 @@
     <row r="205" spans="1:10" ht="16.5">
       <c r="A205" s="31"/>
       <c r="B205" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C205" s="15" t="s">
         <v>135</v>
@@ -7700,7 +7686,7 @@
     <row r="209" spans="1:10" ht="33">
       <c r="A209" s="31"/>
       <c r="B209" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C209" s="15" t="s">
         <v>135</v>
@@ -7718,7 +7704,7 @@
         <v>145</v>
       </c>
       <c r="H209" s="16" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="I209" s="13"/>
       <c r="J209" s="13"/>
@@ -7773,23 +7759,23 @@
       </c>
       <c r="F212" s="18"/>
       <c r="G212" s="19" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H212" s="24" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="I212" s="13" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="J212" s="13"/>
     </row>
     <row r="213" spans="1:10" ht="16.5">
       <c r="A213" s="31"/>
       <c r="B213" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C213" s="15" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D213" s="31">
         <v>2</v>
@@ -7804,7 +7790,7 @@
         <v>145</v>
       </c>
       <c r="H213" s="16" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I213" s="13"/>
       <c r="J213" s="13"/>
@@ -7815,7 +7801,7 @@
         <v>70</v>
       </c>
       <c r="C214" s="15" t="s">
-        <v>327</v>
+        <v>431</v>
       </c>
       <c r="D214" s="28">
         <v>2</v>
@@ -7830,7 +7816,7 @@
         <v>73</v>
       </c>
       <c r="H214" s="41" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="I214" s="13"/>
       <c r="J214" s="13"/>
@@ -7852,7 +7838,7 @@
         <v>156</v>
       </c>
       <c r="H215" s="23" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="I215" s="13"/>
       <c r="J215" s="13"/>
@@ -7889,7 +7875,7 @@
         <v>70</v>
       </c>
       <c r="C218" s="35" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D218" s="30">
         <v>1</v>
@@ -7904,7 +7890,7 @@
       </c>
       <c r="I218" s="10"/>
       <c r="J218" s="12" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="219" spans="1:10" ht="16.5">
@@ -7994,7 +7980,7 @@
       </c>
       <c r="I222" s="13"/>
       <c r="J222" s="34" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="223" spans="1:10" ht="16.5">
@@ -8054,7 +8040,7 @@
         <v>145</v>
       </c>
       <c r="H225" s="16" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="I225" s="13"/>
       <c r="J225" s="13"/>
@@ -8117,7 +8103,7 @@
         <v>70</v>
       </c>
       <c r="C229" s="35" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D229" s="30">
         <v>1</v>
@@ -8132,7 +8118,7 @@
       </c>
       <c r="I229" s="10"/>
       <c r="J229" s="12" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
     </row>
     <row r="230" spans="1:10" ht="16.5">
@@ -8174,7 +8160,7 @@
     <row r="232" spans="1:10" ht="16.5">
       <c r="A232" s="31"/>
       <c r="B232" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C232" s="15" t="s">
         <v>135</v>
@@ -8200,7 +8186,7 @@
     <row r="233" spans="1:10" ht="16.5">
       <c r="A233" s="31"/>
       <c r="B233" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C233" s="15" t="s">
         <v>135</v>
@@ -8222,7 +8208,7 @@
       </c>
       <c r="I233" s="13"/>
       <c r="J233" s="34" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="234" spans="1:10" ht="16.5">
@@ -8264,7 +8250,7 @@
     <row r="236" spans="1:10" ht="33">
       <c r="A236" s="31"/>
       <c r="B236" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C236" s="15" t="s">
         <v>135</v>
@@ -8282,7 +8268,7 @@
         <v>145</v>
       </c>
       <c r="H236" s="16" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="I236" s="13"/>
       <c r="J236" s="13"/>
@@ -8290,7 +8276,7 @@
     <row r="237" spans="1:10" ht="16.5">
       <c r="A237" s="31"/>
       <c r="B237" s="15" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C237" s="15" t="s">
         <v>135</v>
@@ -8345,7 +8331,7 @@
         <v>70</v>
       </c>
       <c r="C240" s="35" t="s">
-        <v>268</v>
+        <v>430</v>
       </c>
       <c r="D240" s="30" t="s">
         <v>72</v>
@@ -8356,11 +8342,11 @@
         <v>73</v>
       </c>
       <c r="H240" s="11" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="I240" s="36"/>
       <c r="J240" s="35" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="241" spans="1:10">
@@ -8378,7 +8364,7 @@
         <v>70</v>
       </c>
       <c r="C242" s="35" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D242" s="30" t="s">
         <v>72</v>
@@ -8389,11 +8375,11 @@
         <v>73</v>
       </c>
       <c r="H242" s="11" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="I242" s="36"/>
       <c r="J242" s="35" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="243" spans="1:10">
@@ -8411,7 +8397,7 @@
         <v>70</v>
       </c>
       <c r="C244" s="35" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D244" s="30" t="s">
         <v>72</v>
@@ -8422,11 +8408,11 @@
         <v>73</v>
       </c>
       <c r="H244" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I244" s="36"/>
       <c r="J244" s="35" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="245" spans="1:10">
@@ -8444,7 +8430,7 @@
         <v>70</v>
       </c>
       <c r="C246" s="35" t="s">
-        <v>274</v>
+        <v>431</v>
       </c>
       <c r="D246" s="30" t="s">
         <v>72</v>
@@ -8455,11 +8441,11 @@
         <v>73</v>
       </c>
       <c r="H246" s="11" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="I246" s="36"/>
       <c r="J246" s="35" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="247" spans="1:10">
@@ -8477,7 +8463,7 @@
         <v>70</v>
       </c>
       <c r="C248" s="35" t="s">
-        <v>274</v>
+        <v>431</v>
       </c>
       <c r="D248" s="30" t="s">
         <v>72</v>
@@ -8488,11 +8474,11 @@
         <v>73</v>
       </c>
       <c r="H248" s="11" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="I248" s="36"/>
       <c r="J248" s="35" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="249" spans="1:10">
@@ -8510,7 +8496,7 @@
         <v>70</v>
       </c>
       <c r="C250" s="35" t="s">
-        <v>274</v>
+        <v>431</v>
       </c>
       <c r="D250" s="30" t="s">
         <v>72</v>
@@ -8521,11 +8507,11 @@
         <v>73</v>
       </c>
       <c r="H250" s="11" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="I250" s="36"/>
       <c r="J250" s="35" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="251" spans="1:10">
@@ -8543,7 +8529,7 @@
         <v>70</v>
       </c>
       <c r="C252" s="35" t="s">
-        <v>274</v>
+        <v>431</v>
       </c>
       <c r="D252" s="30" t="s">
         <v>72</v>
@@ -8554,11 +8540,11 @@
         <v>73</v>
       </c>
       <c r="H252" s="11" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="I252" s="36"/>
       <c r="J252" s="35" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="253" spans="1:10">
@@ -8606,11 +8592,11 @@
         <v>73</v>
       </c>
       <c r="H256" s="11" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="I256" s="10"/>
       <c r="J256" s="12" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
     </row>
     <row r="257" spans="1:10" ht="16.5">
@@ -8630,7 +8616,7 @@
         <v>73</v>
       </c>
       <c r="H257" s="16" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="I257" s="15"/>
       <c r="J257" s="13"/>
@@ -8652,7 +8638,7 @@
         <v>73</v>
       </c>
       <c r="H258" s="17" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="I258" s="15"/>
       <c r="J258" s="13"/>
@@ -8718,7 +8704,7 @@
         <v>73</v>
       </c>
       <c r="H261" s="17" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="I261" s="15"/>
       <c r="J261" s="13"/>
@@ -8744,7 +8730,7 @@
         <v>73</v>
       </c>
       <c r="H262" s="17" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="I262" s="15"/>
       <c r="J262" s="13"/>
@@ -8770,7 +8756,7 @@
         <v>73</v>
       </c>
       <c r="H263" s="17" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="I263" s="15"/>
       <c r="J263" s="13"/>
@@ -8796,7 +8782,7 @@
         <v>73</v>
       </c>
       <c r="H264" s="17" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="I264" s="15"/>
       <c r="J264" s="13"/>
@@ -8822,7 +8808,7 @@
         <v>73</v>
       </c>
       <c r="H265" s="17" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="I265" s="15"/>
       <c r="J265" s="13"/>
@@ -8848,7 +8834,7 @@
         <v>73</v>
       </c>
       <c r="H266" s="14" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="I266" s="14"/>
       <c r="J266" s="14"/>
@@ -8964,7 +8950,7 @@
         <v>73</v>
       </c>
       <c r="H271" s="17" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="I271" s="15"/>
       <c r="J271" s="13"/>
@@ -8975,7 +8961,7 @@
         <v>70</v>
       </c>
       <c r="C272" s="15" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="D272" s="14">
         <v>4</v>
@@ -8990,7 +8976,7 @@
         <v>73</v>
       </c>
       <c r="H272" s="16" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="I272" s="15"/>
       <c r="J272" s="13"/>
@@ -9080,7 +9066,7 @@
         <v>73</v>
       </c>
       <c r="H276" s="27" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="I276" s="15"/>
       <c r="J276" s="13"/>
@@ -9116,11 +9102,11 @@
         <v>73</v>
       </c>
       <c r="H278" s="11" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="I278" s="10"/>
       <c r="J278" s="12" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
     </row>
     <row r="279" spans="1:10" ht="16.5">
@@ -9204,7 +9190,7 @@
         <v>73</v>
       </c>
       <c r="H282" s="17" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="I282" s="15"/>
       <c r="J282" s="13"/>
@@ -9288,7 +9274,7 @@
         <v>73</v>
       </c>
       <c r="H286" s="16" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="I286" s="15"/>
       <c r="J286" s="13"/>
@@ -9372,7 +9358,7 @@
         <v>73</v>
       </c>
       <c r="H290" s="27" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="I290" s="15"/>
       <c r="J290" s="13"/>
@@ -9420,11 +9406,11 @@
         <v>73</v>
       </c>
       <c r="H293" s="11" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="I293" s="10"/>
       <c r="J293" s="12" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="294" spans="1:10" ht="21">
@@ -9496,7 +9482,7 @@
         <v>145</v>
       </c>
       <c r="H297" s="16" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I297" s="13"/>
       <c r="J297" s="13"/>
@@ -9606,7 +9592,7 @@
         <v>145</v>
       </c>
       <c r="H302" s="16" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="I302" s="13"/>
       <c r="J302" s="13"/>
@@ -9632,7 +9618,7 @@
         <v>145</v>
       </c>
       <c r="H303" s="16" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="I303" s="13"/>
       <c r="J303" s="13"/>
@@ -9687,13 +9673,13 @@
       </c>
       <c r="F306" s="18"/>
       <c r="G306" s="19" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H306" s="24" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="I306" s="13" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="J306" s="13"/>
     </row>
@@ -9703,7 +9689,7 @@
         <v>101</v>
       </c>
       <c r="C307" s="15" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D307" s="31">
         <v>2</v>
@@ -9718,7 +9704,7 @@
         <v>145</v>
       </c>
       <c r="H307" s="16" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I307" s="13"/>
       <c r="J307" s="13"/>
@@ -9729,7 +9715,7 @@
         <v>70</v>
       </c>
       <c r="C308" s="15" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="D308" s="28">
         <v>2</v>
@@ -9744,7 +9730,7 @@
         <v>73</v>
       </c>
       <c r="H308" s="41" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="I308" s="13"/>
       <c r="J308" s="13"/>
@@ -9766,7 +9752,7 @@
         <v>156</v>
       </c>
       <c r="H309" s="23" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="I309" s="13"/>
       <c r="J309" s="13"/>
@@ -9814,11 +9800,11 @@
         <v>73</v>
       </c>
       <c r="H312" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="I312" s="10"/>
       <c r="J312" s="12" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="313" spans="1:10" ht="16.5">
@@ -9878,7 +9864,7 @@
         <v>145</v>
       </c>
       <c r="H315" s="16" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="I315" s="13"/>
       <c r="J315" s="13"/>
@@ -9904,7 +9890,7 @@
         <v>145</v>
       </c>
       <c r="H316" s="16" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="I316" s="13"/>
       <c r="J316" s="13"/>
@@ -9934,7 +9920,7 @@
       </c>
       <c r="I317" s="13"/>
       <c r="J317" s="34" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="318" spans="1:10" ht="16.5">
@@ -9994,7 +9980,7 @@
         <v>145</v>
       </c>
       <c r="H320" s="16" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="I320" s="13"/>
       <c r="J320" s="13"/>
@@ -10068,11 +10054,11 @@
         <v>73</v>
       </c>
       <c r="H324" s="11" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="I324" s="10"/>
       <c r="J324" s="12" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="325" spans="1:10" ht="16.5">
@@ -10162,7 +10148,7 @@
       </c>
       <c r="I328" s="13"/>
       <c r="J328" s="34" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="329" spans="1:10" ht="16.5">
@@ -10222,7 +10208,7 @@
         <v>145</v>
       </c>
       <c r="H331" s="16" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="I331" s="13"/>
       <c r="J331" s="13"/>
@@ -10297,7 +10283,7 @@
         <v>70</v>
       </c>
       <c r="C336" s="35" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="D336" s="30" t="s">
         <v>72</v>
@@ -10308,11 +10294,11 @@
         <v>73</v>
       </c>
       <c r="H336" s="11" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="I336" s="36"/>
       <c r="J336" s="35" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="337" spans="1:10">
@@ -10341,11 +10327,11 @@
         <v>73</v>
       </c>
       <c r="H338" s="11" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="I338" s="36"/>
       <c r="J338" s="35" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="339" spans="1:10">
@@ -10374,11 +10360,11 @@
         <v>73</v>
       </c>
       <c r="H340" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I340" s="36"/>
       <c r="J340" s="35" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="341" spans="1:10">
@@ -10396,7 +10382,7 @@
         <v>70</v>
       </c>
       <c r="C342" s="35" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="D342" s="30" t="s">
         <v>72</v>
@@ -10407,11 +10393,11 @@
         <v>73</v>
       </c>
       <c r="H342" s="11" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I342" s="36"/>
       <c r="J342" s="35" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="343" spans="1:10">
@@ -10429,7 +10415,7 @@
         <v>70</v>
       </c>
       <c r="C344" s="35" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="D344" s="30" t="s">
         <v>72</v>
@@ -10440,11 +10426,11 @@
         <v>73</v>
       </c>
       <c r="H344" s="11" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="I344" s="36"/>
       <c r="J344" s="35" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="345" spans="1:10">
@@ -10462,7 +10448,7 @@
         <v>70</v>
       </c>
       <c r="C346" s="35" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="D346" s="30" t="s">
         <v>72</v>
@@ -10473,11 +10459,11 @@
         <v>73</v>
       </c>
       <c r="H346" s="11" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I346" s="36"/>
       <c r="J346" s="35" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="347" spans="1:10">
@@ -10495,7 +10481,7 @@
         <v>70</v>
       </c>
       <c r="C348" s="35" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="D348" s="30" t="s">
         <v>72</v>
@@ -10506,11 +10492,11 @@
         <v>73</v>
       </c>
       <c r="H348" s="11" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="I348" s="36"/>
       <c r="J348" s="35" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="349" spans="1:10">
@@ -10563,11 +10549,11 @@
         <v>73</v>
       </c>
       <c r="H352" s="58" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="I352" s="56"/>
       <c r="J352" s="59" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
     </row>
     <row r="353" spans="1:10" ht="16.5">
@@ -10587,7 +10573,7 @@
         <v>73</v>
       </c>
       <c r="H353" s="61" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="I353" s="60"/>
       <c r="J353" s="62"/>
@@ -10609,7 +10595,7 @@
         <v>73</v>
       </c>
       <c r="H354" s="61" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="I354" s="60"/>
       <c r="J354" s="62"/>
@@ -10631,7 +10617,7 @@
         <v>73</v>
       </c>
       <c r="H355" s="62" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="I355" s="60"/>
       <c r="J355" s="62"/>
@@ -10697,7 +10683,7 @@
         <v>73</v>
       </c>
       <c r="H358" s="62" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="I358" s="60"/>
       <c r="J358" s="62"/>
@@ -10723,7 +10709,7 @@
         <v>73</v>
       </c>
       <c r="H359" s="62" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="I359" s="60"/>
       <c r="J359" s="62"/>
@@ -10749,7 +10735,7 @@
         <v>73</v>
       </c>
       <c r="H360" s="62" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="I360" s="60"/>
       <c r="J360" s="62"/>
@@ -10865,7 +10851,7 @@
         <v>73</v>
       </c>
       <c r="H365" s="62" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="I365" s="60"/>
       <c r="J365" s="62"/>
@@ -10876,7 +10862,7 @@
         <v>70</v>
       </c>
       <c r="C366" s="60" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="D366" s="60">
         <v>5</v>
@@ -10891,7 +10877,7 @@
         <v>73</v>
       </c>
       <c r="H366" s="61" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I366" s="60"/>
       <c r="J366" s="62"/>
@@ -10955,7 +10941,7 @@
         <v>73</v>
       </c>
       <c r="H369" s="68" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="I369" s="60"/>
       <c r="J369" s="62"/>
@@ -10981,7 +10967,7 @@
         <v>73</v>
       </c>
       <c r="H370" s="68" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="I370" s="60"/>
       <c r="J370" s="62"/>
@@ -11017,11 +11003,11 @@
         <v>73</v>
       </c>
       <c r="H372" s="58" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="I372" s="56"/>
       <c r="J372" s="59" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="373" spans="1:10" ht="16.5">
@@ -11105,7 +11091,7 @@
         <v>73</v>
       </c>
       <c r="H376" s="62" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="I376" s="60"/>
       <c r="J376" s="62"/>
@@ -11189,7 +11175,7 @@
         <v>73</v>
       </c>
       <c r="H380" s="61" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="I380" s="60"/>
       <c r="J380" s="62"/>
@@ -11258,7 +11244,7 @@
         <v>70</v>
       </c>
       <c r="C384" s="60" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="D384" s="69">
         <v>2</v>
@@ -11273,7 +11259,7 @@
         <v>73</v>
       </c>
       <c r="H384" s="68" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="I384" s="60"/>
       <c r="J384" s="62"/>
@@ -11321,11 +11307,11 @@
         <v>73</v>
       </c>
       <c r="H387" s="58" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="I387" s="56"/>
       <c r="J387" s="59" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="388" spans="1:10" ht="16.5">
@@ -11385,7 +11371,7 @@
         <v>145</v>
       </c>
       <c r="H390" s="61" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I390" s="62"/>
       <c r="J390" s="62"/>
@@ -11411,7 +11397,7 @@
         <v>73</v>
       </c>
       <c r="H391" s="68" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="I391" s="62"/>
       <c r="J391" s="70"/>
@@ -11495,7 +11481,7 @@
         <v>145</v>
       </c>
       <c r="H395" s="61" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="I395" s="62"/>
       <c r="J395" s="62"/>
@@ -11550,13 +11536,13 @@
       </c>
       <c r="F398" s="63"/>
       <c r="G398" s="63" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H398" s="66" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="I398" s="62" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="J398" s="62"/>
     </row>
@@ -11566,7 +11552,7 @@
         <v>101</v>
       </c>
       <c r="C399" s="60" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D399" s="62">
         <v>2</v>
@@ -11581,7 +11567,7 @@
         <v>145</v>
       </c>
       <c r="H399" s="61" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I399" s="62"/>
       <c r="J399" s="62"/>
@@ -11592,7 +11578,7 @@
         <v>70</v>
       </c>
       <c r="C400" s="60" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="D400" s="69">
         <v>2</v>
@@ -11607,7 +11593,7 @@
         <v>73</v>
       </c>
       <c r="H400" s="73" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="I400" s="62"/>
       <c r="J400" s="62"/>
@@ -11629,7 +11615,7 @@
         <v>156</v>
       </c>
       <c r="H401" s="65" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="I401" s="62"/>
       <c r="J401" s="62"/>
@@ -11677,11 +11663,11 @@
         <v>73</v>
       </c>
       <c r="H404" s="58" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="I404" s="56"/>
       <c r="J404" s="59" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="405" spans="1:10" ht="16.5">
@@ -11771,7 +11757,7 @@
       </c>
       <c r="I408" s="62"/>
       <c r="J408" s="70" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="409" spans="1:10" ht="16.5">
@@ -11831,7 +11817,7 @@
         <v>145</v>
       </c>
       <c r="H411" s="61" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="I411" s="62"/>
       <c r="J411" s="62"/>
@@ -11893,11 +11879,11 @@
         <v>73</v>
       </c>
       <c r="H414" s="58" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="I414" s="56"/>
       <c r="J414" s="59" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="415" spans="1:10" ht="16.5">
@@ -11957,7 +11943,7 @@
         <v>145</v>
       </c>
       <c r="H417" s="61" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="I417" s="62"/>
       <c r="J417" s="62"/>
@@ -11987,7 +11973,7 @@
       </c>
       <c r="I418" s="62"/>
       <c r="J418" s="70" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="419" spans="1:10" ht="16.5">
@@ -12047,7 +12033,7 @@
         <v>145</v>
       </c>
       <c r="H421" s="61" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="I421" s="62"/>
       <c r="J421" s="62"/>
@@ -12110,7 +12096,7 @@
         <v>70</v>
       </c>
       <c r="C425" s="57" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="D425" s="57" t="s">
         <v>72</v>
@@ -12121,11 +12107,11 @@
         <v>73</v>
       </c>
       <c r="H425" s="58" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="I425" s="74"/>
       <c r="J425" s="57" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="426" spans="1:10">
@@ -12159,11 +12145,11 @@
         <v>73</v>
       </c>
       <c r="H427" s="58" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="I427" s="74"/>
       <c r="J427" s="57" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="428" spans="1:10">
@@ -12197,11 +12183,11 @@
         <v>73</v>
       </c>
       <c r="H429" s="58" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I429" s="74"/>
       <c r="J429" s="57" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="430" spans="1:10">
@@ -12224,7 +12210,7 @@
         <v>70</v>
       </c>
       <c r="C431" s="57" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D431" s="57" t="s">
         <v>72</v>
@@ -12235,11 +12221,11 @@
         <v>73</v>
       </c>
       <c r="H431" s="58" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="I431" s="74"/>
       <c r="J431" s="57" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="432" spans="1:10">
@@ -12262,7 +12248,7 @@
         <v>70</v>
       </c>
       <c r="C433" s="57" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D433" s="57" t="s">
         <v>72</v>
@@ -12273,11 +12259,11 @@
         <v>73</v>
       </c>
       <c r="H433" s="58" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="I433" s="74"/>
       <c r="J433" s="57" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="434" spans="1:10">
@@ -12300,7 +12286,7 @@
         <v>70</v>
       </c>
       <c r="C435" s="57" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D435" s="57" t="s">
         <v>72</v>
@@ -12311,11 +12297,11 @@
         <v>73</v>
       </c>
       <c r="H435" s="58" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I435" s="74"/>
       <c r="J435" s="57" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="436" spans="1:10">
@@ -12338,7 +12324,7 @@
         <v>70</v>
       </c>
       <c r="C437" s="57" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D437" s="57" t="s">
         <v>72</v>
@@ -12349,11 +12335,11 @@
         <v>73</v>
       </c>
       <c r="H437" s="58" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="I437" s="74"/>
       <c r="J437" s="57" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="438" spans="1:10">
@@ -12406,11 +12392,11 @@
         <v>73</v>
       </c>
       <c r="H441" s="11" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="I441" s="10"/>
       <c r="J441" s="12" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="442" spans="1:10" ht="16.5">
@@ -12430,7 +12416,7 @@
         <v>73</v>
       </c>
       <c r="H442" s="16" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="I442" s="15"/>
       <c r="J442" s="13"/>
@@ -12452,7 +12438,7 @@
         <v>73</v>
       </c>
       <c r="H443" s="17" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="I443" s="15"/>
       <c r="J443" s="13"/>
@@ -12474,7 +12460,7 @@
         <v>73</v>
       </c>
       <c r="H444" s="17" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="I444" s="15"/>
       <c r="J444" s="13"/>
@@ -12512,7 +12498,7 @@
         <v>135</v>
       </c>
       <c r="D447" s="18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E447" s="18">
         <v>1</v>
@@ -12540,7 +12526,7 @@
         <v>83</v>
       </c>
       <c r="D448" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E448" s="14">
         <v>1</v>
@@ -12552,7 +12538,7 @@
         <v>73</v>
       </c>
       <c r="H448" s="17" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="I448" s="15"/>
       <c r="J448" s="13"/>
@@ -12566,7 +12552,7 @@
         <v>135</v>
       </c>
       <c r="D449" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E449" s="14">
         <v>1</v>
@@ -12578,7 +12564,7 @@
         <v>73</v>
       </c>
       <c r="H449" s="17" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="I449" s="15"/>
       <c r="J449" s="13"/>
@@ -12592,7 +12578,7 @@
         <v>83</v>
       </c>
       <c r="D450" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E450" s="14">
         <v>1</v>
@@ -12604,7 +12590,7 @@
         <v>73</v>
       </c>
       <c r="H450" s="17" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="I450" s="15"/>
       <c r="J450" s="13"/>
@@ -12618,7 +12604,7 @@
         <v>83</v>
       </c>
       <c r="D451" s="21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E451" s="21">
         <v>1</v>
@@ -12656,7 +12642,7 @@
         <v>135</v>
       </c>
       <c r="D453" s="18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E453" s="18">
         <v>2</v>
@@ -12682,7 +12668,7 @@
         <v>83</v>
       </c>
       <c r="D454" s="21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E454" s="21">
         <v>2</v>
@@ -12708,7 +12694,7 @@
         <v>151</v>
       </c>
       <c r="D455" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E455" s="14">
         <v>2</v>
@@ -12720,7 +12706,7 @@
         <v>73</v>
       </c>
       <c r="H455" s="17" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="I455" s="15"/>
       <c r="J455" s="13"/>
@@ -12731,10 +12717,10 @@
         <v>70</v>
       </c>
       <c r="C456" s="15" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="D456" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E456" s="14">
         <v>2</v>
@@ -12746,7 +12732,7 @@
         <v>73</v>
       </c>
       <c r="H456" s="16" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="I456" s="15"/>
       <c r="J456" s="13"/>
@@ -12772,7 +12758,7 @@
         <v>83</v>
       </c>
       <c r="D458" s="18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E458" s="18">
         <v>3</v>
@@ -12798,7 +12784,7 @@
         <v>83</v>
       </c>
       <c r="D459" s="25">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E459" s="25">
         <v>3</v>
@@ -12824,7 +12810,7 @@
         <v>83</v>
       </c>
       <c r="D460" s="28">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E460" s="28">
         <v>3</v>
@@ -12836,7 +12822,7 @@
         <v>73</v>
       </c>
       <c r="H460" s="27" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I460" s="15"/>
       <c r="J460" s="13"/>
@@ -12872,11 +12858,11 @@
         <v>73</v>
       </c>
       <c r="H462" s="11" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="I462" s="10"/>
       <c r="J462" s="12" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="463" spans="1:10" ht="16.5">
@@ -12960,7 +12946,7 @@
         <v>73</v>
       </c>
       <c r="H466" s="17" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="I466" s="15"/>
       <c r="J466" s="13"/>
@@ -13018,7 +13004,7 @@
         <v>145</v>
       </c>
       <c r="H469" s="17" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="I469" s="15"/>
       <c r="J469" s="13"/>
@@ -13044,7 +13030,7 @@
         <v>73</v>
       </c>
       <c r="H470" s="16" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="I470" s="15"/>
       <c r="J470" s="13"/>
@@ -13102,7 +13088,7 @@
         <v>73</v>
       </c>
       <c r="H473" s="27" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="I473" s="15"/>
       <c r="J473" s="13"/>
@@ -13128,7 +13114,7 @@
         <v>73</v>
       </c>
       <c r="H474" s="75" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="I474" s="15"/>
       <c r="J474" s="13"/>
@@ -13176,11 +13162,11 @@
         <v>73</v>
       </c>
       <c r="H477" s="11" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="I477" s="10"/>
       <c r="J477" s="12" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="478" spans="1:10" ht="16.5">
@@ -13240,7 +13226,7 @@
         <v>145</v>
       </c>
       <c r="H480" s="16" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I480" s="13"/>
       <c r="J480" s="13"/>
@@ -13266,7 +13252,7 @@
         <v>73</v>
       </c>
       <c r="H481" s="75" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="I481" s="13"/>
       <c r="J481" s="34"/>
@@ -13350,7 +13336,7 @@
         <v>145</v>
       </c>
       <c r="H485" s="16" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="I485" s="13"/>
       <c r="J485" s="13"/>
@@ -13405,13 +13391,13 @@
       </c>
       <c r="F488" s="18"/>
       <c r="G488" s="19" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H488" s="24" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="I488" s="13" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="J488" s="13"/>
     </row>
@@ -13421,7 +13407,7 @@
         <v>101</v>
       </c>
       <c r="C489" s="15" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D489" s="31">
         <v>2</v>
@@ -13436,7 +13422,7 @@
         <v>145</v>
       </c>
       <c r="H489" s="16" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I489" s="13"/>
       <c r="J489" s="13"/>
@@ -13447,7 +13433,7 @@
         <v>70</v>
       </c>
       <c r="C490" s="15" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="D490" s="28">
         <v>2</v>
@@ -13462,7 +13448,7 @@
         <v>73</v>
       </c>
       <c r="H490" s="41" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="I490" s="13"/>
       <c r="J490" s="13"/>
@@ -13484,7 +13470,7 @@
         <v>156</v>
       </c>
       <c r="H491" s="23" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="I491" s="13"/>
       <c r="J491" s="13"/>
@@ -13532,11 +13518,11 @@
         <v>73</v>
       </c>
       <c r="H494" s="11" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="I494" s="10"/>
       <c r="J494" s="12" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="495" spans="1:10" ht="16.5">
@@ -13626,7 +13612,7 @@
       </c>
       <c r="I498" s="13"/>
       <c r="J498" s="34" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="499" spans="1:10" ht="16.5">
@@ -13686,7 +13672,7 @@
         <v>145</v>
       </c>
       <c r="H501" s="16" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="I501" s="13"/>
       <c r="J501" s="13"/>
@@ -13774,7 +13760,7 @@
       <c r="H506" s="11"/>
       <c r="I506" s="10"/>
       <c r="J506" s="12" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="507" spans="1:10" ht="16.5">
@@ -13864,7 +13850,7 @@
       </c>
       <c r="I510" s="13"/>
       <c r="J510" s="34" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="511" spans="1:10" ht="16.5">
@@ -13924,7 +13910,7 @@
         <v>145</v>
       </c>
       <c r="H513" s="16" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="I513" s="13"/>
       <c r="J513" s="13"/>
@@ -13950,7 +13936,7 @@
         <v>156</v>
       </c>
       <c r="H514" s="23" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="I514" s="13"/>
       <c r="J514" s="13"/>
@@ -13975,7 +13961,7 @@
         <v>70</v>
       </c>
       <c r="C516" s="35" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="D516" s="30" t="s">
         <v>72</v>
@@ -13986,11 +13972,11 @@
         <v>73</v>
       </c>
       <c r="H516" s="11" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="I516" s="36"/>
       <c r="J516" s="35" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="517" spans="1:10">
@@ -14019,11 +14005,11 @@
         <v>73</v>
       </c>
       <c r="H518" s="11" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="I518" s="36"/>
       <c r="J518" s="35" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="519" spans="1:10">
@@ -14052,11 +14038,11 @@
         <v>73</v>
       </c>
       <c r="H520" s="11" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="I520" s="36"/>
       <c r="J520" s="35" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="521" spans="1:10">
@@ -14074,7 +14060,7 @@
         <v>70</v>
       </c>
       <c r="C522" s="35" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D522" s="30" t="s">
         <v>72</v>
@@ -14085,11 +14071,11 @@
         <v>73</v>
       </c>
       <c r="H522" s="11" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="I522" s="36"/>
       <c r="J522" s="35" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="523" spans="1:10">
@@ -14107,7 +14093,7 @@
         <v>70</v>
       </c>
       <c r="C524" s="35" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D524" s="30" t="s">
         <v>72</v>
@@ -14118,11 +14104,11 @@
         <v>73</v>
       </c>
       <c r="H524" s="11" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="I524" s="36"/>
       <c r="J524" s="35" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="525" spans="1:10">
@@ -14140,7 +14126,7 @@
         <v>70</v>
       </c>
       <c r="C526" s="35" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D526" s="30" t="s">
         <v>72</v>
@@ -14151,11 +14137,11 @@
         <v>73</v>
       </c>
       <c r="H526" s="11" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="I526" s="36"/>
       <c r="J526" s="35" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="527" spans="1:10">
@@ -14173,7 +14159,7 @@
         <v>70</v>
       </c>
       <c r="C528" s="35" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D528" s="30" t="s">
         <v>72</v>
@@ -14184,11 +14170,11 @@
         <v>73</v>
       </c>
       <c r="H528" s="11" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="I528" s="36"/>
       <c r="J528" s="35" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="529" spans="1:10">
@@ -14235,11 +14221,11 @@
         <v>73</v>
       </c>
       <c r="H532" s="11" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="I532" s="10"/>
       <c r="J532" s="12" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="533" spans="1:10" ht="33">
@@ -14259,7 +14245,7 @@
         <v>73</v>
       </c>
       <c r="H533" s="16" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="I533" s="15"/>
       <c r="J533" s="13"/>
@@ -14337,7 +14323,7 @@
         <v>73</v>
       </c>
       <c r="H537" s="17" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="I537" s="15"/>
       <c r="J537" s="13"/>
@@ -14363,7 +14349,7 @@
         <v>73</v>
       </c>
       <c r="H538" s="17" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="I538" s="15"/>
       <c r="J538" s="13"/>
@@ -14389,7 +14375,7 @@
         <v>73</v>
       </c>
       <c r="H539" s="17" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="I539" s="15"/>
       <c r="J539" s="13"/>
@@ -14516,7 +14502,7 @@
         <v>70</v>
       </c>
       <c r="C545" s="15" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="D545" s="14">
         <v>3</v>
@@ -14531,7 +14517,7 @@
         <v>73</v>
       </c>
       <c r="H545" s="16" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="I545" s="15"/>
       <c r="J545" s="13"/>
@@ -14621,7 +14607,7 @@
         <v>73</v>
       </c>
       <c r="H549" s="27" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="I549" s="15"/>
       <c r="J549" s="13"/>
@@ -14657,11 +14643,11 @@
         <v>73</v>
       </c>
       <c r="H551" s="11" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="I551" s="10"/>
       <c r="J551" s="12" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="552" spans="1:10" ht="16.5">
@@ -14745,7 +14731,7 @@
         <v>73</v>
       </c>
       <c r="H555" s="17" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="I555" s="15"/>
       <c r="J555" s="13"/>
@@ -14829,7 +14815,7 @@
         <v>73</v>
       </c>
       <c r="H559" s="16" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="I559" s="15"/>
       <c r="J559" s="13"/>
@@ -14913,7 +14899,7 @@
         <v>73</v>
       </c>
       <c r="H563" s="27" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="I563" s="15"/>
       <c r="J563" s="13"/>
@@ -14950,7 +14936,7 @@
         <v>70</v>
       </c>
       <c r="C566" s="35" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="D566" s="30">
         <v>1</v>
@@ -14961,11 +14947,11 @@
         <v>73</v>
       </c>
       <c r="H566" s="11" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="I566" s="10"/>
       <c r="J566" s="12" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="567" spans="1:10" ht="16.5">
@@ -15025,7 +15011,7 @@
         <v>145</v>
       </c>
       <c r="H569" s="16" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I569" s="13"/>
       <c r="J569" s="13"/>
@@ -15036,7 +15022,7 @@
         <v>70</v>
       </c>
       <c r="C570" s="15" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="D570" s="28">
         <v>2</v>
@@ -15051,7 +15037,7 @@
         <v>73</v>
       </c>
       <c r="H570" s="27" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="I570" s="13"/>
       <c r="J570" s="34"/>
@@ -15135,7 +15121,7 @@
         <v>145</v>
       </c>
       <c r="H574" s="16" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="I574" s="13"/>
       <c r="J574" s="13"/>
@@ -15190,13 +15176,13 @@
       </c>
       <c r="F577" s="18"/>
       <c r="G577" s="19" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H577" s="24" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="I577" s="13" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="J577" s="13"/>
     </row>
@@ -15206,7 +15192,7 @@
         <v>101</v>
       </c>
       <c r="C578" s="15" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D578" s="31">
         <v>2</v>
@@ -15221,7 +15207,7 @@
         <v>145</v>
       </c>
       <c r="H578" s="16" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I578" s="13"/>
       <c r="J578" s="13"/>
@@ -15232,7 +15218,7 @@
         <v>70</v>
       </c>
       <c r="C579" s="15" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="D579" s="28">
         <v>2</v>
@@ -15247,7 +15233,7 @@
         <v>73</v>
       </c>
       <c r="H579" s="41" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="I579" s="13"/>
       <c r="J579" s="13"/>
@@ -15269,7 +15255,7 @@
         <v>156</v>
       </c>
       <c r="H580" s="23" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="I580" s="13"/>
       <c r="J580" s="13"/>
@@ -15317,11 +15303,11 @@
         <v>73</v>
       </c>
       <c r="H583" s="11" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="I583" s="10"/>
       <c r="J583" s="12" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="584" spans="1:10" ht="16.5">
@@ -15411,7 +15397,7 @@
       </c>
       <c r="I587" s="13"/>
       <c r="J587" s="34" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="588" spans="1:10" ht="16.5">
@@ -15471,7 +15457,7 @@
         <v>145</v>
       </c>
       <c r="H590" s="16" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="I590" s="13"/>
       <c r="J590" s="13"/>
@@ -15557,11 +15543,11 @@
         <v>73</v>
       </c>
       <c r="H595" s="11" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="I595" s="10"/>
       <c r="J595" s="12" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="596" spans="1:10" ht="16.5">
@@ -15651,7 +15637,7 @@
       </c>
       <c r="I599" s="13"/>
       <c r="J599" s="34" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="600" spans="1:10" ht="16.5">
@@ -15711,7 +15697,7 @@
         <v>145</v>
       </c>
       <c r="H602" s="16" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="I602" s="13"/>
       <c r="J602" s="13"/>
@@ -15774,7 +15760,7 @@
         <v>70</v>
       </c>
       <c r="C606" s="35" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="D606" s="30" t="s">
         <v>72</v>
@@ -15785,11 +15771,11 @@
         <v>73</v>
       </c>
       <c r="H606" s="11" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I606" s="36"/>
       <c r="J606" s="35" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="607" spans="1:10">
@@ -15818,11 +15804,11 @@
         <v>73</v>
       </c>
       <c r="H608" s="11" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I608" s="36"/>
       <c r="J608" s="35" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="609" spans="1:10">
@@ -15851,11 +15837,11 @@
         <v>73</v>
       </c>
       <c r="H610" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I610" s="36"/>
       <c r="J610" s="35" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="611" spans="1:10">
@@ -15873,7 +15859,7 @@
         <v>70</v>
       </c>
       <c r="C612" s="35" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="D612" s="30" t="s">
         <v>72</v>
@@ -15884,11 +15870,11 @@
         <v>73</v>
       </c>
       <c r="H612" s="11" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I612" s="36"/>
       <c r="J612" s="35" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="613" spans="1:10">
@@ -15906,7 +15892,7 @@
         <v>70</v>
       </c>
       <c r="C614" s="35" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="D614" s="30" t="s">
         <v>72</v>
@@ -15917,11 +15903,11 @@
         <v>73</v>
       </c>
       <c r="H614" s="11" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="I614" s="36"/>
       <c r="J614" s="35" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="615" spans="1:10">
@@ -15939,7 +15925,7 @@
         <v>70</v>
       </c>
       <c r="C616" s="35" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="D616" s="30" t="s">
         <v>72</v>
@@ -15950,11 +15936,11 @@
         <v>73</v>
       </c>
       <c r="H616" s="11" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I616" s="36"/>
       <c r="J616" s="35" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="617" spans="1:10">
@@ -15972,7 +15958,7 @@
         <v>70</v>
       </c>
       <c r="C618" s="35" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="D618" s="30" t="s">
         <v>72</v>
@@ -15983,11 +15969,11 @@
         <v>73</v>
       </c>
       <c r="H618" s="11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I618" s="36"/>
       <c r="J618" s="35" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/对话表.xlsx
+++ b/Excel/对话表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xinxinhe\Documents\2026MasterHouse\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE999EAE-5991-4E9E-9095-A62E8360E4CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B72B0908-FE57-43F7-AF42-4266A30B6C86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="对话组" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2141" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2141" uniqueCount="431">
   <si>
     <t>对话组ID</t>
   </si>
@@ -499,10 +499,6 @@
   </si>
   <si>
     <t>猫猫-电路1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>现在有点忙，晚点帮您看。</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -2343,7 +2339,7 @@
         <v>133</v>
       </c>
       <c r="C6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D6" t="s">
         <v>20</v>
@@ -2402,10 +2398,10 @@
         <v>133</v>
       </c>
       <c r="D10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2449,7 +2445,7 @@
         <v>40</v>
       </c>
       <c r="B15" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D15" t="s">
         <v>14</v>
@@ -2463,7 +2459,7 @@
         <v>42</v>
       </c>
       <c r="B16" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D16" t="s">
         <v>17</v>
@@ -2477,10 +2473,10 @@
         <v>30102</v>
       </c>
       <c r="B17" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C17" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D17" t="s">
         <v>20</v>
@@ -2494,7 +2490,7 @@
         <v>30101</v>
       </c>
       <c r="B18" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C18" t="s">
         <v>23</v>
@@ -2511,7 +2507,7 @@
         <v>43</v>
       </c>
       <c r="B19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D19" t="s">
         <v>26</v>
@@ -2525,7 +2521,7 @@
         <v>44</v>
       </c>
       <c r="B20" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D20" t="s">
         <v>29</v>
@@ -2539,7 +2535,7 @@
         <v>40103</v>
       </c>
       <c r="B21" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D21" t="s">
         <v>32</v>
@@ -2553,7 +2549,7 @@
         <v>45</v>
       </c>
       <c r="B22" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D22" t="s">
         <v>34</v>
@@ -2567,7 +2563,7 @@
         <v>46</v>
       </c>
       <c r="B23" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D23" t="s">
         <v>37</v>
@@ -2578,7 +2574,7 @@
         <v>47</v>
       </c>
       <c r="B24" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D24" t="s">
         <v>37</v>
@@ -2589,7 +2585,7 @@
         <v>48</v>
       </c>
       <c r="B25" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D25" t="s">
         <v>37</v>
@@ -2600,10 +2596,10 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="7" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B27" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D27" t="s">
         <v>14</v>
@@ -2614,10 +2610,10 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B28" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D28" t="s">
         <v>17</v>
@@ -2631,10 +2627,10 @@
         <v>30202</v>
       </c>
       <c r="B29" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C29" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D29" t="s">
         <v>20</v>
@@ -2648,16 +2644,16 @@
         <v>30203</v>
       </c>
       <c r="B30" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C30" t="s">
         <v>22</v>
       </c>
       <c r="D30" t="s">
+        <v>216</v>
+      </c>
+      <c r="F30" t="s">
         <v>217</v>
-      </c>
-      <c r="F30" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -2665,7 +2661,7 @@
         <v>30201</v>
       </c>
       <c r="B31" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C31" t="s">
         <v>23</v>
@@ -2679,10 +2675,10 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="7" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B32" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D32" t="s">
         <v>26</v>
@@ -2693,10 +2689,10 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B33" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D33" t="s">
         <v>29</v>
@@ -2707,10 +2703,10 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B34" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D34" t="s">
         <v>32</v>
@@ -2721,13 +2717,13 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="7" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B35" t="s">
+        <v>171</v>
+      </c>
+      <c r="D35" t="s">
         <v>172</v>
-      </c>
-      <c r="D35" t="s">
-        <v>173</v>
       </c>
       <c r="F35" t="s">
         <v>35</v>
@@ -2735,10 +2731,10 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B36" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D36" t="s">
         <v>37</v>
@@ -2746,10 +2742,10 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="7" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B37" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D37" t="s">
         <v>37</v>
@@ -2757,10 +2753,10 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B38" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D38" t="s">
         <v>37</v>
@@ -2771,7 +2767,7 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B40" t="s">
         <v>54</v>
@@ -2785,7 +2781,7 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B41" t="s">
         <v>54</v>
@@ -2805,7 +2801,7 @@
         <v>54</v>
       </c>
       <c r="C42" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D42" t="s">
         <v>20</v>
@@ -2828,7 +2824,7 @@
         <v>20</v>
       </c>
       <c r="F43" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -2850,7 +2846,7 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B45" t="s">
         <v>54</v>
@@ -2864,7 +2860,7 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B46" t="s">
         <v>54</v>
@@ -2878,7 +2874,7 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B47" t="s">
         <v>54</v>
@@ -2892,7 +2888,7 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B48" t="s">
         <v>54</v>
@@ -2906,7 +2902,7 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B49" t="s">
         <v>54</v>
@@ -2917,7 +2913,7 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="7" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B50" t="s">
         <v>54</v>
@@ -2928,7 +2924,7 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B51" t="s">
         <v>54</v>
@@ -2942,7 +2938,7 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B53" t="s">
         <v>13</v>
@@ -2956,7 +2952,7 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="7" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B54" t="s">
         <v>13</v>
@@ -2976,7 +2972,7 @@
         <v>13</v>
       </c>
       <c r="C55" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D55" t="s">
         <v>20</v>
@@ -2999,7 +2995,7 @@
         <v>20</v>
       </c>
       <c r="F56" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -3021,7 +3017,7 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="7" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B58" t="s">
         <v>13</v>
@@ -3035,7 +3031,7 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B59" t="s">
         <v>13</v>
@@ -3049,7 +3045,7 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B60" t="s">
         <v>13</v>
@@ -3063,7 +3059,7 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B61" t="s">
         <v>13</v>
@@ -3077,7 +3073,7 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B62" t="s">
         <v>13</v>
@@ -3088,7 +3084,7 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="7" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B63" t="s">
         <v>13</v>
@@ -3099,7 +3095,7 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="7" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B64" t="s">
         <v>13</v>
@@ -3113,7 +3109,7 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B66" t="s">
         <v>49</v>
@@ -3127,7 +3123,7 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B67" t="s">
         <v>49</v>
@@ -3147,7 +3143,7 @@
         <v>49</v>
       </c>
       <c r="C68" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D68" t="s">
         <v>20</v>
@@ -3170,7 +3166,7 @@
         <v>20</v>
       </c>
       <c r="F69" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -3192,7 +3188,7 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="7" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B71" t="s">
         <v>49</v>
@@ -3206,13 +3202,13 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B72" t="s">
         <v>49</v>
       </c>
       <c r="D72" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F72" t="s">
         <v>30</v>
@@ -3220,7 +3216,7 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B73" t="s">
         <v>49</v>
@@ -3234,7 +3230,7 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B74" t="s">
         <v>49</v>
@@ -3248,7 +3244,7 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B75" t="s">
         <v>49</v>
@@ -3259,7 +3255,7 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B76" t="s">
         <v>49</v>
@@ -3270,7 +3266,7 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B77" t="s">
         <v>49</v>
@@ -3284,13 +3280,13 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B79" t="s">
         <v>52</v>
       </c>
       <c r="D79" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F79" t="s">
         <v>15</v>
@@ -3298,7 +3294,7 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="7" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B80" t="s">
         <v>52</v>
@@ -3318,7 +3314,7 @@
         <v>52</v>
       </c>
       <c r="C81" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D81" t="s">
         <v>20</v>
@@ -3341,7 +3337,7 @@
         <v>20</v>
       </c>
       <c r="F82" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -3363,7 +3359,7 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="7" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B84" t="s">
         <v>52</v>
@@ -3377,7 +3373,7 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B85" t="s">
         <v>52</v>
@@ -3391,7 +3387,7 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B86" t="s">
         <v>52</v>
@@ -3405,7 +3401,7 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B87" t="s">
         <v>52</v>
@@ -3419,7 +3415,7 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="7" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B88" t="s">
         <v>52</v>
@@ -3430,7 +3426,7 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B89" t="s">
         <v>52</v>
@@ -3441,7 +3437,7 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B90" t="s">
         <v>52</v>
@@ -3581,7 +3577,7 @@
         <v>73</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I3" s="10"/>
       <c r="J3" s="12" t="s">
@@ -3591,7 +3587,7 @@
     <row r="4" spans="1:10" s="13" customFormat="1" ht="16.5">
       <c r="A4" s="14"/>
       <c r="B4" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C4" s="15" t="s">
         <v>135</v>
@@ -3626,7 +3622,7 @@
         <v>73</v>
       </c>
       <c r="H5" s="17" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I5" s="15"/>
     </row>
@@ -3644,7 +3640,7 @@
     <row r="7" spans="1:10" s="13" customFormat="1" ht="16.5">
       <c r="A7" s="14"/>
       <c r="B7" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>135</v>
@@ -3697,7 +3693,7 @@
     <row r="9" spans="1:10" s="13" customFormat="1" ht="16.5">
       <c r="A9" s="14"/>
       <c r="B9" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>135</v>
@@ -3715,7 +3711,7 @@
         <v>73</v>
       </c>
       <c r="H9" s="17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I9" s="15"/>
     </row>
@@ -3740,7 +3736,7 @@
         <v>73</v>
       </c>
       <c r="H10" s="17" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="I10" s="15"/>
     </row>
@@ -3783,7 +3779,7 @@
     <row r="13" spans="1:10" s="13" customFormat="1" ht="16.5">
       <c r="A13" s="14"/>
       <c r="B13" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>135</v>
@@ -3809,10 +3805,10 @@
     <row r="14" spans="1:10" s="13" customFormat="1" ht="16.5">
       <c r="A14" s="14"/>
       <c r="B14" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D14" s="14">
         <v>4</v>
@@ -3827,7 +3823,7 @@
         <v>73</v>
       </c>
       <c r="H14" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I14" s="15"/>
     </row>
@@ -3837,7 +3833,7 @@
         <v>70</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D15" s="14">
         <v>4</v>
@@ -3906,7 +3902,7 @@
     <row r="19" spans="1:10" s="13" customFormat="1" ht="16.5">
       <c r="A19" s="14"/>
       <c r="B19" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C19" s="15" t="s">
         <v>135</v>
@@ -3932,7 +3928,7 @@
     <row r="20" spans="1:10" s="13" customFormat="1" ht="16.5">
       <c r="A20" s="14"/>
       <c r="B20" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C20" s="15" t="s">
         <v>135</v>
@@ -3950,7 +3946,7 @@
         <v>73</v>
       </c>
       <c r="H20" s="27" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I20" s="15"/>
     </row>
@@ -3975,7 +3971,7 @@
         <v>73</v>
       </c>
       <c r="H21" s="27" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I21" s="15"/>
     </row>
@@ -4009,11 +4005,11 @@
         <v>73</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I23" s="10"/>
       <c r="J23" s="12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="24" spans="1:10" s="13" customFormat="1" ht="16.5">
@@ -4042,7 +4038,7 @@
         <v>74</v>
       </c>
       <c r="H25" s="24" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I25" s="19" t="s">
         <v>75</v>
@@ -4051,7 +4047,7 @@
     <row r="26" spans="1:10" s="13" customFormat="1" ht="16.5">
       <c r="A26" s="14"/>
       <c r="B26" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C26" s="15" t="s">
         <v>135</v>
@@ -4069,7 +4065,7 @@
         <v>73</v>
       </c>
       <c r="H26" s="16" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I26" s="15"/>
     </row>
@@ -4094,7 +4090,7 @@
         <v>73</v>
       </c>
       <c r="H27" s="17" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I27" s="15"/>
     </row>
@@ -4170,7 +4166,7 @@
         <v>145</v>
       </c>
       <c r="H31" s="16" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I31" s="15"/>
     </row>
@@ -4195,7 +4191,7 @@
         <v>73</v>
       </c>
       <c r="H32" s="16" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I32" s="15"/>
     </row>
@@ -4246,14 +4242,14 @@
         <v>74</v>
       </c>
       <c r="H35" s="24" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I35" s="15"/>
     </row>
     <row r="36" spans="1:10" s="13" customFormat="1" ht="16.5">
       <c r="A36" s="14"/>
       <c r="B36" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C36" s="15" t="s">
         <v>135</v>
@@ -4271,7 +4267,7 @@
         <v>73</v>
       </c>
       <c r="H36" s="27" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I36" s="15"/>
     </row>
@@ -4296,7 +4292,7 @@
         <v>73</v>
       </c>
       <c r="H37" s="27" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I37" s="15"/>
     </row>
@@ -4356,7 +4352,7 @@
       </c>
       <c r="I41" s="10"/>
       <c r="J41" s="12" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="16.5">
@@ -4374,7 +4370,7 @@
     <row r="43" spans="1:10" s="13" customFormat="1" ht="16.5">
       <c r="A43" s="31"/>
       <c r="B43" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C43" s="15" t="s">
         <v>135</v>
@@ -4390,13 +4386,13 @@
         <v>74</v>
       </c>
       <c r="H43" s="24" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="44" spans="1:10" s="13" customFormat="1" ht="16.5">
       <c r="A44" s="31"/>
       <c r="B44" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C44" s="15" t="s">
         <v>135</v>
@@ -4414,34 +4410,34 @@
         <v>145</v>
       </c>
       <c r="H44" s="16" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="45" spans="1:10" s="13" customFormat="1" ht="16.5">
       <c r="A45" s="31"/>
       <c r="B45" s="15" t="s">
+        <v>298</v>
+      </c>
+      <c r="C45" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="D45" s="28">
+        <v>2</v>
+      </c>
+      <c r="E45" s="31">
+        <v>1</v>
+      </c>
+      <c r="F45" s="28">
+        <v>2</v>
+      </c>
+      <c r="G45" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="H45" s="27" t="s">
         <v>299</v>
       </c>
-      <c r="C45" s="15" t="s">
-        <v>208</v>
-      </c>
-      <c r="D45" s="28">
-        <v>2</v>
-      </c>
-      <c r="E45" s="31">
-        <v>1</v>
-      </c>
-      <c r="F45" s="28">
-        <v>2</v>
-      </c>
-      <c r="G45" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="H45" s="27" t="s">
-        <v>300</v>
-      </c>
       <c r="J45" s="34" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.5">
@@ -4481,7 +4477,7 @@
     <row r="48" spans="1:10" s="13" customFormat="1" ht="16.5">
       <c r="A48" s="31"/>
       <c r="B48" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C48" s="15" t="s">
         <v>135</v>
@@ -4497,13 +4493,13 @@
         <v>74</v>
       </c>
       <c r="H48" s="24" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="49" spans="1:10" s="13" customFormat="1" ht="33">
       <c r="A49" s="31"/>
       <c r="B49" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C49" s="15" t="s">
         <v>135</v>
@@ -4521,7 +4517,7 @@
         <v>145</v>
       </c>
       <c r="H49" s="16" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="50" spans="1:10" s="13" customFormat="1" ht="16.5">
@@ -4541,7 +4537,7 @@
         <v>76</v>
       </c>
       <c r="H50" s="23" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="51" spans="1:10" s="13" customFormat="1" ht="16.5">
@@ -4556,7 +4552,7 @@
     <row r="52" spans="1:10" s="13" customFormat="1" ht="16.5">
       <c r="A52" s="31"/>
       <c r="B52" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C52" s="15" t="s">
         <v>135</v>
@@ -4569,13 +4565,13 @@
       </c>
       <c r="F52" s="18"/>
       <c r="G52" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="H52" s="24" t="s">
         <v>210</v>
       </c>
-      <c r="H52" s="24" t="s">
-        <v>211</v>
-      </c>
       <c r="I52" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="53" spans="1:10" s="13" customFormat="1" ht="16.5">
@@ -4595,16 +4591,16 @@
         <v>145</v>
       </c>
       <c r="H53" s="16" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="54" spans="1:10" s="13" customFormat="1" ht="16.5">
       <c r="A54" s="14"/>
       <c r="B54" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C54" s="15" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D54" s="28">
         <v>2</v>
@@ -4619,7 +4615,7 @@
         <v>73</v>
       </c>
       <c r="H54" s="41" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I54" s="15"/>
     </row>
@@ -4637,10 +4633,10 @@
         <v>3</v>
       </c>
       <c r="G55" s="33" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H55" s="23" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I55" s="15"/>
     </row>
@@ -4707,7 +4703,7 @@
     <row r="60" spans="1:10" s="13" customFormat="1" ht="16.5">
       <c r="A60" s="31"/>
       <c r="B60" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C60" s="15" t="s">
         <v>135</v>
@@ -4720,16 +4716,16 @@
       </c>
       <c r="F60" s="18"/>
       <c r="G60" s="19" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H60" s="24" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="61" spans="1:10" s="13" customFormat="1" ht="16.5">
       <c r="A61" s="31"/>
       <c r="B61" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C61" s="15" t="s">
         <v>135</v>
@@ -4747,13 +4743,13 @@
         <v>145</v>
       </c>
       <c r="H61" s="16" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="62" spans="1:10" s="13" customFormat="1" ht="16.5">
       <c r="A62" s="31"/>
       <c r="B62" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C62" s="15" t="s">
         <v>135</v>
@@ -4771,10 +4767,10 @@
         <v>76</v>
       </c>
       <c r="H62" s="23" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J62" s="34" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.5">
@@ -4792,7 +4788,7 @@
     <row r="64" spans="1:10" s="13" customFormat="1" ht="16.5">
       <c r="A64" s="31"/>
       <c r="B64" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C64" s="15" t="s">
         <v>135</v>
@@ -4808,13 +4804,13 @@
         <v>74</v>
       </c>
       <c r="H64" s="24" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" s="13" customFormat="1" ht="16.5">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" s="13" customFormat="1" ht="33">
       <c r="A65" s="31"/>
       <c r="B65" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C65" s="15" t="s">
         <v>135</v>
@@ -4832,13 +4828,13 @@
         <v>145</v>
       </c>
       <c r="H65" s="16" t="s">
-        <v>150</v>
+        <v>300</v>
       </c>
     </row>
     <row r="66" spans="1:10" s="13" customFormat="1" ht="16.5">
       <c r="A66" s="31"/>
       <c r="B66" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C66" s="15" t="s">
         <v>135</v>
@@ -4853,7 +4849,7 @@
         <v>2</v>
       </c>
       <c r="G66" s="33" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H66" s="23" t="s">
         <v>78</v>
@@ -4879,7 +4875,7 @@
         <v>70</v>
       </c>
       <c r="C68" s="35" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D68" s="30" t="s">
         <v>72</v>
@@ -4890,11 +4886,11 @@
         <v>73</v>
       </c>
       <c r="H68" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I68" s="36"/>
       <c r="J68" s="37" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="69" spans="1:10">
@@ -4913,7 +4909,7 @@
         <v>70</v>
       </c>
       <c r="C70" s="35" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D70" s="30" t="s">
         <v>72</v>
@@ -4924,11 +4920,11 @@
         <v>73</v>
       </c>
       <c r="H70" s="11" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I70" s="36"/>
       <c r="J70" s="37" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="71" spans="1:10">
@@ -4947,7 +4943,7 @@
         <v>70</v>
       </c>
       <c r="C72" s="35" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D72" s="30" t="s">
         <v>72</v>
@@ -4958,11 +4954,11 @@
         <v>73</v>
       </c>
       <c r="H72" s="11" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I72" s="36"/>
       <c r="J72" s="37" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="73" spans="1:10">
@@ -4981,7 +4977,7 @@
         <v>70</v>
       </c>
       <c r="C74" s="35" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D74" s="30" t="s">
         <v>72</v>
@@ -4992,11 +4988,11 @@
         <v>73</v>
       </c>
       <c r="H74" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I74" s="36"/>
       <c r="J74" s="37" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="75" spans="1:10">
@@ -5015,7 +5011,7 @@
         <v>70</v>
       </c>
       <c r="C76" s="35" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D76" s="30" t="s">
         <v>72</v>
@@ -5026,11 +5022,11 @@
         <v>73</v>
       </c>
       <c r="H76" s="11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I76" s="36"/>
       <c r="J76" s="37" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="77" spans="1:10">
@@ -5049,7 +5045,7 @@
         <v>70</v>
       </c>
       <c r="C78" s="35" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D78" s="30" t="s">
         <v>72</v>
@@ -5060,11 +5056,11 @@
         <v>73</v>
       </c>
       <c r="H78" s="11" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I78" s="36"/>
       <c r="J78" s="37" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="79" spans="1:10">
@@ -5083,7 +5079,7 @@
         <v>70</v>
       </c>
       <c r="C80" s="35" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D80" s="30" t="s">
         <v>72</v>
@@ -5094,11 +5090,11 @@
         <v>73</v>
       </c>
       <c r="H80" s="11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I80" s="36"/>
       <c r="J80" s="37" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="81" spans="1:10">
@@ -5146,17 +5142,17 @@
         <v>73</v>
       </c>
       <c r="H85" s="11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I85" s="10"/>
       <c r="J85" s="12" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.5">
       <c r="A86" s="14"/>
       <c r="B86" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C86" s="15" t="s">
         <v>135</v>
@@ -5170,7 +5166,7 @@
         <v>73</v>
       </c>
       <c r="H86" s="16" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I86" s="15"/>
       <c r="J86" s="13"/>
@@ -5192,7 +5188,7 @@
         <v>73</v>
       </c>
       <c r="H87" s="17" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I87" s="15"/>
       <c r="J87" s="13"/>
@@ -5212,7 +5208,7 @@
     <row r="89" spans="1:10" ht="16.5">
       <c r="A89" s="14"/>
       <c r="B89" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C89" s="15" t="s">
         <v>135</v>
@@ -5258,7 +5254,7 @@
         <v>73</v>
       </c>
       <c r="H90" s="17" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I90" s="15"/>
       <c r="J90" s="13"/>
@@ -5266,7 +5262,7 @@
     <row r="91" spans="1:10" ht="16.5">
       <c r="A91" s="14"/>
       <c r="B91" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C91" s="15" t="s">
         <v>135</v>
@@ -5284,7 +5280,7 @@
         <v>73</v>
       </c>
       <c r="H91" s="17" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="I91" s="15"/>
       <c r="J91" s="13"/>
@@ -5310,7 +5306,7 @@
         <v>73</v>
       </c>
       <c r="H92" s="17" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I92" s="15"/>
       <c r="J92" s="13"/>
@@ -5356,7 +5352,7 @@
     <row r="95" spans="1:10" ht="16.5">
       <c r="A95" s="14"/>
       <c r="B95" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C95" s="15" t="s">
         <v>135</v>
@@ -5408,10 +5404,10 @@
     <row r="97" spans="1:10" ht="16.5">
       <c r="A97" s="14"/>
       <c r="B97" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C97" s="15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D97" s="14">
         <v>4</v>
@@ -5426,7 +5422,7 @@
         <v>73</v>
       </c>
       <c r="H97" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I97" s="15"/>
       <c r="J97" s="13"/>
@@ -5437,7 +5433,7 @@
         <v>70</v>
       </c>
       <c r="C98" s="15" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D98" s="14">
         <v>4</v>
@@ -5452,7 +5448,7 @@
         <v>73</v>
       </c>
       <c r="H98" s="16" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I98" s="15"/>
       <c r="J98" s="13"/>
@@ -5516,7 +5512,7 @@
         <v>73</v>
       </c>
       <c r="H101" s="27" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I101" s="15"/>
       <c r="J101" s="13"/>
@@ -5542,7 +5538,7 @@
         <v>73</v>
       </c>
       <c r="H102" s="27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I102" s="15"/>
       <c r="J102" s="13"/>
@@ -5578,11 +5574,11 @@
         <v>73</v>
       </c>
       <c r="H104" s="11" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I104" s="10"/>
       <c r="J104" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="105" spans="1:10" ht="16.5">
@@ -5612,7 +5608,7 @@
         <v>74</v>
       </c>
       <c r="H106" s="24" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I106" s="19" t="s">
         <v>75</v>
@@ -5622,7 +5618,7 @@
     <row r="107" spans="1:10" ht="16.5">
       <c r="A107" s="14"/>
       <c r="B107" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C107" s="15" t="s">
         <v>135</v>
@@ -5640,7 +5636,7 @@
         <v>73</v>
       </c>
       <c r="H107" s="16" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I107" s="15"/>
       <c r="J107" s="13"/>
@@ -5666,7 +5662,7 @@
         <v>73</v>
       </c>
       <c r="H108" s="17" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I108" s="15"/>
       <c r="J108" s="13"/>
@@ -5746,7 +5742,7 @@
         <v>145</v>
       </c>
       <c r="H112" s="16" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I112" s="15"/>
       <c r="J112" s="13"/>
@@ -5772,7 +5768,7 @@
         <v>73</v>
       </c>
       <c r="H113" s="16" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I113" s="15"/>
       <c r="J113" s="13"/>
@@ -5826,7 +5822,7 @@
         <v>74</v>
       </c>
       <c r="H116" s="24" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I116" s="15"/>
       <c r="J116" s="13"/>
@@ -5834,7 +5830,7 @@
     <row r="117" spans="1:10" ht="16.5">
       <c r="A117" s="14"/>
       <c r="B117" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C117" s="15" t="s">
         <v>135</v>
@@ -5852,7 +5848,7 @@
         <v>73</v>
       </c>
       <c r="H117" s="27" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I117" s="15"/>
       <c r="J117" s="13"/>
@@ -5878,7 +5874,7 @@
         <v>73</v>
       </c>
       <c r="H118" s="27" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I118" s="15"/>
       <c r="J118" s="13"/>
@@ -5930,7 +5926,7 @@
       </c>
       <c r="I121" s="10"/>
       <c r="J121" s="12" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="122" spans="1:10" ht="16.5">
@@ -5948,7 +5944,7 @@
     <row r="123" spans="1:10" ht="16.5">
       <c r="A123" s="31"/>
       <c r="B123" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C123" s="15" t="s">
         <v>135</v>
@@ -5964,7 +5960,7 @@
         <v>74</v>
       </c>
       <c r="H123" s="24" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I123" s="13"/>
       <c r="J123" s="13"/>
@@ -5972,7 +5968,7 @@
     <row r="124" spans="1:10" ht="16.5">
       <c r="A124" s="31"/>
       <c r="B124" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C124" s="15" t="s">
         <v>135</v>
@@ -5990,7 +5986,7 @@
         <v>145</v>
       </c>
       <c r="H124" s="16" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I124" s="13"/>
       <c r="J124" s="13"/>
@@ -6016,7 +6012,7 @@
         <v>73</v>
       </c>
       <c r="H125" s="27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I125" s="13"/>
       <c r="J125" s="13"/>
@@ -6058,7 +6054,7 @@
     <row r="128" spans="1:10" ht="16.5">
       <c r="A128" s="31"/>
       <c r="B128" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C128" s="15" t="s">
         <v>135</v>
@@ -6074,7 +6070,7 @@
         <v>74</v>
       </c>
       <c r="H128" s="24" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I128" s="13"/>
       <c r="J128" s="34"/>
@@ -6082,7 +6078,7 @@
     <row r="129" spans="1:10" ht="33">
       <c r="A129" s="31"/>
       <c r="B129" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C129" s="15" t="s">
         <v>135</v>
@@ -6100,7 +6096,7 @@
         <v>145</v>
       </c>
       <c r="H129" s="16" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="I129" s="13"/>
       <c r="J129" s="34"/>
@@ -6142,7 +6138,7 @@
     <row r="132" spans="1:10" ht="16.5">
       <c r="A132" s="31"/>
       <c r="B132" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C132" s="15" t="s">
         <v>135</v>
@@ -6155,23 +6151,23 @@
       </c>
       <c r="F132" s="18"/>
       <c r="G132" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="H132" s="24" t="s">
         <v>210</v>
       </c>
-      <c r="H132" s="24" t="s">
-        <v>211</v>
-      </c>
       <c r="I132" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J132" s="13"/>
     </row>
     <row r="133" spans="1:10" ht="16.5">
       <c r="A133" s="31"/>
       <c r="B133" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C133" s="15" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D133" s="31">
         <v>2</v>
@@ -6186,7 +6182,7 @@
         <v>145</v>
       </c>
       <c r="H133" s="16" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I133" s="13"/>
       <c r="J133" s="13"/>
@@ -6197,7 +6193,7 @@
         <v>70</v>
       </c>
       <c r="C134" s="15" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D134" s="28">
         <v>2</v>
@@ -6212,7 +6208,7 @@
         <v>73</v>
       </c>
       <c r="H134" s="41" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="I134" s="13"/>
       <c r="J134" s="13"/>
@@ -6231,10 +6227,10 @@
         <v>3</v>
       </c>
       <c r="G135" s="33" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H135" s="23" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I135" s="13"/>
       <c r="J135" s="34"/>
@@ -6310,7 +6306,7 @@
       </c>
       <c r="I140" s="10"/>
       <c r="J140" s="12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="141" spans="1:10" ht="16.5">
@@ -6328,7 +6324,7 @@
     <row r="142" spans="1:10" ht="16.5">
       <c r="A142" s="31"/>
       <c r="B142" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C142" s="15" t="s">
         <v>135</v>
@@ -6344,7 +6340,7 @@
         <v>74</v>
       </c>
       <c r="H142" s="24" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I142" s="13"/>
       <c r="J142" s="13"/>
@@ -6352,7 +6348,7 @@
     <row r="143" spans="1:10" ht="16.5">
       <c r="A143" s="31"/>
       <c r="B143" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C143" s="15" t="s">
         <v>135</v>
@@ -6370,7 +6366,7 @@
         <v>145</v>
       </c>
       <c r="H143" s="16" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I143" s="13"/>
       <c r="J143" s="13"/>
@@ -6378,7 +6374,7 @@
     <row r="144" spans="1:10" ht="16.5">
       <c r="A144" s="31"/>
       <c r="B144" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C144" s="15" t="s">
         <v>135</v>
@@ -6396,11 +6392,11 @@
         <v>76</v>
       </c>
       <c r="H144" s="23" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I144" s="13"/>
       <c r="J144" s="34" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="145" spans="1:10" ht="16.5">
@@ -6418,7 +6414,7 @@
     <row r="146" spans="1:10" ht="16.5">
       <c r="A146" s="31"/>
       <c r="B146" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C146" s="15" t="s">
         <v>135</v>
@@ -6434,15 +6430,15 @@
         <v>74</v>
       </c>
       <c r="H146" s="24" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I146" s="13"/>
       <c r="J146" s="13"/>
     </row>
-    <row r="147" spans="1:10" ht="16.5">
+    <row r="147" spans="1:10" ht="33">
       <c r="A147" s="31"/>
       <c r="B147" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C147" s="15" t="s">
         <v>135</v>
@@ -6460,7 +6456,7 @@
         <v>145</v>
       </c>
       <c r="H147" s="16" t="s">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="I147" s="13"/>
       <c r="J147" s="13"/>
@@ -6468,7 +6464,7 @@
     <row r="148" spans="1:10" ht="16.5">
       <c r="A148" s="31"/>
       <c r="B148" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C148" s="15" t="s">
         <v>135</v>
@@ -6483,7 +6479,7 @@
         <v>2</v>
       </c>
       <c r="G148" s="33" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H148" s="23" t="s">
         <v>78</v>
@@ -6511,7 +6507,7 @@
         <v>70</v>
       </c>
       <c r="C150" s="35" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D150" s="30" t="s">
         <v>72</v>
@@ -6522,11 +6518,11 @@
         <v>73</v>
       </c>
       <c r="H150" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I150" s="36"/>
       <c r="J150" s="35" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="151" spans="1:10">
@@ -6555,11 +6551,11 @@
         <v>73</v>
       </c>
       <c r="H152" s="11" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I152" s="36"/>
       <c r="J152" s="35" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="153" spans="1:10">
@@ -6588,11 +6584,11 @@
         <v>73</v>
       </c>
       <c r="H154" s="11" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I154" s="36"/>
       <c r="J154" s="35" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="155" spans="1:10">
@@ -6610,7 +6606,7 @@
         <v>70</v>
       </c>
       <c r="C156" s="35" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D156" s="30" t="s">
         <v>72</v>
@@ -6621,11 +6617,11 @@
         <v>73</v>
       </c>
       <c r="H156" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I156" s="36"/>
       <c r="J156" s="35" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="157" spans="1:10">
@@ -6643,7 +6639,7 @@
         <v>70</v>
       </c>
       <c r="C158" s="35" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D158" s="30" t="s">
         <v>72</v>
@@ -6654,11 +6650,11 @@
         <v>73</v>
       </c>
       <c r="H158" s="11" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="I158" s="36"/>
       <c r="J158" s="35" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="159" spans="1:10">
@@ -6676,7 +6672,7 @@
         <v>70</v>
       </c>
       <c r="C160" s="35" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D160" s="30" t="s">
         <v>72</v>
@@ -6687,11 +6683,11 @@
         <v>73</v>
       </c>
       <c r="H160" s="11" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="I160" s="36"/>
       <c r="J160" s="35" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="161" spans="1:10">
@@ -6709,7 +6705,7 @@
         <v>70</v>
       </c>
       <c r="C162" s="35" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D162" s="30" t="s">
         <v>72</v>
@@ -6720,11 +6716,11 @@
         <v>73</v>
       </c>
       <c r="H162" s="11" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I162" s="36"/>
       <c r="J162" s="35" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="163" spans="1:10">
@@ -6772,11 +6768,11 @@
         <v>73</v>
       </c>
       <c r="H166" s="11" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="I166" s="10"/>
       <c r="J166" s="12" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="167" spans="1:10" ht="33">
@@ -6796,7 +6792,7 @@
         <v>73</v>
       </c>
       <c r="H167" s="16" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="I167" s="15"/>
       <c r="J167" s="13"/>
@@ -6804,7 +6800,7 @@
     <row r="168" spans="1:10" ht="16.5">
       <c r="A168" s="14"/>
       <c r="B168" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C168" s="15" t="s">
         <v>135</v>
@@ -6818,7 +6814,7 @@
         <v>73</v>
       </c>
       <c r="H168" s="16" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="I168" s="15"/>
       <c r="J168" s="13"/>
@@ -6826,7 +6822,7 @@
     <row r="169" spans="1:10" ht="16.5">
       <c r="A169" s="14"/>
       <c r="B169" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C169" s="15" t="s">
         <v>135</v>
@@ -6840,7 +6836,7 @@
         <v>145</v>
       </c>
       <c r="H169" s="17" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="I169" s="15"/>
       <c r="J169" s="13"/>
@@ -6860,7 +6856,7 @@
     <row r="171" spans="1:10" ht="16.5">
       <c r="A171" s="14"/>
       <c r="B171" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C171" s="15" t="s">
         <v>135</v>
@@ -6906,7 +6902,7 @@
         <v>73</v>
       </c>
       <c r="H172" s="16" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="I172" s="15"/>
       <c r="J172" s="13"/>
@@ -6914,7 +6910,7 @@
     <row r="173" spans="1:10" ht="16.5">
       <c r="A173" s="14"/>
       <c r="B173" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C173" s="15" t="s">
         <v>135</v>
@@ -6932,7 +6928,7 @@
         <v>73</v>
       </c>
       <c r="H173" s="17" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="I173" s="15"/>
       <c r="J173" s="13"/>
@@ -6958,7 +6954,7 @@
         <v>73</v>
       </c>
       <c r="H174" s="17" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="I174" s="15"/>
       <c r="J174" s="13"/>
@@ -7004,7 +7000,7 @@
     <row r="177" spans="1:10" ht="16.5">
       <c r="A177" s="14"/>
       <c r="B177" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C177" s="15" t="s">
         <v>135</v>
@@ -7056,10 +7052,10 @@
     <row r="179" spans="1:10" ht="16.5">
       <c r="A179" s="14"/>
       <c r="B179" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C179" s="15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D179" s="14">
         <v>5</v>
@@ -7074,7 +7070,7 @@
         <v>73</v>
       </c>
       <c r="H179" s="17" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="I179" s="15"/>
       <c r="J179" s="13"/>
@@ -7085,7 +7081,7 @@
         <v>70</v>
       </c>
       <c r="C180" s="15" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D180" s="14">
         <v>5</v>
@@ -7100,7 +7096,7 @@
         <v>73</v>
       </c>
       <c r="H180" s="16" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I180" s="15"/>
       <c r="J180" s="13"/>
@@ -7164,7 +7160,7 @@
         <v>73</v>
       </c>
       <c r="H183" s="27" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="I183" s="15"/>
       <c r="J183" s="13"/>
@@ -7190,7 +7186,7 @@
         <v>73</v>
       </c>
       <c r="H184" s="27" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="I184" s="15"/>
       <c r="J184" s="13"/>
@@ -7226,11 +7222,11 @@
         <v>73</v>
       </c>
       <c r="H186" s="11" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I186" s="10"/>
       <c r="J186" s="12" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="187" spans="1:10" ht="16.5">
@@ -7260,7 +7256,7 @@
         <v>74</v>
       </c>
       <c r="H188" s="24" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I188" s="19" t="s">
         <v>75</v>
@@ -7270,7 +7266,7 @@
     <row r="189" spans="1:10" ht="16.5">
       <c r="A189" s="14"/>
       <c r="B189" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C189" s="15" t="s">
         <v>135</v>
@@ -7288,7 +7284,7 @@
         <v>73</v>
       </c>
       <c r="H189" s="16" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I189" s="15"/>
       <c r="J189" s="13"/>
@@ -7314,7 +7310,7 @@
         <v>73</v>
       </c>
       <c r="H190" s="17" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I190" s="15"/>
       <c r="J190" s="13"/>
@@ -7372,7 +7368,7 @@
         <v>145</v>
       </c>
       <c r="H193" s="16" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I193" s="15"/>
       <c r="J193" s="13"/>
@@ -7398,7 +7394,7 @@
         <v>73</v>
       </c>
       <c r="H194" s="16" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="I194" s="15"/>
       <c r="J194" s="13"/>
@@ -7430,7 +7426,7 @@
         <v>74</v>
       </c>
       <c r="H196" s="24" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I196" s="15"/>
       <c r="J196" s="13"/>
@@ -7438,7 +7434,7 @@
     <row r="197" spans="1:10" ht="16.5">
       <c r="A197" s="14"/>
       <c r="B197" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C197" s="15" t="s">
         <v>135</v>
@@ -7456,7 +7452,7 @@
         <v>73</v>
       </c>
       <c r="H197" s="27" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I197" s="15"/>
       <c r="J197" s="13"/>
@@ -7482,7 +7478,7 @@
         <v>73</v>
       </c>
       <c r="H198" s="27" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="I198" s="15"/>
       <c r="J198" s="13"/>
@@ -7530,11 +7526,11 @@
         <v>73</v>
       </c>
       <c r="H201" s="11" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I201" s="10"/>
       <c r="J201" s="12" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="202" spans="1:10" ht="16.5">
@@ -7552,7 +7548,7 @@
     <row r="203" spans="1:10" ht="16.5">
       <c r="A203" s="31"/>
       <c r="B203" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C203" s="15" t="s">
         <v>135</v>
@@ -7568,7 +7564,7 @@
         <v>74</v>
       </c>
       <c r="H203" s="24" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I203" s="13"/>
       <c r="J203" s="13"/>
@@ -7576,7 +7572,7 @@
     <row r="204" spans="1:10" ht="16.5">
       <c r="A204" s="31"/>
       <c r="B204" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C204" s="15" t="s">
         <v>135</v>
@@ -7594,7 +7590,7 @@
         <v>145</v>
       </c>
       <c r="H204" s="16" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I204" s="13"/>
       <c r="J204" s="13"/>
@@ -7602,7 +7598,7 @@
     <row r="205" spans="1:10" ht="16.5">
       <c r="A205" s="31"/>
       <c r="B205" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C205" s="15" t="s">
         <v>135</v>
@@ -7620,7 +7616,7 @@
         <v>73</v>
       </c>
       <c r="H205" s="27" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I205" s="13"/>
       <c r="J205" s="34"/>
@@ -7678,7 +7674,7 @@
         <v>74</v>
       </c>
       <c r="H208" s="24" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I208" s="13"/>
       <c r="J208" s="13"/>
@@ -7686,7 +7682,7 @@
     <row r="209" spans="1:10" ht="33">
       <c r="A209" s="31"/>
       <c r="B209" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C209" s="15" t="s">
         <v>135</v>
@@ -7704,7 +7700,7 @@
         <v>145</v>
       </c>
       <c r="H209" s="16" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="I209" s="13"/>
       <c r="J209" s="13"/>
@@ -7759,23 +7755,23 @@
       </c>
       <c r="F212" s="18"/>
       <c r="G212" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="H212" s="24" t="s">
         <v>210</v>
       </c>
-      <c r="H212" s="24" t="s">
-        <v>211</v>
-      </c>
       <c r="I212" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J212" s="13"/>
     </row>
     <row r="213" spans="1:10" ht="16.5">
       <c r="A213" s="31"/>
       <c r="B213" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C213" s="15" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D213" s="31">
         <v>2</v>
@@ -7790,7 +7786,7 @@
         <v>145</v>
       </c>
       <c r="H213" s="16" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I213" s="13"/>
       <c r="J213" s="13"/>
@@ -7801,7 +7797,7 @@
         <v>70</v>
       </c>
       <c r="C214" s="15" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D214" s="28">
         <v>2</v>
@@ -7816,7 +7812,7 @@
         <v>73</v>
       </c>
       <c r="H214" s="41" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I214" s="13"/>
       <c r="J214" s="13"/>
@@ -7835,10 +7831,10 @@
         <v>3</v>
       </c>
       <c r="G215" s="33" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H215" s="23" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I215" s="13"/>
       <c r="J215" s="13"/>
@@ -7890,7 +7886,7 @@
       </c>
       <c r="I218" s="10"/>
       <c r="J218" s="12" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="219" spans="1:10" ht="16.5">
@@ -7924,7 +7920,7 @@
         <v>74</v>
       </c>
       <c r="H220" s="24" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I220" s="13"/>
       <c r="J220" s="13"/>
@@ -7950,7 +7946,7 @@
         <v>145</v>
       </c>
       <c r="H221" s="16" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I221" s="13"/>
       <c r="J221" s="13"/>
@@ -7976,11 +7972,11 @@
         <v>76</v>
       </c>
       <c r="H222" s="23" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I222" s="13"/>
       <c r="J222" s="34" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="223" spans="1:10" ht="16.5">
@@ -8014,7 +8010,7 @@
         <v>74</v>
       </c>
       <c r="H224" s="24" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I224" s="13"/>
       <c r="J224" s="13"/>
@@ -8040,7 +8036,7 @@
         <v>145</v>
       </c>
       <c r="H225" s="16" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="I225" s="13"/>
       <c r="J225" s="13"/>
@@ -8063,7 +8059,7 @@
         <v>2</v>
       </c>
       <c r="G226" s="33" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H226" s="23" t="s">
         <v>78</v>
@@ -8118,7 +8114,7 @@
       </c>
       <c r="I229" s="10"/>
       <c r="J229" s="12" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="230" spans="1:10" ht="16.5">
@@ -8152,7 +8148,7 @@
         <v>74</v>
       </c>
       <c r="H231" s="24" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I231" s="13"/>
       <c r="J231" s="13"/>
@@ -8160,7 +8156,7 @@
     <row r="232" spans="1:10" ht="16.5">
       <c r="A232" s="31"/>
       <c r="B232" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C232" s="15" t="s">
         <v>135</v>
@@ -8178,7 +8174,7 @@
         <v>145</v>
       </c>
       <c r="H232" s="16" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I232" s="13"/>
       <c r="J232" s="13"/>
@@ -8186,7 +8182,7 @@
     <row r="233" spans="1:10" ht="16.5">
       <c r="A233" s="31"/>
       <c r="B233" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C233" s="15" t="s">
         <v>135</v>
@@ -8204,11 +8200,11 @@
         <v>76</v>
       </c>
       <c r="H233" s="23" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I233" s="13"/>
       <c r="J233" s="34" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="234" spans="1:10" ht="16.5">
@@ -8242,7 +8238,7 @@
         <v>74</v>
       </c>
       <c r="H235" s="24" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I235" s="13"/>
       <c r="J235" s="13"/>
@@ -8250,7 +8246,7 @@
     <row r="236" spans="1:10" ht="33">
       <c r="A236" s="31"/>
       <c r="B236" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C236" s="15" t="s">
         <v>135</v>
@@ -8268,7 +8264,7 @@
         <v>145</v>
       </c>
       <c r="H236" s="16" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="I236" s="13"/>
       <c r="J236" s="13"/>
@@ -8276,7 +8272,7 @@
     <row r="237" spans="1:10" ht="16.5">
       <c r="A237" s="31"/>
       <c r="B237" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C237" s="15" t="s">
         <v>135</v>
@@ -8291,7 +8287,7 @@
         <v>2</v>
       </c>
       <c r="G237" s="33" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H237" s="23" t="s">
         <v>78</v>
@@ -8331,7 +8327,7 @@
         <v>70</v>
       </c>
       <c r="C240" s="35" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D240" s="30" t="s">
         <v>72</v>
@@ -8342,11 +8338,11 @@
         <v>73</v>
       </c>
       <c r="H240" s="11" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I240" s="36"/>
       <c r="J240" s="35" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="241" spans="1:10">
@@ -8375,11 +8371,11 @@
         <v>73</v>
       </c>
       <c r="H242" s="11" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I242" s="36"/>
       <c r="J242" s="35" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="243" spans="1:10">
@@ -8408,11 +8404,11 @@
         <v>73</v>
       </c>
       <c r="H244" s="11" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I244" s="36"/>
       <c r="J244" s="35" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="245" spans="1:10">
@@ -8430,7 +8426,7 @@
         <v>70</v>
       </c>
       <c r="C246" s="35" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D246" s="30" t="s">
         <v>72</v>
@@ -8441,11 +8437,11 @@
         <v>73</v>
       </c>
       <c r="H246" s="11" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I246" s="36"/>
       <c r="J246" s="35" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="247" spans="1:10">
@@ -8463,7 +8459,7 @@
         <v>70</v>
       </c>
       <c r="C248" s="35" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D248" s="30" t="s">
         <v>72</v>
@@ -8474,11 +8470,11 @@
         <v>73</v>
       </c>
       <c r="H248" s="11" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="I248" s="36"/>
       <c r="J248" s="35" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="249" spans="1:10">
@@ -8496,7 +8492,7 @@
         <v>70</v>
       </c>
       <c r="C250" s="35" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D250" s="30" t="s">
         <v>72</v>
@@ -8507,11 +8503,11 @@
         <v>73</v>
       </c>
       <c r="H250" s="11" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="I250" s="36"/>
       <c r="J250" s="35" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="251" spans="1:10">
@@ -8529,7 +8525,7 @@
         <v>70</v>
       </c>
       <c r="C252" s="35" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D252" s="30" t="s">
         <v>72</v>
@@ -8540,11 +8536,11 @@
         <v>73</v>
       </c>
       <c r="H252" s="11" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="I252" s="36"/>
       <c r="J252" s="35" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="253" spans="1:10">
@@ -8592,11 +8588,11 @@
         <v>73</v>
       </c>
       <c r="H256" s="11" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="I256" s="10"/>
       <c r="J256" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="257" spans="1:10" ht="16.5">
@@ -8616,7 +8612,7 @@
         <v>73</v>
       </c>
       <c r="H257" s="16" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="I257" s="15"/>
       <c r="J257" s="13"/>
@@ -8638,7 +8634,7 @@
         <v>73</v>
       </c>
       <c r="H258" s="17" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="I258" s="15"/>
       <c r="J258" s="13"/>
@@ -8704,7 +8700,7 @@
         <v>73</v>
       </c>
       <c r="H261" s="17" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="I261" s="15"/>
       <c r="J261" s="13"/>
@@ -8730,7 +8726,7 @@
         <v>73</v>
       </c>
       <c r="H262" s="17" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="I262" s="15"/>
       <c r="J262" s="13"/>
@@ -8756,7 +8752,7 @@
         <v>73</v>
       </c>
       <c r="H263" s="17" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="I263" s="15"/>
       <c r="J263" s="13"/>
@@ -8782,7 +8778,7 @@
         <v>73</v>
       </c>
       <c r="H264" s="17" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="I264" s="15"/>
       <c r="J264" s="13"/>
@@ -8808,7 +8804,7 @@
         <v>73</v>
       </c>
       <c r="H265" s="17" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="I265" s="15"/>
       <c r="J265" s="13"/>
@@ -8834,7 +8830,7 @@
         <v>73</v>
       </c>
       <c r="H266" s="14" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="I266" s="14"/>
       <c r="J266" s="14"/>
@@ -8935,7 +8931,7 @@
         <v>70</v>
       </c>
       <c r="C271" s="15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D271" s="14">
         <v>4</v>
@@ -8950,7 +8946,7 @@
         <v>73</v>
       </c>
       <c r="H271" s="17" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="I271" s="15"/>
       <c r="J271" s="13"/>
@@ -8961,7 +8957,7 @@
         <v>70</v>
       </c>
       <c r="C272" s="15" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D272" s="14">
         <v>4</v>
@@ -8976,7 +8972,7 @@
         <v>73</v>
       </c>
       <c r="H272" s="16" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="I272" s="15"/>
       <c r="J272" s="13"/>
@@ -9040,7 +9036,7 @@
         <v>73</v>
       </c>
       <c r="H275" s="27" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I275" s="15"/>
       <c r="J275" s="13"/>
@@ -9066,7 +9062,7 @@
         <v>73</v>
       </c>
       <c r="H276" s="27" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="I276" s="15"/>
       <c r="J276" s="13"/>
@@ -9102,11 +9098,11 @@
         <v>73</v>
       </c>
       <c r="H278" s="11" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="I278" s="10"/>
       <c r="J278" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="279" spans="1:10" ht="16.5">
@@ -9136,7 +9132,7 @@
         <v>74</v>
       </c>
       <c r="H280" s="24" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I280" s="19" t="s">
         <v>75</v>
@@ -9164,7 +9160,7 @@
         <v>73</v>
       </c>
       <c r="H281" s="16" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I281" s="15"/>
       <c r="J281" s="13"/>
@@ -9190,7 +9186,7 @@
         <v>73</v>
       </c>
       <c r="H282" s="17" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="I282" s="15"/>
       <c r="J282" s="13"/>
@@ -9248,7 +9244,7 @@
         <v>145</v>
       </c>
       <c r="H285" s="16" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I285" s="15"/>
       <c r="J285" s="13"/>
@@ -9274,7 +9270,7 @@
         <v>73</v>
       </c>
       <c r="H286" s="16" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="I286" s="15"/>
       <c r="J286" s="13"/>
@@ -9306,7 +9302,7 @@
         <v>74</v>
       </c>
       <c r="H288" s="24" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I288" s="15"/>
       <c r="J288" s="13"/>
@@ -9332,7 +9328,7 @@
         <v>73</v>
       </c>
       <c r="H289" s="27" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I289" s="15"/>
       <c r="J289" s="13"/>
@@ -9358,7 +9354,7 @@
         <v>73</v>
       </c>
       <c r="H290" s="27" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I290" s="15"/>
       <c r="J290" s="13"/>
@@ -9406,11 +9402,11 @@
         <v>73</v>
       </c>
       <c r="H293" s="11" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="I293" s="10"/>
       <c r="J293" s="12" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="294" spans="1:10" ht="21">
@@ -9456,7 +9452,7 @@
         <v>74</v>
       </c>
       <c r="H296" s="24" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I296" s="13"/>
       <c r="J296" s="13"/>
@@ -9482,7 +9478,7 @@
         <v>145</v>
       </c>
       <c r="H297" s="16" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I297" s="13"/>
       <c r="J297" s="13"/>
@@ -9508,7 +9504,7 @@
         <v>73</v>
       </c>
       <c r="H298" s="27" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I298" s="13"/>
       <c r="J298" s="34"/>
@@ -9566,7 +9562,7 @@
         <v>74</v>
       </c>
       <c r="H301" s="24" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I301" s="13"/>
       <c r="J301" s="13"/>
@@ -9592,7 +9588,7 @@
         <v>145</v>
       </c>
       <c r="H302" s="16" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="I302" s="13"/>
       <c r="J302" s="13"/>
@@ -9618,7 +9614,7 @@
         <v>145</v>
       </c>
       <c r="H303" s="16" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="I303" s="13"/>
       <c r="J303" s="13"/>
@@ -9673,13 +9669,13 @@
       </c>
       <c r="F306" s="18"/>
       <c r="G306" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="H306" s="24" t="s">
         <v>210</v>
       </c>
-      <c r="H306" s="24" t="s">
-        <v>211</v>
-      </c>
       <c r="I306" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J306" s="13"/>
     </row>
@@ -9689,7 +9685,7 @@
         <v>101</v>
       </c>
       <c r="C307" s="15" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D307" s="31">
         <v>2</v>
@@ -9704,7 +9700,7 @@
         <v>145</v>
       </c>
       <c r="H307" s="16" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I307" s="13"/>
       <c r="J307" s="13"/>
@@ -9715,7 +9711,7 @@
         <v>70</v>
       </c>
       <c r="C308" s="15" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D308" s="28">
         <v>2</v>
@@ -9730,7 +9726,7 @@
         <v>73</v>
       </c>
       <c r="H308" s="41" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I308" s="13"/>
       <c r="J308" s="13"/>
@@ -9749,10 +9745,10 @@
         <v>3</v>
       </c>
       <c r="G309" s="33" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H309" s="23" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I309" s="13"/>
       <c r="J309" s="13"/>
@@ -9800,11 +9796,11 @@
         <v>73</v>
       </c>
       <c r="H312" s="11" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="I312" s="10"/>
       <c r="J312" s="12" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="313" spans="1:10" ht="16.5">
@@ -9838,7 +9834,7 @@
         <v>74</v>
       </c>
       <c r="H314" s="24" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I314" s="13"/>
       <c r="J314" s="13"/>
@@ -9864,7 +9860,7 @@
         <v>145</v>
       </c>
       <c r="H315" s="16" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="I315" s="13"/>
       <c r="J315" s="13"/>
@@ -9890,7 +9886,7 @@
         <v>145</v>
       </c>
       <c r="H316" s="16" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="I316" s="13"/>
       <c r="J316" s="13"/>
@@ -9916,11 +9912,11 @@
         <v>76</v>
       </c>
       <c r="H317" s="23" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I317" s="13"/>
       <c r="J317" s="34" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="318" spans="1:10" ht="16.5">
@@ -9954,7 +9950,7 @@
         <v>74</v>
       </c>
       <c r="H319" s="24" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I319" s="13"/>
       <c r="J319" s="13"/>
@@ -9980,7 +9976,7 @@
         <v>145</v>
       </c>
       <c r="H320" s="16" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="I320" s="13"/>
       <c r="J320" s="13"/>
@@ -10003,7 +9999,7 @@
         <v>2</v>
       </c>
       <c r="G321" s="33" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H321" s="23" t="s">
         <v>78</v>
@@ -10054,11 +10050,11 @@
         <v>73</v>
       </c>
       <c r="H324" s="11" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="I324" s="10"/>
       <c r="J324" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="325" spans="1:10" ht="16.5">
@@ -10092,7 +10088,7 @@
         <v>74</v>
       </c>
       <c r="H326" s="24" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I326" s="13"/>
       <c r="J326" s="13"/>
@@ -10118,7 +10114,7 @@
         <v>145</v>
       </c>
       <c r="H327" s="16" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I327" s="13"/>
       <c r="J327" s="13"/>
@@ -10144,11 +10140,11 @@
         <v>76</v>
       </c>
       <c r="H328" s="23" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I328" s="13"/>
       <c r="J328" s="34" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="329" spans="1:10" ht="16.5">
@@ -10182,7 +10178,7 @@
         <v>74</v>
       </c>
       <c r="H330" s="24" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I330" s="13"/>
       <c r="J330" s="13"/>
@@ -10208,7 +10204,7 @@
         <v>145</v>
       </c>
       <c r="H331" s="16" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="I331" s="13"/>
       <c r="J331" s="13"/>
@@ -10231,7 +10227,7 @@
         <v>2</v>
       </c>
       <c r="G332" s="33" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H332" s="23" t="s">
         <v>78</v>
@@ -10283,7 +10279,7 @@
         <v>70</v>
       </c>
       <c r="C336" s="35" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D336" s="30" t="s">
         <v>72</v>
@@ -10294,11 +10290,11 @@
         <v>73</v>
       </c>
       <c r="H336" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="I336" s="36"/>
       <c r="J336" s="35" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="337" spans="1:10">
@@ -10327,11 +10323,11 @@
         <v>73</v>
       </c>
       <c r="H338" s="11" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="I338" s="36"/>
       <c r="J338" s="35" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="339" spans="1:10">
@@ -10360,11 +10356,11 @@
         <v>73</v>
       </c>
       <c r="H340" s="11" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I340" s="36"/>
       <c r="J340" s="35" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="341" spans="1:10">
@@ -10382,7 +10378,7 @@
         <v>70</v>
       </c>
       <c r="C342" s="35" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D342" s="30" t="s">
         <v>72</v>
@@ -10393,11 +10389,11 @@
         <v>73</v>
       </c>
       <c r="H342" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I342" s="36"/>
       <c r="J342" s="35" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="343" spans="1:10">
@@ -10415,7 +10411,7 @@
         <v>70</v>
       </c>
       <c r="C344" s="35" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D344" s="30" t="s">
         <v>72</v>
@@ -10426,11 +10422,11 @@
         <v>73</v>
       </c>
       <c r="H344" s="11" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="I344" s="36"/>
       <c r="J344" s="35" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="345" spans="1:10">
@@ -10448,7 +10444,7 @@
         <v>70</v>
       </c>
       <c r="C346" s="35" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D346" s="30" t="s">
         <v>72</v>
@@ -10459,11 +10455,11 @@
         <v>73</v>
       </c>
       <c r="H346" s="11" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I346" s="36"/>
       <c r="J346" s="35" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="347" spans="1:10">
@@ -10481,7 +10477,7 @@
         <v>70</v>
       </c>
       <c r="C348" s="35" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D348" s="30" t="s">
         <v>72</v>
@@ -10492,11 +10488,11 @@
         <v>73</v>
       </c>
       <c r="H348" s="11" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="I348" s="36"/>
       <c r="J348" s="35" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="349" spans="1:10">
@@ -10549,11 +10545,11 @@
         <v>73</v>
       </c>
       <c r="H352" s="58" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="I352" s="56"/>
       <c r="J352" s="59" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="353" spans="1:10" ht="16.5">
@@ -10573,7 +10569,7 @@
         <v>73</v>
       </c>
       <c r="H353" s="61" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="I353" s="60"/>
       <c r="J353" s="62"/>
@@ -10595,7 +10591,7 @@
         <v>73</v>
       </c>
       <c r="H354" s="61" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="I354" s="60"/>
       <c r="J354" s="62"/>
@@ -10617,7 +10613,7 @@
         <v>73</v>
       </c>
       <c r="H355" s="62" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="I355" s="60"/>
       <c r="J355" s="62"/>
@@ -10683,7 +10679,7 @@
         <v>73</v>
       </c>
       <c r="H358" s="62" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="I358" s="60"/>
       <c r="J358" s="62"/>
@@ -10709,7 +10705,7 @@
         <v>73</v>
       </c>
       <c r="H359" s="62" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="I359" s="60"/>
       <c r="J359" s="62"/>
@@ -10735,7 +10731,7 @@
         <v>73</v>
       </c>
       <c r="H360" s="62" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="I360" s="60"/>
       <c r="J360" s="62"/>
@@ -10836,7 +10832,7 @@
         <v>101</v>
       </c>
       <c r="C365" s="60" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D365" s="60">
         <v>5</v>
@@ -10851,7 +10847,7 @@
         <v>73</v>
       </c>
       <c r="H365" s="62" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="I365" s="60"/>
       <c r="J365" s="62"/>
@@ -10862,7 +10858,7 @@
         <v>70</v>
       </c>
       <c r="C366" s="60" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D366" s="60">
         <v>5</v>
@@ -10877,7 +10873,7 @@
         <v>73</v>
       </c>
       <c r="H366" s="61" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="I366" s="60"/>
       <c r="J366" s="62"/>
@@ -10941,7 +10937,7 @@
         <v>73</v>
       </c>
       <c r="H369" s="68" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="I369" s="60"/>
       <c r="J369" s="62"/>
@@ -10967,7 +10963,7 @@
         <v>73</v>
       </c>
       <c r="H370" s="68" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I370" s="60"/>
       <c r="J370" s="62"/>
@@ -11003,11 +10999,11 @@
         <v>73</v>
       </c>
       <c r="H372" s="58" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I372" s="56"/>
       <c r="J372" s="59" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="373" spans="1:10" ht="16.5">
@@ -11037,7 +11033,7 @@
         <v>74</v>
       </c>
       <c r="H374" s="66" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I374" s="63" t="s">
         <v>75</v>
@@ -11065,7 +11061,7 @@
         <v>73</v>
       </c>
       <c r="H375" s="61" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I375" s="60"/>
       <c r="J375" s="62"/>
@@ -11091,7 +11087,7 @@
         <v>73</v>
       </c>
       <c r="H376" s="62" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I376" s="60"/>
       <c r="J376" s="62"/>
@@ -11149,7 +11145,7 @@
         <v>145</v>
       </c>
       <c r="H379" s="61" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I379" s="60"/>
       <c r="J379" s="62"/>
@@ -11175,7 +11171,7 @@
         <v>73</v>
       </c>
       <c r="H380" s="61" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="I380" s="60"/>
       <c r="J380" s="62"/>
@@ -11207,7 +11203,7 @@
         <v>74</v>
       </c>
       <c r="H382" s="66" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I382" s="60"/>
       <c r="J382" s="62"/>
@@ -11233,7 +11229,7 @@
         <v>73</v>
       </c>
       <c r="H383" s="68" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I383" s="60"/>
       <c r="J383" s="62"/>
@@ -11244,7 +11240,7 @@
         <v>70</v>
       </c>
       <c r="C384" s="60" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D384" s="69">
         <v>2</v>
@@ -11259,7 +11255,7 @@
         <v>73</v>
       </c>
       <c r="H384" s="68" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I384" s="60"/>
       <c r="J384" s="62"/>
@@ -11307,11 +11303,11 @@
         <v>73</v>
       </c>
       <c r="H387" s="58" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="I387" s="56"/>
       <c r="J387" s="59" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="388" spans="1:10" ht="16.5">
@@ -11345,7 +11341,7 @@
         <v>74</v>
       </c>
       <c r="H389" s="66" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I389" s="62"/>
       <c r="J389" s="62"/>
@@ -11371,7 +11367,7 @@
         <v>145</v>
       </c>
       <c r="H390" s="61" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I390" s="62"/>
       <c r="J390" s="62"/>
@@ -11397,7 +11393,7 @@
         <v>73</v>
       </c>
       <c r="H391" s="68" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="I391" s="62"/>
       <c r="J391" s="70"/>
@@ -11455,7 +11451,7 @@
         <v>74</v>
       </c>
       <c r="H394" s="66" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I394" s="62"/>
       <c r="J394" s="62"/>
@@ -11481,7 +11477,7 @@
         <v>145</v>
       </c>
       <c r="H395" s="61" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="I395" s="62"/>
       <c r="J395" s="62"/>
@@ -11536,13 +11532,13 @@
       </c>
       <c r="F398" s="63"/>
       <c r="G398" s="63" t="s">
+        <v>209</v>
+      </c>
+      <c r="H398" s="66" t="s">
         <v>210</v>
       </c>
-      <c r="H398" s="66" t="s">
-        <v>211</v>
-      </c>
       <c r="I398" s="62" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J398" s="62"/>
     </row>
@@ -11552,7 +11548,7 @@
         <v>101</v>
       </c>
       <c r="C399" s="60" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D399" s="62">
         <v>2</v>
@@ -11567,7 +11563,7 @@
         <v>145</v>
       </c>
       <c r="H399" s="61" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I399" s="62"/>
       <c r="J399" s="62"/>
@@ -11578,7 +11574,7 @@
         <v>70</v>
       </c>
       <c r="C400" s="60" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D400" s="69">
         <v>2</v>
@@ -11593,7 +11589,7 @@
         <v>73</v>
       </c>
       <c r="H400" s="73" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="I400" s="62"/>
       <c r="J400" s="62"/>
@@ -11612,10 +11608,10 @@
         <v>3</v>
       </c>
       <c r="G401" s="71" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H401" s="65" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I401" s="62"/>
       <c r="J401" s="62"/>
@@ -11663,11 +11659,11 @@
         <v>73</v>
       </c>
       <c r="H404" s="58" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I404" s="56"/>
       <c r="J404" s="59" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="405" spans="1:10" ht="16.5">
@@ -11701,7 +11697,7 @@
         <v>74</v>
       </c>
       <c r="H406" s="66" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I406" s="62"/>
       <c r="J406" s="62"/>
@@ -11727,7 +11723,7 @@
         <v>145</v>
       </c>
       <c r="H407" s="61" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I407" s="62"/>
       <c r="J407" s="62"/>
@@ -11753,11 +11749,11 @@
         <v>76</v>
       </c>
       <c r="H408" s="65" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I408" s="62"/>
       <c r="J408" s="70" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="409" spans="1:10" ht="16.5">
@@ -11791,7 +11787,7 @@
         <v>74</v>
       </c>
       <c r="H410" s="66" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I410" s="62"/>
       <c r="J410" s="62"/>
@@ -11817,7 +11813,7 @@
         <v>145</v>
       </c>
       <c r="H411" s="61" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I411" s="62"/>
       <c r="J411" s="62"/>
@@ -11840,7 +11836,7 @@
         <v>2</v>
       </c>
       <c r="G412" s="71" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H412" s="65" t="s">
         <v>78</v>
@@ -11879,11 +11875,11 @@
         <v>73</v>
       </c>
       <c r="H414" s="58" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I414" s="56"/>
       <c r="J414" s="59" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="415" spans="1:10" ht="16.5">
@@ -11917,7 +11913,7 @@
         <v>74</v>
       </c>
       <c r="H416" s="66" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I416" s="62"/>
       <c r="J416" s="62"/>
@@ -11943,7 +11939,7 @@
         <v>145</v>
       </c>
       <c r="H417" s="61" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="I417" s="62"/>
       <c r="J417" s="62"/>
@@ -11969,11 +11965,11 @@
         <v>76</v>
       </c>
       <c r="H418" s="65" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I418" s="62"/>
       <c r="J418" s="70" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="419" spans="1:10" ht="16.5">
@@ -12007,7 +12003,7 @@
         <v>74</v>
       </c>
       <c r="H420" s="66" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I420" s="62"/>
       <c r="J420" s="62"/>
@@ -12033,7 +12029,7 @@
         <v>145</v>
       </c>
       <c r="H421" s="61" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I421" s="62"/>
       <c r="J421" s="62"/>
@@ -12056,7 +12052,7 @@
         <v>2</v>
       </c>
       <c r="G422" s="71" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H422" s="65" t="s">
         <v>78</v>
@@ -12096,7 +12092,7 @@
         <v>70</v>
       </c>
       <c r="C425" s="57" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D425" s="57" t="s">
         <v>72</v>
@@ -12107,11 +12103,11 @@
         <v>73</v>
       </c>
       <c r="H425" s="58" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="I425" s="74"/>
       <c r="J425" s="57" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="426" spans="1:10">
@@ -12145,11 +12141,11 @@
         <v>73</v>
       </c>
       <c r="H427" s="58" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="I427" s="74"/>
       <c r="J427" s="57" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="428" spans="1:10">
@@ -12183,11 +12179,11 @@
         <v>73</v>
       </c>
       <c r="H429" s="58" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I429" s="74"/>
       <c r="J429" s="57" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="430" spans="1:10">
@@ -12210,7 +12206,7 @@
         <v>70</v>
       </c>
       <c r="C431" s="57" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D431" s="57" t="s">
         <v>72</v>
@@ -12221,11 +12217,11 @@
         <v>73</v>
       </c>
       <c r="H431" s="58" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="I431" s="74"/>
       <c r="J431" s="57" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="432" spans="1:10">
@@ -12248,7 +12244,7 @@
         <v>70</v>
       </c>
       <c r="C433" s="57" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D433" s="57" t="s">
         <v>72</v>
@@ -12259,11 +12255,11 @@
         <v>73</v>
       </c>
       <c r="H433" s="58" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="I433" s="74"/>
       <c r="J433" s="57" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="434" spans="1:10">
@@ -12286,7 +12282,7 @@
         <v>70</v>
       </c>
       <c r="C435" s="57" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D435" s="57" t="s">
         <v>72</v>
@@ -12297,11 +12293,11 @@
         <v>73</v>
       </c>
       <c r="H435" s="58" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I435" s="74"/>
       <c r="J435" s="57" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="436" spans="1:10">
@@ -12324,7 +12320,7 @@
         <v>70</v>
       </c>
       <c r="C437" s="57" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D437" s="57" t="s">
         <v>72</v>
@@ -12335,11 +12331,11 @@
         <v>73</v>
       </c>
       <c r="H437" s="58" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="I437" s="74"/>
       <c r="J437" s="57" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="438" spans="1:10">
@@ -12392,11 +12388,11 @@
         <v>73</v>
       </c>
       <c r="H441" s="11" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="I441" s="10"/>
       <c r="J441" s="12" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="442" spans="1:10" ht="16.5">
@@ -12416,7 +12412,7 @@
         <v>73</v>
       </c>
       <c r="H442" s="16" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="I442" s="15"/>
       <c r="J442" s="13"/>
@@ -12438,7 +12434,7 @@
         <v>73</v>
       </c>
       <c r="H443" s="17" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="I443" s="15"/>
       <c r="J443" s="13"/>
@@ -12460,7 +12456,7 @@
         <v>73</v>
       </c>
       <c r="H444" s="17" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="I444" s="15"/>
       <c r="J444" s="13"/>
@@ -12538,7 +12534,7 @@
         <v>73</v>
       </c>
       <c r="H448" s="17" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="I448" s="15"/>
       <c r="J448" s="13"/>
@@ -12564,7 +12560,7 @@
         <v>73</v>
       </c>
       <c r="H449" s="17" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="I449" s="15"/>
       <c r="J449" s="13"/>
@@ -12590,7 +12586,7 @@
         <v>73</v>
       </c>
       <c r="H450" s="17" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="I450" s="15"/>
       <c r="J450" s="13"/>
@@ -12691,7 +12687,7 @@
         <v>101</v>
       </c>
       <c r="C455" s="15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D455" s="14">
         <v>5</v>
@@ -12706,7 +12702,7 @@
         <v>73</v>
       </c>
       <c r="H455" s="17" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="I455" s="15"/>
       <c r="J455" s="13"/>
@@ -12717,7 +12713,7 @@
         <v>70</v>
       </c>
       <c r="C456" s="15" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D456" s="14">
         <v>5</v>
@@ -12732,7 +12728,7 @@
         <v>73</v>
       </c>
       <c r="H456" s="16" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="I456" s="15"/>
       <c r="J456" s="13"/>
@@ -12796,7 +12792,7 @@
         <v>73</v>
       </c>
       <c r="H459" s="27" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I459" s="15"/>
       <c r="J459" s="13"/>
@@ -12822,7 +12818,7 @@
         <v>73</v>
       </c>
       <c r="H460" s="27" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I460" s="15"/>
       <c r="J460" s="13"/>
@@ -12858,11 +12854,11 @@
         <v>73</v>
       </c>
       <c r="H462" s="11" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="I462" s="10"/>
       <c r="J462" s="12" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="463" spans="1:10" ht="16.5">
@@ -12892,7 +12888,7 @@
         <v>74</v>
       </c>
       <c r="H464" s="24" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I464" s="19" t="s">
         <v>75</v>
@@ -12920,7 +12916,7 @@
         <v>73</v>
       </c>
       <c r="H465" s="16" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I465" s="15"/>
       <c r="J465" s="13"/>
@@ -12946,7 +12942,7 @@
         <v>73</v>
       </c>
       <c r="H466" s="17" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I466" s="15"/>
       <c r="J466" s="13"/>
@@ -13004,7 +13000,7 @@
         <v>145</v>
       </c>
       <c r="H469" s="17" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="I469" s="15"/>
       <c r="J469" s="13"/>
@@ -13030,7 +13026,7 @@
         <v>73</v>
       </c>
       <c r="H470" s="16" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="I470" s="15"/>
       <c r="J470" s="13"/>
@@ -13062,7 +13058,7 @@
         <v>74</v>
       </c>
       <c r="H472" s="24" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I472" s="15"/>
       <c r="J472" s="13"/>
@@ -13088,7 +13084,7 @@
         <v>73</v>
       </c>
       <c r="H473" s="27" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I473" s="15"/>
       <c r="J473" s="13"/>
@@ -13114,7 +13110,7 @@
         <v>73</v>
       </c>
       <c r="H474" s="75" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="I474" s="15"/>
       <c r="J474" s="13"/>
@@ -13162,11 +13158,11 @@
         <v>73</v>
       </c>
       <c r="H477" s="11" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="I477" s="10"/>
       <c r="J477" s="12" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="478" spans="1:10" ht="16.5">
@@ -13200,7 +13196,7 @@
         <v>74</v>
       </c>
       <c r="H479" s="24" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I479" s="13"/>
       <c r="J479" s="13"/>
@@ -13226,7 +13222,7 @@
         <v>145</v>
       </c>
       <c r="H480" s="16" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I480" s="13"/>
       <c r="J480" s="13"/>
@@ -13252,7 +13248,7 @@
         <v>73</v>
       </c>
       <c r="H481" s="75" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="I481" s="13"/>
       <c r="J481" s="34"/>
@@ -13310,7 +13306,7 @@
         <v>74</v>
       </c>
       <c r="H484" s="24" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I484" s="13"/>
       <c r="J484" s="13"/>
@@ -13336,7 +13332,7 @@
         <v>145</v>
       </c>
       <c r="H485" s="16" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="I485" s="13"/>
       <c r="J485" s="13"/>
@@ -13391,13 +13387,13 @@
       </c>
       <c r="F488" s="18"/>
       <c r="G488" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="H488" s="24" t="s">
         <v>210</v>
       </c>
-      <c r="H488" s="24" t="s">
-        <v>211</v>
-      </c>
       <c r="I488" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J488" s="13"/>
     </row>
@@ -13407,7 +13403,7 @@
         <v>101</v>
       </c>
       <c r="C489" s="15" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D489" s="31">
         <v>2</v>
@@ -13422,7 +13418,7 @@
         <v>145</v>
       </c>
       <c r="H489" s="16" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I489" s="13"/>
       <c r="J489" s="13"/>
@@ -13433,7 +13429,7 @@
         <v>70</v>
       </c>
       <c r="C490" s="15" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D490" s="28">
         <v>2</v>
@@ -13448,7 +13444,7 @@
         <v>73</v>
       </c>
       <c r="H490" s="41" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I490" s="13"/>
       <c r="J490" s="13"/>
@@ -13467,10 +13463,10 @@
         <v>3</v>
       </c>
       <c r="G491" s="33" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H491" s="23" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I491" s="13"/>
       <c r="J491" s="13"/>
@@ -13518,11 +13514,11 @@
         <v>73</v>
       </c>
       <c r="H494" s="11" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="I494" s="10"/>
       <c r="J494" s="12" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="495" spans="1:10" ht="16.5">
@@ -13556,7 +13552,7 @@
         <v>74</v>
       </c>
       <c r="H496" s="24" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I496" s="13"/>
       <c r="J496" s="13"/>
@@ -13582,7 +13578,7 @@
         <v>145</v>
       </c>
       <c r="H497" s="16" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I497" s="13"/>
       <c r="J497" s="13"/>
@@ -13608,11 +13604,11 @@
         <v>76</v>
       </c>
       <c r="H498" s="23" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I498" s="13"/>
       <c r="J498" s="34" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="499" spans="1:10" ht="16.5">
@@ -13646,7 +13642,7 @@
         <v>74</v>
       </c>
       <c r="H500" s="24" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I500" s="13"/>
       <c r="J500" s="13"/>
@@ -13672,7 +13668,7 @@
         <v>145</v>
       </c>
       <c r="H501" s="16" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="I501" s="13"/>
       <c r="J501" s="13"/>
@@ -13695,7 +13691,7 @@
         <v>2</v>
       </c>
       <c r="G502" s="33" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H502" s="23" t="s">
         <v>78</v>
@@ -13760,7 +13756,7 @@
       <c r="H506" s="11"/>
       <c r="I506" s="10"/>
       <c r="J506" s="12" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="507" spans="1:10" ht="16.5">
@@ -13794,7 +13790,7 @@
         <v>74</v>
       </c>
       <c r="H508" s="24" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I508" s="13"/>
       <c r="J508" s="13"/>
@@ -13820,7 +13816,7 @@
         <v>145</v>
       </c>
       <c r="H509" s="16" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I509" s="13"/>
       <c r="J509" s="13"/>
@@ -13846,11 +13842,11 @@
         <v>76</v>
       </c>
       <c r="H510" s="23" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I510" s="13"/>
       <c r="J510" s="34" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="511" spans="1:10" ht="16.5">
@@ -13884,7 +13880,7 @@
         <v>74</v>
       </c>
       <c r="H512" s="24" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I512" s="13"/>
       <c r="J512" s="13"/>
@@ -13910,7 +13906,7 @@
         <v>145</v>
       </c>
       <c r="H513" s="16" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="I513" s="13"/>
       <c r="J513" s="13"/>
@@ -13933,10 +13929,10 @@
         <v>2</v>
       </c>
       <c r="G514" s="33" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H514" s="23" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="I514" s="13"/>
       <c r="J514" s="13"/>
@@ -13961,7 +13957,7 @@
         <v>70</v>
       </c>
       <c r="C516" s="35" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D516" s="30" t="s">
         <v>72</v>
@@ -13972,11 +13968,11 @@
         <v>73</v>
       </c>
       <c r="H516" s="11" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="I516" s="36"/>
       <c r="J516" s="35" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="517" spans="1:10">
@@ -14005,11 +14001,11 @@
         <v>73</v>
       </c>
       <c r="H518" s="11" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="I518" s="36"/>
       <c r="J518" s="35" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="519" spans="1:10">
@@ -14038,11 +14034,11 @@
         <v>73</v>
       </c>
       <c r="H520" s="11" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I520" s="36"/>
       <c r="J520" s="35" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="521" spans="1:10">
@@ -14060,7 +14056,7 @@
         <v>70</v>
       </c>
       <c r="C522" s="35" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D522" s="30" t="s">
         <v>72</v>
@@ -14071,11 +14067,11 @@
         <v>73</v>
       </c>
       <c r="H522" s="11" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="I522" s="36"/>
       <c r="J522" s="35" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="523" spans="1:10">
@@ -14093,7 +14089,7 @@
         <v>70</v>
       </c>
       <c r="C524" s="35" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D524" s="30" t="s">
         <v>72</v>
@@ -14104,11 +14100,11 @@
         <v>73</v>
       </c>
       <c r="H524" s="11" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="I524" s="36"/>
       <c r="J524" s="35" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="525" spans="1:10">
@@ -14126,7 +14122,7 @@
         <v>70</v>
       </c>
       <c r="C526" s="35" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D526" s="30" t="s">
         <v>72</v>
@@ -14137,11 +14133,11 @@
         <v>73</v>
       </c>
       <c r="H526" s="11" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="I526" s="36"/>
       <c r="J526" s="35" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="527" spans="1:10">
@@ -14159,7 +14155,7 @@
         <v>70</v>
       </c>
       <c r="C528" s="35" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D528" s="30" t="s">
         <v>72</v>
@@ -14170,11 +14166,11 @@
         <v>73</v>
       </c>
       <c r="H528" s="11" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I528" s="36"/>
       <c r="J528" s="35" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="529" spans="1:10">
@@ -14221,11 +14217,11 @@
         <v>73</v>
       </c>
       <c r="H532" s="11" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="I532" s="10"/>
       <c r="J532" s="12" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="533" spans="1:10" ht="33">
@@ -14245,7 +14241,7 @@
         <v>73</v>
       </c>
       <c r="H533" s="16" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="I533" s="15"/>
       <c r="J533" s="13"/>
@@ -14323,7 +14319,7 @@
         <v>73</v>
       </c>
       <c r="H537" s="17" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="I537" s="15"/>
       <c r="J537" s="13"/>
@@ -14349,7 +14345,7 @@
         <v>73</v>
       </c>
       <c r="H538" s="17" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="I538" s="15"/>
       <c r="J538" s="13"/>
@@ -14375,7 +14371,7 @@
         <v>73</v>
       </c>
       <c r="H539" s="17" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="I539" s="15"/>
       <c r="J539" s="13"/>
@@ -14476,7 +14472,7 @@
         <v>70</v>
       </c>
       <c r="C544" s="15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D544" s="14">
         <v>3</v>
@@ -14491,7 +14487,7 @@
         <v>73</v>
       </c>
       <c r="H544" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I544" s="15"/>
       <c r="J544" s="13"/>
@@ -14502,7 +14498,7 @@
         <v>70</v>
       </c>
       <c r="C545" s="15" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D545" s="14">
         <v>3</v>
@@ -14517,7 +14513,7 @@
         <v>73</v>
       </c>
       <c r="H545" s="16" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="I545" s="15"/>
       <c r="J545" s="13"/>
@@ -14581,7 +14577,7 @@
         <v>73</v>
       </c>
       <c r="H548" s="27" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I548" s="15"/>
       <c r="J548" s="13"/>
@@ -14607,7 +14603,7 @@
         <v>73</v>
       </c>
       <c r="H549" s="27" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="I549" s="15"/>
       <c r="J549" s="13"/>
@@ -14643,11 +14639,11 @@
         <v>73</v>
       </c>
       <c r="H551" s="11" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="I551" s="10"/>
       <c r="J551" s="12" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="552" spans="1:10" ht="16.5">
@@ -14677,7 +14673,7 @@
         <v>74</v>
       </c>
       <c r="H553" s="24" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I553" s="19" t="s">
         <v>75</v>
@@ -14705,7 +14701,7 @@
         <v>73</v>
       </c>
       <c r="H554" s="16" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I554" s="15"/>
       <c r="J554" s="13"/>
@@ -14731,7 +14727,7 @@
         <v>73</v>
       </c>
       <c r="H555" s="17" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I555" s="15"/>
       <c r="J555" s="13"/>
@@ -14789,7 +14785,7 @@
         <v>145</v>
       </c>
       <c r="H558" s="16" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I558" s="15"/>
       <c r="J558" s="13"/>
@@ -14815,7 +14811,7 @@
         <v>73</v>
       </c>
       <c r="H559" s="16" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="I559" s="15"/>
       <c r="J559" s="13"/>
@@ -14847,7 +14843,7 @@
         <v>74</v>
       </c>
       <c r="H561" s="24" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I561" s="15"/>
       <c r="J561" s="13"/>
@@ -14873,7 +14869,7 @@
         <v>73</v>
       </c>
       <c r="H562" s="27" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I562" s="15"/>
       <c r="J562" s="13"/>
@@ -14899,7 +14895,7 @@
         <v>73</v>
       </c>
       <c r="H563" s="27" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="I563" s="15"/>
       <c r="J563" s="13"/>
@@ -14936,7 +14932,7 @@
         <v>70</v>
       </c>
       <c r="C566" s="35" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D566" s="30">
         <v>1</v>
@@ -14947,11 +14943,11 @@
         <v>73</v>
       </c>
       <c r="H566" s="11" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="I566" s="10"/>
       <c r="J566" s="12" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="567" spans="1:10" ht="16.5">
@@ -14985,7 +14981,7 @@
         <v>74</v>
       </c>
       <c r="H568" s="24" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I568" s="13"/>
       <c r="J568" s="13"/>
@@ -15011,7 +15007,7 @@
         <v>145</v>
       </c>
       <c r="H569" s="16" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I569" s="13"/>
       <c r="J569" s="13"/>
@@ -15022,7 +15018,7 @@
         <v>70</v>
       </c>
       <c r="C570" s="15" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D570" s="28">
         <v>2</v>
@@ -15037,7 +15033,7 @@
         <v>73</v>
       </c>
       <c r="H570" s="27" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="I570" s="13"/>
       <c r="J570" s="34"/>
@@ -15095,7 +15091,7 @@
         <v>74</v>
       </c>
       <c r="H573" s="24" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I573" s="13"/>
       <c r="J573" s="13"/>
@@ -15121,7 +15117,7 @@
         <v>145</v>
       </c>
       <c r="H574" s="16" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="I574" s="13"/>
       <c r="J574" s="13"/>
@@ -15176,13 +15172,13 @@
       </c>
       <c r="F577" s="18"/>
       <c r="G577" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="H577" s="24" t="s">
         <v>210</v>
       </c>
-      <c r="H577" s="24" t="s">
-        <v>211</v>
-      </c>
       <c r="I577" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J577" s="13"/>
     </row>
@@ -15192,7 +15188,7 @@
         <v>101</v>
       </c>
       <c r="C578" s="15" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D578" s="31">
         <v>2</v>
@@ -15207,7 +15203,7 @@
         <v>145</v>
       </c>
       <c r="H578" s="16" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I578" s="13"/>
       <c r="J578" s="13"/>
@@ -15218,7 +15214,7 @@
         <v>70</v>
       </c>
       <c r="C579" s="15" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D579" s="28">
         <v>2</v>
@@ -15233,7 +15229,7 @@
         <v>73</v>
       </c>
       <c r="H579" s="41" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="I579" s="13"/>
       <c r="J579" s="13"/>
@@ -15252,10 +15248,10 @@
         <v>3</v>
       </c>
       <c r="G580" s="33" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H580" s="23" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I580" s="13"/>
       <c r="J580" s="13"/>
@@ -15303,11 +15299,11 @@
         <v>73</v>
       </c>
       <c r="H583" s="11" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="I583" s="10"/>
       <c r="J583" s="12" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="584" spans="1:10" ht="16.5">
@@ -15341,7 +15337,7 @@
         <v>74</v>
       </c>
       <c r="H585" s="24" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I585" s="13"/>
       <c r="J585" s="13"/>
@@ -15367,7 +15363,7 @@
         <v>145</v>
       </c>
       <c r="H586" s="16" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I586" s="13"/>
       <c r="J586" s="13"/>
@@ -15393,11 +15389,11 @@
         <v>76</v>
       </c>
       <c r="H587" s="23" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I587" s="13"/>
       <c r="J587" s="34" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="588" spans="1:10" ht="16.5">
@@ -15431,7 +15427,7 @@
         <v>74</v>
       </c>
       <c r="H589" s="24" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I589" s="13"/>
       <c r="J589" s="13"/>
@@ -15457,7 +15453,7 @@
         <v>145</v>
       </c>
       <c r="H590" s="16" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="I590" s="13"/>
       <c r="J590" s="13"/>
@@ -15480,7 +15476,7 @@
         <v>2</v>
       </c>
       <c r="G591" s="33" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H591" s="23" t="s">
         <v>78</v>
@@ -15543,11 +15539,11 @@
         <v>73</v>
       </c>
       <c r="H595" s="11" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="I595" s="10"/>
       <c r="J595" s="12" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="596" spans="1:10" ht="16.5">
@@ -15581,7 +15577,7 @@
         <v>74</v>
       </c>
       <c r="H597" s="24" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I597" s="13"/>
       <c r="J597" s="13"/>
@@ -15607,7 +15603,7 @@
         <v>145</v>
       </c>
       <c r="H598" s="16" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I598" s="13"/>
       <c r="J598" s="13"/>
@@ -15633,11 +15629,11 @@
         <v>76</v>
       </c>
       <c r="H599" s="23" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I599" s="13"/>
       <c r="J599" s="34" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="600" spans="1:10" ht="16.5">
@@ -15671,7 +15667,7 @@
         <v>74</v>
       </c>
       <c r="H601" s="24" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I601" s="13"/>
       <c r="J601" s="13"/>
@@ -15697,7 +15693,7 @@
         <v>145</v>
       </c>
       <c r="H602" s="16" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="I602" s="13"/>
       <c r="J602" s="13"/>
@@ -15720,7 +15716,7 @@
         <v>2</v>
       </c>
       <c r="G603" s="33" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H603" s="23" t="s">
         <v>78</v>
@@ -15760,7 +15756,7 @@
         <v>70</v>
       </c>
       <c r="C606" s="35" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D606" s="30" t="s">
         <v>72</v>
@@ -15771,11 +15767,11 @@
         <v>73</v>
       </c>
       <c r="H606" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I606" s="36"/>
       <c r="J606" s="35" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="607" spans="1:10">
@@ -15804,11 +15800,11 @@
         <v>73</v>
       </c>
       <c r="H608" s="11" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I608" s="36"/>
       <c r="J608" s="35" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="609" spans="1:10">
@@ -15837,11 +15833,11 @@
         <v>73</v>
       </c>
       <c r="H610" s="11" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I610" s="36"/>
       <c r="J610" s="35" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="611" spans="1:10">
@@ -15859,7 +15855,7 @@
         <v>70</v>
       </c>
       <c r="C612" s="35" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D612" s="30" t="s">
         <v>72</v>
@@ -15870,11 +15866,11 @@
         <v>73</v>
       </c>
       <c r="H612" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I612" s="36"/>
       <c r="J612" s="35" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="613" spans="1:10">
@@ -15892,7 +15888,7 @@
         <v>70</v>
       </c>
       <c r="C614" s="35" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D614" s="30" t="s">
         <v>72</v>
@@ -15903,11 +15899,11 @@
         <v>73</v>
       </c>
       <c r="H614" s="11" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="I614" s="36"/>
       <c r="J614" s="35" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="615" spans="1:10">
@@ -15925,7 +15921,7 @@
         <v>70</v>
       </c>
       <c r="C616" s="35" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D616" s="30" t="s">
         <v>72</v>
@@ -15936,11 +15932,11 @@
         <v>73</v>
       </c>
       <c r="H616" s="11" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I616" s="36"/>
       <c r="J616" s="35" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="617" spans="1:10">
@@ -15958,7 +15954,7 @@
         <v>70</v>
       </c>
       <c r="C618" s="35" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D618" s="30" t="s">
         <v>72</v>
@@ -15969,11 +15965,11 @@
         <v>73</v>
       </c>
       <c r="H618" s="11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I618" s="36"/>
       <c r="J618" s="35" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/对话表.xlsx
+++ b/Excel/对话表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xinxinhe\Documents\2026MasterHouse\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B72B0908-FE57-43F7-AF42-4266A30B6C86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FB74B52-2F56-4D24-AC9B-0DBCC7C99A1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2141" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2141" uniqueCount="432">
   <si>
     <t>对话组ID</t>
   </si>
@@ -1554,6 +1554,10 @@
   </si>
   <si>
     <t>cheetah_开心</t>
+  </si>
+  <si>
+    <t>请快点，我的时间很宝贵。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3482,7 +3486,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J618"/>
+  <dimension ref="A1:J620"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
@@ -12774,10 +12778,10 @@
     <row r="459" spans="1:10" ht="16.5">
       <c r="A459" s="14"/>
       <c r="B459" s="15" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="C459" s="15" t="s">
-        <v>83</v>
+        <v>135</v>
       </c>
       <c r="D459" s="25">
         <v>5</v>
@@ -12817,8 +12821,8 @@
       <c r="G460" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="H460" s="27" t="s">
-        <v>193</v>
+      <c r="H460" s="75" t="s">
+        <v>431</v>
       </c>
       <c r="I460" s="15"/>
       <c r="J460" s="13"/>
@@ -12924,7 +12928,7 @@
     <row r="466" spans="1:10" ht="16.5">
       <c r="A466" s="14"/>
       <c r="B466" s="15" t="s">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="C466" s="15" t="s">
         <v>83</v>
@@ -12955,7 +12959,7 @@
       <c r="E467" s="14"/>
       <c r="F467" s="14"/>
       <c r="G467" s="15"/>
-      <c r="H467" s="16"/>
+      <c r="H467" s="17"/>
       <c r="I467" s="15"/>
       <c r="J467" s="13"/>
     </row>
@@ -12963,44 +12967,30 @@
       <c r="A468" s="14"/>
       <c r="B468" s="15"/>
       <c r="C468" s="15"/>
-      <c r="D468" s="18">
-        <v>2</v>
-      </c>
-      <c r="E468" s="18">
-        <v>2</v>
-      </c>
+      <c r="D468" s="14"/>
+      <c r="E468" s="14"/>
       <c r="F468" s="14"/>
-      <c r="G468" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="H468" s="24" t="s">
-        <v>137</v>
-      </c>
+      <c r="G468" s="15"/>
+      <c r="H468" s="16"/>
       <c r="I468" s="15"/>
       <c r="J468" s="13"/>
     </row>
     <row r="469" spans="1:10" ht="16.5">
       <c r="A469" s="14"/>
-      <c r="B469" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="C469" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="D469" s="14">
-        <v>2</v>
-      </c>
-      <c r="E469" s="14">
-        <v>2</v>
-      </c>
-      <c r="F469" s="14">
-        <v>1</v>
-      </c>
-      <c r="G469" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="H469" s="17" t="s">
-        <v>390</v>
+      <c r="B469" s="15"/>
+      <c r="C469" s="15"/>
+      <c r="D469" s="18">
+        <v>2</v>
+      </c>
+      <c r="E469" s="18">
+        <v>2</v>
+      </c>
+      <c r="F469" s="14"/>
+      <c r="G469" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="H469" s="24" t="s">
+        <v>137</v>
       </c>
       <c r="I469" s="15"/>
       <c r="J469" s="13"/>
@@ -13011,7 +13001,7 @@
         <v>101</v>
       </c>
       <c r="C470" s="15" t="s">
-        <v>83</v>
+        <v>135</v>
       </c>
       <c r="D470" s="14">
         <v>2</v>
@@ -13020,26 +13010,40 @@
         <v>2</v>
       </c>
       <c r="F470" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G470" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="H470" s="16" t="s">
-        <v>391</v>
+        <v>145</v>
+      </c>
+      <c r="H470" s="17" t="s">
+        <v>390</v>
       </c>
       <c r="I470" s="15"/>
       <c r="J470" s="13"/>
     </row>
     <row r="471" spans="1:10" ht="16.5">
       <c r="A471" s="14"/>
-      <c r="B471" s="15"/>
-      <c r="C471" s="15"/>
-      <c r="D471" s="14"/>
-      <c r="E471" s="14"/>
-      <c r="F471" s="14"/>
-      <c r="G471" s="15"/>
-      <c r="H471" s="16"/>
+      <c r="B471" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C471" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="D471" s="14">
+        <v>2</v>
+      </c>
+      <c r="E471" s="14">
+        <v>2</v>
+      </c>
+      <c r="F471" s="14">
+        <v>2</v>
+      </c>
+      <c r="G471" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="H471" s="16" t="s">
+        <v>391</v>
+      </c>
       <c r="I471" s="15"/>
       <c r="J471" s="13"/>
     </row>
@@ -13047,183 +13051,157 @@
       <c r="A472" s="14"/>
       <c r="B472" s="15"/>
       <c r="C472" s="15"/>
-      <c r="D472" s="18">
-        <v>2</v>
-      </c>
-      <c r="E472" s="18">
-        <v>3</v>
-      </c>
+      <c r="D472" s="14"/>
+      <c r="E472" s="14"/>
       <c r="F472" s="14"/>
-      <c r="G472" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="H472" s="24" t="s">
-        <v>160</v>
-      </c>
+      <c r="G472" s="15"/>
+      <c r="H472" s="16"/>
       <c r="I472" s="15"/>
       <c r="J472" s="13"/>
     </row>
     <row r="473" spans="1:10" ht="16.5">
       <c r="A473" s="14"/>
-      <c r="B473" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="C473" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="D473" s="25">
-        <v>2</v>
-      </c>
-      <c r="E473" s="25">
-        <v>3</v>
-      </c>
-      <c r="F473" s="25">
-        <v>1</v>
-      </c>
-      <c r="G473" s="26" t="s">
-        <v>73</v>
-      </c>
-      <c r="H473" s="27" t="s">
-        <v>394</v>
-      </c>
+      <c r="B473" s="15"/>
+      <c r="C473" s="15"/>
+      <c r="D473" s="14"/>
+      <c r="E473" s="14"/>
+      <c r="F473" s="14"/>
+      <c r="G473" s="15"/>
+      <c r="H473" s="16"/>
       <c r="I473" s="15"/>
       <c r="J473" s="13"/>
     </row>
     <row r="474" spans="1:10" ht="16.5">
       <c r="A474" s="14"/>
-      <c r="B474" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="C474" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="D474" s="28">
-        <v>2</v>
-      </c>
-      <c r="E474" s="28">
+      <c r="B474" s="15"/>
+      <c r="C474" s="15"/>
+      <c r="D474" s="18">
+        <v>2</v>
+      </c>
+      <c r="E474" s="18">
         <v>3</v>
       </c>
-      <c r="F474" s="28">
-        <v>2</v>
-      </c>
-      <c r="G474" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="H474" s="75" t="s">
-        <v>395</v>
+      <c r="F474" s="14"/>
+      <c r="G474" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="H474" s="24" t="s">
+        <v>160</v>
       </c>
       <c r="I474" s="15"/>
       <c r="J474" s="13"/>
     </row>
     <row r="475" spans="1:10" ht="16.5">
       <c r="A475" s="14"/>
-      <c r="B475" s="15"/>
-      <c r="C475" s="15"/>
-      <c r="D475" s="18"/>
-      <c r="E475" s="18"/>
-      <c r="F475" s="14"/>
-      <c r="G475" s="19"/>
-      <c r="H475" s="24"/>
+      <c r="B475" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C475" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="D475" s="25">
+        <v>2</v>
+      </c>
+      <c r="E475" s="25">
+        <v>3</v>
+      </c>
+      <c r="F475" s="25">
+        <v>1</v>
+      </c>
+      <c r="G475" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="H475" s="27" t="s">
+        <v>394</v>
+      </c>
       <c r="I475" s="15"/>
       <c r="J475" s="13"/>
     </row>
     <row r="476" spans="1:10" ht="16.5">
       <c r="A476" s="14"/>
-      <c r="B476" s="15"/>
-      <c r="C476" s="15"/>
-      <c r="D476" s="14"/>
-      <c r="E476" s="14"/>
-      <c r="F476" s="14"/>
-      <c r="G476" s="15"/>
-      <c r="H476" s="16"/>
+      <c r="B476" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C476" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="D476" s="28">
+        <v>2</v>
+      </c>
+      <c r="E476" s="28">
+        <v>3</v>
+      </c>
+      <c r="F476" s="28">
+        <v>2</v>
+      </c>
+      <c r="G476" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="H476" s="75" t="s">
+        <v>395</v>
+      </c>
       <c r="I476" s="15"/>
       <c r="J476" s="13"/>
     </row>
-    <row r="477" spans="1:10" ht="21">
-      <c r="A477" s="9">
+    <row r="477" spans="1:10" ht="16.5">
+      <c r="A477" s="14"/>
+      <c r="B477" s="15"/>
+      <c r="C477" s="15"/>
+      <c r="D477" s="18"/>
+      <c r="E477" s="18"/>
+      <c r="F477" s="14"/>
+      <c r="G477" s="19"/>
+      <c r="H477" s="24"/>
+      <c r="I477" s="15"/>
+      <c r="J477" s="13"/>
+    </row>
+    <row r="478" spans="1:10" ht="16.5">
+      <c r="A478" s="14"/>
+      <c r="B478" s="15"/>
+      <c r="C478" s="15"/>
+      <c r="D478" s="14"/>
+      <c r="E478" s="14"/>
+      <c r="F478" s="14"/>
+      <c r="G478" s="15"/>
+      <c r="H478" s="16"/>
+      <c r="I478" s="15"/>
+      <c r="J478" s="13"/>
+    </row>
+    <row r="479" spans="1:10" ht="21">
+      <c r="A479" s="9">
         <v>30501</v>
       </c>
-      <c r="B477" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C477" s="35" t="s">
+      <c r="B479" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C479" s="35" t="s">
         <v>83</v>
       </c>
-      <c r="D477" s="30">
-        <v>1</v>
-      </c>
-      <c r="E477" s="30"/>
-      <c r="F477" s="30"/>
-      <c r="G477" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H477" s="11" t="s">
+      <c r="D479" s="30">
+        <v>1</v>
+      </c>
+      <c r="E479" s="30"/>
+      <c r="F479" s="30"/>
+      <c r="G479" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="H479" s="11" t="s">
         <v>396</v>
       </c>
-      <c r="I477" s="10"/>
-      <c r="J477" s="12" t="s">
+      <c r="I479" s="10"/>
+      <c r="J479" s="12" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="478" spans="1:10" ht="16.5">
-      <c r="A478" s="31"/>
-      <c r="B478" s="13"/>
-      <c r="C478" s="13"/>
-      <c r="D478" s="31"/>
-      <c r="E478" s="31"/>
-      <c r="F478" s="31"/>
-      <c r="G478" s="13"/>
-      <c r="H478" s="16"/>
-      <c r="I478" s="13"/>
-      <c r="J478" s="13"/>
-    </row>
-    <row r="479" spans="1:10" ht="16.5">
-      <c r="A479" s="31"/>
-      <c r="B479" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="C479" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="D479" s="18">
-        <v>2</v>
-      </c>
-      <c r="E479" s="18">
-        <v>1</v>
-      </c>
-      <c r="F479" s="18"/>
-      <c r="G479" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="H479" s="24" t="s">
-        <v>153</v>
-      </c>
-      <c r="I479" s="13"/>
-      <c r="J479" s="13"/>
     </row>
     <row r="480" spans="1:10" ht="16.5">
       <c r="A480" s="31"/>
-      <c r="B480" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="C480" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="D480" s="31">
-        <v>2</v>
-      </c>
-      <c r="E480" s="31">
-        <v>1</v>
-      </c>
-      <c r="F480" s="31">
-        <v>1</v>
-      </c>
-      <c r="G480" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="H480" s="16" t="s">
-        <v>206</v>
-      </c>
+      <c r="B480" s="13"/>
+      <c r="C480" s="13"/>
+      <c r="D480" s="31"/>
+      <c r="E480" s="31"/>
+      <c r="F480" s="31"/>
+      <c r="G480" s="13"/>
+      <c r="H480" s="16"/>
       <c r="I480" s="13"/>
       <c r="J480" s="13"/>
     </row>
@@ -13235,351 +13213,351 @@
       <c r="C481" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="D481" s="28">
-        <v>2</v>
-      </c>
-      <c r="E481" s="31">
-        <v>1</v>
-      </c>
-      <c r="F481" s="28">
-        <v>2</v>
-      </c>
-      <c r="G481" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="H481" s="75" t="s">
-        <v>395</v>
+      <c r="D481" s="18">
+        <v>2</v>
+      </c>
+      <c r="E481" s="18">
+        <v>1</v>
+      </c>
+      <c r="F481" s="18"/>
+      <c r="G481" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="H481" s="24" t="s">
+        <v>153</v>
       </c>
       <c r="I481" s="13"/>
-      <c r="J481" s="34"/>
+      <c r="J481" s="13"/>
     </row>
     <row r="482" spans="1:10" ht="16.5">
       <c r="A482" s="31"/>
-      <c r="B482" s="13"/>
-      <c r="C482" s="13"/>
-      <c r="D482" s="14">
-        <v>2</v>
-      </c>
-      <c r="E482" s="14">
-        <v>1</v>
-      </c>
-      <c r="F482" s="14">
-        <v>3</v>
-      </c>
-      <c r="G482" s="22" t="s">
-        <v>76</v>
-      </c>
-      <c r="H482" s="23" t="s">
-        <v>144</v>
+      <c r="B482" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C482" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="D482" s="31">
+        <v>2</v>
+      </c>
+      <c r="E482" s="31">
+        <v>1</v>
+      </c>
+      <c r="F482" s="31">
+        <v>1</v>
+      </c>
+      <c r="G482" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="H482" s="16" t="s">
+        <v>206</v>
       </c>
       <c r="I482" s="13"/>
       <c r="J482" s="13"/>
     </row>
     <row r="483" spans="1:10" ht="16.5">
       <c r="A483" s="31"/>
-      <c r="B483" s="15"/>
-      <c r="C483" s="15"/>
-      <c r="D483" s="32"/>
-      <c r="E483" s="32"/>
-      <c r="F483" s="32"/>
-      <c r="G483" s="33"/>
-      <c r="H483" s="50"/>
+      <c r="B483" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C483" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="D483" s="28">
+        <v>2</v>
+      </c>
+      <c r="E483" s="31">
+        <v>1</v>
+      </c>
+      <c r="F483" s="28">
+        <v>2</v>
+      </c>
+      <c r="G483" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="H483" s="75" t="s">
+        <v>395</v>
+      </c>
       <c r="I483" s="13"/>
-      <c r="J483" s="13"/>
+      <c r="J483" s="34"/>
     </row>
     <row r="484" spans="1:10" ht="16.5">
       <c r="A484" s="31"/>
-      <c r="B484" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="C484" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="D484" s="18">
-        <v>2</v>
-      </c>
-      <c r="E484" s="18">
-        <v>2</v>
-      </c>
-      <c r="F484" s="18"/>
-      <c r="G484" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="H484" s="24" t="s">
-        <v>154</v>
+      <c r="B484" s="13"/>
+      <c r="C484" s="13"/>
+      <c r="D484" s="14">
+        <v>2</v>
+      </c>
+      <c r="E484" s="14">
+        <v>1</v>
+      </c>
+      <c r="F484" s="14">
+        <v>3</v>
+      </c>
+      <c r="G484" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="H484" s="23" t="s">
+        <v>144</v>
       </c>
       <c r="I484" s="13"/>
       <c r="J484" s="13"/>
     </row>
-    <row r="485" spans="1:10" ht="33">
+    <row r="485" spans="1:10" ht="16.5">
       <c r="A485" s="31"/>
-      <c r="B485" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="C485" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="D485" s="31">
-        <v>2</v>
-      </c>
-      <c r="E485" s="31">
-        <v>2</v>
-      </c>
-      <c r="F485" s="31">
-        <v>1</v>
-      </c>
-      <c r="G485" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="H485" s="16" t="s">
-        <v>300</v>
-      </c>
+      <c r="B485" s="15"/>
+      <c r="C485" s="15"/>
+      <c r="D485" s="32"/>
+      <c r="E485" s="32"/>
+      <c r="F485" s="32"/>
+      <c r="G485" s="33"/>
+      <c r="H485" s="50"/>
       <c r="I485" s="13"/>
       <c r="J485" s="13"/>
     </row>
     <row r="486" spans="1:10" ht="16.5">
       <c r="A486" s="31"/>
-      <c r="B486" s="15"/>
-      <c r="C486" s="15"/>
-      <c r="D486" s="14">
-        <v>2</v>
-      </c>
-      <c r="E486" s="14">
-        <v>2</v>
-      </c>
-      <c r="F486" s="14">
-        <v>2</v>
-      </c>
-      <c r="G486" s="22" t="s">
-        <v>76</v>
-      </c>
-      <c r="H486" s="23" t="s">
-        <v>78</v>
+      <c r="B486" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C486" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="D486" s="18">
+        <v>2</v>
+      </c>
+      <c r="E486" s="18">
+        <v>2</v>
+      </c>
+      <c r="F486" s="18"/>
+      <c r="G486" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="H486" s="24" t="s">
+        <v>154</v>
       </c>
       <c r="I486" s="13"/>
       <c r="J486" s="13"/>
     </row>
-    <row r="487" spans="1:10" ht="16.5">
+    <row r="487" spans="1:10" ht="33">
       <c r="A487" s="31"/>
-      <c r="B487" s="15"/>
-      <c r="C487" s="15"/>
-      <c r="D487" s="31"/>
-      <c r="E487" s="31"/>
-      <c r="F487" s="31"/>
-      <c r="G487" s="13"/>
-      <c r="H487" s="16"/>
+      <c r="B487" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C487" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="D487" s="31">
+        <v>2</v>
+      </c>
+      <c r="E487" s="31">
+        <v>2</v>
+      </c>
+      <c r="F487" s="31">
+        <v>1</v>
+      </c>
+      <c r="G487" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="H487" s="16" t="s">
+        <v>300</v>
+      </c>
       <c r="I487" s="13"/>
       <c r="J487" s="13"/>
     </row>
     <row r="488" spans="1:10" ht="16.5">
       <c r="A488" s="31"/>
-      <c r="B488" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="C488" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="D488" s="18">
-        <v>2</v>
-      </c>
-      <c r="E488" s="18">
-        <v>3</v>
-      </c>
-      <c r="F488" s="18"/>
-      <c r="G488" s="19" t="s">
-        <v>209</v>
-      </c>
-      <c r="H488" s="24" t="s">
-        <v>210</v>
-      </c>
-      <c r="I488" s="13" t="s">
-        <v>200</v>
-      </c>
+      <c r="B488" s="15"/>
+      <c r="C488" s="15"/>
+      <c r="D488" s="14">
+        <v>2</v>
+      </c>
+      <c r="E488" s="14">
+        <v>2</v>
+      </c>
+      <c r="F488" s="14">
+        <v>2</v>
+      </c>
+      <c r="G488" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="H488" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="I488" s="13"/>
       <c r="J488" s="13"/>
     </row>
     <row r="489" spans="1:10" ht="16.5">
       <c r="A489" s="31"/>
-      <c r="B489" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="C489" s="15" t="s">
-        <v>207</v>
-      </c>
-      <c r="D489" s="31">
-        <v>2</v>
-      </c>
-      <c r="E489" s="18">
-        <v>3</v>
-      </c>
-      <c r="F489" s="31">
-        <v>1</v>
-      </c>
-      <c r="G489" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="H489" s="16" t="s">
-        <v>211</v>
-      </c>
+      <c r="B489" s="15"/>
+      <c r="C489" s="15"/>
+      <c r="D489" s="31"/>
+      <c r="E489" s="31"/>
+      <c r="F489" s="31"/>
+      <c r="G489" s="13"/>
+      <c r="H489" s="16"/>
       <c r="I489" s="13"/>
       <c r="J489" s="13"/>
     </row>
     <row r="490" spans="1:10" ht="16.5">
       <c r="A490" s="31"/>
       <c r="B490" s="15" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="C490" s="15" t="s">
-        <v>397</v>
-      </c>
-      <c r="D490" s="28">
-        <v>2</v>
-      </c>
-      <c r="E490" s="28">
+        <v>135</v>
+      </c>
+      <c r="D490" s="18">
+        <v>2</v>
+      </c>
+      <c r="E490" s="18">
         <v>3</v>
       </c>
-      <c r="F490" s="28">
-        <v>2</v>
-      </c>
-      <c r="G490" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="H490" s="41" t="s">
-        <v>398</v>
-      </c>
-      <c r="I490" s="13"/>
+      <c r="F490" s="18"/>
+      <c r="G490" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="H490" s="24" t="s">
+        <v>210</v>
+      </c>
+      <c r="I490" s="13" t="s">
+        <v>200</v>
+      </c>
       <c r="J490" s="13"/>
     </row>
     <row r="491" spans="1:10" ht="16.5">
       <c r="A491" s="31"/>
-      <c r="B491" s="15"/>
-      <c r="C491" s="15"/>
-      <c r="D491" s="32">
-        <v>2</v>
-      </c>
-      <c r="E491" s="32">
+      <c r="B491" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C491" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="D491" s="31">
+        <v>2</v>
+      </c>
+      <c r="E491" s="18">
         <v>3</v>
       </c>
-      <c r="F491" s="32">
-        <v>3</v>
-      </c>
-      <c r="G491" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="H491" s="23" t="s">
-        <v>212</v>
+      <c r="F491" s="31">
+        <v>1</v>
+      </c>
+      <c r="G491" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="H491" s="16" t="s">
+        <v>211</v>
       </c>
       <c r="I491" s="13"/>
       <c r="J491" s="13"/>
     </row>
     <row r="492" spans="1:10" ht="16.5">
-      <c r="A492" s="14"/>
-      <c r="B492" s="15"/>
-      <c r="C492" s="15"/>
-      <c r="D492" s="14"/>
-      <c r="E492" s="14"/>
-      <c r="F492" s="14"/>
-      <c r="G492" s="15"/>
-      <c r="H492" s="16"/>
-      <c r="I492" s="15"/>
+      <c r="A492" s="31"/>
+      <c r="B492" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C492" s="15" t="s">
+        <v>397</v>
+      </c>
+      <c r="D492" s="28">
+        <v>2</v>
+      </c>
+      <c r="E492" s="28">
+        <v>3</v>
+      </c>
+      <c r="F492" s="28">
+        <v>2</v>
+      </c>
+      <c r="G492" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="H492" s="41" t="s">
+        <v>398</v>
+      </c>
+      <c r="I492" s="13"/>
       <c r="J492" s="13"/>
     </row>
     <row r="493" spans="1:10" ht="16.5">
-      <c r="A493" s="14"/>
+      <c r="A493" s="31"/>
       <c r="B493" s="15"/>
       <c r="C493" s="15"/>
-      <c r="D493" s="14"/>
-      <c r="E493" s="14"/>
-      <c r="F493" s="14"/>
-      <c r="G493" s="15"/>
-      <c r="H493" s="16"/>
-      <c r="I493" s="15"/>
+      <c r="D493" s="32">
+        <v>2</v>
+      </c>
+      <c r="E493" s="32">
+        <v>3</v>
+      </c>
+      <c r="F493" s="32">
+        <v>3</v>
+      </c>
+      <c r="G493" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="H493" s="23" t="s">
+        <v>212</v>
+      </c>
+      <c r="I493" s="13"/>
       <c r="J493" s="13"/>
     </row>
-    <row r="494" spans="1:10" ht="33">
-      <c r="A494" s="9">
+    <row r="494" spans="1:10" ht="16.5">
+      <c r="A494" s="14"/>
+      <c r="B494" s="15"/>
+      <c r="C494" s="15"/>
+      <c r="D494" s="14"/>
+      <c r="E494" s="14"/>
+      <c r="F494" s="14"/>
+      <c r="G494" s="15"/>
+      <c r="H494" s="16"/>
+      <c r="I494" s="15"/>
+      <c r="J494" s="13"/>
+    </row>
+    <row r="495" spans="1:10" ht="16.5">
+      <c r="A495" s="14"/>
+      <c r="B495" s="15"/>
+      <c r="C495" s="15"/>
+      <c r="D495" s="14"/>
+      <c r="E495" s="14"/>
+      <c r="F495" s="14"/>
+      <c r="G495" s="15"/>
+      <c r="H495" s="16"/>
+      <c r="I495" s="15"/>
+      <c r="J495" s="13"/>
+    </row>
+    <row r="496" spans="1:10" ht="33">
+      <c r="A496" s="9">
         <v>30502</v>
       </c>
-      <c r="B494" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C494" s="35" t="s">
+      <c r="B496" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C496" s="35" t="s">
         <v>83</v>
       </c>
-      <c r="D494" s="30">
-        <v>1</v>
-      </c>
-      <c r="E494" s="30"/>
-      <c r="F494" s="30"/>
-      <c r="G494" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H494" s="11" t="s">
+      <c r="D496" s="30">
+        <v>1</v>
+      </c>
+      <c r="E496" s="30"/>
+      <c r="F496" s="30"/>
+      <c r="G496" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="H496" s="11" t="s">
         <v>399</v>
       </c>
-      <c r="I494" s="10"/>
-      <c r="J494" s="12" t="s">
+      <c r="I496" s="10"/>
+      <c r="J496" s="12" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="495" spans="1:10" ht="16.5">
-      <c r="A495" s="31"/>
-      <c r="B495" s="13"/>
-      <c r="C495" s="13"/>
-      <c r="D495" s="31"/>
-      <c r="E495" s="31"/>
-      <c r="F495" s="31"/>
-      <c r="G495" s="13"/>
-      <c r="H495" s="16"/>
-      <c r="I495" s="13"/>
-      <c r="J495" s="13"/>
-    </row>
-    <row r="496" spans="1:10" ht="16.5">
-      <c r="A496" s="31"/>
-      <c r="B496" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="C496" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="D496" s="18">
-        <v>2</v>
-      </c>
-      <c r="E496" s="18">
-        <v>1</v>
-      </c>
-      <c r="F496" s="18"/>
-      <c r="G496" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="H496" s="24" t="s">
-        <v>153</v>
-      </c>
-      <c r="I496" s="13"/>
-      <c r="J496" s="13"/>
     </row>
     <row r="497" spans="1:10" ht="16.5">
       <c r="A497" s="31"/>
-      <c r="B497" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="C497" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="D497" s="31">
-        <v>2</v>
-      </c>
-      <c r="E497" s="31">
-        <v>1</v>
-      </c>
-      <c r="F497" s="31">
-        <v>1</v>
-      </c>
-      <c r="G497" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="H497" s="16" t="s">
-        <v>156</v>
-      </c>
+      <c r="B497" s="13"/>
+      <c r="C497" s="13"/>
+      <c r="D497" s="31"/>
+      <c r="E497" s="31"/>
+      <c r="F497" s="31"/>
+      <c r="G497" s="13"/>
+      <c r="H497" s="16"/>
       <c r="I497" s="13"/>
       <c r="J497" s="13"/>
     </row>
@@ -13591,35 +13569,45 @@
       <c r="C498" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="D498" s="32">
-        <v>2</v>
-      </c>
-      <c r="E498" s="32">
-        <v>1</v>
-      </c>
-      <c r="F498" s="32">
-        <v>2</v>
-      </c>
-      <c r="G498" s="33" t="s">
-        <v>76</v>
-      </c>
-      <c r="H498" s="23" t="s">
-        <v>152</v>
+      <c r="D498" s="18">
+        <v>2</v>
+      </c>
+      <c r="E498" s="18">
+        <v>1</v>
+      </c>
+      <c r="F498" s="18"/>
+      <c r="G498" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="H498" s="24" t="s">
+        <v>153</v>
       </c>
       <c r="I498" s="13"/>
-      <c r="J498" s="34" t="s">
-        <v>173</v>
-      </c>
+      <c r="J498" s="13"/>
     </row>
     <row r="499" spans="1:10" ht="16.5">
       <c r="A499" s="31"/>
-      <c r="B499" s="13"/>
-      <c r="C499" s="13"/>
-      <c r="D499" s="31"/>
-      <c r="E499" s="31"/>
-      <c r="F499" s="31"/>
-      <c r="G499" s="13"/>
-      <c r="H499" s="16"/>
+      <c r="B499" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C499" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="D499" s="31">
+        <v>2</v>
+      </c>
+      <c r="E499" s="31">
+        <v>1</v>
+      </c>
+      <c r="F499" s="31">
+        <v>1</v>
+      </c>
+      <c r="G499" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="H499" s="16" t="s">
+        <v>156</v>
+      </c>
       <c r="I499" s="13"/>
       <c r="J499" s="13"/>
     </row>
@@ -13631,45 +13619,35 @@
       <c r="C500" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="D500" s="18">
-        <v>2</v>
-      </c>
-      <c r="E500" s="18">
-        <v>2</v>
-      </c>
-      <c r="F500" s="18"/>
-      <c r="G500" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="H500" s="24" t="s">
-        <v>154</v>
+      <c r="D500" s="32">
+        <v>2</v>
+      </c>
+      <c r="E500" s="32">
+        <v>1</v>
+      </c>
+      <c r="F500" s="32">
+        <v>2</v>
+      </c>
+      <c r="G500" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="H500" s="23" t="s">
+        <v>152</v>
       </c>
       <c r="I500" s="13"/>
-      <c r="J500" s="13"/>
-    </row>
-    <row r="501" spans="1:10" ht="33">
+      <c r="J500" s="34" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="501" spans="1:10" ht="16.5">
       <c r="A501" s="31"/>
-      <c r="B501" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="C501" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="D501" s="31">
-        <v>2</v>
-      </c>
-      <c r="E501" s="31">
-        <v>2</v>
-      </c>
-      <c r="F501" s="31">
-        <v>1</v>
-      </c>
-      <c r="G501" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="H501" s="16" t="s">
-        <v>300</v>
-      </c>
+      <c r="B501" s="13"/>
+      <c r="C501" s="13"/>
+      <c r="D501" s="31"/>
+      <c r="E501" s="31"/>
+      <c r="F501" s="31"/>
+      <c r="G501" s="13"/>
+      <c r="H501" s="16"/>
       <c r="I501" s="13"/>
       <c r="J501" s="13"/>
     </row>
@@ -13681,45 +13659,71 @@
       <c r="C502" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="D502" s="32">
-        <v>2</v>
-      </c>
-      <c r="E502" s="32">
-        <v>2</v>
-      </c>
-      <c r="F502" s="32">
-        <v>2</v>
-      </c>
-      <c r="G502" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="H502" s="23" t="s">
-        <v>78</v>
+      <c r="D502" s="18">
+        <v>2</v>
+      </c>
+      <c r="E502" s="18">
+        <v>2</v>
+      </c>
+      <c r="F502" s="18"/>
+      <c r="G502" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="H502" s="24" t="s">
+        <v>154</v>
       </c>
       <c r="I502" s="13"/>
       <c r="J502" s="13"/>
     </row>
-    <row r="503" spans="1:10" ht="16.5">
+    <row r="503" spans="1:10" ht="33">
       <c r="A503" s="31"/>
-      <c r="B503" s="13"/>
-      <c r="C503" s="13"/>
-      <c r="D503" s="31"/>
-      <c r="E503" s="31"/>
-      <c r="F503" s="31"/>
-      <c r="G503" s="13"/>
-      <c r="H503" s="16"/>
+      <c r="B503" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C503" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="D503" s="31">
+        <v>2</v>
+      </c>
+      <c r="E503" s="31">
+        <v>2</v>
+      </c>
+      <c r="F503" s="31">
+        <v>1</v>
+      </c>
+      <c r="G503" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="H503" s="16" t="s">
+        <v>300</v>
+      </c>
       <c r="I503" s="13"/>
       <c r="J503" s="13"/>
     </row>
     <row r="504" spans="1:10" ht="16.5">
       <c r="A504" s="31"/>
-      <c r="B504" s="13"/>
-      <c r="C504" s="13"/>
-      <c r="D504" s="31"/>
-      <c r="E504" s="31"/>
-      <c r="F504" s="31"/>
-      <c r="G504" s="13"/>
-      <c r="H504" s="16"/>
+      <c r="B504" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C504" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="D504" s="32">
+        <v>2</v>
+      </c>
+      <c r="E504" s="32">
+        <v>2</v>
+      </c>
+      <c r="F504" s="32">
+        <v>2</v>
+      </c>
+      <c r="G504" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="H504" s="23" t="s">
+        <v>78</v>
+      </c>
       <c r="I504" s="13"/>
       <c r="J504" s="13"/>
     </row>
@@ -13735,29 +13739,17 @@
       <c r="I505" s="13"/>
       <c r="J505" s="13"/>
     </row>
-    <row r="506" spans="1:10" ht="21">
-      <c r="A506" s="9">
-        <v>30503</v>
-      </c>
-      <c r="B506" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C506" s="35" t="s">
-        <v>83</v>
-      </c>
-      <c r="D506" s="30">
-        <v>1</v>
-      </c>
-      <c r="E506" s="30"/>
-      <c r="F506" s="30"/>
-      <c r="G506" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H506" s="11"/>
-      <c r="I506" s="10"/>
-      <c r="J506" s="12" t="s">
-        <v>289</v>
-      </c>
+    <row r="506" spans="1:10" ht="16.5">
+      <c r="A506" s="31"/>
+      <c r="B506" s="13"/>
+      <c r="C506" s="13"/>
+      <c r="D506" s="31"/>
+      <c r="E506" s="31"/>
+      <c r="F506" s="31"/>
+      <c r="G506" s="13"/>
+      <c r="H506" s="16"/>
+      <c r="I506" s="13"/>
+      <c r="J506" s="13"/>
     </row>
     <row r="507" spans="1:10" ht="16.5">
       <c r="A507" s="31"/>
@@ -13771,53 +13763,39 @@
       <c r="I507" s="13"/>
       <c r="J507" s="13"/>
     </row>
-    <row r="508" spans="1:10" ht="16.5">
-      <c r="A508" s="31"/>
-      <c r="B508" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="C508" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="D508" s="18">
-        <v>2</v>
-      </c>
-      <c r="E508" s="18">
-        <v>1</v>
-      </c>
-      <c r="F508" s="18"/>
-      <c r="G508" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="H508" s="24" t="s">
-        <v>153</v>
-      </c>
-      <c r="I508" s="13"/>
-      <c r="J508" s="13"/>
+    <row r="508" spans="1:10" ht="21">
+      <c r="A508" s="9">
+        <v>30503</v>
+      </c>
+      <c r="B508" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C508" s="35" t="s">
+        <v>83</v>
+      </c>
+      <c r="D508" s="30">
+        <v>1</v>
+      </c>
+      <c r="E508" s="30"/>
+      <c r="F508" s="30"/>
+      <c r="G508" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="H508" s="11"/>
+      <c r="I508" s="10"/>
+      <c r="J508" s="12" t="s">
+        <v>289</v>
+      </c>
     </row>
     <row r="509" spans="1:10" ht="16.5">
       <c r="A509" s="31"/>
-      <c r="B509" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="C509" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="D509" s="31">
-        <v>2</v>
-      </c>
-      <c r="E509" s="31">
-        <v>1</v>
-      </c>
-      <c r="F509" s="31">
-        <v>1</v>
-      </c>
-      <c r="G509" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="H509" s="16" t="s">
-        <v>156</v>
-      </c>
+      <c r="B509" s="13"/>
+      <c r="C509" s="13"/>
+      <c r="D509" s="31"/>
+      <c r="E509" s="31"/>
+      <c r="F509" s="31"/>
+      <c r="G509" s="13"/>
+      <c r="H509" s="16"/>
       <c r="I509" s="13"/>
       <c r="J509" s="13"/>
     </row>
@@ -13829,35 +13807,45 @@
       <c r="C510" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="D510" s="32">
-        <v>2</v>
-      </c>
-      <c r="E510" s="32">
-        <v>1</v>
-      </c>
-      <c r="F510" s="32">
-        <v>2</v>
-      </c>
-      <c r="G510" s="33" t="s">
-        <v>76</v>
-      </c>
-      <c r="H510" s="23" t="s">
-        <v>152</v>
+      <c r="D510" s="18">
+        <v>2</v>
+      </c>
+      <c r="E510" s="18">
+        <v>1</v>
+      </c>
+      <c r="F510" s="18"/>
+      <c r="G510" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="H510" s="24" t="s">
+        <v>153</v>
       </c>
       <c r="I510" s="13"/>
-      <c r="J510" s="34" t="s">
-        <v>173</v>
-      </c>
+      <c r="J510" s="13"/>
     </row>
     <row r="511" spans="1:10" ht="16.5">
       <c r="A511" s="31"/>
-      <c r="B511" s="13"/>
-      <c r="C511" s="13"/>
-      <c r="D511" s="31"/>
-      <c r="E511" s="31"/>
-      <c r="F511" s="31"/>
-      <c r="G511" s="13"/>
-      <c r="H511" s="16"/>
+      <c r="B511" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C511" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="D511" s="31">
+        <v>2</v>
+      </c>
+      <c r="E511" s="31">
+        <v>1</v>
+      </c>
+      <c r="F511" s="31">
+        <v>1</v>
+      </c>
+      <c r="G511" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="H511" s="16" t="s">
+        <v>156</v>
+      </c>
       <c r="I511" s="13"/>
       <c r="J511" s="13"/>
     </row>
@@ -13869,45 +13857,35 @@
       <c r="C512" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="D512" s="18">
-        <v>2</v>
-      </c>
-      <c r="E512" s="18">
-        <v>2</v>
-      </c>
-      <c r="F512" s="18"/>
-      <c r="G512" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="H512" s="24" t="s">
-        <v>154</v>
+      <c r="D512" s="32">
+        <v>2</v>
+      </c>
+      <c r="E512" s="32">
+        <v>1</v>
+      </c>
+      <c r="F512" s="32">
+        <v>2</v>
+      </c>
+      <c r="G512" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="H512" s="23" t="s">
+        <v>152</v>
       </c>
       <c r="I512" s="13"/>
-      <c r="J512" s="13"/>
-    </row>
-    <row r="513" spans="1:10" ht="33">
+      <c r="J512" s="34" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="513" spans="1:10" ht="16.5">
       <c r="A513" s="31"/>
-      <c r="B513" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="C513" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="D513" s="31">
-        <v>2</v>
-      </c>
-      <c r="E513" s="31">
-        <v>2</v>
-      </c>
-      <c r="F513" s="31">
-        <v>1</v>
-      </c>
-      <c r="G513" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="H513" s="16" t="s">
-        <v>300</v>
-      </c>
+      <c r="B513" s="13"/>
+      <c r="C513" s="13"/>
+      <c r="D513" s="31"/>
+      <c r="E513" s="31"/>
+      <c r="F513" s="31"/>
+      <c r="G513" s="13"/>
+      <c r="H513" s="16"/>
       <c r="I513" s="13"/>
       <c r="J513" s="13"/>
     </row>
@@ -13919,78 +13897,95 @@
       <c r="C514" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="D514" s="32">
-        <v>2</v>
-      </c>
-      <c r="E514" s="32">
-        <v>2</v>
-      </c>
-      <c r="F514" s="32">
-        <v>2</v>
-      </c>
-      <c r="G514" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="H514" s="23" t="s">
-        <v>301</v>
+      <c r="D514" s="18">
+        <v>2</v>
+      </c>
+      <c r="E514" s="18">
+        <v>2</v>
+      </c>
+      <c r="F514" s="18"/>
+      <c r="G514" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="H514" s="24" t="s">
+        <v>154</v>
       </c>
       <c r="I514" s="13"/>
       <c r="J514" s="13"/>
     </row>
-    <row r="515" spans="1:10" ht="16.5">
+    <row r="515" spans="1:10" ht="33">
       <c r="A515" s="31"/>
-      <c r="B515" s="13"/>
-      <c r="C515" s="13"/>
-      <c r="D515" s="31"/>
-      <c r="E515" s="31"/>
-      <c r="F515" s="31"/>
-      <c r="G515" s="13"/>
-      <c r="H515" s="16"/>
+      <c r="B515" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C515" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="D515" s="31">
+        <v>2</v>
+      </c>
+      <c r="E515" s="31">
+        <v>2</v>
+      </c>
+      <c r="F515" s="31">
+        <v>1</v>
+      </c>
+      <c r="G515" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="H515" s="16" t="s">
+        <v>300</v>
+      </c>
       <c r="I515" s="13"/>
       <c r="J515" s="13"/>
     </row>
     <row r="516" spans="1:10" ht="16.5">
-      <c r="A516" s="9">
-        <v>40501</v>
-      </c>
-      <c r="B516" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="C516" s="35" t="s">
-        <v>285</v>
-      </c>
-      <c r="D516" s="30" t="s">
-        <v>72</v>
-      </c>
-      <c r="E516" s="30"/>
-      <c r="F516" s="30"/>
-      <c r="G516" s="35" t="s">
-        <v>73</v>
-      </c>
-      <c r="H516" s="11" t="s">
-        <v>400</v>
-      </c>
-      <c r="I516" s="36"/>
-      <c r="J516" s="35" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="517" spans="1:10">
-      <c r="A517" s="7"/>
-      <c r="D517" s="7"/>
-      <c r="E517" s="7"/>
-      <c r="F517" s="7"/>
-      <c r="H517" s="39"/>
+      <c r="A516" s="31"/>
+      <c r="B516" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C516" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="D516" s="32">
+        <v>2</v>
+      </c>
+      <c r="E516" s="32">
+        <v>2</v>
+      </c>
+      <c r="F516" s="32">
+        <v>2</v>
+      </c>
+      <c r="G516" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="H516" s="23" t="s">
+        <v>301</v>
+      </c>
+      <c r="I516" s="13"/>
+      <c r="J516" s="13"/>
+    </row>
+    <row r="517" spans="1:10" ht="16.5">
+      <c r="A517" s="31"/>
+      <c r="B517" s="13"/>
+      <c r="C517" s="13"/>
+      <c r="D517" s="31"/>
+      <c r="E517" s="31"/>
+      <c r="F517" s="31"/>
+      <c r="G517" s="13"/>
+      <c r="H517" s="16"/>
+      <c r="I517" s="13"/>
+      <c r="J517" s="13"/>
     </row>
     <row r="518" spans="1:10" ht="16.5">
       <c r="A518" s="9">
-        <v>40502</v>
+        <v>40501</v>
       </c>
       <c r="B518" s="35" t="s">
         <v>70</v>
       </c>
       <c r="C518" s="35" t="s">
-        <v>83</v>
+        <v>285</v>
       </c>
       <c r="D518" s="30" t="s">
         <v>72</v>
@@ -14001,11 +13996,11 @@
         <v>73</v>
       </c>
       <c r="H518" s="11" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="I518" s="36"/>
       <c r="J518" s="35" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="519" spans="1:10">
@@ -14017,7 +14012,7 @@
     </row>
     <row r="520" spans="1:10" ht="16.5">
       <c r="A520" s="9">
-        <v>40503</v>
+        <v>40502</v>
       </c>
       <c r="B520" s="35" t="s">
         <v>70</v>
@@ -14034,7 +14029,7 @@
         <v>73</v>
       </c>
       <c r="H520" s="11" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="I520" s="36"/>
       <c r="J520" s="35" t="s">
@@ -14050,13 +14045,13 @@
     </row>
     <row r="522" spans="1:10" ht="16.5">
       <c r="A522" s="9">
-        <v>40504</v>
+        <v>40503</v>
       </c>
       <c r="B522" s="35" t="s">
         <v>70</v>
       </c>
       <c r="C522" s="35" t="s">
-        <v>290</v>
+        <v>83</v>
       </c>
       <c r="D522" s="30" t="s">
         <v>72</v>
@@ -14067,11 +14062,11 @@
         <v>73</v>
       </c>
       <c r="H522" s="11" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I522" s="36"/>
       <c r="J522" s="35" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="523" spans="1:10">
@@ -14083,7 +14078,7 @@
     </row>
     <row r="524" spans="1:10" ht="16.5">
       <c r="A524" s="9">
-        <v>50501</v>
+        <v>40504</v>
       </c>
       <c r="B524" s="35" t="s">
         <v>70</v>
@@ -14100,11 +14095,11 @@
         <v>73</v>
       </c>
       <c r="H524" s="11" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="I524" s="36"/>
       <c r="J524" s="35" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="525" spans="1:10">
@@ -14116,7 +14111,7 @@
     </row>
     <row r="526" spans="1:10" ht="16.5">
       <c r="A526" s="9">
-        <v>50502</v>
+        <v>50501</v>
       </c>
       <c r="B526" s="35" t="s">
         <v>70</v>
@@ -14133,7 +14128,7 @@
         <v>73</v>
       </c>
       <c r="H526" s="11" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="I526" s="36"/>
       <c r="J526" s="35" t="s">
@@ -14149,7 +14144,7 @@
     </row>
     <row r="528" spans="1:10" ht="16.5">
       <c r="A528" s="9">
-        <v>50503</v>
+        <v>50502</v>
       </c>
       <c r="B528" s="35" t="s">
         <v>70</v>
@@ -14166,7 +14161,7 @@
         <v>73</v>
       </c>
       <c r="H528" s="11" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="I528" s="36"/>
       <c r="J528" s="35" t="s">
@@ -14178,149 +14173,128 @@
       <c r="D529" s="7"/>
       <c r="E529" s="7"/>
       <c r="F529" s="7"/>
-    </row>
-    <row r="530" spans="1:10">
-      <c r="A530" s="42"/>
-      <c r="B530" s="43"/>
-      <c r="C530" s="43"/>
-      <c r="D530" s="42"/>
-      <c r="E530" s="42"/>
-      <c r="F530" s="42"/>
-      <c r="G530" s="43"/>
-      <c r="H530" s="44"/>
-      <c r="I530" s="43"/>
-      <c r="J530" s="43"/>
+      <c r="H529" s="39"/>
+    </row>
+    <row r="530" spans="1:10" ht="16.5">
+      <c r="A530" s="9">
+        <v>50503</v>
+      </c>
+      <c r="B530" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="C530" s="35" t="s">
+        <v>290</v>
+      </c>
+      <c r="D530" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="E530" s="30"/>
+      <c r="F530" s="30"/>
+      <c r="G530" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="H530" s="11" t="s">
+        <v>406</v>
+      </c>
+      <c r="I530" s="36"/>
+      <c r="J530" s="35" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="531" spans="1:10">
       <c r="A531" s="7"/>
       <c r="D531" s="7"/>
       <c r="E531" s="7"/>
       <c r="F531" s="7"/>
-      <c r="H531" s="39"/>
-    </row>
-    <row r="532" spans="1:10" ht="21">
-      <c r="A532" s="9">
+    </row>
+    <row r="532" spans="1:10">
+      <c r="A532" s="42"/>
+      <c r="B532" s="43"/>
+      <c r="C532" s="43"/>
+      <c r="D532" s="42"/>
+      <c r="E532" s="42"/>
+      <c r="F532" s="42"/>
+      <c r="G532" s="43"/>
+      <c r="H532" s="44"/>
+      <c r="I532" s="43"/>
+      <c r="J532" s="43"/>
+    </row>
+    <row r="533" spans="1:10">
+      <c r="A533" s="7"/>
+      <c r="D533" s="7"/>
+      <c r="E533" s="7"/>
+      <c r="F533" s="7"/>
+      <c r="H533" s="39"/>
+    </row>
+    <row r="534" spans="1:10" ht="21">
+      <c r="A534" s="9">
         <v>10601</v>
       </c>
-      <c r="B532" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C532" s="35" t="s">
+      <c r="B534" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C534" s="35" t="s">
         <v>86</v>
       </c>
-      <c r="D532" s="9">
-        <v>1</v>
-      </c>
-      <c r="E532" s="9"/>
-      <c r="F532" s="9"/>
-      <c r="G532" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H532" s="11" t="s">
+      <c r="D534" s="9">
+        <v>1</v>
+      </c>
+      <c r="E534" s="9"/>
+      <c r="F534" s="9"/>
+      <c r="G534" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="H534" s="11" t="s">
         <v>407</v>
       </c>
-      <c r="I532" s="10"/>
-      <c r="J532" s="12" t="s">
+      <c r="I534" s="10"/>
+      <c r="J534" s="12" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="533" spans="1:10" ht="33">
-      <c r="A533" s="14"/>
-      <c r="B533" s="15" t="s">
+    <row r="535" spans="1:10" ht="33">
+      <c r="A535" s="14"/>
+      <c r="B535" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="C533" s="15" t="s">
+      <c r="C535" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="D533" s="14">
-        <v>2</v>
-      </c>
-      <c r="E533" s="14"/>
-      <c r="F533" s="14"/>
-      <c r="G533" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="H533" s="16" t="s">
-        <v>408</v>
-      </c>
-      <c r="I533" s="15"/>
-      <c r="J533" s="13"/>
-    </row>
-    <row r="534" spans="1:10" ht="16.5">
-      <c r="A534" s="14"/>
-      <c r="B534" s="15"/>
-      <c r="C534" s="15"/>
-      <c r="D534" s="14"/>
-      <c r="E534" s="14"/>
-      <c r="F534" s="14"/>
-      <c r="G534" s="15"/>
-      <c r="H534" s="17"/>
-      <c r="I534" s="15"/>
-      <c r="J534" s="13"/>
-    </row>
-    <row r="535" spans="1:10" ht="16.5">
-      <c r="A535" s="14"/>
-      <c r="B535" s="15"/>
-      <c r="C535" s="15"/>
-      <c r="D535" s="14"/>
+      <c r="D535" s="14">
+        <v>2</v>
+      </c>
       <c r="E535" s="14"/>
       <c r="F535" s="14"/>
-      <c r="G535" s="15"/>
-      <c r="H535" s="17"/>
+      <c r="G535" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="H535" s="16" t="s">
+        <v>408</v>
+      </c>
       <c r="I535" s="15"/>
       <c r="J535" s="13"/>
     </row>
     <row r="536" spans="1:10" ht="16.5">
       <c r="A536" s="14"/>
-      <c r="B536" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="C536" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="D536" s="18">
-        <v>3</v>
-      </c>
-      <c r="E536" s="18">
-        <v>1</v>
-      </c>
+      <c r="B536" s="15"/>
+      <c r="C536" s="15"/>
+      <c r="D536" s="14"/>
+      <c r="E536" s="14"/>
       <c r="F536" s="14"/>
-      <c r="G536" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="H536" s="20" t="s">
-        <v>136</v>
-      </c>
-      <c r="I536" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="J536" s="13" t="s">
-        <v>138</v>
-      </c>
+      <c r="G536" s="15"/>
+      <c r="H536" s="17"/>
+      <c r="I536" s="15"/>
+      <c r="J536" s="13"/>
     </row>
     <row r="537" spans="1:10" ht="16.5">
       <c r="A537" s="14"/>
-      <c r="B537" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="C537" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="D537" s="14">
-        <v>3</v>
-      </c>
-      <c r="E537" s="14">
-        <v>1</v>
-      </c>
-      <c r="F537" s="14">
-        <v>1</v>
-      </c>
-      <c r="G537" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="H537" s="17" t="s">
-        <v>409</v>
-      </c>
+      <c r="B537" s="15"/>
+      <c r="C537" s="15"/>
+      <c r="D537" s="14"/>
+      <c r="E537" s="14"/>
+      <c r="F537" s="14"/>
+      <c r="G537" s="15"/>
+      <c r="H537" s="17"/>
       <c r="I537" s="15"/>
       <c r="J537" s="13"/>
     </row>
@@ -14332,23 +14306,25 @@
       <c r="C538" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="D538" s="14">
+      <c r="D538" s="18">
         <v>3</v>
       </c>
-      <c r="E538" s="14">
-        <v>1</v>
-      </c>
-      <c r="F538" s="14">
-        <v>2</v>
-      </c>
-      <c r="G538" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="H538" s="17" t="s">
-        <v>410</v>
-      </c>
-      <c r="I538" s="15"/>
-      <c r="J538" s="13"/>
+      <c r="E538" s="18">
+        <v>1</v>
+      </c>
+      <c r="F538" s="14"/>
+      <c r="G538" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="H538" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="I538" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="J538" s="13" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="539" spans="1:10" ht="16.5">
       <c r="A539" s="14"/>
@@ -14365,13 +14341,13 @@
         <v>1</v>
       </c>
       <c r="F539" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G539" s="15" t="s">
         <v>73</v>
       </c>
       <c r="H539" s="17" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="I539" s="15"/>
       <c r="J539" s="13"/>
@@ -14379,118 +14355,118 @@
     <row r="540" spans="1:10" ht="16.5">
       <c r="A540" s="14"/>
       <c r="B540" s="15" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="C540" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="D540" s="21">
+        <v>135</v>
+      </c>
+      <c r="D540" s="14">
         <v>3</v>
       </c>
-      <c r="E540" s="21">
-        <v>1</v>
-      </c>
-      <c r="F540" s="21">
-        <v>4</v>
-      </c>
-      <c r="G540" s="22" t="s">
-        <v>76</v>
-      </c>
-      <c r="H540" s="23" t="s">
-        <v>144</v>
+      <c r="E540" s="14">
+        <v>1</v>
+      </c>
+      <c r="F540" s="14">
+        <v>2</v>
+      </c>
+      <c r="G540" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="H540" s="17" t="s">
+        <v>410</v>
       </c>
       <c r="I540" s="15"/>
       <c r="J540" s="13"/>
     </row>
     <row r="541" spans="1:10" ht="16.5">
       <c r="A541" s="14"/>
-      <c r="B541" s="15"/>
-      <c r="C541" s="15"/>
-      <c r="D541" s="14"/>
-      <c r="E541" s="14"/>
-      <c r="F541" s="14"/>
-      <c r="G541" s="15"/>
-      <c r="H541" s="17"/>
+      <c r="B541" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C541" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="D541" s="14">
+        <v>3</v>
+      </c>
+      <c r="E541" s="14">
+        <v>1</v>
+      </c>
+      <c r="F541" s="14">
+        <v>3</v>
+      </c>
+      <c r="G541" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="H541" s="17" t="s">
+        <v>411</v>
+      </c>
       <c r="I541" s="15"/>
       <c r="J541" s="13"/>
     </row>
     <row r="542" spans="1:10" ht="16.5">
       <c r="A542" s="14"/>
       <c r="B542" s="15" t="s">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="C542" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="D542" s="18">
+        <v>86</v>
+      </c>
+      <c r="D542" s="21">
         <v>3</v>
       </c>
-      <c r="E542" s="18">
-        <v>2</v>
-      </c>
-      <c r="F542" s="14"/>
-      <c r="G542" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="H542" s="24" t="s">
-        <v>137</v>
+      <c r="E542" s="21">
+        <v>1</v>
+      </c>
+      <c r="F542" s="21">
+        <v>4</v>
+      </c>
+      <c r="G542" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="H542" s="23" t="s">
+        <v>144</v>
       </c>
       <c r="I542" s="15"/>
-      <c r="J542" s="13" t="s">
-        <v>139</v>
-      </c>
+      <c r="J542" s="13"/>
     </row>
     <row r="543" spans="1:10" ht="16.5">
       <c r="A543" s="14"/>
-      <c r="B543" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="C543" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="D543" s="21">
-        <v>3</v>
-      </c>
-      <c r="E543" s="21">
-        <v>2</v>
-      </c>
-      <c r="F543" s="21">
-        <v>1</v>
-      </c>
-      <c r="G543" s="22" t="s">
-        <v>76</v>
-      </c>
-      <c r="H543" s="23" t="s">
-        <v>78</v>
-      </c>
+      <c r="B543" s="15"/>
+      <c r="C543" s="15"/>
+      <c r="D543" s="14"/>
+      <c r="E543" s="14"/>
+      <c r="F543" s="14"/>
+      <c r="G543" s="15"/>
+      <c r="H543" s="17"/>
       <c r="I543" s="15"/>
       <c r="J543" s="13"/>
     </row>
     <row r="544" spans="1:10" ht="16.5">
       <c r="A544" s="14"/>
       <c r="B544" s="15" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="C544" s="15" t="s">
-        <v>150</v>
-      </c>
-      <c r="D544" s="14">
+        <v>135</v>
+      </c>
+      <c r="D544" s="18">
         <v>3</v>
       </c>
-      <c r="E544" s="14">
-        <v>2</v>
-      </c>
-      <c r="F544" s="14">
-        <v>2</v>
-      </c>
-      <c r="G544" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="H544" s="17" t="s">
-        <v>151</v>
+      <c r="E544" s="18">
+        <v>2</v>
+      </c>
+      <c r="F544" s="14"/>
+      <c r="G544" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="H544" s="24" t="s">
+        <v>137</v>
       </c>
       <c r="I544" s="15"/>
-      <c r="J544" s="13"/>
+      <c r="J544" s="13" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="545" spans="1:10" ht="16.5">
       <c r="A545" s="14"/>
@@ -14498,153 +14474,167 @@
         <v>70</v>
       </c>
       <c r="C545" s="15" t="s">
-        <v>292</v>
-      </c>
-      <c r="D545" s="14">
+        <v>86</v>
+      </c>
+      <c r="D545" s="21">
         <v>3</v>
       </c>
-      <c r="E545" s="14">
-        <v>2</v>
-      </c>
-      <c r="F545" s="14">
-        <v>3</v>
-      </c>
-      <c r="G545" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="H545" s="16" t="s">
-        <v>412</v>
+      <c r="E545" s="21">
+        <v>2</v>
+      </c>
+      <c r="F545" s="21">
+        <v>1</v>
+      </c>
+      <c r="G545" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="H545" s="23" t="s">
+        <v>78</v>
       </c>
       <c r="I545" s="15"/>
       <c r="J545" s="13"/>
     </row>
     <row r="546" spans="1:10" ht="16.5">
       <c r="A546" s="14"/>
-      <c r="B546" s="15"/>
-      <c r="C546" s="15"/>
-      <c r="D546" s="14"/>
-      <c r="E546" s="14"/>
-      <c r="F546" s="14"/>
-      <c r="G546" s="15"/>
-      <c r="H546" s="17"/>
+      <c r="B546" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C546" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="D546" s="14">
+        <v>3</v>
+      </c>
+      <c r="E546" s="14">
+        <v>2</v>
+      </c>
+      <c r="F546" s="14">
+        <v>2</v>
+      </c>
+      <c r="G546" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="H546" s="17" t="s">
+        <v>151</v>
+      </c>
       <c r="I546" s="15"/>
       <c r="J546" s="13"/>
     </row>
     <row r="547" spans="1:10" ht="16.5">
       <c r="A547" s="14"/>
       <c r="B547" s="15" t="s">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="C547" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="D547" s="18">
+        <v>292</v>
+      </c>
+      <c r="D547" s="14">
         <v>3</v>
       </c>
-      <c r="E547" s="18">
+      <c r="E547" s="14">
+        <v>2</v>
+      </c>
+      <c r="F547" s="14">
         <v>3</v>
       </c>
-      <c r="F547" s="14"/>
-      <c r="G547" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="H547" s="24" t="s">
-        <v>79</v>
+      <c r="G547" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="H547" s="16" t="s">
+        <v>412</v>
       </c>
       <c r="I547" s="15"/>
-      <c r="J547" s="13" t="s">
-        <v>141</v>
-      </c>
+      <c r="J547" s="13"/>
     </row>
     <row r="548" spans="1:10" ht="16.5">
       <c r="A548" s="14"/>
-      <c r="B548" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="C548" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="D548" s="25">
-        <v>3</v>
-      </c>
-      <c r="E548" s="25">
-        <v>3</v>
-      </c>
-      <c r="F548" s="25">
-        <v>1</v>
-      </c>
-      <c r="G548" s="26" t="s">
-        <v>73</v>
-      </c>
-      <c r="H548" s="27" t="s">
-        <v>164</v>
-      </c>
+      <c r="B548" s="15"/>
+      <c r="C548" s="15"/>
+      <c r="D548" s="14"/>
+      <c r="E548" s="14"/>
+      <c r="F548" s="14"/>
+      <c r="G548" s="15"/>
+      <c r="H548" s="17"/>
       <c r="I548" s="15"/>
       <c r="J548" s="13"/>
     </row>
     <row r="549" spans="1:10" ht="16.5">
       <c r="A549" s="14"/>
       <c r="B549" s="15" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="C549" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="D549" s="28">
+      <c r="D549" s="18">
         <v>3</v>
       </c>
-      <c r="E549" s="28">
+      <c r="E549" s="18">
         <v>3</v>
       </c>
-      <c r="F549" s="28">
-        <v>2</v>
-      </c>
-      <c r="G549" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="H549" s="27" t="s">
-        <v>413</v>
+      <c r="F549" s="14"/>
+      <c r="G549" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="H549" s="24" t="s">
+        <v>79</v>
       </c>
       <c r="I549" s="15"/>
-      <c r="J549" s="13"/>
+      <c r="J549" s="13" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="550" spans="1:10" ht="16.5">
       <c r="A550" s="14"/>
-      <c r="B550" s="15"/>
-      <c r="C550" s="15"/>
-      <c r="D550" s="14"/>
-      <c r="E550" s="14"/>
-      <c r="F550" s="14"/>
-      <c r="G550" s="15"/>
-      <c r="H550" s="16"/>
+      <c r="B550" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C550" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="D550" s="25">
+        <v>3</v>
+      </c>
+      <c r="E550" s="25">
+        <v>3</v>
+      </c>
+      <c r="F550" s="25">
+        <v>1</v>
+      </c>
+      <c r="G550" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="H550" s="27" t="s">
+        <v>164</v>
+      </c>
       <c r="I550" s="15"/>
       <c r="J550" s="13"/>
     </row>
-    <row r="551" spans="1:10" ht="21">
-      <c r="A551" s="9">
-        <v>20601</v>
-      </c>
-      <c r="B551" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C551" s="35" t="s">
+    <row r="551" spans="1:10" ht="16.5">
+      <c r="A551" s="14"/>
+      <c r="B551" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C551" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="D551" s="9">
-        <v>1</v>
-      </c>
-      <c r="E551" s="9"/>
-      <c r="F551" s="9"/>
-      <c r="G551" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H551" s="11" t="s">
-        <v>414</v>
-      </c>
-      <c r="I551" s="10"/>
-      <c r="J551" s="12" t="s">
-        <v>293</v>
-      </c>
+      <c r="D551" s="28">
+        <v>3</v>
+      </c>
+      <c r="E551" s="28">
+        <v>3</v>
+      </c>
+      <c r="F551" s="28">
+        <v>2</v>
+      </c>
+      <c r="G551" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="H551" s="27" t="s">
+        <v>413</v>
+      </c>
+      <c r="I551" s="15"/>
+      <c r="J551" s="13"/>
     </row>
     <row r="552" spans="1:10" ht="16.5">
       <c r="A552" s="14"/>
@@ -14658,653 +14648,653 @@
       <c r="I552" s="15"/>
       <c r="J552" s="13"/>
     </row>
-    <row r="553" spans="1:10" ht="16.5">
-      <c r="A553" s="14"/>
-      <c r="B553" s="15"/>
-      <c r="C553" s="15"/>
-      <c r="D553" s="18">
-        <v>2</v>
-      </c>
-      <c r="E553" s="18">
-        <v>1</v>
-      </c>
-      <c r="F553" s="18"/>
-      <c r="G553" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="H553" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="I553" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="J553" s="13"/>
+    <row r="553" spans="1:10" ht="21">
+      <c r="A553" s="9">
+        <v>20601</v>
+      </c>
+      <c r="B553" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C553" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="D553" s="9">
+        <v>1</v>
+      </c>
+      <c r="E553" s="9"/>
+      <c r="F553" s="9"/>
+      <c r="G553" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="H553" s="11" t="s">
+        <v>414</v>
+      </c>
+      <c r="I553" s="10"/>
+      <c r="J553" s="12" t="s">
+        <v>293</v>
+      </c>
     </row>
     <row r="554" spans="1:10" ht="16.5">
       <c r="A554" s="14"/>
-      <c r="B554" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="C554" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="D554" s="14">
-        <v>2</v>
-      </c>
-      <c r="E554" s="14">
-        <v>1</v>
-      </c>
-      <c r="F554" s="14">
-        <v>1</v>
-      </c>
-      <c r="G554" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="H554" s="16" t="s">
-        <v>163</v>
-      </c>
+      <c r="B554" s="15"/>
+      <c r="C554" s="15"/>
+      <c r="D554" s="14"/>
+      <c r="E554" s="14"/>
+      <c r="F554" s="14"/>
+      <c r="G554" s="15"/>
+      <c r="H554" s="16"/>
       <c r="I554" s="15"/>
       <c r="J554" s="13"/>
     </row>
     <row r="555" spans="1:10" ht="16.5">
       <c r="A555" s="14"/>
-      <c r="B555" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="C555" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="D555" s="14">
-        <v>2</v>
-      </c>
-      <c r="E555" s="14">
-        <v>1</v>
-      </c>
-      <c r="F555" s="14">
-        <v>2</v>
-      </c>
-      <c r="G555" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="H555" s="17" t="s">
-        <v>415</v>
-      </c>
-      <c r="I555" s="15"/>
+      <c r="B555" s="15"/>
+      <c r="C555" s="15"/>
+      <c r="D555" s="18">
+        <v>2</v>
+      </c>
+      <c r="E555" s="18">
+        <v>1</v>
+      </c>
+      <c r="F555" s="18"/>
+      <c r="G555" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="H555" s="24" t="s">
+        <v>159</v>
+      </c>
+      <c r="I555" s="19" t="s">
+        <v>75</v>
+      </c>
       <c r="J555" s="13"/>
     </row>
     <row r="556" spans="1:10" ht="16.5">
       <c r="A556" s="14"/>
-      <c r="B556" s="15"/>
-      <c r="C556" s="15"/>
-      <c r="D556" s="14"/>
-      <c r="E556" s="14"/>
-      <c r="F556" s="14"/>
-      <c r="G556" s="15"/>
-      <c r="H556" s="16"/>
+      <c r="B556" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C556" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="D556" s="14">
+        <v>2</v>
+      </c>
+      <c r="E556" s="14">
+        <v>1</v>
+      </c>
+      <c r="F556" s="14">
+        <v>1</v>
+      </c>
+      <c r="G556" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="H556" s="16" t="s">
+        <v>163</v>
+      </c>
       <c r="I556" s="15"/>
       <c r="J556" s="13"/>
     </row>
     <row r="557" spans="1:10" ht="16.5">
       <c r="A557" s="14"/>
-      <c r="B557" s="15"/>
-      <c r="C557" s="15"/>
-      <c r="D557" s="18">
-        <v>2</v>
-      </c>
-      <c r="E557" s="18">
-        <v>2</v>
-      </c>
-      <c r="F557" s="14"/>
-      <c r="G557" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="H557" s="24" t="s">
-        <v>137</v>
+      <c r="B557" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C557" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="D557" s="14">
+        <v>2</v>
+      </c>
+      <c r="E557" s="14">
+        <v>1</v>
+      </c>
+      <c r="F557" s="14">
+        <v>2</v>
+      </c>
+      <c r="G557" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="H557" s="17" t="s">
+        <v>415</v>
       </c>
       <c r="I557" s="15"/>
       <c r="J557" s="13"/>
     </row>
     <row r="558" spans="1:10" ht="16.5">
       <c r="A558" s="14"/>
-      <c r="B558" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="C558" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="D558" s="14">
-        <v>2</v>
-      </c>
-      <c r="E558" s="14">
-        <v>2</v>
-      </c>
-      <c r="F558" s="14">
-        <v>1</v>
-      </c>
-      <c r="G558" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="H558" s="16" t="s">
-        <v>161</v>
-      </c>
+      <c r="B558" s="15"/>
+      <c r="C558" s="15"/>
+      <c r="D558" s="14"/>
+      <c r="E558" s="14"/>
+      <c r="F558" s="14"/>
+      <c r="G558" s="15"/>
+      <c r="H558" s="16"/>
       <c r="I558" s="15"/>
       <c r="J558" s="13"/>
     </row>
     <row r="559" spans="1:10" ht="16.5">
       <c r="A559" s="14"/>
-      <c r="B559" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="C559" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="D559" s="14">
-        <v>2</v>
-      </c>
-      <c r="E559" s="14">
-        <v>2</v>
-      </c>
-      <c r="F559" s="14">
-        <v>2</v>
-      </c>
-      <c r="G559" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="H559" s="16" t="s">
-        <v>412</v>
+      <c r="B559" s="15"/>
+      <c r="C559" s="15"/>
+      <c r="D559" s="18">
+        <v>2</v>
+      </c>
+      <c r="E559" s="18">
+        <v>2</v>
+      </c>
+      <c r="F559" s="14"/>
+      <c r="G559" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="H559" s="24" t="s">
+        <v>137</v>
       </c>
       <c r="I559" s="15"/>
       <c r="J559" s="13"/>
     </row>
     <row r="560" spans="1:10" ht="16.5">
       <c r="A560" s="14"/>
-      <c r="B560" s="15"/>
-      <c r="C560" s="15"/>
-      <c r="D560" s="14"/>
-      <c r="E560" s="14"/>
-      <c r="F560" s="14"/>
-      <c r="G560" s="15"/>
-      <c r="H560" s="16"/>
+      <c r="B560" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C560" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="D560" s="14">
+        <v>2</v>
+      </c>
+      <c r="E560" s="14">
+        <v>2</v>
+      </c>
+      <c r="F560" s="14">
+        <v>1</v>
+      </c>
+      <c r="G560" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="H560" s="16" t="s">
+        <v>161</v>
+      </c>
       <c r="I560" s="15"/>
       <c r="J560" s="13"/>
     </row>
     <row r="561" spans="1:10" ht="16.5">
       <c r="A561" s="14"/>
-      <c r="B561" s="15"/>
-      <c r="C561" s="15"/>
-      <c r="D561" s="18">
-        <v>2</v>
-      </c>
-      <c r="E561" s="18">
-        <v>3</v>
-      </c>
-      <c r="F561" s="14"/>
-      <c r="G561" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="H561" s="24" t="s">
-        <v>160</v>
+      <c r="B561" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C561" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="D561" s="14">
+        <v>2</v>
+      </c>
+      <c r="E561" s="14">
+        <v>2</v>
+      </c>
+      <c r="F561" s="14">
+        <v>2</v>
+      </c>
+      <c r="G561" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="H561" s="16" t="s">
+        <v>412</v>
       </c>
       <c r="I561" s="15"/>
       <c r="J561" s="13"/>
     </row>
     <row r="562" spans="1:10" ht="16.5">
       <c r="A562" s="14"/>
-      <c r="B562" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="C562" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="D562" s="25">
-        <v>2</v>
-      </c>
-      <c r="E562" s="25">
-        <v>3</v>
-      </c>
-      <c r="F562" s="25">
-        <v>1</v>
-      </c>
-      <c r="G562" s="26" t="s">
-        <v>73</v>
-      </c>
-      <c r="H562" s="27" t="s">
-        <v>166</v>
-      </c>
+      <c r="B562" s="15"/>
+      <c r="C562" s="15"/>
+      <c r="D562" s="14"/>
+      <c r="E562" s="14"/>
+      <c r="F562" s="14"/>
+      <c r="G562" s="15"/>
+      <c r="H562" s="16"/>
       <c r="I562" s="15"/>
       <c r="J562" s="13"/>
     </row>
     <row r="563" spans="1:10" ht="16.5">
       <c r="A563" s="14"/>
-      <c r="B563" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="C563" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="D563" s="28">
-        <v>2</v>
-      </c>
-      <c r="E563" s="28">
+      <c r="B563" s="15"/>
+      <c r="C563" s="15"/>
+      <c r="D563" s="18">
+        <v>2</v>
+      </c>
+      <c r="E563" s="18">
         <v>3</v>
       </c>
-      <c r="F563" s="28">
-        <v>2</v>
-      </c>
-      <c r="G563" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="H563" s="27" t="s">
-        <v>413</v>
+      <c r="F563" s="14"/>
+      <c r="G563" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="H563" s="24" t="s">
+        <v>160</v>
       </c>
       <c r="I563" s="15"/>
       <c r="J563" s="13"/>
     </row>
     <row r="564" spans="1:10" ht="16.5">
       <c r="A564" s="14"/>
-      <c r="B564" s="15"/>
-      <c r="C564" s="15"/>
-      <c r="D564" s="18"/>
-      <c r="E564" s="18"/>
-      <c r="F564" s="14"/>
-      <c r="G564" s="19"/>
-      <c r="H564" s="24"/>
+      <c r="B564" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C564" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="D564" s="25">
+        <v>2</v>
+      </c>
+      <c r="E564" s="25">
+        <v>3</v>
+      </c>
+      <c r="F564" s="25">
+        <v>1</v>
+      </c>
+      <c r="G564" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="H564" s="27" t="s">
+        <v>166</v>
+      </c>
       <c r="I564" s="15"/>
       <c r="J564" s="13"/>
     </row>
     <row r="565" spans="1:10" ht="16.5">
       <c r="A565" s="14"/>
-      <c r="B565" s="15"/>
-      <c r="C565" s="15"/>
-      <c r="D565" s="14"/>
-      <c r="E565" s="14"/>
-      <c r="F565" s="14"/>
-      <c r="G565" s="15"/>
-      <c r="H565" s="16"/>
+      <c r="B565" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C565" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="D565" s="28">
+        <v>2</v>
+      </c>
+      <c r="E565" s="28">
+        <v>3</v>
+      </c>
+      <c r="F565" s="28">
+        <v>2</v>
+      </c>
+      <c r="G565" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="H565" s="27" t="s">
+        <v>413</v>
+      </c>
       <c r="I565" s="15"/>
       <c r="J565" s="13"/>
     </row>
-    <row r="566" spans="1:10" ht="33">
-      <c r="A566" s="9">
+    <row r="566" spans="1:10" ht="16.5">
+      <c r="A566" s="14"/>
+      <c r="B566" s="15"/>
+      <c r="C566" s="15"/>
+      <c r="D566" s="18"/>
+      <c r="E566" s="18"/>
+      <c r="F566" s="14"/>
+      <c r="G566" s="19"/>
+      <c r="H566" s="24"/>
+      <c r="I566" s="15"/>
+      <c r="J566" s="13"/>
+    </row>
+    <row r="567" spans="1:10" ht="16.5">
+      <c r="A567" s="14"/>
+      <c r="B567" s="15"/>
+      <c r="C567" s="15"/>
+      <c r="D567" s="14"/>
+      <c r="E567" s="14"/>
+      <c r="F567" s="14"/>
+      <c r="G567" s="15"/>
+      <c r="H567" s="16"/>
+      <c r="I567" s="15"/>
+      <c r="J567" s="13"/>
+    </row>
+    <row r="568" spans="1:10" ht="33">
+      <c r="A568" s="9">
         <v>30601</v>
       </c>
-      <c r="B566" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C566" s="35" t="s">
+      <c r="B568" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C568" s="35" t="s">
         <v>416</v>
       </c>
-      <c r="D566" s="30">
-        <v>1</v>
-      </c>
-      <c r="E566" s="30"/>
-      <c r="F566" s="30"/>
-      <c r="G566" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H566" s="11" t="s">
+      <c r="D568" s="30">
+        <v>1</v>
+      </c>
+      <c r="E568" s="30"/>
+      <c r="F568" s="30"/>
+      <c r="G568" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="H568" s="11" t="s">
         <v>417</v>
       </c>
-      <c r="I566" s="10"/>
-      <c r="J566" s="12" t="s">
+      <c r="I568" s="10"/>
+      <c r="J568" s="12" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="567" spans="1:10" ht="16.5">
-      <c r="A567" s="31"/>
-      <c r="B567" s="13"/>
-      <c r="C567" s="13"/>
-      <c r="D567" s="31"/>
-      <c r="E567" s="31"/>
-      <c r="F567" s="31"/>
-      <c r="G567" s="13"/>
-      <c r="H567" s="16"/>
-      <c r="I567" s="13"/>
-      <c r="J567" s="13"/>
-    </row>
-    <row r="568" spans="1:10" ht="16.5">
-      <c r="A568" s="31"/>
-      <c r="B568" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="C568" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="D568" s="18">
-        <v>2</v>
-      </c>
-      <c r="E568" s="18">
-        <v>1</v>
-      </c>
-      <c r="F568" s="18"/>
-      <c r="G568" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="H568" s="24" t="s">
-        <v>153</v>
-      </c>
-      <c r="I568" s="13"/>
-      <c r="J568" s="13"/>
     </row>
     <row r="569" spans="1:10" ht="16.5">
       <c r="A569" s="31"/>
-      <c r="B569" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="C569" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="D569" s="31">
-        <v>2</v>
-      </c>
-      <c r="E569" s="31">
-        <v>1</v>
-      </c>
-      <c r="F569" s="31">
-        <v>1</v>
-      </c>
-      <c r="G569" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="H569" s="16" t="s">
-        <v>206</v>
-      </c>
+      <c r="B569" s="13"/>
+      <c r="C569" s="13"/>
+      <c r="D569" s="31"/>
+      <c r="E569" s="31"/>
+      <c r="F569" s="31"/>
+      <c r="G569" s="13"/>
+      <c r="H569" s="16"/>
       <c r="I569" s="13"/>
       <c r="J569" s="13"/>
     </row>
     <row r="570" spans="1:10" ht="16.5">
       <c r="A570" s="31"/>
       <c r="B570" s="15" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="C570" s="15" t="s">
-        <v>416</v>
-      </c>
-      <c r="D570" s="28">
-        <v>2</v>
-      </c>
-      <c r="E570" s="31">
-        <v>1</v>
-      </c>
-      <c r="F570" s="28">
-        <v>2</v>
-      </c>
-      <c r="G570" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="H570" s="27" t="s">
-        <v>418</v>
+        <v>135</v>
+      </c>
+      <c r="D570" s="18">
+        <v>2</v>
+      </c>
+      <c r="E570" s="18">
+        <v>1</v>
+      </c>
+      <c r="F570" s="18"/>
+      <c r="G570" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="H570" s="24" t="s">
+        <v>153</v>
       </c>
       <c r="I570" s="13"/>
-      <c r="J570" s="34"/>
+      <c r="J570" s="13"/>
     </row>
     <row r="571" spans="1:10" ht="16.5">
       <c r="A571" s="31"/>
-      <c r="B571" s="13"/>
-      <c r="C571" s="13"/>
-      <c r="D571" s="14">
-        <v>2</v>
-      </c>
-      <c r="E571" s="14">
-        <v>1</v>
-      </c>
-      <c r="F571" s="14">
-        <v>3</v>
-      </c>
-      <c r="G571" s="22" t="s">
-        <v>76</v>
-      </c>
-      <c r="H571" s="23" t="s">
-        <v>144</v>
+      <c r="B571" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C571" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="D571" s="31">
+        <v>2</v>
+      </c>
+      <c r="E571" s="31">
+        <v>1</v>
+      </c>
+      <c r="F571" s="31">
+        <v>1</v>
+      </c>
+      <c r="G571" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="H571" s="16" t="s">
+        <v>206</v>
       </c>
       <c r="I571" s="13"/>
       <c r="J571" s="13"/>
     </row>
     <row r="572" spans="1:10" ht="16.5">
       <c r="A572" s="31"/>
-      <c r="B572" s="15"/>
-      <c r="C572" s="15"/>
-      <c r="D572" s="32"/>
-      <c r="E572" s="32"/>
-      <c r="F572" s="32"/>
-      <c r="G572" s="33"/>
-      <c r="H572" s="50"/>
+      <c r="B572" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C572" s="15" t="s">
+        <v>416</v>
+      </c>
+      <c r="D572" s="28">
+        <v>2</v>
+      </c>
+      <c r="E572" s="31">
+        <v>1</v>
+      </c>
+      <c r="F572" s="28">
+        <v>2</v>
+      </c>
+      <c r="G572" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="H572" s="27" t="s">
+        <v>418</v>
+      </c>
       <c r="I572" s="13"/>
-      <c r="J572" s="13"/>
+      <c r="J572" s="34"/>
     </row>
     <row r="573" spans="1:10" ht="16.5">
       <c r="A573" s="31"/>
-      <c r="B573" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="C573" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="D573" s="18">
-        <v>2</v>
-      </c>
-      <c r="E573" s="18">
-        <v>2</v>
-      </c>
-      <c r="F573" s="18"/>
-      <c r="G573" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="H573" s="24" t="s">
-        <v>154</v>
+      <c r="B573" s="13"/>
+      <c r="C573" s="13"/>
+      <c r="D573" s="14">
+        <v>2</v>
+      </c>
+      <c r="E573" s="14">
+        <v>1</v>
+      </c>
+      <c r="F573" s="14">
+        <v>3</v>
+      </c>
+      <c r="G573" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="H573" s="23" t="s">
+        <v>144</v>
       </c>
       <c r="I573" s="13"/>
       <c r="J573" s="13"/>
     </row>
-    <row r="574" spans="1:10" ht="33">
+    <row r="574" spans="1:10" ht="16.5">
       <c r="A574" s="31"/>
-      <c r="B574" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="C574" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="D574" s="31">
-        <v>2</v>
-      </c>
-      <c r="E574" s="31">
-        <v>2</v>
-      </c>
-      <c r="F574" s="31">
-        <v>1</v>
-      </c>
-      <c r="G574" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="H574" s="16" t="s">
-        <v>300</v>
-      </c>
+      <c r="B574" s="15"/>
+      <c r="C574" s="15"/>
+      <c r="D574" s="32"/>
+      <c r="E574" s="32"/>
+      <c r="F574" s="32"/>
+      <c r="G574" s="33"/>
+      <c r="H574" s="50"/>
       <c r="I574" s="13"/>
       <c r="J574" s="13"/>
     </row>
     <row r="575" spans="1:10" ht="16.5">
       <c r="A575" s="31"/>
-      <c r="B575" s="15"/>
-      <c r="C575" s="15"/>
-      <c r="D575" s="14">
-        <v>2</v>
-      </c>
-      <c r="E575" s="14">
-        <v>2</v>
-      </c>
-      <c r="F575" s="14">
-        <v>2</v>
-      </c>
-      <c r="G575" s="22" t="s">
-        <v>76</v>
-      </c>
-      <c r="H575" s="23" t="s">
-        <v>78</v>
+      <c r="B575" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C575" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="D575" s="18">
+        <v>2</v>
+      </c>
+      <c r="E575" s="18">
+        <v>2</v>
+      </c>
+      <c r="F575" s="18"/>
+      <c r="G575" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="H575" s="24" t="s">
+        <v>154</v>
       </c>
       <c r="I575" s="13"/>
       <c r="J575" s="13"/>
     </row>
-    <row r="576" spans="1:10" ht="16.5">
+    <row r="576" spans="1:10" ht="33">
       <c r="A576" s="31"/>
-      <c r="B576" s="15"/>
-      <c r="C576" s="15"/>
-      <c r="D576" s="31"/>
-      <c r="E576" s="31"/>
-      <c r="F576" s="31"/>
-      <c r="G576" s="13"/>
-      <c r="H576" s="16"/>
+      <c r="B576" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C576" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="D576" s="31">
+        <v>2</v>
+      </c>
+      <c r="E576" s="31">
+        <v>2</v>
+      </c>
+      <c r="F576" s="31">
+        <v>1</v>
+      </c>
+      <c r="G576" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="H576" s="16" t="s">
+        <v>300</v>
+      </c>
       <c r="I576" s="13"/>
       <c r="J576" s="13"/>
     </row>
     <row r="577" spans="1:10" ht="16.5">
       <c r="A577" s="31"/>
-      <c r="B577" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="C577" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="D577" s="18">
-        <v>2</v>
-      </c>
-      <c r="E577" s="18">
-        <v>3</v>
-      </c>
-      <c r="F577" s="18"/>
-      <c r="G577" s="19" t="s">
-        <v>209</v>
-      </c>
-      <c r="H577" s="24" t="s">
-        <v>210</v>
-      </c>
-      <c r="I577" s="13" t="s">
-        <v>200</v>
-      </c>
+      <c r="B577" s="15"/>
+      <c r="C577" s="15"/>
+      <c r="D577" s="14">
+        <v>2</v>
+      </c>
+      <c r="E577" s="14">
+        <v>2</v>
+      </c>
+      <c r="F577" s="14">
+        <v>2</v>
+      </c>
+      <c r="G577" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="H577" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="I577" s="13"/>
       <c r="J577" s="13"/>
     </row>
     <row r="578" spans="1:10" ht="16.5">
       <c r="A578" s="31"/>
-      <c r="B578" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="C578" s="15" t="s">
-        <v>207</v>
-      </c>
-      <c r="D578" s="31">
-        <v>2</v>
-      </c>
-      <c r="E578" s="18">
-        <v>3</v>
-      </c>
-      <c r="F578" s="31">
-        <v>1</v>
-      </c>
-      <c r="G578" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="H578" s="16" t="s">
-        <v>211</v>
-      </c>
+      <c r="B578" s="15"/>
+      <c r="C578" s="15"/>
+      <c r="D578" s="31"/>
+      <c r="E578" s="31"/>
+      <c r="F578" s="31"/>
+      <c r="G578" s="13"/>
+      <c r="H578" s="16"/>
       <c r="I578" s="13"/>
       <c r="J578" s="13"/>
     </row>
     <row r="579" spans="1:10" ht="16.5">
-      <c r="A579" s="14"/>
+      <c r="A579" s="31"/>
       <c r="B579" s="15" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="C579" s="15" t="s">
-        <v>419</v>
-      </c>
-      <c r="D579" s="28">
-        <v>2</v>
-      </c>
-      <c r="E579" s="28">
+        <v>135</v>
+      </c>
+      <c r="D579" s="18">
+        <v>2</v>
+      </c>
+      <c r="E579" s="18">
         <v>3</v>
       </c>
-      <c r="F579" s="28">
-        <v>2</v>
-      </c>
-      <c r="G579" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="H579" s="41" t="s">
-        <v>420</v>
-      </c>
-      <c r="I579" s="13"/>
+      <c r="F579" s="18"/>
+      <c r="G579" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="H579" s="24" t="s">
+        <v>210</v>
+      </c>
+      <c r="I579" s="13" t="s">
+        <v>200</v>
+      </c>
       <c r="J579" s="13"/>
     </row>
     <row r="580" spans="1:10" ht="16.5">
-      <c r="A580" s="14"/>
-      <c r="B580" s="15"/>
-      <c r="C580" s="15"/>
-      <c r="D580" s="32">
-        <v>2</v>
-      </c>
-      <c r="E580" s="32">
+      <c r="A580" s="31"/>
+      <c r="B580" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C580" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="D580" s="31">
+        <v>2</v>
+      </c>
+      <c r="E580" s="18">
         <v>3</v>
       </c>
-      <c r="F580" s="32">
-        <v>3</v>
-      </c>
-      <c r="G580" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="H580" s="23" t="s">
-        <v>212</v>
+      <c r="F580" s="31">
+        <v>1</v>
+      </c>
+      <c r="G580" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="H580" s="16" t="s">
+        <v>211</v>
       </c>
       <c r="I580" s="13"/>
       <c r="J580" s="13"/>
     </row>
     <row r="581" spans="1:10" ht="16.5">
       <c r="A581" s="14"/>
-      <c r="B581" s="15"/>
-      <c r="C581" s="15"/>
-      <c r="D581" s="32"/>
-      <c r="E581" s="32"/>
-      <c r="F581" s="32"/>
-      <c r="G581" s="33"/>
-      <c r="H581" s="23"/>
+      <c r="B581" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C581" s="15" t="s">
+        <v>419</v>
+      </c>
+      <c r="D581" s="28">
+        <v>2</v>
+      </c>
+      <c r="E581" s="28">
+        <v>3</v>
+      </c>
+      <c r="F581" s="28">
+        <v>2</v>
+      </c>
+      <c r="G581" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="H581" s="41" t="s">
+        <v>420</v>
+      </c>
       <c r="I581" s="13"/>
       <c r="J581" s="13"/>
     </row>
     <row r="582" spans="1:10" ht="16.5">
-      <c r="A582" s="31"/>
-      <c r="B582" s="13"/>
-      <c r="C582" s="13"/>
-      <c r="D582" s="31"/>
-      <c r="E582" s="31"/>
-      <c r="F582" s="31"/>
-      <c r="G582" s="13"/>
-      <c r="H582" s="16"/>
+      <c r="A582" s="14"/>
+      <c r="B582" s="15"/>
+      <c r="C582" s="15"/>
+      <c r="D582" s="32">
+        <v>2</v>
+      </c>
+      <c r="E582" s="32">
+        <v>3</v>
+      </c>
+      <c r="F582" s="32">
+        <v>3</v>
+      </c>
+      <c r="G582" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="H582" s="23" t="s">
+        <v>212</v>
+      </c>
       <c r="I582" s="13"/>
       <c r="J582" s="13"/>
     </row>
-    <row r="583" spans="1:10" ht="21">
-      <c r="A583" s="9">
-        <v>30602</v>
-      </c>
-      <c r="B583" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C583" s="35" t="s">
-        <v>86</v>
-      </c>
-      <c r="D583" s="30">
-        <v>1</v>
-      </c>
-      <c r="E583" s="30"/>
-      <c r="F583" s="30"/>
-      <c r="G583" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H583" s="11" t="s">
-        <v>421</v>
-      </c>
-      <c r="I583" s="10"/>
-      <c r="J583" s="12" t="s">
-        <v>295</v>
-      </c>
+    <row r="583" spans="1:10" ht="16.5">
+      <c r="A583" s="14"/>
+      <c r="B583" s="15"/>
+      <c r="C583" s="15"/>
+      <c r="D583" s="32"/>
+      <c r="E583" s="32"/>
+      <c r="F583" s="32"/>
+      <c r="G583" s="33"/>
+      <c r="H583" s="23"/>
+      <c r="I583" s="13"/>
+      <c r="J583" s="13"/>
     </row>
     <row r="584" spans="1:10" ht="16.5">
       <c r="A584" s="31"/>
@@ -15318,53 +15308,41 @@
       <c r="I584" s="13"/>
       <c r="J584" s="13"/>
     </row>
-    <row r="585" spans="1:10" ht="16.5">
-      <c r="A585" s="31"/>
-      <c r="B585" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="C585" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="D585" s="18">
-        <v>2</v>
-      </c>
-      <c r="E585" s="18">
-        <v>1</v>
-      </c>
-      <c r="F585" s="18"/>
-      <c r="G585" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="H585" s="24" t="s">
-        <v>153</v>
-      </c>
-      <c r="I585" s="13"/>
-      <c r="J585" s="13"/>
+    <row r="585" spans="1:10" ht="21">
+      <c r="A585" s="9">
+        <v>30602</v>
+      </c>
+      <c r="B585" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C585" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="D585" s="30">
+        <v>1</v>
+      </c>
+      <c r="E585" s="30"/>
+      <c r="F585" s="30"/>
+      <c r="G585" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="H585" s="11" t="s">
+        <v>421</v>
+      </c>
+      <c r="I585" s="10"/>
+      <c r="J585" s="12" t="s">
+        <v>295</v>
+      </c>
     </row>
     <row r="586" spans="1:10" ht="16.5">
       <c r="A586" s="31"/>
-      <c r="B586" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="C586" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="D586" s="31">
-        <v>2</v>
-      </c>
-      <c r="E586" s="31">
-        <v>1</v>
-      </c>
-      <c r="F586" s="31">
-        <v>1</v>
-      </c>
-      <c r="G586" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="H586" s="16" t="s">
-        <v>156</v>
-      </c>
+      <c r="B586" s="13"/>
+      <c r="C586" s="13"/>
+      <c r="D586" s="31"/>
+      <c r="E586" s="31"/>
+      <c r="F586" s="31"/>
+      <c r="G586" s="13"/>
+      <c r="H586" s="16"/>
       <c r="I586" s="13"/>
       <c r="J586" s="13"/>
     </row>
@@ -15376,35 +15354,45 @@
       <c r="C587" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="D587" s="32">
-        <v>2</v>
-      </c>
-      <c r="E587" s="32">
-        <v>1</v>
-      </c>
-      <c r="F587" s="32">
-        <v>2</v>
-      </c>
-      <c r="G587" s="33" t="s">
-        <v>76</v>
-      </c>
-      <c r="H587" s="23" t="s">
-        <v>152</v>
+      <c r="D587" s="18">
+        <v>2</v>
+      </c>
+      <c r="E587" s="18">
+        <v>1</v>
+      </c>
+      <c r="F587" s="18"/>
+      <c r="G587" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="H587" s="24" t="s">
+        <v>153</v>
       </c>
       <c r="I587" s="13"/>
-      <c r="J587" s="34" t="s">
-        <v>173</v>
-      </c>
+      <c r="J587" s="13"/>
     </row>
     <row r="588" spans="1:10" ht="16.5">
       <c r="A588" s="31"/>
-      <c r="B588" s="13"/>
-      <c r="C588" s="13"/>
-      <c r="D588" s="31"/>
-      <c r="E588" s="31"/>
-      <c r="F588" s="31"/>
-      <c r="G588" s="13"/>
-      <c r="H588" s="16"/>
+      <c r="B588" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C588" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="D588" s="31">
+        <v>2</v>
+      </c>
+      <c r="E588" s="31">
+        <v>1</v>
+      </c>
+      <c r="F588" s="31">
+        <v>1</v>
+      </c>
+      <c r="G588" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="H588" s="16" t="s">
+        <v>156</v>
+      </c>
       <c r="I588" s="13"/>
       <c r="J588" s="13"/>
     </row>
@@ -15416,45 +15404,35 @@
       <c r="C589" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="D589" s="18">
-        <v>2</v>
-      </c>
-      <c r="E589" s="18">
-        <v>2</v>
-      </c>
-      <c r="F589" s="18"/>
-      <c r="G589" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="H589" s="24" t="s">
-        <v>154</v>
+      <c r="D589" s="32">
+        <v>2</v>
+      </c>
+      <c r="E589" s="32">
+        <v>1</v>
+      </c>
+      <c r="F589" s="32">
+        <v>2</v>
+      </c>
+      <c r="G589" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="H589" s="23" t="s">
+        <v>152</v>
       </c>
       <c r="I589" s="13"/>
-      <c r="J589" s="13"/>
-    </row>
-    <row r="590" spans="1:10" ht="33">
+      <c r="J589" s="34" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="590" spans="1:10" ht="16.5">
       <c r="A590" s="31"/>
-      <c r="B590" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="C590" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="D590" s="31">
-        <v>2</v>
-      </c>
-      <c r="E590" s="31">
-        <v>2</v>
-      </c>
-      <c r="F590" s="31">
-        <v>1</v>
-      </c>
-      <c r="G590" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="H590" s="16" t="s">
-        <v>300</v>
-      </c>
+      <c r="B590" s="13"/>
+      <c r="C590" s="13"/>
+      <c r="D590" s="31"/>
+      <c r="E590" s="31"/>
+      <c r="F590" s="31"/>
+      <c r="G590" s="13"/>
+      <c r="H590" s="16"/>
       <c r="I590" s="13"/>
       <c r="J590" s="13"/>
     </row>
@@ -15466,45 +15444,71 @@
       <c r="C591" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="D591" s="32">
-        <v>2</v>
-      </c>
-      <c r="E591" s="32">
-        <v>2</v>
-      </c>
-      <c r="F591" s="32">
-        <v>2</v>
-      </c>
-      <c r="G591" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="H591" s="23" t="s">
-        <v>78</v>
+      <c r="D591" s="18">
+        <v>2</v>
+      </c>
+      <c r="E591" s="18">
+        <v>2</v>
+      </c>
+      <c r="F591" s="18"/>
+      <c r="G591" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="H591" s="24" t="s">
+        <v>154</v>
       </c>
       <c r="I591" s="13"/>
       <c r="J591" s="13"/>
     </row>
-    <row r="592" spans="1:10" ht="16.5">
+    <row r="592" spans="1:10" ht="33">
       <c r="A592" s="31"/>
-      <c r="B592" s="13"/>
-      <c r="C592" s="13"/>
-      <c r="D592" s="31"/>
-      <c r="E592" s="31"/>
-      <c r="F592" s="31"/>
-      <c r="G592" s="13"/>
-      <c r="H592" s="16"/>
+      <c r="B592" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C592" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="D592" s="31">
+        <v>2</v>
+      </c>
+      <c r="E592" s="31">
+        <v>2</v>
+      </c>
+      <c r="F592" s="31">
+        <v>1</v>
+      </c>
+      <c r="G592" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="H592" s="16" t="s">
+        <v>300</v>
+      </c>
       <c r="I592" s="13"/>
       <c r="J592" s="13"/>
     </row>
     <row r="593" spans="1:10" ht="16.5">
       <c r="A593" s="31"/>
-      <c r="B593" s="13"/>
-      <c r="C593" s="13"/>
-      <c r="D593" s="31"/>
-      <c r="E593" s="31"/>
-      <c r="F593" s="31"/>
-      <c r="G593" s="13"/>
-      <c r="H593" s="16"/>
+      <c r="B593" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C593" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="D593" s="32">
+        <v>2</v>
+      </c>
+      <c r="E593" s="32">
+        <v>2</v>
+      </c>
+      <c r="F593" s="32">
+        <v>2</v>
+      </c>
+      <c r="G593" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="H593" s="23" t="s">
+        <v>78</v>
+      </c>
       <c r="I593" s="13"/>
       <c r="J593" s="13"/>
     </row>
@@ -15520,31 +15524,17 @@
       <c r="I594" s="13"/>
       <c r="J594" s="13"/>
     </row>
-    <row r="595" spans="1:10" ht="21">
-      <c r="A595" s="9">
-        <v>30603</v>
-      </c>
-      <c r="B595" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C595" s="35" t="s">
-        <v>86</v>
-      </c>
-      <c r="D595" s="30">
-        <v>1</v>
-      </c>
-      <c r="E595" s="30"/>
-      <c r="F595" s="30"/>
-      <c r="G595" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H595" s="11" t="s">
-        <v>422</v>
-      </c>
-      <c r="I595" s="10"/>
-      <c r="J595" s="12" t="s">
-        <v>296</v>
-      </c>
+    <row r="595" spans="1:10" ht="16.5">
+      <c r="A595" s="31"/>
+      <c r="B595" s="13"/>
+      <c r="C595" s="13"/>
+      <c r="D595" s="31"/>
+      <c r="E595" s="31"/>
+      <c r="F595" s="31"/>
+      <c r="G595" s="13"/>
+      <c r="H595" s="16"/>
+      <c r="I595" s="13"/>
+      <c r="J595" s="13"/>
     </row>
     <row r="596" spans="1:10" ht="16.5">
       <c r="A596" s="31"/>
@@ -15558,53 +15548,41 @@
       <c r="I596" s="13"/>
       <c r="J596" s="13"/>
     </row>
-    <row r="597" spans="1:10" ht="16.5">
-      <c r="A597" s="31"/>
-      <c r="B597" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="C597" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="D597" s="18">
-        <v>2</v>
-      </c>
-      <c r="E597" s="18">
-        <v>1</v>
-      </c>
-      <c r="F597" s="18"/>
-      <c r="G597" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="H597" s="24" t="s">
-        <v>153</v>
-      </c>
-      <c r="I597" s="13"/>
-      <c r="J597" s="13"/>
+    <row r="597" spans="1:10" ht="21">
+      <c r="A597" s="9">
+        <v>30603</v>
+      </c>
+      <c r="B597" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C597" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="D597" s="30">
+        <v>1</v>
+      </c>
+      <c r="E597" s="30"/>
+      <c r="F597" s="30"/>
+      <c r="G597" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="H597" s="11" t="s">
+        <v>422</v>
+      </c>
+      <c r="I597" s="10"/>
+      <c r="J597" s="12" t="s">
+        <v>296</v>
+      </c>
     </row>
     <row r="598" spans="1:10" ht="16.5">
       <c r="A598" s="31"/>
-      <c r="B598" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="C598" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="D598" s="31">
-        <v>2</v>
-      </c>
-      <c r="E598" s="31">
-        <v>1</v>
-      </c>
-      <c r="F598" s="31">
-        <v>1</v>
-      </c>
-      <c r="G598" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="H598" s="16" t="s">
-        <v>156</v>
-      </c>
+      <c r="B598" s="13"/>
+      <c r="C598" s="13"/>
+      <c r="D598" s="31"/>
+      <c r="E598" s="31"/>
+      <c r="F598" s="31"/>
+      <c r="G598" s="13"/>
+      <c r="H598" s="16"/>
       <c r="I598" s="13"/>
       <c r="J598" s="13"/>
     </row>
@@ -15616,35 +15594,45 @@
       <c r="C599" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="D599" s="32">
-        <v>2</v>
-      </c>
-      <c r="E599" s="32">
-        <v>1</v>
-      </c>
-      <c r="F599" s="32">
-        <v>2</v>
-      </c>
-      <c r="G599" s="33" t="s">
-        <v>76</v>
-      </c>
-      <c r="H599" s="23" t="s">
-        <v>152</v>
+      <c r="D599" s="18">
+        <v>2</v>
+      </c>
+      <c r="E599" s="18">
+        <v>1</v>
+      </c>
+      <c r="F599" s="18"/>
+      <c r="G599" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="H599" s="24" t="s">
+        <v>153</v>
       </c>
       <c r="I599" s="13"/>
-      <c r="J599" s="34" t="s">
-        <v>173</v>
-      </c>
+      <c r="J599" s="13"/>
     </row>
     <row r="600" spans="1:10" ht="16.5">
       <c r="A600" s="31"/>
-      <c r="B600" s="13"/>
-      <c r="C600" s="13"/>
-      <c r="D600" s="31"/>
-      <c r="E600" s="31"/>
-      <c r="F600" s="31"/>
-      <c r="G600" s="13"/>
-      <c r="H600" s="16"/>
+      <c r="B600" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C600" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="D600" s="31">
+        <v>2</v>
+      </c>
+      <c r="E600" s="31">
+        <v>1</v>
+      </c>
+      <c r="F600" s="31">
+        <v>1</v>
+      </c>
+      <c r="G600" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="H600" s="16" t="s">
+        <v>156</v>
+      </c>
       <c r="I600" s="13"/>
       <c r="J600" s="13"/>
     </row>
@@ -15656,45 +15644,35 @@
       <c r="C601" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="D601" s="18">
-        <v>2</v>
-      </c>
-      <c r="E601" s="18">
-        <v>2</v>
-      </c>
-      <c r="F601" s="18"/>
-      <c r="G601" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="H601" s="24" t="s">
-        <v>154</v>
+      <c r="D601" s="32">
+        <v>2</v>
+      </c>
+      <c r="E601" s="32">
+        <v>1</v>
+      </c>
+      <c r="F601" s="32">
+        <v>2</v>
+      </c>
+      <c r="G601" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="H601" s="23" t="s">
+        <v>152</v>
       </c>
       <c r="I601" s="13"/>
-      <c r="J601" s="13"/>
-    </row>
-    <row r="602" spans="1:10" ht="33">
+      <c r="J601" s="34" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="602" spans="1:10" ht="16.5">
       <c r="A602" s="31"/>
-      <c r="B602" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="C602" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="D602" s="31">
-        <v>2</v>
-      </c>
-      <c r="E602" s="31">
-        <v>2</v>
-      </c>
-      <c r="F602" s="31">
-        <v>1</v>
-      </c>
-      <c r="G602" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="H602" s="16" t="s">
-        <v>300</v>
-      </c>
+      <c r="B602" s="13"/>
+      <c r="C602" s="13"/>
+      <c r="D602" s="31"/>
+      <c r="E602" s="31"/>
+      <c r="F602" s="31"/>
+      <c r="G602" s="13"/>
+      <c r="H602" s="16"/>
       <c r="I602" s="13"/>
       <c r="J602" s="13"/>
     </row>
@@ -15706,90 +15684,107 @@
       <c r="C603" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="D603" s="32">
-        <v>2</v>
-      </c>
-      <c r="E603" s="32">
-        <v>2</v>
-      </c>
-      <c r="F603" s="32">
-        <v>2</v>
-      </c>
-      <c r="G603" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="H603" s="23" t="s">
-        <v>78</v>
+      <c r="D603" s="18">
+        <v>2</v>
+      </c>
+      <c r="E603" s="18">
+        <v>2</v>
+      </c>
+      <c r="F603" s="18"/>
+      <c r="G603" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="H603" s="24" t="s">
+        <v>154</v>
       </c>
       <c r="I603" s="13"/>
       <c r="J603" s="13"/>
     </row>
-    <row r="604" spans="1:10" ht="16.5">
+    <row r="604" spans="1:10" ht="33">
       <c r="A604" s="31"/>
-      <c r="B604" s="13"/>
-      <c r="C604" s="13"/>
-      <c r="D604" s="31"/>
-      <c r="E604" s="31"/>
-      <c r="F604" s="31"/>
-      <c r="G604" s="13"/>
-      <c r="H604" s="16"/>
+      <c r="B604" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C604" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="D604" s="31">
+        <v>2</v>
+      </c>
+      <c r="E604" s="31">
+        <v>2</v>
+      </c>
+      <c r="F604" s="31">
+        <v>1</v>
+      </c>
+      <c r="G604" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="H604" s="16" t="s">
+        <v>300</v>
+      </c>
       <c r="I604" s="13"/>
       <c r="J604" s="13"/>
     </row>
     <row r="605" spans="1:10" ht="16.5">
       <c r="A605" s="31"/>
-      <c r="B605" s="13"/>
-      <c r="C605" s="13"/>
-      <c r="D605" s="31"/>
-      <c r="E605" s="31"/>
-      <c r="F605" s="31"/>
-      <c r="G605" s="13"/>
-      <c r="H605" s="16"/>
+      <c r="B605" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C605" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="D605" s="32">
+        <v>2</v>
+      </c>
+      <c r="E605" s="32">
+        <v>2</v>
+      </c>
+      <c r="F605" s="32">
+        <v>2</v>
+      </c>
+      <c r="G605" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="H605" s="23" t="s">
+        <v>78</v>
+      </c>
       <c r="I605" s="13"/>
       <c r="J605" s="13"/>
     </row>
     <row r="606" spans="1:10" ht="16.5">
-      <c r="A606" s="9">
-        <v>40601</v>
-      </c>
-      <c r="B606" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="C606" s="35" t="s">
-        <v>292</v>
-      </c>
-      <c r="D606" s="30" t="s">
-        <v>72</v>
-      </c>
-      <c r="E606" s="30"/>
-      <c r="F606" s="30"/>
-      <c r="G606" s="35" t="s">
-        <v>73</v>
-      </c>
-      <c r="H606" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="I606" s="36"/>
-      <c r="J606" s="35" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="607" spans="1:10">
-      <c r="A607" s="7"/>
-      <c r="D607" s="7"/>
-      <c r="E607" s="7"/>
-      <c r="F607" s="7"/>
-      <c r="H607" s="39"/>
+      <c r="A606" s="31"/>
+      <c r="B606" s="13"/>
+      <c r="C606" s="13"/>
+      <c r="D606" s="31"/>
+      <c r="E606" s="31"/>
+      <c r="F606" s="31"/>
+      <c r="G606" s="13"/>
+      <c r="H606" s="16"/>
+      <c r="I606" s="13"/>
+      <c r="J606" s="13"/>
+    </row>
+    <row r="607" spans="1:10" ht="16.5">
+      <c r="A607" s="31"/>
+      <c r="B607" s="13"/>
+      <c r="C607" s="13"/>
+      <c r="D607" s="31"/>
+      <c r="E607" s="31"/>
+      <c r="F607" s="31"/>
+      <c r="G607" s="13"/>
+      <c r="H607" s="16"/>
+      <c r="I607" s="13"/>
+      <c r="J607" s="13"/>
     </row>
     <row r="608" spans="1:10" ht="16.5">
       <c r="A608" s="9">
-        <v>40602</v>
+        <v>40601</v>
       </c>
       <c r="B608" s="35" t="s">
         <v>70</v>
       </c>
       <c r="C608" s="35" t="s">
-        <v>86</v>
+        <v>292</v>
       </c>
       <c r="D608" s="30" t="s">
         <v>72</v>
@@ -15800,11 +15795,11 @@
         <v>73</v>
       </c>
       <c r="H608" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I608" s="36"/>
       <c r="J608" s="35" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="609" spans="1:10">
@@ -15816,7 +15811,7 @@
     </row>
     <row r="610" spans="1:10" ht="16.5">
       <c r="A610" s="9">
-        <v>40603</v>
+        <v>40602</v>
       </c>
       <c r="B610" s="35" t="s">
         <v>70</v>
@@ -15833,7 +15828,7 @@
         <v>73</v>
       </c>
       <c r="H610" s="11" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I610" s="36"/>
       <c r="J610" s="35" t="s">
@@ -15849,13 +15844,13 @@
     </row>
     <row r="612" spans="1:10" ht="16.5">
       <c r="A612" s="9">
-        <v>40604</v>
+        <v>40603</v>
       </c>
       <c r="B612" s="35" t="s">
         <v>70</v>
       </c>
       <c r="C612" s="35" t="s">
-        <v>297</v>
+        <v>86</v>
       </c>
       <c r="D612" s="30" t="s">
         <v>72</v>
@@ -15866,11 +15861,11 @@
         <v>73</v>
       </c>
       <c r="H612" s="11" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I612" s="36"/>
       <c r="J612" s="35" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="613" spans="1:10">
@@ -15882,7 +15877,7 @@
     </row>
     <row r="614" spans="1:10" ht="16.5">
       <c r="A614" s="9">
-        <v>50601</v>
+        <v>40604</v>
       </c>
       <c r="B614" s="35" t="s">
         <v>70</v>
@@ -15899,11 +15894,11 @@
         <v>73</v>
       </c>
       <c r="H614" s="11" t="s">
-        <v>423</v>
+        <v>181</v>
       </c>
       <c r="I614" s="36"/>
       <c r="J614" s="35" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="615" spans="1:10">
@@ -15915,7 +15910,7 @@
     </row>
     <row r="616" spans="1:10" ht="16.5">
       <c r="A616" s="9">
-        <v>50602</v>
+        <v>50601</v>
       </c>
       <c r="B616" s="35" t="s">
         <v>70</v>
@@ -15932,7 +15927,7 @@
         <v>73</v>
       </c>
       <c r="H616" s="11" t="s">
-        <v>182</v>
+        <v>423</v>
       </c>
       <c r="I616" s="36"/>
       <c r="J616" s="35" t="s">
@@ -15948,7 +15943,7 @@
     </row>
     <row r="618" spans="1:10" ht="16.5">
       <c r="A618" s="9">
-        <v>50603</v>
+        <v>50602</v>
       </c>
       <c r="B618" s="35" t="s">
         <v>70</v>
@@ -15965,10 +15960,43 @@
         <v>73</v>
       </c>
       <c r="H618" s="11" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="I618" s="36"/>
       <c r="J618" s="35" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="619" spans="1:10">
+      <c r="A619" s="7"/>
+      <c r="D619" s="7"/>
+      <c r="E619" s="7"/>
+      <c r="F619" s="7"/>
+      <c r="H619" s="39"/>
+    </row>
+    <row r="620" spans="1:10" ht="16.5">
+      <c r="A620" s="9">
+        <v>50603</v>
+      </c>
+      <c r="B620" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="C620" s="35" t="s">
+        <v>297</v>
+      </c>
+      <c r="D620" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="E620" s="30"/>
+      <c r="F620" s="30"/>
+      <c r="G620" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="H620" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="I620" s="36"/>
+      <c r="J620" s="35" t="s">
         <v>186</v>
       </c>
     </row>
@@ -15983,13 +16011,13 @@
           <x14:formula1>
             <xm:f>参考!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>B3:B2046 G3:G2046</xm:sqref>
+          <xm:sqref>G3:G2048 B3:B2048</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="可选值" prompt="Excel/立绘表.xlsx 里的立绘ID。**留空 = 沿用上一句**；组内首句留空则用种族默认立绘" xr:uid="{00000000-0002-0000-0100-000002000000}">
           <x14:formula1>
             <xm:f>参考!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>C3:C2046</xm:sqref>
+          <xm:sqref>C3:C2048</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Excel/对话表.xlsx
+++ b/Excel/对话表.xlsx
@@ -1381,7 +1381,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Need_新需求</t>
+          <t>Need_修理电路_02</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Need_新需求</t>
+          <t>Need_修理电路_02</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Need_新需求</t>
+          <t>Need_修理电路_02</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Need_新需求</t>
+          <t>Need_修理电路_02</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Need_新需求</t>
+          <t>Need_修理电路_02</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">

--- a/Excel/对话表.xlsx
+++ b/Excel/对话表.xlsx
@@ -4734,6 +4734,7 @@
       <c r="F81" s="7" t="n"/>
       <c r="H81" s="39" t="n"/>
     </row>
+    <row r="82"/>
     <row r="83">
       <c r="A83" s="42" t="n"/>
       <c r="B83" s="43" t="n"/>

--- a/Excel/对话表.xlsx
+++ b/Excel/对话表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xinxinhe\Documents\2026MasterHouse\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{600A2348-FF74-43FB-98DE-7891585F892A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7103278-D441-45C2-8605-5F93E14DC7E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/对话表.xlsx
+++ b/Excel/对话表.xlsx
@@ -5321,12 +5321,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>visitor</t>
+          <t>player</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>leopard_平静</t>
+          <t>goat_伤心</t>
         </is>
       </c>
       <c r="D96">
@@ -5336,16 +5336,16 @@
         <v>2</v>
       </c>
       <c r="F96">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>Line</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Reject</t>
+          <t>非常抱歉，目前没有能够满足您要求的房间。</t>
         </is>
       </c>
     </row>
@@ -5355,12 +5355,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>player</t>
+          <t>visitor</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>goat_伤心</t>
+          <t>leopard_伤心</t>
         </is>
       </c>
       <c r="D97">
@@ -5379,7 +5379,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>非常抱歉，目前没有能够满足您要求的房间。</t>
+          <t>那，那好吧，那我只能去其他地方看看了，55555……</t>
         </is>
       </c>
     </row>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>leopard_伤心</t>
+          <t>leopard_平静</t>
         </is>
       </c>
       <c r="D98">
@@ -5408,12 +5408,12 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Line</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>那，那好吧，那我只能去其他地方看看了，55555……</t>
+          <t>Reject</t>
         </is>
       </c>
     </row>
@@ -6975,12 +6975,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>visitor</t>
+          <t>player</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>cheetah_平静</t>
+          <t>goat_伤心</t>
         </is>
       </c>
       <c r="D178">
@@ -6990,16 +6990,16 @@
         <v>2</v>
       </c>
       <c r="F178">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>Line</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Reject</t>
+          <t>非常抱歉，目前没有能够满足您要求的房间咩。</t>
         </is>
       </c>
     </row>
@@ -7009,12 +7009,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>player</t>
+          <t>visitor</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>goat_伤心</t>
+          <t>cheetah_伤心</t>
         </is>
       </c>
       <c r="D179">
@@ -7033,7 +7033,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>非常抱歉，目前没有能够满足您要求的房间咩。</t>
+          <t>没关系，我再去其他地方看看。</t>
         </is>
       </c>
     </row>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>cheetah_伤心</t>
+          <t>cheetah_平静</t>
         </is>
       </c>
       <c r="D180">
@@ -7062,12 +7062,12 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Line</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>没关系，我再去其他地方看看。</t>
+          <t>Reject</t>
         </is>
       </c>
     </row>
@@ -8929,12 +8929,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>visitor</t>
+          <t>player</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>yak_平静</t>
+          <t>goat_伤心</t>
         </is>
       </c>
       <c r="D270">
@@ -8944,16 +8944,16 @@
         <v>2</v>
       </c>
       <c r="F270">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>Line</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>Reject</t>
+          <t>非常抱歉咩，目前没有能够满足您要求的房间。</t>
         </is>
       </c>
     </row>
@@ -8963,12 +8963,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>player</t>
+          <t>visitor</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>goat_伤心</t>
+          <t>yak_伤心</t>
         </is>
       </c>
       <c r="D271">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>非常抱歉咩，目前没有能够满足您要求的房间。</t>
+          <t>没关系，那我先走了哞。</t>
         </is>
       </c>
     </row>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>yak_伤心</t>
+          <t>yak_平静</t>
         </is>
       </c>
       <c r="D272">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Line</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>没关系，那我先走了哞。</t>
+          <t>Reject</t>
         </is>
       </c>
     </row>
@@ -10877,12 +10877,12 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>visitor</t>
+          <t>player</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>rabbit_平静</t>
+          <t>goat_伤心</t>
         </is>
       </c>
       <c r="D364">
@@ -10892,16 +10892,16 @@
         <v>2</v>
       </c>
       <c r="F364">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>Line</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>Reject</t>
+          <t>非常抱歉咩，目前没有能够满足您要求的房间咩。</t>
         </is>
       </c>
     </row>
@@ -10911,12 +10911,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>player</t>
+          <t>visitor</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>goat_伤心</t>
+          <t>rabbit_伤心</t>
         </is>
       </c>
       <c r="D365">
@@ -10935,7 +10935,7 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>非常抱歉咩，目前没有能够满足您要求的房间咩。</t>
+          <t>啊……没关系啦，我再去其他地方看看。</t>
         </is>
       </c>
     </row>
@@ -10950,7 +10950,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>rabbit_伤心</t>
+          <t>rabbit_平静</t>
         </is>
       </c>
       <c r="D366">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>Line</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>啊……没关系啦，我再去其他地方看看。</t>
+          <t>Reject</t>
         </is>
       </c>
     </row>
@@ -12757,12 +12757,12 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>visitor</t>
+          <t>player</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>wolf_平静</t>
+          <t>goat_伤心</t>
         </is>
       </c>
       <c r="D454">
@@ -12772,16 +12772,16 @@
         <v>2</v>
       </c>
       <c r="F454">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>Line</t>
         </is>
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>Reject</t>
+          <t>非常抱歉咩，目前没有合适房间咩。</t>
         </is>
       </c>
     </row>
@@ -12791,12 +12791,12 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>player</t>
+          <t>visitor</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>goat_伤心</t>
+          <t>wolf_伤心</t>
         </is>
       </c>
       <c r="D455">
@@ -12815,7 +12815,7 @@
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>非常抱歉咩，目前没有合适房间咩。</t>
+          <t>好吧，不过你们酒店的接待能力也该提升下了。</t>
         </is>
       </c>
     </row>
@@ -12830,7 +12830,7 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>wolf_伤心</t>
+          <t>wolf_平静</t>
         </is>
       </c>
       <c r="D456">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>Line</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>好吧，不过你们酒店的接待能力也该提升下了。</t>
+          <t>Reject</t>
         </is>
       </c>
     </row>
@@ -14576,12 +14576,12 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>visitor</t>
+          <t>player</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>ox_平静</t>
+          <t>goat_伤心</t>
         </is>
       </c>
       <c r="D545">
@@ -14591,16 +14591,16 @@
         <v>2</v>
       </c>
       <c r="F545">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G545" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>Line</t>
         </is>
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>Reject</t>
+          <t>非常抱歉，目前没有能够满足您要求的房间。</t>
         </is>
       </c>
     </row>
@@ -14610,12 +14610,12 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>player</t>
+          <t>visitor</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>goat_伤心</t>
+          <t>ox_伤心</t>
         </is>
       </c>
       <c r="D546">
@@ -14634,7 +14634,7 @@
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>非常抱歉，目前没有能够满足您要求的房间。</t>
+          <t>好的，不过一旦有，请立马通知我哞。</t>
         </is>
       </c>
     </row>
@@ -14649,7 +14649,7 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>ox_伤心</t>
+          <t>ox_平静</t>
         </is>
       </c>
       <c r="D547">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="G547" t="inlineStr">
         <is>
-          <t>Line</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>好的，不过一旦有，请立马通知我哞。</t>
+          <t>Reject</t>
         </is>
       </c>
     </row>
@@ -17278,7 +17278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -17287,354 +17287,506 @@
     <col min="6" max="6" width="74.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>362</v>
-      </c>
-      <c r="E2" t="s">
-        <v>132</v>
-      </c>
-      <c r="F2" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" t="s">
-        <v>364</v>
-      </c>
-      <c r="E3" t="s">
-        <v>139</v>
-      </c>
-      <c r="F3" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" t="s">
-        <v>366</v>
-      </c>
-      <c r="E4" t="s">
-        <v>367</v>
-      </c>
-      <c r="F4" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" t="s">
-        <v>369</v>
-      </c>
-      <c r="E5" t="s">
-        <v>169</v>
-      </c>
-      <c r="F5" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" t="s">
-        <v>371</v>
-      </c>
-      <c r="E6" t="s">
-        <v>372</v>
-      </c>
-      <c r="F6" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" t="s">
-        <v>374</v>
-      </c>
-      <c r="E7" t="s">
-        <v>375</v>
-      </c>
-      <c r="F7" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" t="s">
-        <v>377</v>
-      </c>
-      <c r="E8" t="s">
-        <v>378</v>
-      </c>
-      <c r="F8" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" t="s">
-        <v>117</v>
-      </c>
-      <c r="B13" t="s">
-        <v>381</v>
-      </c>
-      <c r="E13" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" t="s">
-        <v>131</v>
-      </c>
-      <c r="B14" t="s">
-        <v>383</v>
-      </c>
-      <c r="E14" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" t="s">
-        <v>124</v>
-      </c>
-      <c r="B15" t="s">
-        <v>385</v>
-      </c>
-      <c r="E15" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" t="s">
-        <v>115</v>
-      </c>
-      <c r="B19" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" t="s">
-        <v>120</v>
-      </c>
-      <c r="B20" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" t="s">
-        <v>388</v>
-      </c>
-      <c r="B21" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="C23" s="3"/>
-      <c r="E23" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" t="s">
-        <v>272</v>
-      </c>
-      <c r="E24" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25" t="s">
-        <v>121</v>
-      </c>
-      <c r="E25" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26" t="s">
-        <v>305</v>
-      </c>
-      <c r="E26" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" t="s">
-        <v>182</v>
-      </c>
-      <c r="E27" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" t="s">
-        <v>207</v>
-      </c>
-      <c r="E28" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" t="s">
-        <v>337</v>
-      </c>
-      <c r="E29" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" t="s">
-        <v>116</v>
-      </c>
-      <c r="E30" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31" t="s">
-        <v>238</v>
-      </c>
-      <c r="E31" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" t="s">
-        <v>393</v>
-      </c>
-      <c r="B35" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36" t="s">
-        <v>126</v>
-      </c>
-      <c r="B36" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" t="s">
-        <v>163</v>
-      </c>
-      <c r="B37" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" t="s">
-        <v>397</v>
-      </c>
-      <c r="B38" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" t="s">
-        <v>399</v>
-      </c>
-      <c r="B39" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" t="s">
-        <v>401</v>
-      </c>
-      <c r="B40" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41" t="s">
-        <v>403</v>
-      </c>
-      <c r="B41" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42" t="s">
-        <v>405</v>
-      </c>
-      <c r="B42" t="s">
-        <v>406</v>
+    <row r="1" spans="1:5">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>所属对话池</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>事件函数</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>firstMeeting</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>初次见面：首次点击前台队首访客。组内要有「接待 / 拒绝」分支</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>waitingReception</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>等待接待：同一位前台访客的二次点击。**同样要带接待/拒绝分支**</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>needTalk</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>需求对话：入住并示意后点击他。说需求 + 交付/推迟/放弃分支。**需求ID 必填**</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>CompleteNeed(档)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>feedbackDisappointed</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>需求反馈·失望：服务超时，需求没办到</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>StartMinigame</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>feedbackPlain</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>需求反馈·一般：小游戏低分。条件类走不到这一档</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AddCurrency(N)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>feedbackFine</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>需求反馈·还行：小游戏中间分。条件类走不到这一档</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AddReputation(N)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>feedbackPerfect</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>需求反馈·完美：条件类交付成功 / 小游戏满分</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Log(文本)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>smallTalk</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>闲聊：停留期冒泡，走场景气泡。**一组只显示第一句**，多句请拆成多组</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Leave</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>farewell</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>告别：待告别时点击访客。组末尾必须有 Action | Leave</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>需求ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>说一句话。填说话人 / 立绘ID / 文本</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Need_修理电路_01</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>执行事件。「文本」列写调用串（如 Accept），说话人与立绘ID 留空</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Need_修理电路_02</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>一个选项。填「选项」列（从 1 起），「文本」是选项文字，「条件」是它的可选条件</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Need_要蓝色椅子</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>说话人</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>visitor</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>访客：显示立绘与名字条</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>玩家：无立绘、另一种框</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>narration</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>旁白：居中无框</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>立绘ID</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>390</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>rabbit_平静</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>rabbit</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>goat_平静</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>goat</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>wolf_平静</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>wolf</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>leopard_平静</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>leopard</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>cheetah_平静</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>cheetah</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ox_平静</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>ox</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>cat_平静</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>cat</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>yak_平静</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>yak</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>条件函数</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>HasEmptyRoom</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>还有空客房（只看房，不看队列）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>CanAcceptGuest</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>现在能接待新客人（有空房 且 没有别人正在等分房）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>RoomHasNeedFurniture</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>所住房间里摆着他要的家具之一（条件类需求的验收判据）</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>DayAtLeast(N)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>第 N 天或更晚</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>CurrencyAtLeast(N)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>货币不少于 N</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ReputationAtLeast(N)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>声望不少于 N</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SatisfactionAtLeast(档)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>本次满意度不低于 disappointed/plain/fine/perfect</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>VisitorStateIs(状态)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>访客处于 FrontDesk/AwaitingRoom/Serving/Wandering</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Excel/对话表.xlsx
+++ b/Excel/对话表.xlsx
@@ -2504,7 +2504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J680"/>
+  <dimension ref="A1:J687"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="9.5" bestFit="1" customWidth="1" style="15" min="1" max="1"/>
@@ -15833,65 +15833,60 @@
       <c r="A635" t="n">
         <v>50004</v>
       </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>narration</t>
+        </is>
+      </c>
       <c r="D635" t="n">
         <v>5</v>
       </c>
       <c r="G635" t="inlineStr">
         <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>完成{访客名}服务，获得住宿费【货币+320】</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="n">
+        <v>50004</v>
+      </c>
+      <c r="D636" t="n">
+        <v>5</v>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="H635" t="inlineStr">
+      <c r="H636" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
     </row>
-    <row r="636"/>
-    <row r="637">
-      <c r="A637" t="n">
-        <v>50104</v>
-      </c>
-      <c r="B637" t="inlineStr">
-        <is>
-          <t>visitor</t>
-        </is>
-      </c>
-      <c r="C637" t="inlineStr">
-        <is>
-          <t>leopard_平静</t>
-        </is>
-      </c>
-      <c r="D637" t="n">
-        <v>1</v>
-      </c>
-      <c r="G637" t="inlineStr">
-        <is>
-          <t>Line</t>
-        </is>
-      </c>
-      <c r="H637" t="inlineStr">
-        <is>
-          <t>老板老板！我休息得超好！今天训练感觉都能多跑两圈！</t>
-        </is>
-      </c>
-    </row>
+    <row r="637"/>
     <row r="638">
       <c r="A638" t="n">
         <v>50104</v>
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>player</t>
+          <t>visitor</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>goat_平静</t>
+          <t>leopard_平静</t>
         </is>
       </c>
       <c r="D638" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G638" t="inlineStr">
         <is>
@@ -15900,7 +15895,7 @@
       </c>
       <c r="H638" t="inlineStr">
         <is>
-          <t>太好啦，豹冲冲恢复精神了咩。</t>
+          <t>老板老板！我休息得超好！今天训练感觉都能多跑两圈！</t>
         </is>
       </c>
     </row>
@@ -15910,16 +15905,16 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>visitor</t>
+          <t>player</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>leopard_平静</t>
+          <t>goat_平静</t>
         </is>
       </c>
       <c r="D639" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G639" t="inlineStr">
         <is>
@@ -15928,7 +15923,7 @@
       </c>
       <c r="H639" t="inlineStr">
         <is>
-          <t>房间也亮亮的，床也舒服，连做梦都梦见自己打出全垒打！</t>
+          <t>太好啦，豹冲冲恢复精神了咩。</t>
         </is>
       </c>
     </row>
@@ -15938,16 +15933,16 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>player</t>
+          <t>visitor</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>goat_平静</t>
+          <t>leopard_平静</t>
         </is>
       </c>
       <c r="D640" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G640" t="inlineStr">
         <is>
@@ -15956,7 +15951,7 @@
       </c>
       <c r="H640" t="inlineStr">
         <is>
-          <t>那一定是好兆头咩！</t>
+          <t>房间也亮亮的，床也舒服，连做梦都梦见自己打出全垒打！</t>
         </is>
       </c>
     </row>
@@ -15966,16 +15961,16 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>visitor</t>
+          <t>player</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>leopard_平静</t>
+          <t>goat_平静</t>
         </is>
       </c>
       <c r="D641" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G641" t="inlineStr">
         <is>
@@ -15984,7 +15979,7 @@
       </c>
       <c r="H641" t="inlineStr">
         <is>
-          <t>嘿嘿，下次比赛前我还要来这里住！我先走啦，拜拜！</t>
+          <t>那一定是好兆头咩！</t>
         </is>
       </c>
     </row>
@@ -15992,78 +15987,73 @@
       <c r="A642" t="n">
         <v>50104</v>
       </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>visitor</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>leopard_平静</t>
+        </is>
+      </c>
       <c r="D642" t="n">
+        <v>5</v>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>嘿嘿，下次比赛前我还要来这里住！我先走啦，拜拜！</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="n">
+        <v>50104</v>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>narration</t>
+        </is>
+      </c>
+      <c r="D643" t="n">
         <v>6</v>
       </c>
-      <c r="G642" t="inlineStr">
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>完成{访客名}服务，获得住宿费【货币+320】</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="n">
+        <v>50104</v>
+      </c>
+      <c r="D644" t="n">
+        <v>6</v>
+      </c>
+      <c r="G644" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="H642" t="inlineStr">
+      <c r="H644" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
       </c>
     </row>
-    <row r="643"/>
-    <row r="644"/>
-    <row r="645">
-      <c r="A645" t="n">
-        <v>50204</v>
-      </c>
-      <c r="B645" t="inlineStr">
-        <is>
-          <t>visitor</t>
-        </is>
-      </c>
-      <c r="C645" t="inlineStr">
-        <is>
-          <t>cheetah_平静</t>
-        </is>
-      </c>
-      <c r="D645" t="n">
-        <v>1</v>
-      </c>
-      <c r="G645" t="inlineStr">
-        <is>
-          <t>Line</t>
-        </is>
-      </c>
-      <c r="H645" t="inlineStr">
-        <is>
-          <t>老板，谢谢您这几天的照顾。</t>
-        </is>
-      </c>
-    </row>
-    <row r="646">
-      <c r="A646" t="n">
-        <v>50204</v>
-      </c>
-      <c r="B646" t="inlineStr">
-        <is>
-          <t>player</t>
-        </is>
-      </c>
-      <c r="C646" t="inlineStr">
-        <is>
-          <t>goat_平静</t>
-        </is>
-      </c>
-      <c r="D646" t="n">
-        <v>2</v>
-      </c>
-      <c r="G646" t="inlineStr">
-        <is>
-          <t>Line</t>
-        </is>
-      </c>
-      <c r="H646" t="inlineStr">
-        <is>
-          <t>不客气咩，队长住得还舒服吗？</t>
-        </is>
-      </c>
-    </row>
+    <row r="645"/>
+    <row r="646"/>
     <row r="647">
       <c r="A647" t="n">
         <v>50204</v>
@@ -16079,7 +16069,7 @@
         </is>
       </c>
       <c r="D647" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G647" t="inlineStr">
         <is>
@@ -16088,7 +16078,7 @@
       </c>
       <c r="H647" t="inlineStr">
         <is>
-          <t>很安静，也没有被豹冲冲打扰。休息质量比我预期更好。</t>
+          <t>老板，谢谢您这几天的照顾。</t>
         </is>
       </c>
     </row>
@@ -16107,7 +16097,7 @@
         </is>
       </c>
       <c r="D648" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G648" t="inlineStr">
         <is>
@@ -16116,7 +16106,7 @@
       </c>
       <c r="H648" t="inlineStr">
         <is>
-          <t>能帮上忙就太好咩。</t>
+          <t>不客气咩，队长住得还舒服吗？</t>
         </is>
       </c>
     </row>
@@ -16135,7 +16125,7 @@
         </is>
       </c>
       <c r="D649" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G649" t="inlineStr">
         <is>
@@ -16144,7 +16134,7 @@
       </c>
       <c r="H649" t="inlineStr">
         <is>
-          <t>之后如果有比赛安排在附近，我会再联系您。再见。</t>
+          <t>很安静，也没有被豹冲冲打扰。休息质量比我预期更好。</t>
         </is>
       </c>
     </row>
@@ -16152,37 +16142,69 @@
       <c r="A650" t="n">
         <v>50204</v>
       </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>goat_平静</t>
+        </is>
+      </c>
       <c r="D650" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G650" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>Line</t>
         </is>
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t>Leave</t>
-        </is>
-      </c>
-    </row>
-    <row r="651"/>
+          <t>能帮上忙就太好咩。</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="n">
+        <v>50204</v>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>visitor</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>cheetah_平静</t>
+        </is>
+      </c>
+      <c r="D651" t="n">
+        <v>5</v>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="H651" t="inlineStr">
+        <is>
+          <t>之后如果有比赛安排在附近，我会再联系您。再见。</t>
+        </is>
+      </c>
+    </row>
     <row r="652">
       <c r="A652" t="n">
-        <v>50304</v>
+        <v>50204</v>
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>visitor</t>
-        </is>
-      </c>
-      <c r="C652" t="inlineStr">
-        <is>
-          <t>yak_平静</t>
+          <t>narration</t>
         </is>
       </c>
       <c r="D652" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G652" t="inlineStr">
         <is>
@@ -16191,82 +16213,45 @@
       </c>
       <c r="H652" t="inlineStr">
         <is>
-          <t>您好，我来退房。</t>
+          <t>完成{访客名}服务，获得住宿费【货币+320】</t>
         </is>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="n">
-        <v>50304</v>
-      </c>
-      <c r="B653" t="inlineStr">
-        <is>
-          <t>player</t>
-        </is>
-      </c>
-      <c r="C653" t="inlineStr">
-        <is>
-          <t>goat_平静</t>
-        </is>
+        <v>50204</v>
       </c>
       <c r="D653" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G653" t="inlineStr">
         <is>
-          <t>Line</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="H653" t="inlineStr">
         <is>
-          <t>好的咩，牛莱老师住得还满意吗？</t>
-        </is>
-      </c>
-    </row>
-    <row r="654">
-      <c r="A654" t="n">
-        <v>50304</v>
-      </c>
-      <c r="B654" t="inlineStr">
-        <is>
-          <t>visitor</t>
-        </is>
-      </c>
-      <c r="C654" t="inlineStr">
-        <is>
-          <t>yak_平静</t>
-        </is>
-      </c>
-      <c r="D654" t="n">
-        <v>3</v>
-      </c>
-      <c r="G654" t="inlineStr">
-        <is>
-          <t>Line</t>
-        </is>
-      </c>
-      <c r="H654" t="inlineStr">
-        <is>
-          <t>很满意。这里很舒适，像一段处理得恰到好处的休止符。</t>
-        </is>
-      </c>
-    </row>
+          <t>Leave</t>
+        </is>
+      </c>
+    </row>
+    <row r="654"/>
     <row r="655">
       <c r="A655" t="n">
         <v>50304</v>
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>player</t>
+          <t>visitor</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>goat_平静</t>
+          <t>yak_平静</t>
         </is>
       </c>
       <c r="D655" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G655" t="inlineStr">
         <is>
@@ -16275,7 +16260,7 @@
       </c>
       <c r="H655" t="inlineStr">
         <is>
-          <t>哇，听起来很优雅咩。</t>
+          <t>您好，我来退房。</t>
         </is>
       </c>
     </row>
@@ -16285,16 +16270,16 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>visitor</t>
+          <t>player</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>yak_平静</t>
+          <t>goat_平静</t>
         </is>
       </c>
       <c r="D656" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G656" t="inlineStr">
         <is>
@@ -16303,7 +16288,7 @@
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t>服务也很得体。你没有说多余的话，这点尤其值得称赞。</t>
+          <t>好的咩，牛莱老师住得还满意吗？</t>
         </is>
       </c>
     </row>
@@ -16313,16 +16298,16 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>player</t>
+          <t>visitor</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>goat_平静</t>
+          <t>yak_平静</t>
         </is>
       </c>
       <c r="D657" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G657" t="inlineStr">
         <is>
@@ -16331,7 +16316,7 @@
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t>谢谢老师认可咩！</t>
+          <t>很满意。这里很舒适，像一段处理得恰到好处的休止符。</t>
         </is>
       </c>
     </row>
@@ -16339,37 +16324,74 @@
       <c r="A658" t="n">
         <v>50304</v>
       </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>goat_平静</t>
+        </is>
+      </c>
       <c r="D658" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G658" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>Line</t>
         </is>
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t>Leave</t>
-        </is>
-      </c>
-    </row>
-    <row r="659"/>
+          <t>哇，听起来很优雅咩。</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="n">
+        <v>50304</v>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>visitor</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>yak_平静</t>
+        </is>
+      </c>
+      <c r="D659" t="n">
+        <v>5</v>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="H659" t="inlineStr">
+        <is>
+          <t>服务也很得体。你没有说多余的话，这点尤其值得称赞。</t>
+        </is>
+      </c>
+    </row>
     <row r="660">
       <c r="A660" t="n">
-        <v>50404</v>
+        <v>50304</v>
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>visitor</t>
+          <t>player</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>rabbit_平静</t>
+          <t>goat_平静</t>
         </is>
       </c>
       <c r="D660" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G660" t="inlineStr">
         <is>
@@ -16378,26 +16400,21 @@
       </c>
       <c r="H660" t="inlineStr">
         <is>
-          <t>老板，我来退房啦~这里很安静，休息得很舒服~</t>
+          <t>谢谢老师认可咩！</t>
         </is>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="n">
-        <v>50404</v>
+        <v>50304</v>
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>player</t>
-        </is>
-      </c>
-      <c r="C661" t="inlineStr">
-        <is>
-          <t>goat_平静</t>
+          <t>narration</t>
         </is>
       </c>
       <c r="D661" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G661" t="inlineStr">
         <is>
@@ -16406,66 +16423,29 @@
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>嘿嘿，能让偶像满意太开心咩。</t>
+          <t>完成{访客名}服务，获得住宿费【货币+320】</t>
         </is>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="n">
-        <v>50404</v>
-      </c>
-      <c r="B662" t="inlineStr">
-        <is>
-          <t>visitor</t>
-        </is>
-      </c>
-      <c r="C662" t="inlineStr">
-        <is>
-          <t>rabbit_平静</t>
-        </is>
+        <v>50304</v>
       </c>
       <c r="D662" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G662" t="inlineStr">
         <is>
-          <t>Line</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="H662" t="inlineStr">
         <is>
-          <t>谢谢你，下次行程经过这里，我会偷偷再来的。</t>
-        </is>
-      </c>
-    </row>
-    <row r="663">
-      <c r="A663" t="n">
-        <v>50404</v>
-      </c>
-      <c r="B663" t="inlineStr">
-        <is>
-          <t>player</t>
-        </is>
-      </c>
-      <c r="C663" t="inlineStr">
-        <is>
-          <t>goat_平静</t>
-        </is>
-      </c>
-      <c r="D663" t="n">
-        <v>4</v>
-      </c>
-      <c r="G663" t="inlineStr">
-        <is>
-          <t>Line</t>
-        </is>
-      </c>
-      <c r="H663" t="inlineStr">
-        <is>
-          <t>我会欢迎你的咩！（小声）</t>
-        </is>
-      </c>
-    </row>
+          <t>Leave</t>
+        </is>
+      </c>
+    </row>
+    <row r="663"/>
     <row r="664">
       <c r="A664" t="n">
         <v>50404</v>
@@ -16481,7 +16461,7 @@
         </is>
       </c>
       <c r="D664" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G664" t="inlineStr">
         <is>
@@ -16490,7 +16470,7 @@
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t>那我先走啦，拜拜~</t>
+          <t>老板，我来退房啦~这里很安静，休息得很舒服~</t>
         </is>
       </c>
     </row>
@@ -16498,37 +16478,74 @@
       <c r="A665" t="n">
         <v>50404</v>
       </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>goat_平静</t>
+        </is>
+      </c>
       <c r="D665" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G665" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>Line</t>
         </is>
       </c>
       <c r="H665" t="inlineStr">
         <is>
-          <t>Leave</t>
-        </is>
-      </c>
-    </row>
-    <row r="666"/>
+          <t>嘿嘿，能让偶像满意太开心咩。</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="n">
+        <v>50404</v>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>visitor</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>rabbit_平静</t>
+        </is>
+      </c>
+      <c r="D666" t="n">
+        <v>3</v>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="H666" t="inlineStr">
+        <is>
+          <t>谢谢你，下次行程经过这里，我会偷偷再来的。</t>
+        </is>
+      </c>
+    </row>
     <row r="667">
       <c r="A667" t="n">
-        <v>50504</v>
+        <v>50404</v>
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>visitor</t>
+          <t>player</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>wolf_平静</t>
+          <t>goat_平静</t>
         </is>
       </c>
       <c r="D667" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G667" t="inlineStr">
         <is>
@@ -16537,26 +16554,26 @@
       </c>
       <c r="H667" t="inlineStr">
         <is>
-          <t>小羊老板，我来退房。</t>
+          <t>我会欢迎你的咩！（小声）</t>
         </is>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="n">
-        <v>50504</v>
+        <v>50404</v>
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>player</t>
+          <t>visitor</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>goat_平静</t>
+          <t>rabbit_平静</t>
         </is>
       </c>
       <c r="D668" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G668" t="inlineStr">
         <is>
@@ -16565,26 +16582,21 @@
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t>好的咩，总裁这次入住还满意吗？</t>
+          <t>那我先走啦，拜拜~</t>
         </is>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="n">
-        <v>50504</v>
+        <v>50404</v>
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>visitor</t>
-        </is>
-      </c>
-      <c r="C669" t="inlineStr">
-        <is>
-          <t>wolf_平静</t>
+          <t>narration</t>
         </is>
       </c>
       <c r="D669" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G669" t="inlineStr">
         <is>
@@ -16593,82 +16605,45 @@
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t>勉强超过了我的预期。房间整洁，响应也算及时。</t>
+          <t>完成{访客名}服务，获得住宿费【货币+320】</t>
         </is>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="n">
-        <v>50504</v>
-      </c>
-      <c r="B670" t="inlineStr">
-        <is>
-          <t>player</t>
-        </is>
-      </c>
-      <c r="C670" t="inlineStr">
-        <is>
-          <t>goat_平静</t>
-        </is>
+        <v>50404</v>
       </c>
       <c r="D670" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G670" t="inlineStr">
         <is>
-          <t>Line</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="H670" t="inlineStr">
         <is>
-          <t>谢谢您的认可咩！</t>
-        </is>
-      </c>
-    </row>
-    <row r="671">
-      <c r="A671" t="n">
-        <v>50504</v>
-      </c>
-      <c r="B671" t="inlineStr">
-        <is>
-          <t>visitor</t>
-        </is>
-      </c>
-      <c r="C671" t="inlineStr">
-        <is>
-          <t>wolf_平静</t>
-        </is>
-      </c>
-      <c r="D671" t="n">
-        <v>5</v>
-      </c>
-      <c r="G671" t="inlineStr">
-        <is>
-          <t>Line</t>
-        </is>
-      </c>
-      <c r="H671" t="inlineStr">
-        <is>
-          <t>继续保持这个标准。下次我来，希望你们已经准备好了的总裁套房。</t>
-        </is>
-      </c>
-    </row>
+          <t>Leave</t>
+        </is>
+      </c>
+    </row>
+    <row r="671"/>
     <row r="672">
       <c r="A672" t="n">
         <v>50504</v>
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>player</t>
+          <t>visitor</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>goat_平静</t>
+          <t>wolf_平静</t>
         </is>
       </c>
       <c r="D672" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G672" t="inlineStr">
         <is>
@@ -16677,7 +16652,7 @@
       </c>
       <c r="H672" t="inlineStr">
         <is>
-          <t>我会努力准备咩！</t>
+          <t>小羊老板，我来退房。</t>
         </is>
       </c>
     </row>
@@ -16685,37 +16660,74 @@
       <c r="A673" t="n">
         <v>50504</v>
       </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>goat_平静</t>
+        </is>
+      </c>
       <c r="D673" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G673" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>Line</t>
         </is>
       </c>
       <c r="H673" t="inlineStr">
         <is>
-          <t>Leave</t>
-        </is>
-      </c>
-    </row>
-    <row r="674"/>
+          <t>好的咩，总裁这次入住还满意吗？</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="n">
+        <v>50504</v>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>visitor</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>wolf_平静</t>
+        </is>
+      </c>
+      <c r="D674" t="n">
+        <v>3</v>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>勉强超过了我的预期。房间整洁，响应也算及时。</t>
+        </is>
+      </c>
+    </row>
     <row r="675">
       <c r="A675" t="n">
-        <v>50604</v>
+        <v>50504</v>
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>visitor</t>
+          <t>player</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>ox_平静</t>
+          <t>goat_平静</t>
         </is>
       </c>
       <c r="D675" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G675" t="inlineStr">
         <is>
@@ -16724,26 +16736,26 @@
       </c>
       <c r="H675" t="inlineStr">
         <is>
-          <t>您好，我来办理退房。</t>
+          <t>谢谢您的认可咩！</t>
         </is>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="n">
-        <v>50604</v>
+        <v>50504</v>
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>player</t>
+          <t>visitor</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>goat_平静</t>
+          <t>wolf_平静</t>
         </is>
       </c>
       <c r="D676" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G676" t="inlineStr">
         <is>
@@ -16752,26 +16764,26 @@
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t>好的咩，牛小顿先生这次住得怎么样？</t>
+          <t>继续保持这个标准。下次我来，希望你们已经准备好了的总裁套房。</t>
         </is>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="n">
-        <v>50604</v>
+        <v>50504</v>
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>visitor</t>
+          <t>player</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>ox_平静</t>
+          <t>goat_平静</t>
         </is>
       </c>
       <c r="D677" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G677" t="inlineStr">
         <is>
@@ -16780,26 +16792,21 @@
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t>很安静，布局也合理。昨晚我整理线索时，思路顺了很多哞。</t>
+          <t>我会努力准备咩！</t>
         </is>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="n">
-        <v>50604</v>
+        <v>50504</v>
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>player</t>
-        </is>
-      </c>
-      <c r="C678" t="inlineStr">
-        <is>
-          <t>goat_平静</t>
+          <t>narration</t>
         </is>
       </c>
       <c r="D678" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G678" t="inlineStr">
         <is>
@@ -16808,51 +16815,205 @@
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>那真是太好啦咩，随时欢迎您再来~</t>
+          <t>完成{访客名}服务，获得住宿费【货币+320】</t>
         </is>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="n">
+        <v>50504</v>
+      </c>
+      <c r="D679" t="n">
+        <v>7</v>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="H679" t="inlineStr">
+        <is>
+          <t>Leave</t>
+        </is>
+      </c>
+    </row>
+    <row r="680"/>
+    <row r="681">
+      <c r="A681" t="n">
         <v>50604</v>
       </c>
-      <c r="B679" t="inlineStr">
-        <is>
-          <t>visitor</t>
-        </is>
-      </c>
-      <c r="C679" t="inlineStr">
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>visitor</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
         <is>
           <t>ox_平静</t>
         </is>
       </c>
-      <c r="D679" t="n">
+      <c r="D681" t="n">
+        <v>1</v>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="H681" t="inlineStr">
+        <is>
+          <t>您好，我来办理退房。</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="n">
+        <v>50604</v>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>goat_平静</t>
+        </is>
+      </c>
+      <c r="D682" t="n">
+        <v>2</v>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="H682" t="inlineStr">
+        <is>
+          <t>好的咩，牛小顿先生这次住得怎么样？</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="n">
+        <v>50604</v>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>visitor</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>ox_平静</t>
+        </is>
+      </c>
+      <c r="D683" t="n">
+        <v>3</v>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="H683" t="inlineStr">
+        <is>
+          <t>很安静，布局也合理。昨晚我整理线索时，思路顺了很多哞。</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="n">
+        <v>50604</v>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>goat_平静</t>
+        </is>
+      </c>
+      <c r="D684" t="n">
+        <v>4</v>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="H684" t="inlineStr">
+        <is>
+          <t>那真是太好啦咩，随时欢迎您再来~</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="n">
+        <v>50604</v>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>visitor</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>ox_平静</t>
+        </is>
+      </c>
+      <c r="D685" t="n">
         <v>5</v>
       </c>
-      <c r="G679" t="inlineStr">
-        <is>
-          <t>Line</t>
-        </is>
-      </c>
-      <c r="H679" t="inlineStr">
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="H685" t="inlineStr">
         <is>
           <t>嗯，我先继续去追查下一条线索了。</t>
         </is>
       </c>
     </row>
-    <row r="680">
-      <c r="A680" t="n">
+    <row r="686">
+      <c r="A686" t="n">
         <v>50604</v>
       </c>
-      <c r="D680" t="n">
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>narration</t>
+        </is>
+      </c>
+      <c r="D686" t="n">
         <v>6</v>
       </c>
-      <c r="G680" t="inlineStr">
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="H686" t="inlineStr">
+        <is>
+          <t>完成{访客名}服务，获得住宿费【货币+320】</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="n">
+        <v>50604</v>
+      </c>
+      <c r="D687" t="n">
+        <v>6</v>
+      </c>
+      <c r="G687" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="H680" t="inlineStr">
+      <c r="H687" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>

--- a/Excel/对话表.xlsx
+++ b/Excel/对话表.xlsx
@@ -2572,7 +2572,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="n">
         <v>10001</v>
@@ -2657,7 +2656,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" t="n">
         <v>10001</v>
@@ -2830,7 +2828,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" t="n">
         <v>10001</v>
@@ -2964,8 +2961,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18"/>
     <row r="19">
       <c r="A19" t="n">
         <v>10001</v>
@@ -3065,7 +3060,6 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
     <row r="23">
       <c r="A23" t="n">
         <v>20001</v>
@@ -3094,7 +3088,6 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="A25" t="n">
         <v>20001</v>
@@ -3213,7 +3206,6 @@
         </is>
       </c>
     </row>
-    <row r="29"/>
     <row r="30">
       <c r="A30" t="n">
         <v>20001</v>
@@ -3327,7 +3319,6 @@
         </is>
       </c>
     </row>
-    <row r="34"/>
     <row r="35">
       <c r="A35" t="n">
         <v>20001</v>
@@ -3417,9 +3408,6 @@
         </is>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
     <row r="41">
       <c r="A41" t="n">
         <v>30001</v>
@@ -3448,7 +3436,6 @@
         </is>
       </c>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" t="n">
         <v>30001</v>
@@ -3572,7 +3559,6 @@
         </is>
       </c>
     </row>
-    <row r="47"/>
     <row r="48">
       <c r="A48" t="n">
         <v>30001</v>
@@ -3662,7 +3648,6 @@
         </is>
       </c>
     </row>
-    <row r="51"/>
     <row r="52">
       <c r="A52" t="n">
         <v>30001</v>
@@ -3820,8 +3805,6 @@
         </is>
       </c>
     </row>
-    <row r="57"/>
-    <row r="58"/>
     <row r="59">
       <c r="A59" t="n">
         <v>30002</v>
@@ -3850,7 +3833,6 @@
         </is>
       </c>
     </row>
-    <row r="60"/>
     <row r="61">
       <c r="A61" t="n">
         <v>30002</v>
@@ -3950,7 +3932,6 @@
         </is>
       </c>
     </row>
-    <row r="64"/>
     <row r="65">
       <c r="A65" t="n">
         <v>30002</v>
@@ -4050,7 +4031,6 @@
         </is>
       </c>
     </row>
-    <row r="68"/>
     <row r="69">
       <c r="A69" t="n">
         <v>40001</v>
@@ -4079,7 +4059,6 @@
         </is>
       </c>
     </row>
-    <row r="70"/>
     <row r="71">
       <c r="A71" t="n">
         <v>40002</v>
@@ -4108,7 +4087,6 @@
         </is>
       </c>
     </row>
-    <row r="72"/>
     <row r="73">
       <c r="A73" t="n">
         <v>40003</v>
@@ -4137,7 +4115,6 @@
         </is>
       </c>
     </row>
-    <row r="74"/>
     <row r="75">
       <c r="A75" t="n">
         <v>40004</v>
@@ -4166,7 +4143,6 @@
         </is>
       </c>
     </row>
-    <row r="76"/>
     <row r="77">
       <c r="A77" t="n">
         <v>50001</v>
@@ -4195,7 +4171,6 @@
         </is>
       </c>
     </row>
-    <row r="78"/>
     <row r="79">
       <c r="A79" t="n">
         <v>50002</v>
@@ -4224,7 +4199,6 @@
         </is>
       </c>
     </row>
-    <row r="80"/>
     <row r="81">
       <c r="A81" t="n">
         <v>50003</v>
@@ -4253,10 +4227,6 @@
         </is>
       </c>
     </row>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
     <row r="86">
       <c r="A86" t="n">
         <v>10101</v>
@@ -4341,7 +4311,6 @@
         </is>
       </c>
     </row>
-    <row r="89"/>
     <row r="90">
       <c r="A90" t="n">
         <v>10101</v>
@@ -4514,7 +4483,6 @@
         </is>
       </c>
     </row>
-    <row r="95"/>
     <row r="96">
       <c r="A96" t="n">
         <v>10101</v>
@@ -4648,7 +4616,6 @@
         </is>
       </c>
     </row>
-    <row r="100"/>
     <row r="101">
       <c r="A101" t="n">
         <v>10101</v>
@@ -4748,7 +4715,6 @@
         </is>
       </c>
     </row>
-    <row r="104"/>
     <row r="105">
       <c r="A105" t="n">
         <v>20101</v>
@@ -4777,7 +4743,6 @@
         </is>
       </c>
     </row>
-    <row r="106"/>
     <row r="107">
       <c r="A107" t="n">
         <v>20101</v>
@@ -4896,7 +4861,6 @@
         </is>
       </c>
     </row>
-    <row r="111"/>
     <row r="112">
       <c r="A112" t="n">
         <v>20101</v>
@@ -5010,7 +4974,6 @@
         </is>
       </c>
     </row>
-    <row r="116"/>
     <row r="117">
       <c r="A117" t="n">
         <v>20101</v>
@@ -5100,8 +5063,6 @@
         </is>
       </c>
     </row>
-    <row r="120"/>
-    <row r="121"/>
     <row r="122">
       <c r="A122" t="n">
         <v>30101</v>
@@ -5130,7 +5091,6 @@
         </is>
       </c>
     </row>
-    <row r="123"/>
     <row r="124">
       <c r="A124" t="n">
         <v>30101</v>
@@ -5254,7 +5214,6 @@
         </is>
       </c>
     </row>
-    <row r="128"/>
     <row r="129">
       <c r="A129" t="n">
         <v>30101</v>
@@ -5344,7 +5303,6 @@
         </is>
       </c>
     </row>
-    <row r="132"/>
     <row r="133">
       <c r="A133" t="n">
         <v>30101</v>
@@ -5502,10 +5460,6 @@
         </is>
       </c>
     </row>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
     <row r="142">
       <c r="A142" t="n">
         <v>30102</v>
@@ -5534,7 +5488,6 @@
         </is>
       </c>
     </row>
-    <row r="143"/>
     <row r="144">
       <c r="A144" t="n">
         <v>30102</v>
@@ -5634,7 +5587,6 @@
         </is>
       </c>
     </row>
-    <row r="147"/>
     <row r="148">
       <c r="A148" t="n">
         <v>30102</v>
@@ -5734,7 +5686,6 @@
         </is>
       </c>
     </row>
-    <row r="151"/>
     <row r="152">
       <c r="A152" t="n">
         <v>40101</v>
@@ -5763,7 +5714,6 @@
         </is>
       </c>
     </row>
-    <row r="153"/>
     <row r="154">
       <c r="A154" t="n">
         <v>40102</v>
@@ -5792,7 +5742,6 @@
         </is>
       </c>
     </row>
-    <row r="155"/>
     <row r="156">
       <c r="A156" t="n">
         <v>40103</v>
@@ -5821,7 +5770,6 @@
         </is>
       </c>
     </row>
-    <row r="157"/>
     <row r="158">
       <c r="A158" t="n">
         <v>40104</v>
@@ -5850,7 +5798,6 @@
         </is>
       </c>
     </row>
-    <row r="159"/>
     <row r="160">
       <c r="A160" t="n">
         <v>50101</v>
@@ -5879,7 +5826,6 @@
         </is>
       </c>
     </row>
-    <row r="161"/>
     <row r="162">
       <c r="A162" t="n">
         <v>50102</v>
@@ -5908,7 +5854,6 @@
         </is>
       </c>
     </row>
-    <row r="163"/>
     <row r="164">
       <c r="A164" t="n">
         <v>50103</v>
@@ -5937,9 +5882,6 @@
         </is>
       </c>
     </row>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
     <row r="168">
       <c r="A168" t="n">
         <v>10201</v>
@@ -6052,7 +5994,6 @@
         </is>
       </c>
     </row>
-    <row r="172"/>
     <row r="173">
       <c r="A173" t="n">
         <v>10201</v>
@@ -6225,7 +6166,6 @@
         </is>
       </c>
     </row>
-    <row r="178"/>
     <row r="179">
       <c r="A179" t="n">
         <v>10201</v>
@@ -6359,7 +6299,6 @@
         </is>
       </c>
     </row>
-    <row r="183"/>
     <row r="184">
       <c r="A184" t="n">
         <v>10201</v>
@@ -6459,7 +6398,6 @@
         </is>
       </c>
     </row>
-    <row r="187"/>
     <row r="188">
       <c r="A188" t="n">
         <v>20201</v>
@@ -6488,7 +6426,6 @@
         </is>
       </c>
     </row>
-    <row r="189"/>
     <row r="190">
       <c r="A190" t="n">
         <v>20201</v>
@@ -6809,8 +6746,6 @@
         </is>
       </c>
     </row>
-    <row r="201"/>
-    <row r="202"/>
     <row r="203">
       <c r="A203" t="n">
         <v>30201</v>
@@ -6839,7 +6774,6 @@
         </is>
       </c>
     </row>
-    <row r="204"/>
     <row r="205">
       <c r="A205" t="n">
         <v>30201</v>
@@ -6963,7 +6897,6 @@
         </is>
       </c>
     </row>
-    <row r="209"/>
     <row r="210">
       <c r="A210" t="n">
         <v>30201</v>
@@ -7053,7 +6986,6 @@
         </is>
       </c>
     </row>
-    <row r="213"/>
     <row r="214">
       <c r="A214" t="n">
         <v>30201</v>
@@ -7211,8 +7143,6 @@
         </is>
       </c>
     </row>
-    <row r="219"/>
-    <row r="220"/>
     <row r="221">
       <c r="A221" t="n">
         <v>30202</v>
@@ -7241,7 +7171,6 @@
         </is>
       </c>
     </row>
-    <row r="222"/>
     <row r="223">
       <c r="A223" t="n">
         <v>30202</v>
@@ -7341,7 +7270,6 @@
         </is>
       </c>
     </row>
-    <row r="226"/>
     <row r="227">
       <c r="A227" t="n">
         <v>30202</v>
@@ -7441,8 +7369,6 @@
         </is>
       </c>
     </row>
-    <row r="230"/>
-    <row r="231"/>
     <row r="232">
       <c r="A232" t="n">
         <v>30203</v>
@@ -7471,7 +7397,6 @@
         </is>
       </c>
     </row>
-    <row r="233"/>
     <row r="234">
       <c r="A234" t="n">
         <v>30203</v>
@@ -7571,7 +7496,6 @@
         </is>
       </c>
     </row>
-    <row r="237"/>
     <row r="238">
       <c r="A238" t="n">
         <v>30203</v>
@@ -7671,8 +7595,6 @@
         </is>
       </c>
     </row>
-    <row r="241"/>
-    <row r="242"/>
     <row r="243">
       <c r="A243" t="n">
         <v>40201</v>
@@ -7701,7 +7623,6 @@
         </is>
       </c>
     </row>
-    <row r="244"/>
     <row r="245">
       <c r="A245" t="n">
         <v>40202</v>
@@ -7730,7 +7651,6 @@
         </is>
       </c>
     </row>
-    <row r="246"/>
     <row r="247">
       <c r="A247" t="n">
         <v>40203</v>
@@ -7759,7 +7679,6 @@
         </is>
       </c>
     </row>
-    <row r="248"/>
     <row r="249">
       <c r="A249" t="n">
         <v>40204</v>
@@ -7788,7 +7707,6 @@
         </is>
       </c>
     </row>
-    <row r="250"/>
     <row r="251">
       <c r="A251" t="n">
         <v>50201</v>
@@ -7817,7 +7735,6 @@
         </is>
       </c>
     </row>
-    <row r="252"/>
     <row r="253">
       <c r="A253" t="n">
         <v>50202</v>
@@ -7846,7 +7763,6 @@
         </is>
       </c>
     </row>
-    <row r="254"/>
     <row r="255">
       <c r="A255" t="n">
         <v>50203</v>
@@ -7875,9 +7791,6 @@
         </is>
       </c>
     </row>
-    <row r="256"/>
-    <row r="257"/>
-    <row r="258"/>
     <row r="259">
       <c r="A259" t="n">
         <v>10301</v>
@@ -7962,7 +7875,6 @@
         </is>
       </c>
     </row>
-    <row r="262"/>
     <row r="263">
       <c r="A263" t="n">
         <v>10301</v>
@@ -8237,7 +8149,6 @@
         </is>
       </c>
     </row>
-    <row r="271"/>
     <row r="272">
       <c r="A272" t="n">
         <v>10301</v>
@@ -8371,7 +8282,6 @@
         </is>
       </c>
     </row>
-    <row r="276"/>
     <row r="277">
       <c r="A277" t="n">
         <v>10301</v>
@@ -8471,7 +8381,6 @@
         </is>
       </c>
     </row>
-    <row r="280"/>
     <row r="281">
       <c r="A281" t="n">
         <v>20301</v>
@@ -8500,7 +8409,6 @@
         </is>
       </c>
     </row>
-    <row r="282"/>
     <row r="283">
       <c r="A283" t="n">
         <v>20301</v>
@@ -8821,8 +8729,6 @@
         </is>
       </c>
     </row>
-    <row r="294"/>
-    <row r="295"/>
     <row r="296">
       <c r="A296" t="n">
         <v>30301</v>
@@ -8851,8 +8757,6 @@
         </is>
       </c>
     </row>
-    <row r="297"/>
-    <row r="298"/>
     <row r="299">
       <c r="A299" t="n">
         <v>30301</v>
@@ -8976,7 +8880,6 @@
         </is>
       </c>
     </row>
-    <row r="303"/>
     <row r="304">
       <c r="A304" t="n">
         <v>30301</v>
@@ -9100,7 +9003,6 @@
         </is>
       </c>
     </row>
-    <row r="308"/>
     <row r="309">
       <c r="A309" t="n">
         <v>30301</v>
@@ -9258,8 +9160,6 @@
         </is>
       </c>
     </row>
-    <row r="314"/>
-    <row r="315"/>
     <row r="316">
       <c r="A316" t="n">
         <v>30302</v>
@@ -9288,7 +9188,6 @@
         </is>
       </c>
     </row>
-    <row r="317"/>
     <row r="318">
       <c r="A318" t="n">
         <v>30302</v>
@@ -9422,7 +9321,6 @@
         </is>
       </c>
     </row>
-    <row r="322"/>
     <row r="323">
       <c r="A323" t="n">
         <v>30302</v>
@@ -9522,8 +9420,6 @@
         </is>
       </c>
     </row>
-    <row r="326"/>
-    <row r="327"/>
     <row r="328">
       <c r="A328" t="n">
         <v>30303</v>
@@ -9552,7 +9448,6 @@
         </is>
       </c>
     </row>
-    <row r="329"/>
     <row r="330">
       <c r="A330" t="n">
         <v>30303</v>
@@ -9652,7 +9547,6 @@
         </is>
       </c>
     </row>
-    <row r="333"/>
     <row r="334">
       <c r="A334" t="n">
         <v>30303</v>
@@ -9752,9 +9646,6 @@
         </is>
       </c>
     </row>
-    <row r="337"/>
-    <row r="338"/>
-    <row r="339"/>
     <row r="340">
       <c r="A340" t="n">
         <v>40301</v>
@@ -9783,7 +9674,6 @@
         </is>
       </c>
     </row>
-    <row r="341"/>
     <row r="342">
       <c r="A342" t="n">
         <v>40302</v>
@@ -9812,7 +9702,6 @@
         </is>
       </c>
     </row>
-    <row r="343"/>
     <row r="344">
       <c r="A344" t="n">
         <v>40303</v>
@@ -9841,7 +9730,6 @@
         </is>
       </c>
     </row>
-    <row r="345"/>
     <row r="346">
       <c r="A346" t="n">
         <v>40304</v>
@@ -9870,7 +9758,6 @@
         </is>
       </c>
     </row>
-    <row r="347"/>
     <row r="348">
       <c r="A348" t="n">
         <v>50301</v>
@@ -9899,7 +9786,6 @@
         </is>
       </c>
     </row>
-    <row r="349"/>
     <row r="350">
       <c r="A350" t="n">
         <v>50302</v>
@@ -9928,7 +9814,6 @@
         </is>
       </c>
     </row>
-    <row r="351"/>
     <row r="352">
       <c r="A352" t="n">
         <v>50303</v>
@@ -9957,9 +9842,6 @@
         </is>
       </c>
     </row>
-    <row r="353"/>
-    <row r="354"/>
-    <row r="355"/>
     <row r="356">
       <c r="A356" t="n">
         <v>10401</v>
@@ -10072,7 +9954,6 @@
         </is>
       </c>
     </row>
-    <row r="360"/>
     <row r="361">
       <c r="A361" t="n">
         <v>10401</v>
@@ -10245,7 +10126,6 @@
         </is>
       </c>
     </row>
-    <row r="366"/>
     <row r="367">
       <c r="A367" t="n">
         <v>10401</v>
@@ -10379,7 +10259,6 @@
         </is>
       </c>
     </row>
-    <row r="371"/>
     <row r="372">
       <c r="A372" t="n">
         <v>10401</v>
@@ -10479,7 +10358,6 @@
         </is>
       </c>
     </row>
-    <row r="375"/>
     <row r="376">
       <c r="A376" t="n">
         <v>20401</v>
@@ -10508,7 +10386,6 @@
         </is>
       </c>
     </row>
-    <row r="377"/>
     <row r="378">
       <c r="A378" t="n">
         <v>20401</v>
@@ -10829,8 +10706,6 @@
         </is>
       </c>
     </row>
-    <row r="389"/>
-    <row r="390"/>
     <row r="391">
       <c r="A391" t="n">
         <v>30401</v>
@@ -10859,7 +10734,6 @@
         </is>
       </c>
     </row>
-    <row r="392"/>
     <row r="393">
       <c r="A393" t="n">
         <v>30401</v>
@@ -10983,7 +10857,6 @@
         </is>
       </c>
     </row>
-    <row r="397"/>
     <row r="398">
       <c r="A398" t="n">
         <v>30401</v>
@@ -11073,7 +10946,6 @@
         </is>
       </c>
     </row>
-    <row r="401"/>
     <row r="402">
       <c r="A402" t="n">
         <v>30401</v>
@@ -11231,8 +11103,6 @@
         </is>
       </c>
     </row>
-    <row r="407"/>
-    <row r="408"/>
     <row r="409">
       <c r="A409" t="n">
         <v>30402</v>
@@ -11261,7 +11131,6 @@
         </is>
       </c>
     </row>
-    <row r="410"/>
     <row r="411">
       <c r="A411" t="n">
         <v>30402</v>
@@ -11361,7 +11230,6 @@
         </is>
       </c>
     </row>
-    <row r="414"/>
     <row r="415">
       <c r="A415" t="n">
         <v>30402</v>
@@ -11461,7 +11329,6 @@
         </is>
       </c>
     </row>
-    <row r="418"/>
     <row r="419">
       <c r="A419" t="n">
         <v>30403</v>
@@ -11490,7 +11357,6 @@
         </is>
       </c>
     </row>
-    <row r="420"/>
     <row r="421">
       <c r="A421" t="n">
         <v>30403</v>
@@ -11590,7 +11456,6 @@
         </is>
       </c>
     </row>
-    <row r="424"/>
     <row r="425">
       <c r="A425" t="n">
         <v>30403</v>
@@ -11690,8 +11555,6 @@
         </is>
       </c>
     </row>
-    <row r="428"/>
-    <row r="429"/>
     <row r="430">
       <c r="A430" t="n">
         <v>40401</v>
@@ -11720,7 +11583,6 @@
         </is>
       </c>
     </row>
-    <row r="431"/>
     <row r="432">
       <c r="A432" t="n">
         <v>40402</v>
@@ -11749,7 +11611,6 @@
         </is>
       </c>
     </row>
-    <row r="433"/>
     <row r="434">
       <c r="A434" t="n">
         <v>40403</v>
@@ -11778,7 +11639,6 @@
         </is>
       </c>
     </row>
-    <row r="435"/>
     <row r="436">
       <c r="A436" t="n">
         <v>40404</v>
@@ -11807,7 +11667,6 @@
         </is>
       </c>
     </row>
-    <row r="437"/>
     <row r="438">
       <c r="A438" t="n">
         <v>50401</v>
@@ -11836,7 +11695,6 @@
         </is>
       </c>
     </row>
-    <row r="439"/>
     <row r="440">
       <c r="A440" t="n">
         <v>50402</v>
@@ -11865,7 +11723,6 @@
         </is>
       </c>
     </row>
-    <row r="441"/>
     <row r="442">
       <c r="A442" t="n">
         <v>50403</v>
@@ -11894,9 +11751,6 @@
         </is>
       </c>
     </row>
-    <row r="443"/>
-    <row r="444"/>
-    <row r="445"/>
     <row r="446">
       <c r="A446" t="n">
         <v>10501</v>
@@ -12009,8 +11863,6 @@
         </is>
       </c>
     </row>
-    <row r="450"/>
-    <row r="451"/>
     <row r="452">
       <c r="A452" t="n">
         <v>10501</v>
@@ -12183,7 +12035,6 @@
         </is>
       </c>
     </row>
-    <row r="457"/>
     <row r="458">
       <c r="A458" t="n">
         <v>10501</v>
@@ -12317,7 +12168,6 @@
         </is>
       </c>
     </row>
-    <row r="462"/>
     <row r="463">
       <c r="A463" t="n">
         <v>10501</v>
@@ -12417,7 +12267,6 @@
         </is>
       </c>
     </row>
-    <row r="466"/>
     <row r="467">
       <c r="A467" t="n">
         <v>20501</v>
@@ -12446,7 +12295,6 @@
         </is>
       </c>
     </row>
-    <row r="468"/>
     <row r="469">
       <c r="A469" t="n">
         <v>20501</v>
@@ -12565,7 +12413,6 @@
         </is>
       </c>
     </row>
-    <row r="473"/>
     <row r="474">
       <c r="A474" t="n">
         <v>20501</v>
@@ -12679,7 +12526,6 @@
         </is>
       </c>
     </row>
-    <row r="478"/>
     <row r="479">
       <c r="A479" t="n">
         <v>20501</v>
@@ -12769,8 +12615,6 @@
         </is>
       </c>
     </row>
-    <row r="482"/>
-    <row r="483"/>
     <row r="484">
       <c r="A484" t="n">
         <v>30501</v>
@@ -12799,7 +12643,6 @@
         </is>
       </c>
     </row>
-    <row r="485"/>
     <row r="486">
       <c r="A486" t="n">
         <v>30501</v>
@@ -12923,7 +12766,6 @@
         </is>
       </c>
     </row>
-    <row r="490"/>
     <row r="491">
       <c r="A491" t="n">
         <v>30501</v>
@@ -13013,7 +12855,6 @@
         </is>
       </c>
     </row>
-    <row r="494"/>
     <row r="495">
       <c r="A495" t="n">
         <v>30501</v>
@@ -13171,8 +13012,6 @@
         </is>
       </c>
     </row>
-    <row r="500"/>
-    <row r="501"/>
     <row r="502">
       <c r="A502" t="n">
         <v>30502</v>
@@ -13201,7 +13040,6 @@
         </is>
       </c>
     </row>
-    <row r="503"/>
     <row r="504">
       <c r="A504" t="n">
         <v>30502</v>
@@ -13301,7 +13139,6 @@
         </is>
       </c>
     </row>
-    <row r="507"/>
     <row r="508">
       <c r="A508" t="n">
         <v>30502</v>
@@ -13401,9 +13238,6 @@
         </is>
       </c>
     </row>
-    <row r="511"/>
-    <row r="512"/>
-    <row r="513"/>
     <row r="514">
       <c r="A514" t="n">
         <v>30503</v>
@@ -13427,7 +13261,6 @@
         </is>
       </c>
     </row>
-    <row r="515"/>
     <row r="516">
       <c r="A516" t="n">
         <v>30503</v>
@@ -13527,7 +13360,6 @@
         </is>
       </c>
     </row>
-    <row r="519"/>
     <row r="520">
       <c r="A520" t="n">
         <v>30503</v>
@@ -13627,7 +13459,6 @@
         </is>
       </c>
     </row>
-    <row r="523"/>
     <row r="524">
       <c r="A524" t="n">
         <v>40501</v>
@@ -13656,7 +13487,6 @@
         </is>
       </c>
     </row>
-    <row r="525"/>
     <row r="526">
       <c r="A526" t="n">
         <v>40502</v>
@@ -13685,7 +13515,6 @@
         </is>
       </c>
     </row>
-    <row r="527"/>
     <row r="528">
       <c r="A528" t="n">
         <v>40503</v>
@@ -13714,7 +13543,6 @@
         </is>
       </c>
     </row>
-    <row r="529"/>
     <row r="530">
       <c r="A530" t="n">
         <v>40504</v>
@@ -13743,7 +13571,6 @@
         </is>
       </c>
     </row>
-    <row r="531"/>
     <row r="532">
       <c r="A532" t="n">
         <v>50501</v>
@@ -13772,7 +13599,6 @@
         </is>
       </c>
     </row>
-    <row r="533"/>
     <row r="534">
       <c r="A534" t="n">
         <v>50502</v>
@@ -13801,7 +13627,6 @@
         </is>
       </c>
     </row>
-    <row r="535"/>
     <row r="536">
       <c r="A536" t="n">
         <v>50503</v>
@@ -13830,9 +13655,6 @@
         </is>
       </c>
     </row>
-    <row r="537"/>
-    <row r="538"/>
-    <row r="539"/>
     <row r="540">
       <c r="A540" t="n">
         <v>10601</v>
@@ -13889,8 +13711,6 @@
         </is>
       </c>
     </row>
-    <row r="542"/>
-    <row r="543"/>
     <row r="544">
       <c r="A544" t="n">
         <v>10601</v>
@@ -14063,7 +13883,6 @@
         </is>
       </c>
     </row>
-    <row r="549"/>
     <row r="550">
       <c r="A550" t="n">
         <v>10601</v>
@@ -14197,7 +14016,6 @@
         </is>
       </c>
     </row>
-    <row r="554"/>
     <row r="555">
       <c r="A555" t="n">
         <v>10601</v>
@@ -14297,7 +14115,6 @@
         </is>
       </c>
     </row>
-    <row r="558"/>
     <row r="559">
       <c r="A559" t="n">
         <v>20601</v>
@@ -14326,7 +14143,6 @@
         </is>
       </c>
     </row>
-    <row r="560"/>
     <row r="561">
       <c r="A561" t="n">
         <v>20601</v>
@@ -14647,8 +14463,6 @@
         </is>
       </c>
     </row>
-    <row r="572"/>
-    <row r="573"/>
     <row r="574">
       <c r="A574" t="n">
         <v>30601</v>
@@ -14677,7 +14491,6 @@
         </is>
       </c>
     </row>
-    <row r="575"/>
     <row r="576">
       <c r="A576" t="n">
         <v>30601</v>
@@ -14801,7 +14614,6 @@
         </is>
       </c>
     </row>
-    <row r="580"/>
     <row r="581">
       <c r="A581" t="n">
         <v>30601</v>
@@ -14891,7 +14703,6 @@
         </is>
       </c>
     </row>
-    <row r="584"/>
     <row r="585">
       <c r="A585" t="n">
         <v>30601</v>
@@ -15049,8 +14860,6 @@
         </is>
       </c>
     </row>
-    <row r="590"/>
-    <row r="591"/>
     <row r="592">
       <c r="A592" t="n">
         <v>30602</v>
@@ -15079,7 +14888,6 @@
         </is>
       </c>
     </row>
-    <row r="593"/>
     <row r="594">
       <c r="A594" t="n">
         <v>30602</v>
@@ -15179,7 +14987,6 @@
         </is>
       </c>
     </row>
-    <row r="597"/>
     <row r="598">
       <c r="A598" t="n">
         <v>30602</v>
@@ -15279,9 +15086,6 @@
         </is>
       </c>
     </row>
-    <row r="601"/>
-    <row r="602"/>
-    <row r="603"/>
     <row r="604">
       <c r="A604" t="n">
         <v>30603</v>
@@ -15310,7 +15114,6 @@
         </is>
       </c>
     </row>
-    <row r="605"/>
     <row r="606">
       <c r="A606" t="n">
         <v>30603</v>
@@ -15410,7 +15213,6 @@
         </is>
       </c>
     </row>
-    <row r="609"/>
     <row r="610">
       <c r="A610" t="n">
         <v>30603</v>
@@ -15510,8 +15312,6 @@
         </is>
       </c>
     </row>
-    <row r="613"/>
-    <row r="614"/>
     <row r="615">
       <c r="A615" t="n">
         <v>40601</v>
@@ -15540,7 +15340,6 @@
         </is>
       </c>
     </row>
-    <row r="616"/>
     <row r="617">
       <c r="A617" t="n">
         <v>40602</v>
@@ -15569,7 +15368,6 @@
         </is>
       </c>
     </row>
-    <row r="618"/>
     <row r="619">
       <c r="A619" t="n">
         <v>40603</v>
@@ -15598,7 +15396,6 @@
         </is>
       </c>
     </row>
-    <row r="620"/>
     <row r="621">
       <c r="A621" t="n">
         <v>40604</v>
@@ -15627,7 +15424,6 @@
         </is>
       </c>
     </row>
-    <row r="622"/>
     <row r="623">
       <c r="A623" t="n">
         <v>50601</v>
@@ -15656,7 +15452,6 @@
         </is>
       </c>
     </row>
-    <row r="624"/>
     <row r="625">
       <c r="A625" t="n">
         <v>50602</v>
@@ -15685,7 +15480,6 @@
         </is>
       </c>
     </row>
-    <row r="626"/>
     <row r="627">
       <c r="A627" t="n">
         <v>50603</v>
@@ -15714,9 +15508,6 @@
         </is>
       </c>
     </row>
-    <row r="628"/>
-    <row r="629"/>
-    <row r="630"/>
     <row r="631">
       <c r="A631" t="n">
         <v>50004</v>
@@ -15857,7 +15648,7 @@
         <v>50004</v>
       </c>
       <c r="D636" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G636" t="inlineStr">
         <is>
@@ -15870,7 +15661,6 @@
         </is>
       </c>
     </row>
-    <row r="637"/>
     <row r="638">
       <c r="A638" t="n">
         <v>50104</v>
@@ -16039,7 +15829,7 @@
         <v>50104</v>
       </c>
       <c r="D644" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G644" t="inlineStr">
         <is>
@@ -16052,8 +15842,6 @@
         </is>
       </c>
     </row>
-    <row r="645"/>
-    <row r="646"/>
     <row r="647">
       <c r="A647" t="n">
         <v>50204</v>
@@ -16222,7 +16010,7 @@
         <v>50204</v>
       </c>
       <c r="D653" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G653" t="inlineStr">
         <is>
@@ -16235,7 +16023,6 @@
         </is>
       </c>
     </row>
-    <row r="654"/>
     <row r="655">
       <c r="A655" t="n">
         <v>50304</v>
@@ -16432,7 +16219,7 @@
         <v>50304</v>
       </c>
       <c r="D662" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G662" t="inlineStr">
         <is>
@@ -16445,7 +16232,6 @@
         </is>
       </c>
     </row>
-    <row r="663"/>
     <row r="664">
       <c r="A664" t="n">
         <v>50404</v>
@@ -16614,7 +16400,7 @@
         <v>50404</v>
       </c>
       <c r="D670" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G670" t="inlineStr">
         <is>
@@ -16627,7 +16413,6 @@
         </is>
       </c>
     </row>
-    <row r="671"/>
     <row r="672">
       <c r="A672" t="n">
         <v>50504</v>
@@ -16824,7 +16609,7 @@
         <v>50504</v>
       </c>
       <c r="D679" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G679" t="inlineStr">
         <is>
@@ -16837,7 +16622,6 @@
         </is>
       </c>
     </row>
-    <row r="680"/>
     <row r="681">
       <c r="A681" t="n">
         <v>50604</v>
@@ -17006,7 +16790,7 @@
         <v>50604</v>
       </c>
       <c r="D687" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G687" t="inlineStr">
         <is>

--- a/Excel/对话表.xlsx
+++ b/Excel/对话表.xlsx
@@ -626,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F98"/>
+  <dimension ref="A1:F103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="11" customWidth="1" style="7" min="1" max="1"/>
@@ -2490,7 +2490,160 @@
       </c>
     </row>
     <row r="98" customFormat="1" s="4">
-      <c r="A98" s="8" t="n"/>
+      <c r="A98" t="n">
+        <v>30003</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>cat</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Need_制作咖啡</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>needTalk</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>猫-制作咖啡(小游戏)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>30304</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>yak</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Need_制作咖啡</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>needTalk</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>牛莱-制作咖啡(小游戏)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>30504</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>wolf</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Need_修理电路_03</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>needTalk</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>狼-修理电路03(小游戏)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>30404</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>rabbit</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Need_兔-化妆台</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>needTalk</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>兔-化妆台(条件)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>30604</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>ox</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Need_顿-收音机</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>needTalk</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>牛顿-收音机(条件)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>30305</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>yak</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Need_莱-节拍器</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>needTalk</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>牛莱-节拍器(条件)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2504,7 +2657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J687"/>
+  <dimension ref="A1:J753"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="9.5" bestFit="1" customWidth="1" style="15" min="1" max="1"/>
@@ -2572,6 +2725,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="n">
         <v>10001</v>
@@ -2656,6 +2810,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="n">
         <v>10001</v>
@@ -2828,6 +2983,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="n">
         <v>10001</v>
@@ -2961,6 +3117,8 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="n">
         <v>10001</v>
@@ -3060,6 +3218,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="n">
         <v>20001</v>
@@ -3088,6 +3247,7 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="n">
         <v>20001</v>
@@ -3206,6 +3366,7 @@
         </is>
       </c>
     </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" t="n">
         <v>20001</v>
@@ -3319,6 +3480,7 @@
         </is>
       </c>
     </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" t="n">
         <v>20001</v>
@@ -3408,6 +3570,9 @@
         </is>
       </c>
     </row>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
     <row r="41">
       <c r="A41" t="n">
         <v>30001</v>
@@ -3436,6 +3601,7 @@
         </is>
       </c>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" t="n">
         <v>30001</v>
@@ -3559,6 +3725,7 @@
         </is>
       </c>
     </row>
+    <row r="47"/>
     <row r="48">
       <c r="A48" t="n">
         <v>30001</v>
@@ -3648,6 +3815,7 @@
         </is>
       </c>
     </row>
+    <row r="51"/>
     <row r="52">
       <c r="A52" t="n">
         <v>30001</v>
@@ -3805,6 +3973,8 @@
         </is>
       </c>
     </row>
+    <row r="57"/>
+    <row r="58"/>
     <row r="59">
       <c r="A59" t="n">
         <v>30002</v>
@@ -3833,6 +4003,7 @@
         </is>
       </c>
     </row>
+    <row r="60"/>
     <row r="61">
       <c r="A61" t="n">
         <v>30002</v>
@@ -3932,6 +4103,7 @@
         </is>
       </c>
     </row>
+    <row r="64"/>
     <row r="65">
       <c r="A65" t="n">
         <v>30002</v>
@@ -4031,6 +4203,7 @@
         </is>
       </c>
     </row>
+    <row r="68"/>
     <row r="69">
       <c r="A69" t="n">
         <v>40001</v>
@@ -4059,6 +4232,7 @@
         </is>
       </c>
     </row>
+    <row r="70"/>
     <row r="71">
       <c r="A71" t="n">
         <v>40002</v>
@@ -4087,6 +4261,7 @@
         </is>
       </c>
     </row>
+    <row r="72"/>
     <row r="73">
       <c r="A73" t="n">
         <v>40003</v>
@@ -4115,6 +4290,7 @@
         </is>
       </c>
     </row>
+    <row r="74"/>
     <row r="75">
       <c r="A75" t="n">
         <v>40004</v>
@@ -4143,6 +4319,7 @@
         </is>
       </c>
     </row>
+    <row r="76"/>
     <row r="77">
       <c r="A77" t="n">
         <v>50001</v>
@@ -4171,6 +4348,7 @@
         </is>
       </c>
     </row>
+    <row r="78"/>
     <row r="79">
       <c r="A79" t="n">
         <v>50002</v>
@@ -4199,6 +4377,7 @@
         </is>
       </c>
     </row>
+    <row r="80"/>
     <row r="81">
       <c r="A81" t="n">
         <v>50003</v>
@@ -4227,6 +4406,10 @@
         </is>
       </c>
     </row>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
     <row r="86">
       <c r="A86" t="n">
         <v>10101</v>
@@ -4311,6 +4494,7 @@
         </is>
       </c>
     </row>
+    <row r="89"/>
     <row r="90">
       <c r="A90" t="n">
         <v>10101</v>
@@ -4483,6 +4667,7 @@
         </is>
       </c>
     </row>
+    <row r="95"/>
     <row r="96">
       <c r="A96" t="n">
         <v>10101</v>
@@ -4616,6 +4801,7 @@
         </is>
       </c>
     </row>
+    <row r="100"/>
     <row r="101">
       <c r="A101" t="n">
         <v>10101</v>
@@ -4715,6 +4901,7 @@
         </is>
       </c>
     </row>
+    <row r="104"/>
     <row r="105">
       <c r="A105" t="n">
         <v>20101</v>
@@ -4743,6 +4930,7 @@
         </is>
       </c>
     </row>
+    <row r="106"/>
     <row r="107">
       <c r="A107" t="n">
         <v>20101</v>
@@ -4861,6 +5049,7 @@
         </is>
       </c>
     </row>
+    <row r="111"/>
     <row r="112">
       <c r="A112" t="n">
         <v>20101</v>
@@ -4974,6 +5163,7 @@
         </is>
       </c>
     </row>
+    <row r="116"/>
     <row r="117">
       <c r="A117" t="n">
         <v>20101</v>
@@ -5063,6 +5253,8 @@
         </is>
       </c>
     </row>
+    <row r="120"/>
+    <row r="121"/>
     <row r="122">
       <c r="A122" t="n">
         <v>30101</v>
@@ -5091,6 +5283,7 @@
         </is>
       </c>
     </row>
+    <row r="123"/>
     <row r="124">
       <c r="A124" t="n">
         <v>30101</v>
@@ -5214,6 +5407,7 @@
         </is>
       </c>
     </row>
+    <row r="128"/>
     <row r="129">
       <c r="A129" t="n">
         <v>30101</v>
@@ -5303,6 +5497,7 @@
         </is>
       </c>
     </row>
+    <row r="132"/>
     <row r="133">
       <c r="A133" t="n">
         <v>30101</v>
@@ -5460,6 +5655,10 @@
         </is>
       </c>
     </row>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
     <row r="142">
       <c r="A142" t="n">
         <v>30102</v>
@@ -5488,6 +5687,7 @@
         </is>
       </c>
     </row>
+    <row r="143"/>
     <row r="144">
       <c r="A144" t="n">
         <v>30102</v>
@@ -5587,6 +5787,7 @@
         </is>
       </c>
     </row>
+    <row r="147"/>
     <row r="148">
       <c r="A148" t="n">
         <v>30102</v>
@@ -5686,6 +5887,7 @@
         </is>
       </c>
     </row>
+    <row r="151"/>
     <row r="152">
       <c r="A152" t="n">
         <v>40101</v>
@@ -5714,6 +5916,7 @@
         </is>
       </c>
     </row>
+    <row r="153"/>
     <row r="154">
       <c r="A154" t="n">
         <v>40102</v>
@@ -5742,6 +5945,7 @@
         </is>
       </c>
     </row>
+    <row r="155"/>
     <row r="156">
       <c r="A156" t="n">
         <v>40103</v>
@@ -5770,6 +5974,7 @@
         </is>
       </c>
     </row>
+    <row r="157"/>
     <row r="158">
       <c r="A158" t="n">
         <v>40104</v>
@@ -5798,6 +6003,7 @@
         </is>
       </c>
     </row>
+    <row r="159"/>
     <row r="160">
       <c r="A160" t="n">
         <v>50101</v>
@@ -5826,6 +6032,7 @@
         </is>
       </c>
     </row>
+    <row r="161"/>
     <row r="162">
       <c r="A162" t="n">
         <v>50102</v>
@@ -5854,6 +6061,7 @@
         </is>
       </c>
     </row>
+    <row r="163"/>
     <row r="164">
       <c r="A164" t="n">
         <v>50103</v>
@@ -5882,6 +6090,9 @@
         </is>
       </c>
     </row>
+    <row r="165"/>
+    <row r="166"/>
+    <row r="167"/>
     <row r="168">
       <c r="A168" t="n">
         <v>10201</v>
@@ -5994,6 +6205,7 @@
         </is>
       </c>
     </row>
+    <row r="172"/>
     <row r="173">
       <c r="A173" t="n">
         <v>10201</v>
@@ -6166,6 +6378,7 @@
         </is>
       </c>
     </row>
+    <row r="178"/>
     <row r="179">
       <c r="A179" t="n">
         <v>10201</v>
@@ -6299,6 +6512,7 @@
         </is>
       </c>
     </row>
+    <row r="183"/>
     <row r="184">
       <c r="A184" t="n">
         <v>10201</v>
@@ -6398,6 +6612,7 @@
         </is>
       </c>
     </row>
+    <row r="187"/>
     <row r="188">
       <c r="A188" t="n">
         <v>20201</v>
@@ -6426,6 +6641,7 @@
         </is>
       </c>
     </row>
+    <row r="189"/>
     <row r="190">
       <c r="A190" t="n">
         <v>20201</v>
@@ -6746,6 +6962,8 @@
         </is>
       </c>
     </row>
+    <row r="201"/>
+    <row r="202"/>
     <row r="203">
       <c r="A203" t="n">
         <v>30201</v>
@@ -6774,6 +6992,7 @@
         </is>
       </c>
     </row>
+    <row r="204"/>
     <row r="205">
       <c r="A205" t="n">
         <v>30201</v>
@@ -6897,6 +7116,7 @@
         </is>
       </c>
     </row>
+    <row r="209"/>
     <row r="210">
       <c r="A210" t="n">
         <v>30201</v>
@@ -6986,6 +7206,7 @@
         </is>
       </c>
     </row>
+    <row r="213"/>
     <row r="214">
       <c r="A214" t="n">
         <v>30201</v>
@@ -7143,6 +7364,8 @@
         </is>
       </c>
     </row>
+    <row r="219"/>
+    <row r="220"/>
     <row r="221">
       <c r="A221" t="n">
         <v>30202</v>
@@ -7171,6 +7394,7 @@
         </is>
       </c>
     </row>
+    <row r="222"/>
     <row r="223">
       <c r="A223" t="n">
         <v>30202</v>
@@ -7270,6 +7494,7 @@
         </is>
       </c>
     </row>
+    <row r="226"/>
     <row r="227">
       <c r="A227" t="n">
         <v>30202</v>
@@ -7369,6 +7594,8 @@
         </is>
       </c>
     </row>
+    <row r="230"/>
+    <row r="231"/>
     <row r="232">
       <c r="A232" t="n">
         <v>30203</v>
@@ -7397,6 +7624,7 @@
         </is>
       </c>
     </row>
+    <row r="233"/>
     <row r="234">
       <c r="A234" t="n">
         <v>30203</v>
@@ -7496,6 +7724,7 @@
         </is>
       </c>
     </row>
+    <row r="237"/>
     <row r="238">
       <c r="A238" t="n">
         <v>30203</v>
@@ -7595,6 +7824,8 @@
         </is>
       </c>
     </row>
+    <row r="241"/>
+    <row r="242"/>
     <row r="243">
       <c r="A243" t="n">
         <v>40201</v>
@@ -7623,6 +7854,7 @@
         </is>
       </c>
     </row>
+    <row r="244"/>
     <row r="245">
       <c r="A245" t="n">
         <v>40202</v>
@@ -7651,6 +7883,7 @@
         </is>
       </c>
     </row>
+    <row r="246"/>
     <row r="247">
       <c r="A247" t="n">
         <v>40203</v>
@@ -7679,6 +7912,7 @@
         </is>
       </c>
     </row>
+    <row r="248"/>
     <row r="249">
       <c r="A249" t="n">
         <v>40204</v>
@@ -7707,6 +7941,7 @@
         </is>
       </c>
     </row>
+    <row r="250"/>
     <row r="251">
       <c r="A251" t="n">
         <v>50201</v>
@@ -7735,6 +7970,7 @@
         </is>
       </c>
     </row>
+    <row r="252"/>
     <row r="253">
       <c r="A253" t="n">
         <v>50202</v>
@@ -7763,6 +7999,7 @@
         </is>
       </c>
     </row>
+    <row r="254"/>
     <row r="255">
       <c r="A255" t="n">
         <v>50203</v>
@@ -7791,6 +8028,9 @@
         </is>
       </c>
     </row>
+    <row r="256"/>
+    <row r="257"/>
+    <row r="258"/>
     <row r="259">
       <c r="A259" t="n">
         <v>10301</v>
@@ -7875,6 +8115,7 @@
         </is>
       </c>
     </row>
+    <row r="262"/>
     <row r="263">
       <c r="A263" t="n">
         <v>10301</v>
@@ -8149,6 +8390,7 @@
         </is>
       </c>
     </row>
+    <row r="271"/>
     <row r="272">
       <c r="A272" t="n">
         <v>10301</v>
@@ -8282,6 +8524,7 @@
         </is>
       </c>
     </row>
+    <row r="276"/>
     <row r="277">
       <c r="A277" t="n">
         <v>10301</v>
@@ -8381,6 +8624,7 @@
         </is>
       </c>
     </row>
+    <row r="280"/>
     <row r="281">
       <c r="A281" t="n">
         <v>20301</v>
@@ -8409,6 +8653,7 @@
         </is>
       </c>
     </row>
+    <row r="282"/>
     <row r="283">
       <c r="A283" t="n">
         <v>20301</v>
@@ -8729,6 +8974,8 @@
         </is>
       </c>
     </row>
+    <row r="294"/>
+    <row r="295"/>
     <row r="296">
       <c r="A296" t="n">
         <v>30301</v>
@@ -8757,6 +9004,8 @@
         </is>
       </c>
     </row>
+    <row r="297"/>
+    <row r="298"/>
     <row r="299">
       <c r="A299" t="n">
         <v>30301</v>
@@ -8880,6 +9129,7 @@
         </is>
       </c>
     </row>
+    <row r="303"/>
     <row r="304">
       <c r="A304" t="n">
         <v>30301</v>
@@ -9003,6 +9253,7 @@
         </is>
       </c>
     </row>
+    <row r="308"/>
     <row r="309">
       <c r="A309" t="n">
         <v>30301</v>
@@ -9160,6 +9411,8 @@
         </is>
       </c>
     </row>
+    <row r="314"/>
+    <row r="315"/>
     <row r="316">
       <c r="A316" t="n">
         <v>30302</v>
@@ -9188,6 +9441,7 @@
         </is>
       </c>
     </row>
+    <row r="317"/>
     <row r="318">
       <c r="A318" t="n">
         <v>30302</v>
@@ -9321,6 +9575,7 @@
         </is>
       </c>
     </row>
+    <row r="322"/>
     <row r="323">
       <c r="A323" t="n">
         <v>30302</v>
@@ -9420,6 +9675,8 @@
         </is>
       </c>
     </row>
+    <row r="326"/>
+    <row r="327"/>
     <row r="328">
       <c r="A328" t="n">
         <v>30303</v>
@@ -9448,6 +9705,7 @@
         </is>
       </c>
     </row>
+    <row r="329"/>
     <row r="330">
       <c r="A330" t="n">
         <v>30303</v>
@@ -9547,6 +9805,7 @@
         </is>
       </c>
     </row>
+    <row r="333"/>
     <row r="334">
       <c r="A334" t="n">
         <v>30303</v>
@@ -9646,6 +9905,9 @@
         </is>
       </c>
     </row>
+    <row r="337"/>
+    <row r="338"/>
+    <row r="339"/>
     <row r="340">
       <c r="A340" t="n">
         <v>40301</v>
@@ -9674,6 +9936,7 @@
         </is>
       </c>
     </row>
+    <row r="341"/>
     <row r="342">
       <c r="A342" t="n">
         <v>40302</v>
@@ -9702,6 +9965,7 @@
         </is>
       </c>
     </row>
+    <row r="343"/>
     <row r="344">
       <c r="A344" t="n">
         <v>40303</v>
@@ -9730,6 +9994,7 @@
         </is>
       </c>
     </row>
+    <row r="345"/>
     <row r="346">
       <c r="A346" t="n">
         <v>40304</v>
@@ -9758,6 +10023,7 @@
         </is>
       </c>
     </row>
+    <row r="347"/>
     <row r="348">
       <c r="A348" t="n">
         <v>50301</v>
@@ -9786,6 +10052,7 @@
         </is>
       </c>
     </row>
+    <row r="349"/>
     <row r="350">
       <c r="A350" t="n">
         <v>50302</v>
@@ -9814,6 +10081,7 @@
         </is>
       </c>
     </row>
+    <row r="351"/>
     <row r="352">
       <c r="A352" t="n">
         <v>50303</v>
@@ -9842,6 +10110,9 @@
         </is>
       </c>
     </row>
+    <row r="353"/>
+    <row r="354"/>
+    <row r="355"/>
     <row r="356">
       <c r="A356" t="n">
         <v>10401</v>
@@ -9954,6 +10225,7 @@
         </is>
       </c>
     </row>
+    <row r="360"/>
     <row r="361">
       <c r="A361" t="n">
         <v>10401</v>
@@ -10126,6 +10398,7 @@
         </is>
       </c>
     </row>
+    <row r="366"/>
     <row r="367">
       <c r="A367" t="n">
         <v>10401</v>
@@ -10259,6 +10532,7 @@
         </is>
       </c>
     </row>
+    <row r="371"/>
     <row r="372">
       <c r="A372" t="n">
         <v>10401</v>
@@ -10358,6 +10632,7 @@
         </is>
       </c>
     </row>
+    <row r="375"/>
     <row r="376">
       <c r="A376" t="n">
         <v>20401</v>
@@ -10386,6 +10661,7 @@
         </is>
       </c>
     </row>
+    <row r="377"/>
     <row r="378">
       <c r="A378" t="n">
         <v>20401</v>
@@ -10706,6 +10982,8 @@
         </is>
       </c>
     </row>
+    <row r="389"/>
+    <row r="390"/>
     <row r="391">
       <c r="A391" t="n">
         <v>30401</v>
@@ -10734,6 +11012,7 @@
         </is>
       </c>
     </row>
+    <row r="392"/>
     <row r="393">
       <c r="A393" t="n">
         <v>30401</v>
@@ -10857,6 +11136,7 @@
         </is>
       </c>
     </row>
+    <row r="397"/>
     <row r="398">
       <c r="A398" t="n">
         <v>30401</v>
@@ -10946,6 +11226,7 @@
         </is>
       </c>
     </row>
+    <row r="401"/>
     <row r="402">
       <c r="A402" t="n">
         <v>30401</v>
@@ -11103,6 +11384,8 @@
         </is>
       </c>
     </row>
+    <row r="407"/>
+    <row r="408"/>
     <row r="409">
       <c r="A409" t="n">
         <v>30402</v>
@@ -11131,6 +11414,7 @@
         </is>
       </c>
     </row>
+    <row r="410"/>
     <row r="411">
       <c r="A411" t="n">
         <v>30402</v>
@@ -11230,6 +11514,7 @@
         </is>
       </c>
     </row>
+    <row r="414"/>
     <row r="415">
       <c r="A415" t="n">
         <v>30402</v>
@@ -11329,6 +11614,7 @@
         </is>
       </c>
     </row>
+    <row r="418"/>
     <row r="419">
       <c r="A419" t="n">
         <v>30403</v>
@@ -11357,6 +11643,7 @@
         </is>
       </c>
     </row>
+    <row r="420"/>
     <row r="421">
       <c r="A421" t="n">
         <v>30403</v>
@@ -11456,6 +11743,7 @@
         </is>
       </c>
     </row>
+    <row r="424"/>
     <row r="425">
       <c r="A425" t="n">
         <v>30403</v>
@@ -11555,6 +11843,8 @@
         </is>
       </c>
     </row>
+    <row r="428"/>
+    <row r="429"/>
     <row r="430">
       <c r="A430" t="n">
         <v>40401</v>
@@ -11583,6 +11873,7 @@
         </is>
       </c>
     </row>
+    <row r="431"/>
     <row r="432">
       <c r="A432" t="n">
         <v>40402</v>
@@ -11611,6 +11902,7 @@
         </is>
       </c>
     </row>
+    <row r="433"/>
     <row r="434">
       <c r="A434" t="n">
         <v>40403</v>
@@ -11639,6 +11931,7 @@
         </is>
       </c>
     </row>
+    <row r="435"/>
     <row r="436">
       <c r="A436" t="n">
         <v>40404</v>
@@ -11667,6 +11960,7 @@
         </is>
       </c>
     </row>
+    <row r="437"/>
     <row r="438">
       <c r="A438" t="n">
         <v>50401</v>
@@ -11695,6 +11989,7 @@
         </is>
       </c>
     </row>
+    <row r="439"/>
     <row r="440">
       <c r="A440" t="n">
         <v>50402</v>
@@ -11723,6 +12018,7 @@
         </is>
       </c>
     </row>
+    <row r="441"/>
     <row r="442">
       <c r="A442" t="n">
         <v>50403</v>
@@ -11751,6 +12047,9 @@
         </is>
       </c>
     </row>
+    <row r="443"/>
+    <row r="444"/>
+    <row r="445"/>
     <row r="446">
       <c r="A446" t="n">
         <v>10501</v>
@@ -11863,6 +12162,8 @@
         </is>
       </c>
     </row>
+    <row r="450"/>
+    <row r="451"/>
     <row r="452">
       <c r="A452" t="n">
         <v>10501</v>
@@ -12035,6 +12336,7 @@
         </is>
       </c>
     </row>
+    <row r="457"/>
     <row r="458">
       <c r="A458" t="n">
         <v>10501</v>
@@ -12168,6 +12470,7 @@
         </is>
       </c>
     </row>
+    <row r="462"/>
     <row r="463">
       <c r="A463" t="n">
         <v>10501</v>
@@ -12267,6 +12570,7 @@
         </is>
       </c>
     </row>
+    <row r="466"/>
     <row r="467">
       <c r="A467" t="n">
         <v>20501</v>
@@ -12295,6 +12599,7 @@
         </is>
       </c>
     </row>
+    <row r="468"/>
     <row r="469">
       <c r="A469" t="n">
         <v>20501</v>
@@ -12413,6 +12718,7 @@
         </is>
       </c>
     </row>
+    <row r="473"/>
     <row r="474">
       <c r="A474" t="n">
         <v>20501</v>
@@ -12526,6 +12832,7 @@
         </is>
       </c>
     </row>
+    <row r="478"/>
     <row r="479">
       <c r="A479" t="n">
         <v>20501</v>
@@ -12615,6 +12922,8 @@
         </is>
       </c>
     </row>
+    <row r="482"/>
+    <row r="483"/>
     <row r="484">
       <c r="A484" t="n">
         <v>30501</v>
@@ -12643,6 +12952,7 @@
         </is>
       </c>
     </row>
+    <row r="485"/>
     <row r="486">
       <c r="A486" t="n">
         <v>30501</v>
@@ -12766,6 +13076,7 @@
         </is>
       </c>
     </row>
+    <row r="490"/>
     <row r="491">
       <c r="A491" t="n">
         <v>30501</v>
@@ -12855,6 +13166,7 @@
         </is>
       </c>
     </row>
+    <row r="494"/>
     <row r="495">
       <c r="A495" t="n">
         <v>30501</v>
@@ -13012,6 +13324,8 @@
         </is>
       </c>
     </row>
+    <row r="500"/>
+    <row r="501"/>
     <row r="502">
       <c r="A502" t="n">
         <v>30502</v>
@@ -13040,6 +13354,7 @@
         </is>
       </c>
     </row>
+    <row r="503"/>
     <row r="504">
       <c r="A504" t="n">
         <v>30502</v>
@@ -13139,6 +13454,7 @@
         </is>
       </c>
     </row>
+    <row r="507"/>
     <row r="508">
       <c r="A508" t="n">
         <v>30502</v>
@@ -13238,6 +13554,9 @@
         </is>
       </c>
     </row>
+    <row r="511"/>
+    <row r="512"/>
+    <row r="513"/>
     <row r="514">
       <c r="A514" t="n">
         <v>30503</v>
@@ -13261,6 +13580,7 @@
         </is>
       </c>
     </row>
+    <row r="515"/>
     <row r="516">
       <c r="A516" t="n">
         <v>30503</v>
@@ -13360,6 +13680,7 @@
         </is>
       </c>
     </row>
+    <row r="519"/>
     <row r="520">
       <c r="A520" t="n">
         <v>30503</v>
@@ -13459,6 +13780,7 @@
         </is>
       </c>
     </row>
+    <row r="523"/>
     <row r="524">
       <c r="A524" t="n">
         <v>40501</v>
@@ -13487,6 +13809,7 @@
         </is>
       </c>
     </row>
+    <row r="525"/>
     <row r="526">
       <c r="A526" t="n">
         <v>40502</v>
@@ -13515,6 +13838,7 @@
         </is>
       </c>
     </row>
+    <row r="527"/>
     <row r="528">
       <c r="A528" t="n">
         <v>40503</v>
@@ -13543,6 +13867,7 @@
         </is>
       </c>
     </row>
+    <row r="529"/>
     <row r="530">
       <c r="A530" t="n">
         <v>40504</v>
@@ -13571,6 +13896,7 @@
         </is>
       </c>
     </row>
+    <row r="531"/>
     <row r="532">
       <c r="A532" t="n">
         <v>50501</v>
@@ -13599,6 +13925,7 @@
         </is>
       </c>
     </row>
+    <row r="533"/>
     <row r="534">
       <c r="A534" t="n">
         <v>50502</v>
@@ -13627,6 +13954,7 @@
         </is>
       </c>
     </row>
+    <row r="535"/>
     <row r="536">
       <c r="A536" t="n">
         <v>50503</v>
@@ -13655,6 +13983,9 @@
         </is>
       </c>
     </row>
+    <row r="537"/>
+    <row r="538"/>
+    <row r="539"/>
     <row r="540">
       <c r="A540" t="n">
         <v>10601</v>
@@ -13711,6 +14042,8 @@
         </is>
       </c>
     </row>
+    <row r="542"/>
+    <row r="543"/>
     <row r="544">
       <c r="A544" t="n">
         <v>10601</v>
@@ -13883,6 +14216,7 @@
         </is>
       </c>
     </row>
+    <row r="549"/>
     <row r="550">
       <c r="A550" t="n">
         <v>10601</v>
@@ -14016,6 +14350,7 @@
         </is>
       </c>
     </row>
+    <row r="554"/>
     <row r="555">
       <c r="A555" t="n">
         <v>10601</v>
@@ -14115,6 +14450,7 @@
         </is>
       </c>
     </row>
+    <row r="558"/>
     <row r="559">
       <c r="A559" t="n">
         <v>20601</v>
@@ -14143,6 +14479,7 @@
         </is>
       </c>
     </row>
+    <row r="560"/>
     <row r="561">
       <c r="A561" t="n">
         <v>20601</v>
@@ -14463,6 +14800,8 @@
         </is>
       </c>
     </row>
+    <row r="572"/>
+    <row r="573"/>
     <row r="574">
       <c r="A574" t="n">
         <v>30601</v>
@@ -14491,6 +14830,7 @@
         </is>
       </c>
     </row>
+    <row r="575"/>
     <row r="576">
       <c r="A576" t="n">
         <v>30601</v>
@@ -14614,6 +14954,7 @@
         </is>
       </c>
     </row>
+    <row r="580"/>
     <row r="581">
       <c r="A581" t="n">
         <v>30601</v>
@@ -14703,6 +15044,7 @@
         </is>
       </c>
     </row>
+    <row r="584"/>
     <row r="585">
       <c r="A585" t="n">
         <v>30601</v>
@@ -14860,6 +15202,8 @@
         </is>
       </c>
     </row>
+    <row r="590"/>
+    <row r="591"/>
     <row r="592">
       <c r="A592" t="n">
         <v>30602</v>
@@ -14888,6 +15232,7 @@
         </is>
       </c>
     </row>
+    <row r="593"/>
     <row r="594">
       <c r="A594" t="n">
         <v>30602</v>
@@ -14987,6 +15332,7 @@
         </is>
       </c>
     </row>
+    <row r="597"/>
     <row r="598">
       <c r="A598" t="n">
         <v>30602</v>
@@ -15086,6 +15432,9 @@
         </is>
       </c>
     </row>
+    <row r="601"/>
+    <row r="602"/>
+    <row r="603"/>
     <row r="604">
       <c r="A604" t="n">
         <v>30603</v>
@@ -15114,6 +15463,7 @@
         </is>
       </c>
     </row>
+    <row r="605"/>
     <row r="606">
       <c r="A606" t="n">
         <v>30603</v>
@@ -15213,6 +15563,7 @@
         </is>
       </c>
     </row>
+    <row r="609"/>
     <row r="610">
       <c r="A610" t="n">
         <v>30603</v>
@@ -15312,6 +15663,8 @@
         </is>
       </c>
     </row>
+    <row r="613"/>
+    <row r="614"/>
     <row r="615">
       <c r="A615" t="n">
         <v>40601</v>
@@ -15340,6 +15693,7 @@
         </is>
       </c>
     </row>
+    <row r="616"/>
     <row r="617">
       <c r="A617" t="n">
         <v>40602</v>
@@ -15368,6 +15722,7 @@
         </is>
       </c>
     </row>
+    <row r="618"/>
     <row r="619">
       <c r="A619" t="n">
         <v>40603</v>
@@ -15396,6 +15751,7 @@
         </is>
       </c>
     </row>
+    <row r="620"/>
     <row r="621">
       <c r="A621" t="n">
         <v>40604</v>
@@ -15424,6 +15780,7 @@
         </is>
       </c>
     </row>
+    <row r="622"/>
     <row r="623">
       <c r="A623" t="n">
         <v>50601</v>
@@ -15452,6 +15809,7 @@
         </is>
       </c>
     </row>
+    <row r="624"/>
     <row r="625">
       <c r="A625" t="n">
         <v>50602</v>
@@ -15480,6 +15838,7 @@
         </is>
       </c>
     </row>
+    <row r="626"/>
     <row r="627">
       <c r="A627" t="n">
         <v>50603</v>
@@ -15508,6 +15867,9 @@
         </is>
       </c>
     </row>
+    <row r="628"/>
+    <row r="629"/>
+    <row r="630"/>
     <row r="631">
       <c r="A631" t="n">
         <v>50004</v>
@@ -15661,6 +16023,7 @@
         </is>
       </c>
     </row>
+    <row r="637"/>
     <row r="638">
       <c r="A638" t="n">
         <v>50104</v>
@@ -15842,6 +16205,8 @@
         </is>
       </c>
     </row>
+    <row r="645"/>
+    <row r="646"/>
     <row r="647">
       <c r="A647" t="n">
         <v>50204</v>
@@ -16023,6 +16388,7 @@
         </is>
       </c>
     </row>
+    <row r="654"/>
     <row r="655">
       <c r="A655" t="n">
         <v>50304</v>
@@ -16232,6 +16598,7 @@
         </is>
       </c>
     </row>
+    <row r="663"/>
     <row r="664">
       <c r="A664" t="n">
         <v>50404</v>
@@ -16413,6 +16780,7 @@
         </is>
       </c>
     </row>
+    <row r="671"/>
     <row r="672">
       <c r="A672" t="n">
         <v>50504</v>
@@ -16622,6 +16990,7 @@
         </is>
       </c>
     </row>
+    <row r="680"/>
     <row r="681">
       <c r="A681" t="n">
         <v>50604</v>
@@ -16800,6 +17169,1875 @@
       <c r="H687" t="inlineStr">
         <is>
           <t>Leave</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="n">
+        <v>30003</v>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>visitor</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>cat_平静</t>
+        </is>
+      </c>
+      <c r="D689" t="n">
+        <v>1</v>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="H689" t="inlineStr">
+        <is>
+          <t>{需求}</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="n">
+        <v>30003</v>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>goat_平静</t>
+        </is>
+      </c>
+      <c r="D690" t="n">
+        <v>2</v>
+      </c>
+      <c r="E690" t="n">
+        <v>1</v>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="H690" t="inlineStr">
+        <is>
+          <t>同意</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="n">
+        <v>30003</v>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>goat_平静</t>
+        </is>
+      </c>
+      <c r="D691" t="n">
+        <v>2</v>
+      </c>
+      <c r="E691" t="n">
+        <v>1</v>
+      </c>
+      <c r="F691" t="n">
+        <v>1</v>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>好的，我去看看咩。</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="n">
+        <v>30003</v>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>goat_平静</t>
+        </is>
+      </c>
+      <c r="D692" t="n">
+        <v>2</v>
+      </c>
+      <c r="E692" t="n">
+        <v>1</v>
+      </c>
+      <c r="F692" t="n">
+        <v>2</v>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="H692" t="inlineStr">
+        <is>
+          <t>StartMinigame</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="n">
+        <v>30003</v>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>goat_平静</t>
+        </is>
+      </c>
+      <c r="D693" t="n">
+        <v>2</v>
+      </c>
+      <c r="E693" t="n">
+        <v>2</v>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="H693" t="inlineStr">
+        <is>
+          <t>暂不同意</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="n">
+        <v>30003</v>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>goat_平静</t>
+        </is>
+      </c>
+      <c r="D694" t="n">
+        <v>2</v>
+      </c>
+      <c r="E694" t="n">
+        <v>2</v>
+      </c>
+      <c r="F694" t="n">
+        <v>1</v>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="H694" t="inlineStr">
+        <is>
+          <t>不好意思咩，现在有些忙碌，暂时没有办法满足您的需求咩。</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="n">
+        <v>30003</v>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>goat_平静</t>
+        </is>
+      </c>
+      <c r="D695" t="n">
+        <v>2</v>
+      </c>
+      <c r="E695" t="n">
+        <v>2</v>
+      </c>
+      <c r="F695" t="n">
+        <v>2</v>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="H695" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="n">
+        <v>30304</v>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>visitor</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>yak_平静</t>
+        </is>
+      </c>
+      <c r="D697" t="n">
+        <v>1</v>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="H697" t="inlineStr">
+        <is>
+          <t>{需求}</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="n">
+        <v>30304</v>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>goat_平静</t>
+        </is>
+      </c>
+      <c r="D698" t="n">
+        <v>2</v>
+      </c>
+      <c r="E698" t="n">
+        <v>1</v>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="H698" t="inlineStr">
+        <is>
+          <t>同意</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="n">
+        <v>30304</v>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>goat_平静</t>
+        </is>
+      </c>
+      <c r="D699" t="n">
+        <v>2</v>
+      </c>
+      <c r="E699" t="n">
+        <v>1</v>
+      </c>
+      <c r="F699" t="n">
+        <v>1</v>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="H699" t="inlineStr">
+        <is>
+          <t>好的，我去看看咩。</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="n">
+        <v>30304</v>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>goat_平静</t>
+        </is>
+      </c>
+      <c r="D700" t="n">
+        <v>2</v>
+      </c>
+      <c r="E700" t="n">
+        <v>1</v>
+      </c>
+      <c r="F700" t="n">
+        <v>2</v>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="H700" t="inlineStr">
+        <is>
+          <t>StartMinigame</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="n">
+        <v>30304</v>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>goat_平静</t>
+        </is>
+      </c>
+      <c r="D701" t="n">
+        <v>2</v>
+      </c>
+      <c r="E701" t="n">
+        <v>2</v>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="H701" t="inlineStr">
+        <is>
+          <t>暂不同意</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="n">
+        <v>30304</v>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>goat_平静</t>
+        </is>
+      </c>
+      <c r="D702" t="n">
+        <v>2</v>
+      </c>
+      <c r="E702" t="n">
+        <v>2</v>
+      </c>
+      <c r="F702" t="n">
+        <v>1</v>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="H702" t="inlineStr">
+        <is>
+          <t>不好意思咩，现在有些忙碌，暂时没有办法满足您的需求咩。</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="n">
+        <v>30304</v>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>goat_平静</t>
+        </is>
+      </c>
+      <c r="D703" t="n">
+        <v>2</v>
+      </c>
+      <c r="E703" t="n">
+        <v>2</v>
+      </c>
+      <c r="F703" t="n">
+        <v>2</v>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="H703" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="n">
+        <v>30504</v>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>visitor</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>wolf_平静</t>
+        </is>
+      </c>
+      <c r="D705" t="n">
+        <v>1</v>
+      </c>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="H705" t="inlineStr">
+        <is>
+          <t>{需求}</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="n">
+        <v>30504</v>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>goat_平静</t>
+        </is>
+      </c>
+      <c r="D706" t="n">
+        <v>2</v>
+      </c>
+      <c r="E706" t="n">
+        <v>1</v>
+      </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="H706" t="inlineStr">
+        <is>
+          <t>同意</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="n">
+        <v>30504</v>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>goat_平静</t>
+        </is>
+      </c>
+      <c r="D707" t="n">
+        <v>2</v>
+      </c>
+      <c r="E707" t="n">
+        <v>1</v>
+      </c>
+      <c r="F707" t="n">
+        <v>1</v>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="H707" t="inlineStr">
+        <is>
+          <t>好的，我去看看咩。</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="n">
+        <v>30504</v>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>goat_平静</t>
+        </is>
+      </c>
+      <c r="D708" t="n">
+        <v>2</v>
+      </c>
+      <c r="E708" t="n">
+        <v>1</v>
+      </c>
+      <c r="F708" t="n">
+        <v>2</v>
+      </c>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="H708" t="inlineStr">
+        <is>
+          <t>StartMinigame</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="n">
+        <v>30504</v>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>goat_平静</t>
+        </is>
+      </c>
+      <c r="D709" t="n">
+        <v>2</v>
+      </c>
+      <c r="E709" t="n">
+        <v>2</v>
+      </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="H709" t="inlineStr">
+        <is>
+          <t>暂不同意</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="n">
+        <v>30504</v>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>goat_平静</t>
+        </is>
+      </c>
+      <c r="D710" t="n">
+        <v>2</v>
+      </c>
+      <c r="E710" t="n">
+        <v>2</v>
+      </c>
+      <c r="F710" t="n">
+        <v>1</v>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="H710" t="inlineStr">
+        <is>
+          <t>不好意思咩，现在有些忙碌，暂时没有办法满足您的需求咩。</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="n">
+        <v>30504</v>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>goat_平静</t>
+        </is>
+      </c>
+      <c r="D711" t="n">
+        <v>2</v>
+      </c>
+      <c r="E711" t="n">
+        <v>2</v>
+      </c>
+      <c r="F711" t="n">
+        <v>2</v>
+      </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="H711" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="n">
+        <v>30404</v>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>visitor</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>rabbit_平静</t>
+        </is>
+      </c>
+      <c r="D713" t="n">
+        <v>1</v>
+      </c>
+      <c r="G713" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="H713" t="inlineStr">
+        <is>
+          <t>{需求}</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="n">
+        <v>30404</v>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>goat_平静</t>
+        </is>
+      </c>
+      <c r="D714" t="n">
+        <v>2</v>
+      </c>
+      <c r="E714" t="n">
+        <v>1</v>
+      </c>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="H714" t="inlineStr">
+        <is>
+          <t>同意</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="n">
+        <v>30404</v>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>goat_平静</t>
+        </is>
+      </c>
+      <c r="D715" t="n">
+        <v>2</v>
+      </c>
+      <c r="E715" t="n">
+        <v>1</v>
+      </c>
+      <c r="F715" t="n">
+        <v>1</v>
+      </c>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="H715" t="inlineStr">
+        <is>
+          <t>好的，我去找找咩，安排好了跟您说~</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="n">
+        <v>30404</v>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>visitor</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>rabbit_平静</t>
+        </is>
+      </c>
+      <c r="D716" t="n">
+        <v>2</v>
+      </c>
+      <c r="E716" t="n">
+        <v>1</v>
+      </c>
+      <c r="F716" t="n">
+        <v>2</v>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="H716" t="inlineStr">
+        <is>
+          <t>好，我会等你的。</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="n">
+        <v>30404</v>
+      </c>
+      <c r="D717" t="n">
+        <v>2</v>
+      </c>
+      <c r="E717" t="n">
+        <v>1</v>
+      </c>
+      <c r="F717" t="n">
+        <v>3</v>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="H717" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="n">
+        <v>30404</v>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>goat_平静</t>
+        </is>
+      </c>
+      <c r="D718" t="n">
+        <v>2</v>
+      </c>
+      <c r="E718" t="n">
+        <v>2</v>
+      </c>
+      <c r="G718" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="H718" t="inlineStr">
+        <is>
+          <t>暂不同意</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="n">
+        <v>30404</v>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>goat_平静</t>
+        </is>
+      </c>
+      <c r="D719" t="n">
+        <v>2</v>
+      </c>
+      <c r="E719" t="n">
+        <v>2</v>
+      </c>
+      <c r="F719" t="n">
+        <v>1</v>
+      </c>
+      <c r="G719" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="H719" t="inlineStr">
+        <is>
+          <t>不好意思咩，现在有些忙碌，暂时没有办法满足您的需求咩。</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="n">
+        <v>30404</v>
+      </c>
+      <c r="D720" t="n">
+        <v>2</v>
+      </c>
+      <c r="E720" t="n">
+        <v>2</v>
+      </c>
+      <c r="F720" t="n">
+        <v>2</v>
+      </c>
+      <c r="G720" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="H720" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="n">
+        <v>30404</v>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>goat_平静</t>
+        </is>
+      </c>
+      <c r="D721" t="n">
+        <v>2</v>
+      </c>
+      <c r="E721" t="n">
+        <v>3</v>
+      </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="H721" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="I721" t="inlineStr">
+        <is>
+          <t>RoomHasNeedFurniture</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="n">
+        <v>30404</v>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>goat_平静</t>
+        </is>
+      </c>
+      <c r="D722" t="n">
+        <v>2</v>
+      </c>
+      <c r="E722" t="n">
+        <v>3</v>
+      </c>
+      <c r="F722" t="n">
+        <v>1</v>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="H722" t="inlineStr">
+        <is>
+          <t>已经按照你的要求布置好房间啦~</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="n">
+        <v>30404</v>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>visitor</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>rabbit_平静</t>
+        </is>
+      </c>
+      <c r="D723" t="n">
+        <v>2</v>
+      </c>
+      <c r="E723" t="n">
+        <v>3</v>
+      </c>
+      <c r="F723" t="n">
+        <v>2</v>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="H723" t="inlineStr">
+        <is>
+          <t>是我预期中的样子，谢谢你。</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="n">
+        <v>30404</v>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>narration</t>
+        </is>
+      </c>
+      <c r="D724" t="n">
+        <v>2</v>
+      </c>
+      <c r="E724" t="n">
+        <v>3</v>
+      </c>
+      <c r="F724" t="n">
+        <v>3</v>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="H724" t="inlineStr">
+        <is>
+          <t>完成服务需求奖励【货币+300，声望+10】</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="n">
+        <v>30404</v>
+      </c>
+      <c r="D725" t="n">
+        <v>2</v>
+      </c>
+      <c r="E725" t="n">
+        <v>3</v>
+      </c>
+      <c r="F725" t="n">
+        <v>4</v>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="H725" t="inlineStr">
+        <is>
+          <t>CompleteNeed(perfect)</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="n">
+        <v>30604</v>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>visitor</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>ox_平静</t>
+        </is>
+      </c>
+      <c r="D727" t="n">
+        <v>1</v>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="H727" t="inlineStr">
+        <is>
+          <t>{需求}</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="n">
+        <v>30604</v>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>goat_平静</t>
+        </is>
+      </c>
+      <c r="D728" t="n">
+        <v>2</v>
+      </c>
+      <c r="E728" t="n">
+        <v>1</v>
+      </c>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="H728" t="inlineStr">
+        <is>
+          <t>同意</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="n">
+        <v>30604</v>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>goat_平静</t>
+        </is>
+      </c>
+      <c r="D729" t="n">
+        <v>2</v>
+      </c>
+      <c r="E729" t="n">
+        <v>1</v>
+      </c>
+      <c r="F729" t="n">
+        <v>1</v>
+      </c>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="H729" t="inlineStr">
+        <is>
+          <t>好的，我去找找咩，安排好了跟您说~</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="n">
+        <v>30604</v>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>visitor</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>ox_平静</t>
+        </is>
+      </c>
+      <c r="D730" t="n">
+        <v>2</v>
+      </c>
+      <c r="E730" t="n">
+        <v>1</v>
+      </c>
+      <c r="F730" t="n">
+        <v>2</v>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="H730" t="inlineStr">
+        <is>
+          <t>好，我会等你的。</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="n">
+        <v>30604</v>
+      </c>
+      <c r="D731" t="n">
+        <v>2</v>
+      </c>
+      <c r="E731" t="n">
+        <v>1</v>
+      </c>
+      <c r="F731" t="n">
+        <v>3</v>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="H731" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="n">
+        <v>30604</v>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>goat_平静</t>
+        </is>
+      </c>
+      <c r="D732" t="n">
+        <v>2</v>
+      </c>
+      <c r="E732" t="n">
+        <v>2</v>
+      </c>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="H732" t="inlineStr">
+        <is>
+          <t>暂不同意</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="n">
+        <v>30604</v>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>goat_平静</t>
+        </is>
+      </c>
+      <c r="D733" t="n">
+        <v>2</v>
+      </c>
+      <c r="E733" t="n">
+        <v>2</v>
+      </c>
+      <c r="F733" t="n">
+        <v>1</v>
+      </c>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="H733" t="inlineStr">
+        <is>
+          <t>不好意思咩，现在有些忙碌，暂时没有办法满足您的需求咩。</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="n">
+        <v>30604</v>
+      </c>
+      <c r="D734" t="n">
+        <v>2</v>
+      </c>
+      <c r="E734" t="n">
+        <v>2</v>
+      </c>
+      <c r="F734" t="n">
+        <v>2</v>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="H734" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="n">
+        <v>30604</v>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>goat_平静</t>
+        </is>
+      </c>
+      <c r="D735" t="n">
+        <v>2</v>
+      </c>
+      <c r="E735" t="n">
+        <v>3</v>
+      </c>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="H735" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="I735" t="inlineStr">
+        <is>
+          <t>RoomHasNeedFurniture</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="n">
+        <v>30604</v>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>goat_平静</t>
+        </is>
+      </c>
+      <c r="D736" t="n">
+        <v>2</v>
+      </c>
+      <c r="E736" t="n">
+        <v>3</v>
+      </c>
+      <c r="F736" t="n">
+        <v>1</v>
+      </c>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="H736" t="inlineStr">
+        <is>
+          <t>已经按照你的要求布置好房间啦~</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="n">
+        <v>30604</v>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>visitor</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>ox_平静</t>
+        </is>
+      </c>
+      <c r="D737" t="n">
+        <v>2</v>
+      </c>
+      <c r="E737" t="n">
+        <v>3</v>
+      </c>
+      <c r="F737" t="n">
+        <v>2</v>
+      </c>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="H737" t="inlineStr">
+        <is>
+          <t>是我预期中的样子，谢谢你。</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="n">
+        <v>30604</v>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>narration</t>
+        </is>
+      </c>
+      <c r="D738" t="n">
+        <v>2</v>
+      </c>
+      <c r="E738" t="n">
+        <v>3</v>
+      </c>
+      <c r="F738" t="n">
+        <v>3</v>
+      </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="H738" t="inlineStr">
+        <is>
+          <t>完成服务需求奖励【货币+300，声望+10】</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="n">
+        <v>30604</v>
+      </c>
+      <c r="D739" t="n">
+        <v>2</v>
+      </c>
+      <c r="E739" t="n">
+        <v>3</v>
+      </c>
+      <c r="F739" t="n">
+        <v>4</v>
+      </c>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="H739" t="inlineStr">
+        <is>
+          <t>CompleteNeed(perfect)</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="n">
+        <v>30305</v>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>visitor</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>yak_平静</t>
+        </is>
+      </c>
+      <c r="D741" t="n">
+        <v>1</v>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="H741" t="inlineStr">
+        <is>
+          <t>{需求}</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="n">
+        <v>30305</v>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>goat_平静</t>
+        </is>
+      </c>
+      <c r="D742" t="n">
+        <v>2</v>
+      </c>
+      <c r="E742" t="n">
+        <v>1</v>
+      </c>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="H742" t="inlineStr">
+        <is>
+          <t>同意</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="n">
+        <v>30305</v>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>goat_平静</t>
+        </is>
+      </c>
+      <c r="D743" t="n">
+        <v>2</v>
+      </c>
+      <c r="E743" t="n">
+        <v>1</v>
+      </c>
+      <c r="F743" t="n">
+        <v>1</v>
+      </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="H743" t="inlineStr">
+        <is>
+          <t>好的，我去找找咩，安排好了跟您说~</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="n">
+        <v>30305</v>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>visitor</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>yak_平静</t>
+        </is>
+      </c>
+      <c r="D744" t="n">
+        <v>2</v>
+      </c>
+      <c r="E744" t="n">
+        <v>1</v>
+      </c>
+      <c r="F744" t="n">
+        <v>2</v>
+      </c>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="H744" t="inlineStr">
+        <is>
+          <t>好，我会等你的。</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="n">
+        <v>30305</v>
+      </c>
+      <c r="D745" t="n">
+        <v>2</v>
+      </c>
+      <c r="E745" t="n">
+        <v>1</v>
+      </c>
+      <c r="F745" t="n">
+        <v>3</v>
+      </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="H745" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="n">
+        <v>30305</v>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>goat_平静</t>
+        </is>
+      </c>
+      <c r="D746" t="n">
+        <v>2</v>
+      </c>
+      <c r="E746" t="n">
+        <v>2</v>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="H746" t="inlineStr">
+        <is>
+          <t>暂不同意</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="n">
+        <v>30305</v>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>goat_平静</t>
+        </is>
+      </c>
+      <c r="D747" t="n">
+        <v>2</v>
+      </c>
+      <c r="E747" t="n">
+        <v>2</v>
+      </c>
+      <c r="F747" t="n">
+        <v>1</v>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="H747" t="inlineStr">
+        <is>
+          <t>不好意思咩，现在有些忙碌，暂时没有办法满足您的需求咩。</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="n">
+        <v>30305</v>
+      </c>
+      <c r="D748" t="n">
+        <v>2</v>
+      </c>
+      <c r="E748" t="n">
+        <v>2</v>
+      </c>
+      <c r="F748" t="n">
+        <v>2</v>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="H748" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="n">
+        <v>30305</v>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>goat_平静</t>
+        </is>
+      </c>
+      <c r="D749" t="n">
+        <v>2</v>
+      </c>
+      <c r="E749" t="n">
+        <v>3</v>
+      </c>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="H749" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="I749" t="inlineStr">
+        <is>
+          <t>RoomHasNeedFurniture</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="n">
+        <v>30305</v>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>goat_平静</t>
+        </is>
+      </c>
+      <c r="D750" t="n">
+        <v>2</v>
+      </c>
+      <c r="E750" t="n">
+        <v>3</v>
+      </c>
+      <c r="F750" t="n">
+        <v>1</v>
+      </c>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="H750" t="inlineStr">
+        <is>
+          <t>已经按照你的要求布置好房间啦~</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="n">
+        <v>30305</v>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>visitor</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>yak_平静</t>
+        </is>
+      </c>
+      <c r="D751" t="n">
+        <v>2</v>
+      </c>
+      <c r="E751" t="n">
+        <v>3</v>
+      </c>
+      <c r="F751" t="n">
+        <v>2</v>
+      </c>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="H751" t="inlineStr">
+        <is>
+          <t>是我预期中的样子，谢谢你。</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="n">
+        <v>30305</v>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>narration</t>
+        </is>
+      </c>
+      <c r="D752" t="n">
+        <v>2</v>
+      </c>
+      <c r="E752" t="n">
+        <v>3</v>
+      </c>
+      <c r="F752" t="n">
+        <v>3</v>
+      </c>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="H752" t="inlineStr">
+        <is>
+          <t>完成服务需求奖励【货币+300，声望+10】</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="n">
+        <v>30305</v>
+      </c>
+      <c r="D753" t="n">
+        <v>2</v>
+      </c>
+      <c r="E753" t="n">
+        <v>3</v>
+      </c>
+      <c r="F753" t="n">
+        <v>4</v>
+      </c>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="H753" t="inlineStr">
+        <is>
+          <t>CompleteNeed(perfect)</t>
         </is>
       </c>
     </row>
